--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -51363,6 +51363,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2218">
+      <c r="A2218" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B2218" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2218" t="n">
+        <v>4.48999977111816</v>
+      </c>
+      <c r="D2218" t="n">
+        <v>4.48999977111816</v>
+      </c>
+      <c r="E2218" t="n">
+        <v>4.48999977111816</v>
+      </c>
+      <c r="F2218" t="n">
+        <v>4.48999977111816</v>
+      </c>
+      <c r="G2218" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2219" t="n">
+        <v>7800</v>
+      </c>
+      <c r="C2219" t="n">
+        <v>4.44000005722046</v>
+      </c>
+      <c r="D2219" t="n">
+        <v>4.36999988555908</v>
+      </c>
+      <c r="E2219" t="n">
+        <v>4.42000007629395</v>
+      </c>
+      <c r="F2219" t="n">
+        <v>4.44999980926514</v>
+      </c>
+      <c r="G2219" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -51394,7 +51394,7 @@
         <v>7800</v>
       </c>
       <c r="C2219" t="n">
-        <v>4.44000005722046</v>
+        <v>4.44999980926514</v>
       </c>
       <c r="D2219" t="n">
         <v>4.36999988555908</v>
@@ -51406,6 +51406,29 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2219" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2220" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C2220" t="n">
+        <v>4.51000022888184</v>
+      </c>
+      <c r="D2220" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="E2220" t="n">
+        <v>4.42000007629395</v>
+      </c>
+      <c r="F2220" t="n">
+        <v>4.51000022888184</v>
+      </c>
+      <c r="G2220" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -51432,6 +51432,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2221">
+      <c r="A2221" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2221" t="n">
+        <v>23100</v>
+      </c>
+      <c r="C2221" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2221" t="n">
+        <v>4.48000001907349</v>
+      </c>
+      <c r="E2221" t="n">
+        <v>4.51000022888184</v>
+      </c>
+      <c r="F2221" t="n">
+        <v>4.59000015258789</v>
+      </c>
+      <c r="G2221" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -51455,6 +51455,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2222">
+      <c r="A2222" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2222" t="n">
+        <v>45300</v>
+      </c>
+      <c r="C2222" t="n">
+        <v>4.69000005722046</v>
+      </c>
+      <c r="D2222" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="E2222" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2222" t="n">
+        <v>4.63000011444092</v>
+      </c>
+      <c r="G2222" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -51296,19 +51296,19 @@
     </row>
     <row r="2215">
       <c r="A2215" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2215" t="n">
-        <v>2100</v>
+        <v>21600</v>
       </c>
       <c r="C2215" t="n">
         <v>4.48000001907349</v>
       </c>
       <c r="D2215" t="n">
-        <v>4.46000003814697</v>
+        <v>4.3899998664856</v>
       </c>
       <c r="E2215" t="n">
-        <v>4.46999979019165</v>
+        <v>4.3899998664856</v>
       </c>
       <c r="F2215" t="n">
         <v>4.46999979019165</v>
@@ -51319,22 +51319,22 @@
     </row>
     <row r="2216">
       <c r="A2216" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2216" t="n">
-        <v>9300</v>
+        <v>2100</v>
       </c>
       <c r="C2216" t="n">
-        <v>4.5</v>
+        <v>4.48000001907349</v>
       </c>
       <c r="D2216" t="n">
-        <v>4.3899998664856</v>
+        <v>4.46000003814697</v>
       </c>
       <c r="E2216" t="n">
-        <v>4.3899998664856</v>
+        <v>4.46999979019165</v>
       </c>
       <c r="F2216" t="n">
-        <v>4.48999977111816</v>
+        <v>4.46999979019165</v>
       </c>
       <c r="G2216" t="s">
         <v>7</v>
@@ -51342,19 +51342,19 @@
     </row>
     <row r="2217">
       <c r="A2217" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2217" t="n">
-        <v>7200</v>
+        <v>9300</v>
       </c>
       <c r="C2217" t="n">
-        <v>4.48999977111816</v>
+        <v>4.5</v>
       </c>
       <c r="D2217" t="n">
-        <v>4.40999984741211</v>
+        <v>4.3899998664856</v>
       </c>
       <c r="E2217" t="n">
-        <v>4.42000007629395</v>
+        <v>4.3899998664856</v>
       </c>
       <c r="F2217" t="n">
         <v>4.48999977111816</v>
@@ -51365,19 +51365,19 @@
     </row>
     <row r="2218">
       <c r="A2218" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2218" t="n">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="C2218" t="n">
         <v>4.48999977111816</v>
       </c>
       <c r="D2218" t="n">
-        <v>4.48999977111816</v>
+        <v>4.40999984741211</v>
       </c>
       <c r="E2218" t="n">
-        <v>4.48999977111816</v>
+        <v>4.42000007629395</v>
       </c>
       <c r="F2218" t="n">
         <v>4.48999977111816</v>
@@ -51388,22 +51388,22 @@
     </row>
     <row r="2219">
       <c r="A2219" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2219" t="n">
-        <v>7800</v>
+        <v>0</v>
       </c>
       <c r="C2219" t="n">
-        <v>4.44999980926514</v>
+        <v>4.48999977111816</v>
       </c>
       <c r="D2219" t="n">
-        <v>4.36999988555908</v>
+        <v>4.48999977111816</v>
       </c>
       <c r="E2219" t="n">
-        <v>4.42000007629395</v>
+        <v>4.48999977111816</v>
       </c>
       <c r="F2219" t="n">
-        <v>4.44999980926514</v>
+        <v>4.48999977111816</v>
       </c>
       <c r="G2219" t="s">
         <v>7</v>
@@ -51411,22 +51411,22 @@
     </row>
     <row r="2220">
       <c r="A2220" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2220" t="n">
-        <v>7500</v>
+        <v>7800</v>
       </c>
       <c r="C2220" t="n">
-        <v>4.51000022888184</v>
+        <v>4.44999980926514</v>
       </c>
       <c r="D2220" t="n">
-        <v>4.40000009536743</v>
+        <v>4.36999988555908</v>
       </c>
       <c r="E2220" t="n">
         <v>4.42000007629395</v>
       </c>
       <c r="F2220" t="n">
-        <v>4.51000022888184</v>
+        <v>4.44999980926514</v>
       </c>
       <c r="G2220" t="s">
         <v>7</v>
@@ -51434,22 +51434,22 @@
     </row>
     <row r="2221">
       <c r="A2221" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2221" t="n">
-        <v>23100</v>
+        <v>7500</v>
       </c>
       <c r="C2221" t="n">
-        <v>4.59999990463257</v>
+        <v>4.51000022888184</v>
       </c>
       <c r="D2221" t="n">
-        <v>4.48000001907349</v>
+        <v>4.40000009536743</v>
       </c>
       <c r="E2221" t="n">
+        <v>4.42000007629395</v>
+      </c>
+      <c r="F2221" t="n">
         <v>4.51000022888184</v>
-      </c>
-      <c r="F2221" t="n">
-        <v>4.59000015258789</v>
       </c>
       <c r="G2221" t="s">
         <v>7</v>
@@ -51457,24 +51457,47 @@
     </row>
     <row r="2222">
       <c r="A2222" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2222" t="n">
-        <v>45300</v>
+        <v>23100</v>
       </c>
       <c r="C2222" t="n">
-        <v>4.69000005722046</v>
+        <v>4.59999990463257</v>
       </c>
       <c r="D2222" t="n">
-        <v>4.53999996185303</v>
+        <v>4.48000001907349</v>
       </c>
       <c r="E2222" t="n">
-        <v>4.59999990463257</v>
+        <v>4.51000022888184</v>
       </c>
       <c r="F2222" t="n">
-        <v>4.63000011444092</v>
+        <v>4.59000015258789</v>
       </c>
       <c r="G2222" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="A2223" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2223" t="n">
+        <v>22200</v>
+      </c>
+      <c r="C2223" t="n">
+        <v>4.73000001907349</v>
+      </c>
+      <c r="D2223" t="n">
+        <v>4.55000019073486</v>
+      </c>
+      <c r="E2223" t="n">
+        <v>4.59000015258789</v>
+      </c>
+      <c r="F2223" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="G2223" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G3" t="n">
-        <v>3.66393160820007</v>
+        <v>3.66393184661865</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G6" t="n">
-        <v>3.59711766242981</v>
+        <v>3.59711790084839</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G14" t="n">
-        <v>3.64406776428223</v>
+        <v>3.64406800270081</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5989236831665</v>
+        <v>3.59892344474792</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>3.56641936302185</v>
+        <v>3.56641960144043</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G27" t="n">
-        <v>3.62059307098389</v>
+        <v>3.62059330940247</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G30" t="n">
-        <v>3.57544851303101</v>
+        <v>3.57544827461243</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>3.57544851303101</v>
+        <v>3.57544827461243</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G32" t="n">
-        <v>3.60253524780273</v>
+        <v>3.60253500938416</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G33" t="n">
-        <v>3.60253524780273</v>
+        <v>3.60253500938416</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G34" t="n">
-        <v>3.60253524780273</v>
+        <v>3.60253500938416</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G35" t="n">
-        <v>3.60253524780273</v>
+        <v>3.60253500938416</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G41" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>3.5032172203064</v>
+        <v>3.50321698188782</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>3.57544851303101</v>
+        <v>3.57544827461243</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G64" t="n">
-        <v>3.44001460075378</v>
+        <v>3.44001483917236</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G72" t="n">
-        <v>3.47613024711609</v>
+        <v>3.47613048553467</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G73" t="n">
-        <v>3.47613024711609</v>
+        <v>3.47613048553467</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G74" t="n">
-        <v>3.47613024711609</v>
+        <v>3.47613048553467</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G92" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>3.3587543964386</v>
+        <v>3.35875463485718</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G107" t="n">
-        <v>3.22332072257996</v>
+        <v>3.22332096099854</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G111" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G114" t="n">
-        <v>3.00662708282471</v>
+        <v>3.00662684440613</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>3.04274249076843</v>
+        <v>3.04274272918701</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>3.04274249076843</v>
+        <v>3.04274272918701</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G119" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G120" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G127" t="n">
-        <v>3.45807266235352</v>
+        <v>3.45807242393494</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>3.47613024711609</v>
+        <v>3.47613048553467</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G138" t="n">
-        <v>3.28652310371399</v>
+        <v>3.28652358055115</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G176" t="n">
-        <v>3.24137878417969</v>
+        <v>3.24137854576111</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G186" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>3.19623398780823</v>
+        <v>3.19623422622681</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G188" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G190" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.5</v>
       </c>
       <c r="G191" t="n">
-        <v>3.16011881828308</v>
+        <v>3.16011834144592</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.5</v>
       </c>
       <c r="G192" t="n">
-        <v>3.16011881828308</v>
+        <v>3.16011834144592</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>3.19623398780823</v>
+        <v>3.19623422622681</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G210" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G211" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G212" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G213" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G220" t="n">
-        <v>2.66352868080139</v>
+        <v>2.66352844238281</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G221" t="n">
-        <v>2.60032606124878</v>
+        <v>2.60032629966736</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G223" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G225" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G226" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G230" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G231" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G232" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489214897156</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489214897156</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489214897156</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G241" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489214897156</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489214897156</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G250" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G252" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G253" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G255" t="n">
-        <v>2.27528548240662</v>
+        <v>2.27528524398804</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.5</v>
       </c>
       <c r="G259" t="n">
-        <v>2.25722742080688</v>
+        <v>2.25722765922546</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.5</v>
       </c>
       <c r="G261" t="n">
-        <v>2.25722742080688</v>
+        <v>2.25722765922546</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.5</v>
       </c>
       <c r="G262" t="n">
-        <v>2.25722742080688</v>
+        <v>2.25722765922546</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G263" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G264" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G265" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>2.27528548240662</v>
+        <v>2.27528524398804</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>2.18499612808228</v>
+        <v>2.18499636650085</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G289" t="n">
-        <v>2.18499612808228</v>
+        <v>2.18499636650085</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>2.12179398536682</v>
+        <v>2.12179374694824</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G296" t="n">
-        <v>2.0224757194519</v>
+        <v>2.02247595787048</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G298" t="n">
-        <v>1.93218684196472</v>
+        <v>1.93218672275543</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G299" t="n">
-        <v>1.9412157535553</v>
+        <v>1.94121563434601</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G301" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>1.97733128070831</v>
+        <v>1.97733116149902</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G303" t="n">
-        <v>1.97733128070831</v>
+        <v>1.97733116149902</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G304" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>1.95927345752716</v>
+        <v>1.95927357673645</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G306" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G311" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G312" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G313" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G314" t="n">
-        <v>2.0224757194519</v>
+        <v>2.02247595787048</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G316" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G318" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G319" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G320" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>1.92315793037415</v>
+        <v>1.92315804958344</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>2.04956269264221</v>
+        <v>2.04956245422363</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>1.84189772605896</v>
+        <v>1.84189760684967</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G337" t="n">
-        <v>2.0224757194519</v>
+        <v>2.02247595787048</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G338" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G341" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G344" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G345" t="n">
-        <v>1.93218684196472</v>
+        <v>1.93218672275543</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2</v>
       </c>
       <c r="G354" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2</v>
       </c>
       <c r="G356" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2</v>
       </c>
       <c r="G357" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2</v>
       </c>
       <c r="G358" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2</v>
       </c>
       <c r="G359" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2</v>
       </c>
       <c r="G360" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2</v>
       </c>
       <c r="G361" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2</v>
       </c>
       <c r="G362" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2</v>
       </c>
       <c r="G363" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2</v>
       </c>
       <c r="G365" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2</v>
       </c>
       <c r="G366" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2</v>
       </c>
       <c r="G378" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2</v>
       </c>
       <c r="G379" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2</v>
       </c>
       <c r="G380" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>1.7877242565155</v>
+        <v>1.78772413730621</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G386" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326179027557</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G390" t="n">
-        <v>1.6793771982193</v>
+        <v>1.67937731742859</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G394" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>1.75</v>
       </c>
       <c r="G395" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G396" t="n">
-        <v>1.59811699390411</v>
+        <v>1.5981171131134</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G399" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G400" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G405" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G407" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G408" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G409" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G410" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G411" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G421" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G425" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G426" t="n">
-        <v>1.28210532665253</v>
+        <v>1.28210508823395</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G428" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G429" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G430" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G431" t="n">
-        <v>1.28210532665253</v>
+        <v>1.28210508823395</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G432" t="n">
-        <v>1.30016303062439</v>
+        <v>1.30016314983368</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G433" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>1.30016303062439</v>
+        <v>1.30016314983368</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G437" t="n">
-        <v>1.30016303062439</v>
+        <v>1.30016314983368</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G438" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G439" t="n">
-        <v>1.30016303062439</v>
+        <v>1.30016314983368</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G440" t="n">
-        <v>1.30016303062439</v>
+        <v>1.30016314983368</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G441" t="n">
-        <v>1.30016303062439</v>
+        <v>1.30016314983368</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G442" t="n">
-        <v>1.24598968029022</v>
+        <v>1.24598956108093</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G443" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G449" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326179027557</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>1.75</v>
       </c>
       <c r="G451" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G467" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G469" t="n">
-        <v>1.6793771982193</v>
+        <v>1.67937731742859</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G471" t="n">
-        <v>1.59811699390411</v>
+        <v>1.5981171131134</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>1.75</v>
       </c>
       <c r="G476" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G477" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G478" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G480" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G483" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G494" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G499" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>1.59811699390411</v>
+        <v>1.5981171131134</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G501" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G503" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G504" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G506" t="n">
-        <v>1.59811699390411</v>
+        <v>1.5981171131134</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G507" t="n">
-        <v>1.59811699390411</v>
+        <v>1.5981171131134</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G508" t="n">
-        <v>1.59811699390411</v>
+        <v>1.5981171131134</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G515" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326179027557</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G519" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G521" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>1.75</v>
       </c>
       <c r="G523" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G525" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>1.75</v>
       </c>
       <c r="G526" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G534" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G535" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G536" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G542" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G544" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G547" t="n">
-        <v>1.20084500312805</v>
+        <v>1.20084512233734</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G548" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G549" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G550" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G554" t="n">
-        <v>1.08346915245056</v>
+        <v>1.08346927165985</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G556" t="n">
-        <v>1.02026689052582</v>
+        <v>1.02026677131653</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G557" t="n">
-        <v>1.02026689052582</v>
+        <v>1.02026677131653</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G559" t="n">
-        <v>1.01123785972595</v>
+        <v>1.01123797893524</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G560" t="n">
-        <v>1.01123785972595</v>
+        <v>1.01123797893524</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G561" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G566" t="n">
-        <v>0.83968859910965</v>
+        <v>0.839688658714294</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G568" t="n">
-        <v>0.803572952747345</v>
+        <v>0.80357301235199</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>0.884833216667175</v>
+        <v>0.884833157062531</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G571" t="n">
-        <v>0.875804305076599</v>
+        <v>0.875804245471954</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G575" t="n">
-        <v>0.884833216667175</v>
+        <v>0.884833157062531</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G581" t="n">
-        <v>1.01123785972595</v>
+        <v>1.01123797893524</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G582" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G585" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G586" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G590" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G591" t="n">
-        <v>0.952549874782562</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G592" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G593" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G594" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G597" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G598" t="n">
-        <v>0.952549874782562</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G599" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G602" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G604" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G605" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G606" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G607" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G608" t="n">
-        <v>0.934492170810699</v>
+        <v>0.934492230415344</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G612" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G616" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G617" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G619" t="n">
-        <v>0.893862128257751</v>
+        <v>0.893862068653107</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G620" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G622" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>1</v>
       </c>
       <c r="G623" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G625" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G628" t="n">
-        <v>0.988665640354156</v>
+        <v>0.988665580749512</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G629" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G630" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G633" t="n">
-        <v>1.01123785972595</v>
+        <v>1.01123797893524</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G634" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G637" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>0.97963672876358</v>
+        <v>0.979636788368225</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G642" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G643" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G644" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G648" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G650" t="n">
-        <v>0.934492170810699</v>
+        <v>0.934492230415344</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G654" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607817173004</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>0.97963672876358</v>
+        <v>0.979636788368225</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G657" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G659" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607817173004</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G660" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607817173004</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G662" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G664" t="n">
-        <v>0.952549874782562</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G665" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G666" t="n">
-        <v>0.934492170810699</v>
+        <v>0.934492230415344</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G667" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G669" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G670" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607817173004</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G672" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.988665640354156</v>
+        <v>0.988665580749512</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G674" t="n">
-        <v>0.988665640354156</v>
+        <v>0.988665580749512</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G679" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G687" t="n">
-        <v>0.952549874782562</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G688" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G692" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G695" t="n">
-        <v>0.934492170810699</v>
+        <v>0.934492230415344</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G696" t="n">
-        <v>0.952549874782562</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G697" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G698" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607817173004</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>1</v>
       </c>
       <c r="G700" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>1</v>
       </c>
       <c r="G701" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G705" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G706" t="n">
-        <v>0.843300223350525</v>
+        <v>0.84330016374588</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G714" t="n">
-        <v>0.776486337184906</v>
+        <v>0.776486277580261</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G715" t="n">
-        <v>0.80718457698822</v>
+        <v>0.807184517383575</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G721" t="n">
-        <v>0.698837697505951</v>
+        <v>0.698837637901306</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G724" t="n">
-        <v>0.749399483203888</v>
+        <v>0.749399542808533</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G725" t="n">
-        <v>0.749399483203888</v>
+        <v>0.749399542808533</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G728" t="n">
-        <v>0.622994840145111</v>
+        <v>0.622994780540466</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G729" t="n">
-        <v>0.619383156299591</v>
+        <v>0.619383215904236</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G736" t="n">
-        <v>0.678974032402039</v>
+        <v>0.678973972797394</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G738" t="n">
-        <v>0.641052663326263</v>
+        <v>0.641052544116974</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G739" t="n">
-        <v>0.637440979480743</v>
+        <v>0.637441039085388</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G741" t="n">
-        <v>0.657304584980011</v>
+        <v>0.657304704189301</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G744" t="n">
-        <v>0.675362467765808</v>
+        <v>0.675362527370453</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G745" t="n">
-        <v>0.69342029094696</v>
+        <v>0.693420350551605</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G752" t="n">
-        <v>0.675362467765808</v>
+        <v>0.675362527370453</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G754" t="n">
-        <v>0.675362467765808</v>
+        <v>0.675362527370453</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G755" t="n">
-        <v>0.698837697505951</v>
+        <v>0.698837637901306</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G756" t="n">
-        <v>0.69342029094696</v>
+        <v>0.693420350551605</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G762" t="n">
-        <v>0.700643479824066</v>
+        <v>0.700643420219421</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G766" t="n">
-        <v>0.80718457698822</v>
+        <v>0.807184517383575</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G770" t="n">
-        <v>0.765651524066925</v>
+        <v>0.76565158367157</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G771" t="n">
-        <v>0.765651524066925</v>
+        <v>0.76565158367157</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G773" t="n">
-        <v>0.776486337184906</v>
+        <v>0.776486277580261</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G775" t="n">
-        <v>0.776486337184906</v>
+        <v>0.776486277580261</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G776" t="n">
-        <v>0.80176717042923</v>
+        <v>0.801767230033875</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G778" t="n">
-        <v>0.792738318443298</v>
+        <v>0.792738258838654</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G779" t="n">
-        <v>0.792738318443298</v>
+        <v>0.792738258838654</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G780" t="n">
-        <v>0.80899041891098</v>
+        <v>0.808990359306335</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G781" t="n">
-        <v>0.803572952747345</v>
+        <v>0.80357301235199</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G782" t="n">
-        <v>0.80176717042923</v>
+        <v>0.801767230033875</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G783" t="n">
-        <v>0.794544041156769</v>
+        <v>0.794544100761414</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G784" t="n">
-        <v>0.80899041891098</v>
+        <v>0.808990359306335</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G785" t="n">
-        <v>0.803572952747345</v>
+        <v>0.80357301235199</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G786" t="n">
-        <v>0.792738318443298</v>
+        <v>0.792738258838654</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>0.769263088703156</v>
+        <v>0.7692631483078</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G800" t="n">
-        <v>0.823436558246613</v>
+        <v>0.823436617851257</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G805" t="n">
-        <v>0.859552204608917</v>
+        <v>0.859552264213562</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>0.893862128257751</v>
+        <v>0.893862068653107</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G808" t="n">
-        <v>0.890250504016876</v>
+        <v>0.890250563621521</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G815" t="n">
-        <v>0.859552204608917</v>
+        <v>0.859552264213562</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1</v>
       </c>
       <c r="G817" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G819" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G822" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G827" t="n">
-        <v>0.88302743434906</v>
+        <v>0.883027374744415</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G829" t="n">
-        <v>0.87941575050354</v>
+        <v>0.879415810108185</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G830" t="n">
-        <v>0.88302743434906</v>
+        <v>0.883027374744415</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G831" t="n">
-        <v>0.875804305076599</v>
+        <v>0.875804245471954</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G832" t="n">
-        <v>0.893862128257751</v>
+        <v>0.893862068653107</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G833" t="n">
-        <v>0.88302743434906</v>
+        <v>0.883027374744415</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1</v>
       </c>
       <c r="G834" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G835" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G841" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G842" t="n">
-        <v>0.890250504016876</v>
+        <v>0.890250563621521</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G844" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G846" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G847" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G848" t="n">
-        <v>0.97963672876358</v>
+        <v>0.979636788368225</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G852" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G856" t="n">
-        <v>1.13764274120331</v>
+        <v>1.13764262199402</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G857" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G858" t="n">
-        <v>1.11507046222687</v>
+        <v>1.11507034301758</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G860" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G861" t="n">
-        <v>1.06541132926941</v>
+        <v>1.06541121006012</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G863" t="n">
-        <v>1.06089699268341</v>
+        <v>1.06089687347412</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G867" t="n">
-        <v>1.08346915245056</v>
+        <v>1.08346927165985</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G871" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G872" t="n">
-        <v>1.1421571969986</v>
+        <v>1.14215707778931</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G877" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>1.20535945892334</v>
+        <v>1.20535957813263</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G882" t="n">
-        <v>1.24598968029022</v>
+        <v>1.24598956108093</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G885" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G886" t="n">
-        <v>1.20535945892334</v>
+        <v>1.20535957813263</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G887" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244607448578</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G888" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G890" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244607448578</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G892" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G893" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244607448578</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G894" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244607448578</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G895" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244607448578</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G896" t="n">
-        <v>1.1827871799469</v>
+        <v>1.18278729915619</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G899" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G900" t="n">
-        <v>1.17827272415161</v>
+        <v>1.1782728433609</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G901" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G903" t="n">
-        <v>1.20084500312805</v>
+        <v>1.20084512233734</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G904" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G905" t="n">
-        <v>1.1827871799469</v>
+        <v>1.18278729915619</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G907" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G908" t="n">
-        <v>1.1421571969986</v>
+        <v>1.14215707778931</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G911" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G912" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G915" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G917" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G918" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G920" t="n">
-        <v>1.16021478176117</v>
+        <v>1.16021490097046</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G921" t="n">
-        <v>1.16021478176117</v>
+        <v>1.16021490097046</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G923" t="n">
-        <v>1.1421571969986</v>
+        <v>1.14215707778931</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G925" t="n">
-        <v>1.1421571969986</v>
+        <v>1.14215707778931</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G926" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G927" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G928" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G929" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G930" t="n">
-        <v>1.24598968029022</v>
+        <v>1.24598956108093</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G935" t="n">
-        <v>1.6793771982193</v>
+        <v>1.67937731742859</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G937" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G938" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.75</v>
       </c>
       <c r="G939" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G940" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G946" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G947" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G949" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G952" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G960" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G966" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G967" t="n">
-        <v>1.35885107517242</v>
+        <v>1.35885083675385</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G972" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G974" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G975" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G977" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G978" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G981" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G983" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G984" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G985" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G990" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G994" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G996" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G998" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G999" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.43108236789703</v>
+        <v>1.43108224868774</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.32273542881012</v>
+        <v>1.32273530960083</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.30467748641968</v>
+        <v>1.30467760562897</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.28210532665253</v>
+        <v>1.28210508823395</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.28210532665253</v>
+        <v>1.28210508823395</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.27759063243866</v>
+        <v>1.27759075164795</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.3317643404007</v>
+        <v>1.33176422119141</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.40399551391602</v>
+        <v>1.40399539470673</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.28210532665253</v>
+        <v>1.28210508823395</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244607448578</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.1827871799469</v>
+        <v>1.18278729915619</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.17827272415161</v>
+        <v>1.1782728433609</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.1827871799469</v>
+        <v>1.18278729915619</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.1827871799469</v>
+        <v>1.18278729915619</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>1.75</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.35885107517242</v>
+        <v>1.35885083675385</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1114" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.44011116027832</v>
+        <v>1.44011127948761</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.30016303062439</v>
+        <v>1.30016314983368</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.50331354141235</v>
+        <v>1.50331342220306</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.53040027618408</v>
+        <v>1.53040015697479</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.53040027618408</v>
+        <v>1.53040015697479</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1193" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.53040027618408</v>
+        <v>1.53040015697479</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.44011116027832</v>
+        <v>1.44011127948761</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.44011116027832</v>
+        <v>1.44011127948761</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.43108236789703</v>
+        <v>1.43108224868774</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.40399551391602</v>
+        <v>1.40399539470673</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.43108236789703</v>
+        <v>1.43108224868774</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.35885107517242</v>
+        <v>1.35885083675385</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.34982204437256</v>
+        <v>1.34982216358185</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.40399551391602</v>
+        <v>1.40399539470673</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.40399551391602</v>
+        <v>1.40399539470673</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.40399551391602</v>
+        <v>1.40399539470673</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.40399551391602</v>
+        <v>1.40399539470673</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.40399551391602</v>
+        <v>1.40399539470673</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326179027557</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1410" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>1.75</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>1.75</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>1.75</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.59811699390411</v>
+        <v>1.5981171131134</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>1.75</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>1.75</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1463" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1469" t="n">
-        <v>1.53040027618408</v>
+        <v>1.53040015697479</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1470" t="n">
-        <v>1.44011116027832</v>
+        <v>1.44011127948761</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>1.75</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1488" t="n">
-        <v>1.53040027618408</v>
+        <v>1.53040015697479</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1489" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.50331354141235</v>
+        <v>1.50331342220306</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1494" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>1.75</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1503" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1505" t="n">
-        <v>1.53040027618408</v>
+        <v>1.53040015697479</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>1.75</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>1.75</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>1.75</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.65680515766144</v>
+        <v>1.65680503845215</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.71097850799561</v>
+        <v>1.71097838878632</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1538" t="n">
-        <v>1.65680515766144</v>
+        <v>1.65680503845215</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1546" t="n">
-        <v>1.62068939208984</v>
+        <v>1.62068927288055</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1553" t="n">
-        <v>1.70194959640503</v>
+        <v>1.70194947719574</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1556" t="n">
-        <v>1.6793771982193</v>
+        <v>1.67937731742859</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.70194959640503</v>
+        <v>1.70194947719574</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1566" t="n">
-        <v>1.65680515766144</v>
+        <v>1.65680503845215</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.75</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1573" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326179027557</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326179027557</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.62068939208984</v>
+        <v>1.62068927288055</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.62068939208984</v>
+        <v>1.62068927288055</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326179027557</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.84189772605896</v>
+        <v>1.84189760684967</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.88704216480255</v>
+        <v>1.88704204559326</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.04956269264221</v>
+        <v>2.04956245422363</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.12179398536682</v>
+        <v>2.12179374694824</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.12179398536682</v>
+        <v>2.12179374694824</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.04956269264221</v>
+        <v>2.04956245422363</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.95927345752716</v>
+        <v>1.95927357673645</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1615" t="n">
-        <v>1.95927345752716</v>
+        <v>1.95927357673645</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.01344680786133</v>
+        <v>2.01344704627991</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.0224757194519</v>
+        <v>2.02247595787048</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1618" t="n">
-        <v>2.0224757194519</v>
+        <v>2.02247595787048</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.0224757194519</v>
+        <v>2.02247595787048</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.01344680786133</v>
+        <v>2.01344704627991</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.0224757194519</v>
+        <v>2.02247595787048</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.01344680786133</v>
+        <v>2.01344704627991</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.10373592376709</v>
+        <v>2.10373616218567</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.5172746181488</v>
+        <v>2.51727485656738</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.59213781356812</v>
+        <v>2.59213805198669</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.13489580154419</v>
+        <v>3.13489603996277</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.87287497520447</v>
+        <v>2.87287473678589</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.81672763824463</v>
+        <v>2.81672739982605</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1697" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.87287497520447</v>
+        <v>2.87287473678589</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.92902255058289</v>
+        <v>2.92902231216431</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1709" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.87287497520447</v>
+        <v>2.87287473678589</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.92902255058289</v>
+        <v>2.92902231216431</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.92902255058289</v>
+        <v>2.92902231216431</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1732" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1738" t="n">
-        <v>2.35819053649902</v>
+        <v>2.35819029808044</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.35819053649902</v>
+        <v>2.35819029808044</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.35819053649902</v>
+        <v>2.35819029808044</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.36754846572876</v>
+        <v>2.36754822731018</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.47048544883728</v>
+        <v>2.4704852104187</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1759" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.64828515052795</v>
+        <v>2.64828538894653</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.65764331817627</v>
+        <v>2.65764307975769</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.69507479667664</v>
+        <v>2.69507503509521</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1787" t="n">
-        <v>2.69507479667664</v>
+        <v>2.69507503509521</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1788" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.64828515052795</v>
+        <v>2.64828538894653</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.64828515052795</v>
+        <v>2.64828538894653</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.69507479667664</v>
+        <v>2.69507503509521</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.65764331817627</v>
+        <v>2.65764307975769</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.19104337692261</v>
+        <v>3.19104361534119</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.29398012161255</v>
+        <v>3.29398036003113</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.29398012161255</v>
+        <v>3.29398036003113</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.31269598007202</v>
+        <v>3.3126962184906</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.31269598007202</v>
+        <v>3.3126962184906</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.54664373397827</v>
+        <v>3.54664349555969</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1870" t="n">
-        <v>3.65893840789795</v>
+        <v>3.65893864631653</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1877" t="n">
-        <v>3.69636988639832</v>
+        <v>3.69637012481689</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1879" t="n">
-        <v>3.75251746177673</v>
+        <v>3.75251770019531</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1881" t="n">
-        <v>3.75251746177673</v>
+        <v>3.75251770019531</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -58222,6 +58222,32 @@
         <v>4.67999982833862</v>
       </c>
       <c r="H2225" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2226">
+      <c r="A2226" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2226" t="n">
+        <v>15600</v>
+      </c>
+      <c r="C2226" t="n">
+        <v>4.76999998092651</v>
+      </c>
+      <c r="D2226" t="n">
+        <v>4.65000009536743</v>
+      </c>
+      <c r="E2226" t="n">
+        <v>4.69000005722046</v>
+      </c>
+      <c r="F2226" t="n">
+        <v>4.76999998092651</v>
+      </c>
+      <c r="G2226" t="n">
+        <v>4.76999998092651</v>
+      </c>
+      <c r="H2226" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -525,7 +525,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G6" t="n">
-        <v>3.59711790084839</v>
+        <v>3.59711766242981</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G18" t="n">
-        <v>3.6549026966095</v>
+        <v>3.65490245819092</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G19" t="n">
-        <v>3.65851426124573</v>
+        <v>3.65851449966431</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G27" t="n">
-        <v>3.62059330940247</v>
+        <v>3.62059307098389</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G32" t="n">
-        <v>3.60253500938416</v>
+        <v>3.60253524780273</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G33" t="n">
-        <v>3.60253500938416</v>
+        <v>3.60253524780273</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G34" t="n">
-        <v>3.60253500938416</v>
+        <v>3.60253524780273</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G35" t="n">
-        <v>3.60253500938416</v>
+        <v>3.60253524780273</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>3.50321698188782</v>
+        <v>3.5032172203064</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>3.33166790008545</v>
+        <v>3.33166766166687</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G72" t="n">
-        <v>3.47613048553467</v>
+        <v>3.47613024711609</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G73" t="n">
-        <v>3.47613048553467</v>
+        <v>3.47613024711609</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G74" t="n">
-        <v>3.47613048553467</v>
+        <v>3.47613024711609</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>3.2052628993988</v>
+        <v>3.20526313781738</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G114" t="n">
-        <v>3.00662684440613</v>
+        <v>3.00662708282471</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>3.04274272918701</v>
+        <v>3.04274249076843</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>3.04274272918701</v>
+        <v>3.04274249076843</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G121" t="n">
-        <v>3.13303184509277</v>
+        <v>3.13303208351135</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G127" t="n">
-        <v>3.45807242393494</v>
+        <v>3.45807266235352</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>3.47613048553467</v>
+        <v>3.47613024711609</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G133" t="n">
-        <v>3.33166790008545</v>
+        <v>3.33166766166687</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>3.33166790008545</v>
+        <v>3.33166766166687</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G135" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G138" t="n">
-        <v>3.28652358055115</v>
+        <v>3.28652334213257</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G149" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G151" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G208" t="n">
-        <v>3.05177164077759</v>
+        <v>3.05177187919617</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G215" t="n">
-        <v>2.87119340896606</v>
+        <v>2.87119364738464</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G216" t="n">
-        <v>2.87119340896606</v>
+        <v>2.87119364738464</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G217" t="n">
-        <v>2.87119340896606</v>
+        <v>2.87119364738464</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G236" t="n">
-        <v>2.5100371837616</v>
+        <v>2.51003694534302</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G237" t="n">
-        <v>2.5100371837616</v>
+        <v>2.51003694534302</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>2.46489214897156</v>
+        <v>2.46489238739014</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>2.46489214897156</v>
+        <v>2.46489238739014</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>2.46489214897156</v>
+        <v>2.46489238739014</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G241" t="n">
-        <v>2.46489214897156</v>
+        <v>2.46489238739014</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>2.46489214897156</v>
+        <v>2.46489238739014</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G249" t="n">
-        <v>2.5100371837616</v>
+        <v>2.51003694534302</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G250" t="n">
-        <v>2.41071915626526</v>
+        <v>2.41071891784668</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>2.41071915626526</v>
+        <v>2.41071891784668</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G252" t="n">
-        <v>2.41071915626526</v>
+        <v>2.41071891784668</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G253" t="n">
-        <v>2.41071915626526</v>
+        <v>2.41071891784668</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>2.41071915626526</v>
+        <v>2.41071891784668</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G255" t="n">
-        <v>2.27528524398804</v>
+        <v>2.27528548240662</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>2.32945871353149</v>
+        <v>2.32945895195007</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>2.32945871353149</v>
+        <v>2.32945895195007</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>2.27528524398804</v>
+        <v>2.27528548240662</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G278" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G282" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G283" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G284" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G285" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G286" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G287" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>2.12179374694824</v>
+        <v>2.12179350852966</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G298" t="n">
-        <v>1.93218672275543</v>
+        <v>1.93218684196472</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G299" t="n">
-        <v>1.94121563434601</v>
+        <v>1.94121587276459</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>1.95927357673645</v>
+        <v>1.95927345752716</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>1.92315804958344</v>
+        <v>1.92315793037415</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G328" t="n">
-        <v>1.91412889957428</v>
+        <v>1.91412878036499</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G345" t="n">
-        <v>1.93218672275543</v>
+        <v>1.93218684196472</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G386" t="n">
-        <v>1.64326179027557</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G399" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G400" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G405" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G407" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G408" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G409" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G410" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G411" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G416" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G420" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G421" t="n">
-        <v>1.34530770778656</v>
+        <v>1.34530758857727</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>1.5</v>
       </c>
       <c r="G422" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>1.5</v>
       </c>
       <c r="G423" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>1.5</v>
       </c>
       <c r="G424" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G425" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G426" t="n">
-        <v>1.28210508823395</v>
+        <v>1.28210520744324</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G428" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G429" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G430" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G431" t="n">
-        <v>1.28210508823395</v>
+        <v>1.28210520744324</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>1.34530770778656</v>
+        <v>1.34530758857727</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G449" t="n">
-        <v>1.64326179027557</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>1.5</v>
       </c>
       <c r="G457" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>1.5</v>
       </c>
       <c r="G458" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>1.5</v>
       </c>
       <c r="G459" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>1.5</v>
       </c>
       <c r="G460" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>1.5</v>
       </c>
       <c r="G461" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>1.5</v>
       </c>
       <c r="G462" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>1.5</v>
       </c>
       <c r="G463" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>1.5</v>
       </c>
       <c r="G465" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>1.5</v>
       </c>
       <c r="G466" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G467" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G480" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G481" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G483" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G486" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G488" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G494" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G509" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G515" t="n">
-        <v>1.64326179027557</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G533" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G534" t="n">
-        <v>1.34530770778656</v>
+        <v>1.34530758857727</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G535" t="n">
-        <v>1.34530770778656</v>
+        <v>1.34530758857727</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G536" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G539" t="n">
-        <v>1.2550185918808</v>
+        <v>1.25501847267151</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G545" t="n">
-        <v>1.2550185918808</v>
+        <v>1.25501847267151</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G547" t="n">
-        <v>1.20084512233734</v>
+        <v>1.20084500312805</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G558" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G571" t="n">
-        <v>0.875804245471954</v>
+        <v>0.875804305076599</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G592" t="n">
-        <v>0.966093361377716</v>
+        <v>0.966093420982361</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G593" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G594" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G597" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G599" t="n">
-        <v>0.966093361377716</v>
+        <v>0.966093420982361</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G601" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G604" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G605" t="n">
-        <v>0.966093361377716</v>
+        <v>0.966093420982361</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G606" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G607" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G608" t="n">
-        <v>0.934492230415344</v>
+        <v>0.934492170810699</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G627" t="n">
-        <v>1.04283905029297</v>
+        <v>1.04283916950226</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G629" t="n">
-        <v>0.966093361377716</v>
+        <v>0.966093420982361</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G630" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>0.979636788368225</v>
+        <v>0.97963672876358</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G640" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G642" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G643" t="n">
-        <v>0.966093361377716</v>
+        <v>0.966093420982361</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G648" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G649" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G650" t="n">
-        <v>0.934492230415344</v>
+        <v>0.934492170810699</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G654" t="n">
-        <v>0.970607817173004</v>
+        <v>0.970607936382294</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>0.979636788368225</v>
+        <v>0.97963672876358</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G659" t="n">
-        <v>0.970607817173004</v>
+        <v>0.970607936382294</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G660" t="n">
-        <v>0.970607817173004</v>
+        <v>0.970607936382294</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G662" t="n">
-        <v>0.966093361377716</v>
+        <v>0.966093420982361</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G665" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G666" t="n">
-        <v>0.934492230415344</v>
+        <v>0.934492170810699</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G667" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G669" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G670" t="n">
-        <v>0.970607817173004</v>
+        <v>0.970607936382294</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G672" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G678" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G679" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G688" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G690" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G691" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G692" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G695" t="n">
-        <v>0.934492230415344</v>
+        <v>0.934492170810699</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G697" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G698" t="n">
-        <v>0.970607817173004</v>
+        <v>0.970607936382294</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>0.911919891834259</v>
+        <v>0.911919951438904</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G707" t="n">
-        <v>0.852329075336456</v>
+        <v>0.852329134941101</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G721" t="n">
-        <v>0.698837637901306</v>
+        <v>0.698837578296661</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G724" t="n">
-        <v>0.749399542808533</v>
+        <v>0.749399483203888</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G725" t="n">
-        <v>0.749399542808533</v>
+        <v>0.749399483203888</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G729" t="n">
-        <v>0.619383215904236</v>
+        <v>0.619383275508881</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G733" t="n">
-        <v>0.65188729763031</v>
+        <v>0.651887357234955</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G734" t="n">
-        <v>0.653693079948425</v>
+        <v>0.653693020343781</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G737" t="n">
-        <v>0.684391379356384</v>
+        <v>0.68439131975174</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G738" t="n">
-        <v>0.641052544116974</v>
+        <v>0.641052603721619</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G740" t="n">
-        <v>0.644664168357849</v>
+        <v>0.644664227962494</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G741" t="n">
-        <v>0.657304704189301</v>
+        <v>0.657304644584656</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G745" t="n">
-        <v>0.693420350551605</v>
+        <v>0.69342029094696</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G749" t="n">
-        <v>0.720507025718689</v>
+        <v>0.720506966114044</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G750" t="n">
-        <v>0.709672331809998</v>
+        <v>0.709672272205353</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>0.75</v>
       </c>
       <c r="G753" t="n">
-        <v>0.677168250083923</v>
+        <v>0.677168309688568</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G755" t="n">
-        <v>0.698837637901306</v>
+        <v>0.698837578296661</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G756" t="n">
-        <v>0.693420350551605</v>
+        <v>0.69342029094696</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G757" t="n">
-        <v>0.684391379356384</v>
+        <v>0.68439131975174</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G762" t="n">
-        <v>0.700643420219421</v>
+        <v>0.700643479824066</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G778" t="n">
-        <v>0.792738258838654</v>
+        <v>0.792738318443298</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G779" t="n">
-        <v>0.792738258838654</v>
+        <v>0.792738318443298</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G780" t="n">
-        <v>0.808990359306335</v>
+        <v>0.80899041891098</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G784" t="n">
-        <v>0.808990359306335</v>
+        <v>0.80899041891098</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G786" t="n">
-        <v>0.792738258838654</v>
+        <v>0.792738318443298</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G799" t="n">
-        <v>0.819824993610382</v>
+        <v>0.819825053215027</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G800" t="n">
-        <v>0.823436617851257</v>
+        <v>0.823436677455902</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G801" t="n">
-        <v>0.834271311759949</v>
+        <v>0.834271371364594</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G812" t="n">
-        <v>0.873998522758484</v>
+        <v>0.873998463153839</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G822" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G824" t="n">
-        <v>0.911919891834259</v>
+        <v>0.911919951438904</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G831" t="n">
-        <v>0.875804245471954</v>
+        <v>0.875804305076599</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G839" t="n">
-        <v>0.911919891834259</v>
+        <v>0.911919951438904</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G846" t="n">
-        <v>0.966093361377716</v>
+        <v>0.966093420982361</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G848" t="n">
-        <v>0.979636788368225</v>
+        <v>0.97963672876358</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G856" t="n">
-        <v>1.13764262199402</v>
+        <v>1.13764274120331</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G858" t="n">
-        <v>1.11507034301758</v>
+        <v>1.11507046222687</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G861" t="n">
-        <v>1.06541121006012</v>
+        <v>1.06541132926941</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G863" t="n">
-        <v>1.06089687347412</v>
+        <v>1.06089675426483</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G864" t="n">
-        <v>1.10604155063629</v>
+        <v>1.106041431427</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G872" t="n">
-        <v>1.14215707778931</v>
+        <v>1.14215695858002</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G873" t="n">
-        <v>1.16472935676575</v>
+        <v>1.16472947597504</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>1.16472935676575</v>
+        <v>1.16472947597504</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>1.20535957813263</v>
+        <v>1.20535945892334</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G879" t="n">
-        <v>1.27307629585266</v>
+        <v>1.27307617664337</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G881" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G884" t="n">
-        <v>1.2550185918808</v>
+        <v>1.25501847267151</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G886" t="n">
-        <v>1.20535957813263</v>
+        <v>1.20535945892334</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G887" t="n">
-        <v>1.23244607448578</v>
+        <v>1.23244619369507</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G890" t="n">
-        <v>1.23244607448578</v>
+        <v>1.23244619369507</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G893" t="n">
-        <v>1.23244607448578</v>
+        <v>1.23244619369507</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G894" t="n">
-        <v>1.23244607448578</v>
+        <v>1.23244619369507</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G895" t="n">
-        <v>1.23244607448578</v>
+        <v>1.23244619369507</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G896" t="n">
-        <v>1.18278729915619</v>
+        <v>1.1827871799469</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G900" t="n">
-        <v>1.1782728433609</v>
+        <v>1.17827272415161</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G902" t="n">
-        <v>1.19633054733276</v>
+        <v>1.19633066654205</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G903" t="n">
-        <v>1.20084512233734</v>
+        <v>1.20084500312805</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G905" t="n">
-        <v>1.18278729915619</v>
+        <v>1.1827871799469</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G908" t="n">
-        <v>1.14215707778931</v>
+        <v>1.14215695858002</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G914" t="n">
-        <v>1.10604155063629</v>
+        <v>1.106041431427</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>1.16472935676575</v>
+        <v>1.16472947597504</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G922" t="n">
-        <v>1.16472935676575</v>
+        <v>1.16472947597504</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G923" t="n">
-        <v>1.14215707778931</v>
+        <v>1.14215695858002</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G925" t="n">
-        <v>1.14215707778931</v>
+        <v>1.14215695858002</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G931" t="n">
-        <v>1.2550185918808</v>
+        <v>1.25501847267151</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G932" t="n">
-        <v>1.2550185918808</v>
+        <v>1.25501847267151</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G940" t="n">
-        <v>1.52137136459351</v>
+        <v>1.52137124538422</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G941" t="n">
-        <v>1.64777612686157</v>
+        <v>1.64777624607086</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G947" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G949" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G952" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>1.5</v>
       </c>
       <c r="G955" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>1.5</v>
       </c>
       <c r="G956" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G960" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G961" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.5</v>
       </c>
       <c r="G964" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G965" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G966" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G968" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G970" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G972" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G974" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G975" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G977" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G978" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G981" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G982" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G983" t="n">
-        <v>1.47622692584991</v>
+        <v>1.47622680664062</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G984" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G985" t="n">
-        <v>1.52137136459351</v>
+        <v>1.52137124538422</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G987" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G989" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G990" t="n">
-        <v>1.52137136459351</v>
+        <v>1.52137124538422</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G998" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.5</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.26856184005737</v>
+        <v>1.26856195926666</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.28210508823395</v>
+        <v>1.28210520744324</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.28210508823395</v>
+        <v>1.28210520744324</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.34079313278198</v>
+        <v>1.34079325199127</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.27307629585266</v>
+        <v>1.27307617664337</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.28210508823395</v>
+        <v>1.28210520744324</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.2595329284668</v>
+        <v>1.25953304767609</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.2595329284668</v>
+        <v>1.25953304767609</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.2595329284668</v>
+        <v>1.25953304767609</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.23244607448578</v>
+        <v>1.23244619369507</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.18278729915619</v>
+        <v>1.1827871799469</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.1782728433609</v>
+        <v>1.17827272415161</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.18730163574219</v>
+        <v>1.18730175495148</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.18278729915619</v>
+        <v>1.1827871799469</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.18278729915619</v>
+        <v>1.1827871799469</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.2956485748291</v>
+        <v>1.29564845561981</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>1.5</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.47622692584991</v>
+        <v>1.47622680664062</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.47622692584991</v>
+        <v>1.47622680664062</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1114" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.44011127948761</v>
+        <v>1.44011116027832</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1.5</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>1.5</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.50331342220306</v>
+        <v>1.50331354141235</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.5</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.53040015697479</v>
+        <v>1.53040027618408</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.53040015697479</v>
+        <v>1.53040027618408</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1193" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.47622692584991</v>
+        <v>1.47622680664062</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.52137136459351</v>
+        <v>1.52137124538422</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.53040015697479</v>
+        <v>1.53040027618408</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.47622692584991</v>
+        <v>1.47622680664062</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.47622692584991</v>
+        <v>1.47622680664062</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.44011127948761</v>
+        <v>1.44011116027832</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.44011127948761</v>
+        <v>1.44011116027832</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.5</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>1.5</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>1.5</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>1.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.34530770778656</v>
+        <v>1.34530758857727</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>1.5</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>1.5</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>1.5</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>1.5</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.64777612686157</v>
+        <v>1.64777624607086</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.6026314496994</v>
+        <v>1.60263156890869</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.64326179027557</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1410" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.57554471492767</v>
+        <v>1.57554483413696</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.6026314496994</v>
+        <v>1.60263156890869</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.57554471492767</v>
+        <v>1.57554483413696</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1463" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.50782787799835</v>
+        <v>1.50782799720764</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1469" t="n">
-        <v>1.53040015697479</v>
+        <v>1.53040027618408</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1470" t="n">
-        <v>1.44011127948761</v>
+        <v>1.44011116027832</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.6026314496994</v>
+        <v>1.60263156890869</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1488" t="n">
-        <v>1.53040015697479</v>
+        <v>1.53040027618408</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1489" t="n">
-        <v>1.52137136459351</v>
+        <v>1.52137124538422</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.50331342220306</v>
+        <v>1.50331354141235</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1505" t="n">
-        <v>1.53040015697479</v>
+        <v>1.53040027618408</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.57554471492767</v>
+        <v>1.57554483413696</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.56651592254639</v>
+        <v>1.56651604175568</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1518" t="n">
-        <v>1.57554471492767</v>
+        <v>1.57554483413696</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1541" t="n">
-        <v>1.64777612686157</v>
+        <v>1.64777624607086</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1550" t="n">
-        <v>1.66583395004272</v>
+        <v>1.66583383083344</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1565" t="n">
-        <v>1.66583395004272</v>
+        <v>1.66583383083344</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.64777612686157</v>
+        <v>1.64777624607086</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.64326179027557</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.64326179027557</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.64326179027557</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.88704204559326</v>
+        <v>1.88704216480255</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.12179374694824</v>
+        <v>2.12179350852966</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.12179374694824</v>
+        <v>2.12179350852966</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.95927357673645</v>
+        <v>1.95927345752716</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1615" t="n">
-        <v>1.95927357673645</v>
+        <v>1.95927345752716</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -58248,6 +58248,32 @@
         <v>4.76999998092651</v>
       </c>
       <c r="H2226" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="A2227" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2227" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C2227" t="n">
+        <v>4.78999996185303</v>
+      </c>
+      <c r="D2227" t="n">
+        <v>4.71999979019165</v>
+      </c>
+      <c r="E2227" t="n">
+        <v>4.78000020980835</v>
+      </c>
+      <c r="F2227" t="n">
+        <v>4.78999996185303</v>
+      </c>
+      <c r="G2227" t="n">
+        <v>4.78999996185303</v>
+      </c>
+      <c r="H2227" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -447,7 +447,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G3" t="n">
-        <v>3.66393184661865</v>
+        <v>3.66393160820007</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G14" t="n">
-        <v>3.64406800270081</v>
+        <v>3.64406776428223</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G17" t="n">
-        <v>3.59892344474792</v>
+        <v>3.5989236831665</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G18" t="n">
-        <v>3.65490245819092</v>
+        <v>3.6549026966095</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G19" t="n">
-        <v>3.65851449966431</v>
+        <v>3.65851426124573</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G22" t="n">
-        <v>3.62962198257446</v>
+        <v>3.62962174415588</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>3.56641960144043</v>
+        <v>3.56641936302185</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>3.62962198257446</v>
+        <v>3.62962174415588</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G30" t="n">
-        <v>3.57544827461243</v>
+        <v>3.57544851303101</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>3.57544827461243</v>
+        <v>3.57544851303101</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G37" t="n">
-        <v>3.53030395507812</v>
+        <v>3.53030371665955</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>3.52127504348755</v>
+        <v>3.52127528190613</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G39" t="n">
-        <v>3.52127504348755</v>
+        <v>3.52127528190613</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G41" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.75</v>
       </c>
       <c r="G43" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.75</v>
       </c>
       <c r="G44" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>3.57544827461243</v>
+        <v>3.57544851303101</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G53" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G54" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G55" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G56" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G57" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G58" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G60" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G61" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>3.33166766166687</v>
+        <v>3.33166790008545</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G64" t="n">
-        <v>3.44001483917236</v>
+        <v>3.44001460075378</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G65" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G66" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G67" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G68" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G69" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G70" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G71" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G87" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G88" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G89" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>3.34972548484802</v>
+        <v>3.3497257232666</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.34972548484802</v>
+        <v>3.3497257232666</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G92" t="n">
-        <v>3.34972548484802</v>
+        <v>3.3497257232666</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>3.34972548484802</v>
+        <v>3.3497257232666</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>3.34972548484802</v>
+        <v>3.3497257232666</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.75</v>
       </c>
       <c r="G101" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.75</v>
       </c>
       <c r="G102" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.75</v>
       </c>
       <c r="G103" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.75</v>
       </c>
       <c r="G104" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G107" t="n">
-        <v>3.22332096099854</v>
+        <v>3.22332072257996</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G111" t="n">
-        <v>3.21429204940796</v>
+        <v>3.21429181098938</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>3.04274249076843</v>
+        <v>3.04274272918701</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>3.04274249076843</v>
+        <v>3.04274272918701</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G119" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G120" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G121" t="n">
-        <v>3.13303208351135</v>
+        <v>3.13303184509277</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>3.75</v>
       </c>
       <c r="G124" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.75</v>
       </c>
       <c r="G125" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G127" t="n">
-        <v>3.45807266235352</v>
+        <v>3.45807242393494</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G133" t="n">
-        <v>3.33166766166687</v>
+        <v>3.33166790008545</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>3.33166766166687</v>
+        <v>3.33166790008545</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G135" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G138" t="n">
-        <v>3.28652334213257</v>
+        <v>3.28652310371399</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G141" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G142" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G143" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G145" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G146" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G148" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G149" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G151" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G152" t="n">
-        <v>3.37681245803833</v>
+        <v>3.37681221961975</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G153" t="n">
-        <v>3.37681245803833</v>
+        <v>3.37681221961975</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G154" t="n">
-        <v>3.37681245803833</v>
+        <v>3.37681221961975</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G155" t="n">
-        <v>3.37681245803833</v>
+        <v>3.37681221961975</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G156" t="n">
-        <v>3.37681245803833</v>
+        <v>3.37681221961975</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G176" t="n">
-        <v>3.24137854576111</v>
+        <v>3.24137878417969</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.75</v>
       </c>
       <c r="G178" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G186" t="n">
-        <v>3.21429204940796</v>
+        <v>3.21429181098938</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G188" t="n">
-        <v>3.21429204940796</v>
+        <v>3.21429181098938</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>3.21429204940796</v>
+        <v>3.21429181098938</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G190" t="n">
-        <v>3.21429204940796</v>
+        <v>3.21429181098938</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.5</v>
       </c>
       <c r="G191" t="n">
-        <v>3.16011834144592</v>
+        <v>3.1601185798645</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.5</v>
       </c>
       <c r="G192" t="n">
-        <v>3.16011834144592</v>
+        <v>3.1601185798645</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G208" t="n">
-        <v>3.05177187919617</v>
+        <v>3.05177140235901</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G210" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G211" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G212" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G213" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G215" t="n">
-        <v>2.87119364738464</v>
+        <v>2.87119340896606</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G216" t="n">
-        <v>2.87119364738464</v>
+        <v>2.87119340896606</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G217" t="n">
-        <v>2.87119364738464</v>
+        <v>2.87119340896606</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G220" t="n">
-        <v>2.66352844238281</v>
+        <v>2.66352868080139</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489262580872</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489262580872</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489262580872</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G241" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489262580872</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489262580872</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G250" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G252" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G253" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>2.32945895195007</v>
+        <v>2.32945871353149</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>2.32945895195007</v>
+        <v>2.32945871353149</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.5</v>
       </c>
       <c r="G259" t="n">
-        <v>2.25722765922546</v>
+        <v>2.25722742080688</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.5</v>
       </c>
       <c r="G261" t="n">
-        <v>2.25722765922546</v>
+        <v>2.25722742080688</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.5</v>
       </c>
       <c r="G262" t="n">
-        <v>2.25722765922546</v>
+        <v>2.25722742080688</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G263" t="n">
-        <v>2.32042980194092</v>
+        <v>2.32042956352234</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G264" t="n">
-        <v>2.32042980194092</v>
+        <v>2.32042956352234</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G265" t="n">
-        <v>2.32042980194092</v>
+        <v>2.32042956352234</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.32042980194092</v>
+        <v>2.32042956352234</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G268" t="n">
-        <v>2.47392129898071</v>
+        <v>2.47392153739929</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G269" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G275" t="n">
-        <v>2.30237197875977</v>
+        <v>2.30237221717834</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G276" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G277" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G278" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G281" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G282" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G283" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G284" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G285" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G286" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G287" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>2.15790963172913</v>
+        <v>2.15790939331055</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>2.12179350852966</v>
+        <v>2.12179398536682</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G292" t="n">
-        <v>2.05859136581421</v>
+        <v>2.05859160423279</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G298" t="n">
-        <v>1.93218684196472</v>
+        <v>1.93218672275543</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G299" t="n">
-        <v>1.94121587276459</v>
+        <v>1.9412157535553</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G300" t="n">
-        <v>1.87801325321198</v>
+        <v>1.87801313400269</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G301" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>1.97733116149902</v>
+        <v>1.9773313999176</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G303" t="n">
-        <v>1.97733116149902</v>
+        <v>1.9773313999176</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G304" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G306" t="n">
-        <v>2.04053354263306</v>
+        <v>2.04053378105164</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>2.04053354263306</v>
+        <v>2.04053378105164</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G311" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G312" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G313" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G316" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G318" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G319" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G320" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G321" t="n">
-        <v>1.95024478435516</v>
+        <v>1.95024466514587</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G322" t="n">
-        <v>1.95024478435516</v>
+        <v>1.95024466514587</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G323" t="n">
-        <v>1.95024478435516</v>
+        <v>1.95024466514587</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G324" t="n">
-        <v>1.95024478435516</v>
+        <v>1.95024466514587</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>1.92315793037415</v>
+        <v>1.92315804958344</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>2.04956245422363</v>
+        <v>2.04956269264221</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G328" t="n">
-        <v>1.91412878036499</v>
+        <v>1.91412889957428</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>1.84189760684967</v>
+        <v>1.84189772605896</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G338" t="n">
-        <v>2.04053354263306</v>
+        <v>2.04053378105164</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G339" t="n">
-        <v>2.05859136581421</v>
+        <v>2.05859160423279</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G340" t="n">
-        <v>2.00441813468933</v>
+        <v>2.00441789627075</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G341" t="n">
-        <v>2.04053354263306</v>
+        <v>2.04053378105164</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G342" t="n">
-        <v>2.00441813468933</v>
+        <v>2.00441789627075</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G344" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G345" t="n">
-        <v>1.93218684196472</v>
+        <v>1.93218672275543</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G350" t="n">
-        <v>1.87801325321198</v>
+        <v>1.87801313400269</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G364" t="n">
-        <v>1.73355066776276</v>
+        <v>1.73355054855347</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G370" t="n">
-        <v>1.68840622901917</v>
+        <v>1.68840610980988</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G371" t="n">
-        <v>1.68840622901917</v>
+        <v>1.68840610980988</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>1.78772413730621</v>
+        <v>1.7877242565155</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G382" t="n">
-        <v>1.7154928445816</v>
+        <v>1.71549296379089</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G383" t="n">
-        <v>1.7154928445816</v>
+        <v>1.71549296379089</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G386" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G387" t="n">
-        <v>1.68840622901917</v>
+        <v>1.68840610980988</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G391" t="n">
-        <v>1.7154928445816</v>
+        <v>1.71549296379089</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G394" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>1.75</v>
       </c>
       <c r="G395" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G421" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>1.5</v>
       </c>
       <c r="G422" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>1.5</v>
       </c>
       <c r="G423" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>1.5</v>
       </c>
       <c r="G424" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G443" t="n">
-        <v>1.22793173789978</v>
+        <v>1.22793185710907</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G449" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>1.75</v>
       </c>
       <c r="G451" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>1.5</v>
       </c>
       <c r="G457" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>1.5</v>
       </c>
       <c r="G458" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>1.5</v>
       </c>
       <c r="G459" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>1.5</v>
       </c>
       <c r="G460" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>1.5</v>
       </c>
       <c r="G461" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>1.5</v>
       </c>
       <c r="G462" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>1.5</v>
       </c>
       <c r="G463" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>1.5</v>
       </c>
       <c r="G465" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>1.5</v>
       </c>
       <c r="G466" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>1.75</v>
       </c>
       <c r="G476" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G477" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G478" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G481" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G486" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G488" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G494" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G499" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G501" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G502" t="n">
-        <v>1.63423264026642</v>
+        <v>1.63423275947571</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G503" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G504" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G509" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G515" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G519" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G521" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>1.75</v>
       </c>
       <c r="G523" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G525" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>1.75</v>
       </c>
       <c r="G526" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G533" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G534" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G535" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G537" t="n">
-        <v>1.29113411903381</v>
+        <v>1.29113399982452</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G543" t="n">
-        <v>1.29113411903381</v>
+        <v>1.29113399982452</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G548" t="n">
-        <v>1.22793173789978</v>
+        <v>1.22793185710907</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G549" t="n">
-        <v>1.19181609153748</v>
+        <v>1.19181621074677</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G550" t="n">
-        <v>1.19181609153748</v>
+        <v>1.19181621074677</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G554" t="n">
-        <v>1.08346927165985</v>
+        <v>1.08346915245056</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G556" t="n">
-        <v>1.02026677131653</v>
+        <v>1.02026689052582</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G557" t="n">
-        <v>1.02026677131653</v>
+        <v>1.02026689052582</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G558" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G561" t="n">
-        <v>0.984151244163513</v>
+        <v>0.984151303768158</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G565" t="n">
-        <v>0.939006626605988</v>
+        <v>0.939006567001343</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G568" t="n">
-        <v>0.80357301235199</v>
+        <v>0.803572952747345</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G573" t="n">
-        <v>0.866775333881378</v>
+        <v>0.866775274276733</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G578" t="n">
-        <v>0.975122392177582</v>
+        <v>0.975122332572937</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G580" t="n">
-        <v>1.00220906734467</v>
+        <v>1.00220894813538</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G582" t="n">
-        <v>1.02478122711182</v>
+        <v>1.02478134632111</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G585" t="n">
-        <v>1.02478122711182</v>
+        <v>1.02478134632111</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G586" t="n">
-        <v>1.02478122711182</v>
+        <v>1.02478134632111</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G589" t="n">
-        <v>1.00220906734467</v>
+        <v>1.00220894813538</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G590" t="n">
-        <v>0.984151244163513</v>
+        <v>0.984151303768158</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G591" t="n">
-        <v>0.952549993991852</v>
+        <v>0.952549934387207</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G592" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G593" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G594" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>0.939006626605988</v>
+        <v>0.939006567001343</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G597" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G598" t="n">
-        <v>0.952549993991852</v>
+        <v>0.952549934387207</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G599" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G601" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G602" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G603" t="n">
-        <v>0.939006626605988</v>
+        <v>0.939006567001343</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G605" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G607" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G609" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G611" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G617" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G619" t="n">
-        <v>0.893862068653107</v>
+        <v>0.893862128257751</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G627" t="n">
-        <v>1.04283916950226</v>
+        <v>1.04283905029297</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G628" t="n">
-        <v>0.988665580749512</v>
+        <v>0.988665699958801</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G629" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G630" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>0.997694611549377</v>
+        <v>0.997694551944733</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G634" t="n">
-        <v>1.02478122711182</v>
+        <v>1.02478134632111</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G635" t="n">
-        <v>1.0292956829071</v>
+        <v>1.02929580211639</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G637" t="n">
-        <v>0.984151244163513</v>
+        <v>0.984151303768158</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G640" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G643" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G644" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G645" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>0.939006626605988</v>
+        <v>0.939006567001343</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>0.939006626605988</v>
+        <v>0.939006567001343</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G649" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G651" t="n">
-        <v>0.975122392177582</v>
+        <v>0.975122332572937</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G654" t="n">
-        <v>0.970607936382294</v>
+        <v>0.970607876777649</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G655" t="n">
-        <v>1.00220906734467</v>
+        <v>1.00220894813538</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G657" t="n">
-        <v>0.984151244163513</v>
+        <v>0.984151303768158</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G659" t="n">
-        <v>0.970607936382294</v>
+        <v>0.970607876777649</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G660" t="n">
-        <v>0.970607936382294</v>
+        <v>0.970607876777649</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G662" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G664" t="n">
-        <v>0.952549993991852</v>
+        <v>0.952549934387207</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G665" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G667" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G669" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G670" t="n">
-        <v>0.970607936382294</v>
+        <v>0.970607876777649</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G672" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.988665580749512</v>
+        <v>0.988665699958801</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G674" t="n">
-        <v>0.988665580749512</v>
+        <v>0.988665699958801</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G677" t="n">
-        <v>0.975122392177582</v>
+        <v>0.975122332572937</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G678" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>0.939006626605988</v>
+        <v>0.939006567001343</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G684" t="n">
-        <v>0.907405495643616</v>
+        <v>0.907405436038971</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G687" t="n">
-        <v>0.952549993991852</v>
+        <v>0.952549934387207</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G690" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G691" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G693" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G694" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G696" t="n">
-        <v>0.952549993991852</v>
+        <v>0.952549934387207</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G698" t="n">
-        <v>0.970607936382294</v>
+        <v>0.970607876777649</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>0.911919951438904</v>
+        <v>0.911919891834259</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G705" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G706" t="n">
-        <v>0.84330016374588</v>
+        <v>0.843300223350525</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G712" t="n">
-        <v>0.787320911884308</v>
+        <v>0.787320971488953</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G714" t="n">
-        <v>0.776486277580261</v>
+        <v>0.776486337184906</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G721" t="n">
-        <v>0.698837578296661</v>
+        <v>0.698837637901306</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G729" t="n">
-        <v>0.619383275508881</v>
+        <v>0.619383215904236</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G730" t="n">
-        <v>0.662722051143646</v>
+        <v>0.662721991539001</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G733" t="n">
-        <v>0.651887357234955</v>
+        <v>0.65188729763031</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G734" t="n">
-        <v>0.653693020343781</v>
+        <v>0.65369313955307</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G736" t="n">
-        <v>0.678973972797394</v>
+        <v>0.678974032402039</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G737" t="n">
-        <v>0.68439131975174</v>
+        <v>0.684391379356384</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G740" t="n">
-        <v>0.644664227962494</v>
+        <v>0.644664168357849</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G741" t="n">
-        <v>0.657304644584656</v>
+        <v>0.657304584980011</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G743" t="n">
-        <v>0.662722051143646</v>
+        <v>0.662721991539001</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G744" t="n">
-        <v>0.675362527370453</v>
+        <v>0.675362467765808</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G749" t="n">
-        <v>0.720506966114044</v>
+        <v>0.720507025718689</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G750" t="n">
-        <v>0.709672272205353</v>
+        <v>0.709672331809998</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G752" t="n">
-        <v>0.675362527370453</v>
+        <v>0.675362467765808</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>0.75</v>
       </c>
       <c r="G753" t="n">
-        <v>0.677168309688568</v>
+        <v>0.677168250083923</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G754" t="n">
-        <v>0.675362527370453</v>
+        <v>0.675362467765808</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G755" t="n">
-        <v>0.698837578296661</v>
+        <v>0.698837637901306</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G757" t="n">
-        <v>0.68439131975174</v>
+        <v>0.684391379356384</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G768" t="n">
-        <v>0.798155665397644</v>
+        <v>0.798155605792999</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G769" t="n">
-        <v>0.787320911884308</v>
+        <v>0.787320971488953</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G772" t="n">
-        <v>0.798155665397644</v>
+        <v>0.798155605792999</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G773" t="n">
-        <v>0.776486277580261</v>
+        <v>0.776486337184906</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G775" t="n">
-        <v>0.776486277580261</v>
+        <v>0.776486337184906</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G776" t="n">
-        <v>0.801767230033875</v>
+        <v>0.80176717042923</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G777" t="n">
-        <v>0.787320911884308</v>
+        <v>0.787320971488953</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G780" t="n">
-        <v>0.80899041891098</v>
+        <v>0.808990359306335</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G781" t="n">
-        <v>0.80357301235199</v>
+        <v>0.803572952747345</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G782" t="n">
-        <v>0.801767230033875</v>
+        <v>0.80176717042923</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G783" t="n">
-        <v>0.794544100761414</v>
+        <v>0.794544041156769</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G784" t="n">
-        <v>0.80899041891098</v>
+        <v>0.808990359306335</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G785" t="n">
-        <v>0.80357301235199</v>
+        <v>0.803572952747345</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>0.7692631483078</v>
+        <v>0.769263088703156</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G798" t="n">
-        <v>0.798155665397644</v>
+        <v>0.798155605792999</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G799" t="n">
-        <v>0.819825053215027</v>
+        <v>0.819824993610382</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G800" t="n">
-        <v>0.823436677455902</v>
+        <v>0.823436617851257</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G801" t="n">
-        <v>0.834271371364594</v>
+        <v>0.834271311759949</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G802" t="n">
-        <v>0.827048182487488</v>
+        <v>0.827048122882843</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G804" t="n">
-        <v>0.857746422290802</v>
+        <v>0.857746481895447</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>0.893862068653107</v>
+        <v>0.893862128257751</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G808" t="n">
-        <v>0.890250563621521</v>
+        <v>0.890250504016876</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G811" t="n">
-        <v>0.857746422290802</v>
+        <v>0.857746481895447</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G819" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G820" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G824" t="n">
-        <v>0.911919951438904</v>
+        <v>0.911919891834259</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G828" t="n">
-        <v>0.872192740440369</v>
+        <v>0.872192680835724</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G829" t="n">
-        <v>0.879415810108185</v>
+        <v>0.87941575050354</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G832" t="n">
-        <v>0.893862068653107</v>
+        <v>0.893862128257751</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G835" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G836" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G838" t="n">
-        <v>0.907405495643616</v>
+        <v>0.907405436038971</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G839" t="n">
-        <v>0.911919951438904</v>
+        <v>0.911919891834259</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G840" t="n">
-        <v>0.907405495643616</v>
+        <v>0.907405436038971</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G842" t="n">
-        <v>0.890250563621521</v>
+        <v>0.890250504016876</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G844" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G846" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G847" t="n">
-        <v>0.984151244163513</v>
+        <v>0.984151303768158</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G849" t="n">
-        <v>1.0292956829071</v>
+        <v>1.02929580211639</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G852" t="n">
-        <v>1.02478122711182</v>
+        <v>1.02478134632111</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G854" t="n">
-        <v>1.0292956829071</v>
+        <v>1.02929580211639</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G857" t="n">
-        <v>1.10152697563171</v>
+        <v>1.101527094841</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G863" t="n">
-        <v>1.06089675426483</v>
+        <v>1.06089699268341</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G864" t="n">
-        <v>1.106041431427</v>
+        <v>1.10604155063629</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G865" t="n">
-        <v>1.09701263904572</v>
+        <v>1.09701251983643</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G866" t="n">
-        <v>1.07895481586456</v>
+        <v>1.07895469665527</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G867" t="n">
-        <v>1.08346927165985</v>
+        <v>1.08346915245056</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G871" t="n">
-        <v>1.10152697563171</v>
+        <v>1.101527094841</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G872" t="n">
-        <v>1.14215695858002</v>
+        <v>1.14215707778931</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G873" t="n">
-        <v>1.16472947597504</v>
+        <v>1.16472935676575</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G874" t="n">
-        <v>1.15570044517517</v>
+        <v>1.15570056438446</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>1.16472947597504</v>
+        <v>1.16472935676575</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G877" t="n">
-        <v>1.19181609153748</v>
+        <v>1.19181621074677</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>1.20535945892334</v>
+        <v>1.20535957813263</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G879" t="n">
-        <v>1.27307617664337</v>
+        <v>1.27307629585266</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G880" t="n">
-        <v>1.31370639801025</v>
+        <v>1.31370651721954</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G885" t="n">
-        <v>1.22341740131378</v>
+        <v>1.22341728210449</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G886" t="n">
-        <v>1.20535945892334</v>
+        <v>1.20535957813263</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G887" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244631290436</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G888" t="n">
-        <v>1.22793173789978</v>
+        <v>1.22793185710907</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G890" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244631290436</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G892" t="n">
-        <v>1.22793173789978</v>
+        <v>1.22793185710907</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G893" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244631290436</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G894" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244631290436</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G895" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244631290436</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G899" t="n">
-        <v>1.22341740131378</v>
+        <v>1.22341728210449</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G901" t="n">
-        <v>1.19181609153748</v>
+        <v>1.19181621074677</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G904" t="n">
-        <v>1.22341740131378</v>
+        <v>1.22341728210449</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G907" t="n">
-        <v>1.19181609153748</v>
+        <v>1.19181621074677</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G908" t="n">
-        <v>1.14215695858002</v>
+        <v>1.14215707778931</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G911" t="n">
-        <v>1.10152697563171</v>
+        <v>1.101527094841</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G912" t="n">
-        <v>1.10152697563171</v>
+        <v>1.101527094841</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G914" t="n">
-        <v>1.106041431427</v>
+        <v>1.10604155063629</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G916" t="n">
-        <v>1.07895481586456</v>
+        <v>1.07895469665527</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>1.16472947597504</v>
+        <v>1.16472935676575</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G920" t="n">
-        <v>1.16021490097046</v>
+        <v>1.16021478176117</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G921" t="n">
-        <v>1.16021490097046</v>
+        <v>1.16021478176117</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G922" t="n">
-        <v>1.16472947597504</v>
+        <v>1.16472935676575</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G923" t="n">
-        <v>1.14215695858002</v>
+        <v>1.14215707778931</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G924" t="n">
-        <v>1.15118598937988</v>
+        <v>1.15118610858917</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G925" t="n">
-        <v>1.14215695858002</v>
+        <v>1.14215707778931</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G926" t="n">
-        <v>1.22793173789978</v>
+        <v>1.22793185710907</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G927" t="n">
-        <v>1.22793173789978</v>
+        <v>1.22793185710907</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G928" t="n">
-        <v>1.22341740131378</v>
+        <v>1.22341728210449</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G929" t="n">
-        <v>1.22341740131378</v>
+        <v>1.22341728210449</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.875</v>
       </c>
       <c r="G936" t="n">
-        <v>1.69292068481445</v>
+        <v>1.69292056560516</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G937" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G938" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.75</v>
       </c>
       <c r="G939" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G940" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G941" t="n">
-        <v>1.64777624607086</v>
+        <v>1.64777612686157</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G946" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>1.5</v>
       </c>
       <c r="G955" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>1.5</v>
       </c>
       <c r="G956" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G961" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.5</v>
       </c>
       <c r="G964" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G967" t="n">
-        <v>1.35885083675385</v>
+        <v>1.35885095596313</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G970" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G982" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G983" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G985" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G987" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G989" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G990" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G994" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G996" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G999" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.4897700548172</v>
+        <v>1.48977017402649</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.5</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.30467760562897</v>
+        <v>1.30467748641968</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.33176422119141</v>
+        <v>1.3317643404007</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.34079325199127</v>
+        <v>1.34079313278198</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.27307617664337</v>
+        <v>1.27307629585266</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.29113411903381</v>
+        <v>1.29113399982452</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.25953304767609</v>
+        <v>1.2595329284668</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.25953304767609</v>
+        <v>1.2595329284668</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.25953304767609</v>
+        <v>1.2595329284668</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244631290436</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.29564845561981</v>
+        <v>1.2956485748291</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>1.5</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>1.75</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.35885083675385</v>
+        <v>1.35885095596313</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1114" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1.5</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>1.5</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.5</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.4897700548172</v>
+        <v>1.48977017402649</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.4897700548172</v>
+        <v>1.48977017402649</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.4897700548172</v>
+        <v>1.48977017402649</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.4897700548172</v>
+        <v>1.48977017402649</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.5</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>1.5</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>1.5</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>1.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.35885083675385</v>
+        <v>1.35885095596313</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.34982216358185</v>
+        <v>1.34982204437256</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>1.5</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>1.5</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>1.5</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>1.5</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.64777624607086</v>
+        <v>1.64777612686157</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.63423264026642</v>
+        <v>1.63423275947571</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.63423264026642</v>
+        <v>1.63423275947571</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.57554483413696</v>
+        <v>1.57554471492767</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>1.75</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.61166048049927</v>
+        <v>1.61166036128998</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>1.75</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>1.75</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.61166048049927</v>
+        <v>1.61166036128998</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.61166048049927</v>
+        <v>1.61166036128998</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.57554483413696</v>
+        <v>1.57554471492767</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>1.75</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>1.75</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>1.75</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1489" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1494" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>1.75</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1503" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.57554483413696</v>
+        <v>1.57554471492767</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.56651604175568</v>
+        <v>1.56651592254639</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>1.75</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1518" t="n">
-        <v>1.57554483413696</v>
+        <v>1.57554471492767</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>1.75</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>1.75</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.61166048049927</v>
+        <v>1.61166036128998</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.71097838878632</v>
+        <v>1.71097850799561</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.63423264026642</v>
+        <v>1.63423275947571</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1541" t="n">
-        <v>1.64777624607086</v>
+        <v>1.64777612686157</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.67486274242401</v>
+        <v>1.6748628616333</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.63423264026642</v>
+        <v>1.63423275947571</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1546" t="n">
-        <v>1.62068927288055</v>
+        <v>1.62068939208984</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1550" t="n">
-        <v>1.66583383083344</v>
+        <v>1.66583395004272</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.67486274242401</v>
+        <v>1.6748628616333</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.67486274242401</v>
+        <v>1.6748628616333</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1555" t="n">
-        <v>1.68840622901917</v>
+        <v>1.68840610980988</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.68840622901917</v>
+        <v>1.68840610980988</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.68840622901917</v>
+        <v>1.68840610980988</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1562" t="n">
-        <v>1.68840622901917</v>
+        <v>1.68840610980988</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>1.875</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.69292068481445</v>
+        <v>1.69292056560516</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.67486274242401</v>
+        <v>1.6748628616333</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1565" t="n">
-        <v>1.66583383083344</v>
+        <v>1.66583395004272</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.75</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.64777624607086</v>
+        <v>1.64777612686157</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1573" t="n">
-        <v>1.61166048049927</v>
+        <v>1.61166036128998</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.63423264026642</v>
+        <v>1.63423275947571</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.63423264026642</v>
+        <v>1.63423275947571</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.62068927288055</v>
+        <v>1.62068939208984</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.62068927288055</v>
+        <v>1.62068939208984</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.84189760684967</v>
+        <v>1.84189772605896</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.04956245422363</v>
+        <v>2.04956269264221</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.12179350852966</v>
+        <v>2.12179398536682</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.12179350852966</v>
+        <v>2.12179398536682</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1606" t="n">
-        <v>2.05859136581421</v>
+        <v>2.05859160423279</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.04956245422363</v>
+        <v>2.04956269264221</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1611" t="n">
-        <v>1.99538922309875</v>
+        <v>1.99538910388947</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.01344704627991</v>
+        <v>2.01344680786133</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.01344704627991</v>
+        <v>2.01344680786133</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.00441813468933</v>
+        <v>2.00441789627075</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1623" t="n">
-        <v>2.00441813468933</v>
+        <v>2.00441789627075</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.01344704627991</v>
+        <v>2.01344680786133</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1625" t="n">
-        <v>2.00441813468933</v>
+        <v>2.00441789627075</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.10373616218567</v>
+        <v>2.10373592376709</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.51727485656738</v>
+        <v>2.5172746181488</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.59213805198669</v>
+        <v>2.59213781356812</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.13489603996277</v>
+        <v>3.13489580154419</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.87287473678589</v>
+        <v>2.87287497520447</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.73250651359558</v>
+        <v>2.732506275177</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.81672739982605</v>
+        <v>2.81672763824463</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.73250651359558</v>
+        <v>2.732506275177</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.91030621528625</v>
+        <v>2.91030645370483</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1697" t="n">
-        <v>2.91030621528625</v>
+        <v>2.91030645370483</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.87287473678589</v>
+        <v>2.87287497520447</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.92902231216431</v>
+        <v>2.92902255058289</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1709" t="n">
-        <v>2.91030621528625</v>
+        <v>2.91030645370483</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.91030621528625</v>
+        <v>2.91030645370483</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.87287473678589</v>
+        <v>2.87287497520447</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.91030621528625</v>
+        <v>2.91030645370483</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.92902231216431</v>
+        <v>2.92902255058289</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.92902231216431</v>
+        <v>2.92902255058289</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1732" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1738" t="n">
-        <v>2.35819029808044</v>
+        <v>2.35819053649902</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.35819029808044</v>
+        <v>2.35819053649902</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.35819029808044</v>
+        <v>2.35819053649902</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.36754822731018</v>
+        <v>2.36754846572876</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.4704852104187</v>
+        <v>2.47048544883728</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1759" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.64828538894653</v>
+        <v>2.64828515052795</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.65764307975769</v>
+        <v>2.65764331817627</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.73250651359558</v>
+        <v>2.732506275177</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.73250651359558</v>
+        <v>2.732506275177</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.73250651359558</v>
+        <v>2.732506275177</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.69507503509521</v>
+        <v>2.69507479667664</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1787" t="n">
-        <v>2.69507503509521</v>
+        <v>2.69507479667664</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1788" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.64828538894653</v>
+        <v>2.64828515052795</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.64828538894653</v>
+        <v>2.64828515052795</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.69507503509521</v>
+        <v>2.69507479667664</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.65764307975769</v>
+        <v>2.65764331817627</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.19104361534119</v>
+        <v>3.19104337692261</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.29398036003113</v>
+        <v>3.29398012161255</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.29398036003113</v>
+        <v>3.29398012161255</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.3126962184906</v>
+        <v>3.31269598007202</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.3126962184906</v>
+        <v>3.31269598007202</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.54664349555969</v>
+        <v>3.54664373397827</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1870" t="n">
-        <v>3.65893864631653</v>
+        <v>3.65893840789795</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1877" t="n">
-        <v>3.69637012481689</v>
+        <v>3.69636988639832</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1879" t="n">
-        <v>3.75251770019531</v>
+        <v>3.75251746177673</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1881" t="n">
-        <v>3.75251770019531</v>
+        <v>3.75251746177673</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -58274,6 +58274,32 @@
         <v>4.78999996185303</v>
       </c>
       <c r="H2227" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="A2228" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2228" t="n">
+        <v>8700</v>
+      </c>
+      <c r="C2228" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D2228" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2228" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F2228" t="n">
+        <v>4.73999977111816</v>
+      </c>
+      <c r="G2228" t="n">
+        <v>4.73999977111816</v>
+      </c>
+      <c r="H2228" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -447,7 +447,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G3" t="n">
-        <v>3.66393160820007</v>
+        <v>3.66393184661865</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G6" t="n">
-        <v>3.59711766242981</v>
+        <v>3.59711790084839</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G14" t="n">
-        <v>3.64406776428223</v>
+        <v>3.64406800270081</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5989236831665</v>
+        <v>3.59892344474792</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G22" t="n">
-        <v>3.62962174415588</v>
+        <v>3.62962198257446</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>3.56641936302185</v>
+        <v>3.56641960144043</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>3.62962174415588</v>
+        <v>3.62962198257446</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G27" t="n">
-        <v>3.62059307098389</v>
+        <v>3.62059330940247</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G30" t="n">
-        <v>3.57544851303101</v>
+        <v>3.57544827461243</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>3.57544851303101</v>
+        <v>3.57544827461243</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G32" t="n">
-        <v>3.60253524780273</v>
+        <v>3.60253500938416</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G33" t="n">
-        <v>3.60253524780273</v>
+        <v>3.60253500938416</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G34" t="n">
-        <v>3.60253524780273</v>
+        <v>3.60253500938416</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G35" t="n">
-        <v>3.60253524780273</v>
+        <v>3.60253500938416</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G37" t="n">
-        <v>3.53030371665955</v>
+        <v>3.53030395507812</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>3.52127528190613</v>
+        <v>3.52127504348755</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G39" t="n">
-        <v>3.52127528190613</v>
+        <v>3.52127504348755</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G41" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.75</v>
       </c>
       <c r="G43" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.75</v>
       </c>
       <c r="G44" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>3.5032172203064</v>
+        <v>3.50321698188782</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>3.57544851303101</v>
+        <v>3.57544827461243</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G53" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G54" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G55" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G56" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G57" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G58" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G60" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G61" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G64" t="n">
-        <v>3.44001460075378</v>
+        <v>3.44001483917236</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G65" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G66" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G67" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G68" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G69" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G70" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G71" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G72" t="n">
-        <v>3.47613024711609</v>
+        <v>3.47613048553467</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G73" t="n">
-        <v>3.47613024711609</v>
+        <v>3.47613048553467</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G74" t="n">
-        <v>3.47613024711609</v>
+        <v>3.47613048553467</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G87" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G88" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G89" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G92" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.75</v>
       </c>
       <c r="G101" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.75</v>
       </c>
       <c r="G102" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.75</v>
       </c>
       <c r="G103" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.75</v>
       </c>
       <c r="G104" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G107" t="n">
-        <v>3.22332072257996</v>
+        <v>3.22332096099854</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G111" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>3.20526313781738</v>
+        <v>3.2052628993988</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G114" t="n">
-        <v>3.00662708282471</v>
+        <v>3.00662684440613</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G119" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G120" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>3.75</v>
       </c>
       <c r="G124" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.75</v>
       </c>
       <c r="G125" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>3.47613024711609</v>
+        <v>3.47613048553467</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G138" t="n">
-        <v>3.28652310371399</v>
+        <v>3.28652358055115</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G141" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G142" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G143" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G145" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G146" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G148" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G152" t="n">
-        <v>3.37681221961975</v>
+        <v>3.37681245803833</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G153" t="n">
-        <v>3.37681221961975</v>
+        <v>3.37681245803833</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G154" t="n">
-        <v>3.37681221961975</v>
+        <v>3.37681245803833</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G155" t="n">
-        <v>3.37681221961975</v>
+        <v>3.37681245803833</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G156" t="n">
-        <v>3.37681221961975</v>
+        <v>3.37681245803833</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G176" t="n">
-        <v>3.24137878417969</v>
+        <v>3.24137854576111</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.75</v>
       </c>
       <c r="G178" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G186" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G188" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G190" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.5</v>
       </c>
       <c r="G191" t="n">
-        <v>3.1601185798645</v>
+        <v>3.16011834144592</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.5</v>
       </c>
       <c r="G192" t="n">
-        <v>3.1601185798645</v>
+        <v>3.16011834144592</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G208" t="n">
-        <v>3.05177140235901</v>
+        <v>3.05177164077759</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G210" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G211" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G212" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G213" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G220" t="n">
-        <v>2.66352868080139</v>
+        <v>2.66352844238281</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G236" t="n">
-        <v>2.51003694534302</v>
+        <v>2.5100371837616</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G237" t="n">
-        <v>2.51003694534302</v>
+        <v>2.5100371837616</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>2.46489262580872</v>
+        <v>2.46489214897156</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>2.46489262580872</v>
+        <v>2.46489214897156</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>2.46489262580872</v>
+        <v>2.46489214897156</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G241" t="n">
-        <v>2.46489262580872</v>
+        <v>2.46489214897156</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>2.46489262580872</v>
+        <v>2.46489214897156</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G249" t="n">
-        <v>2.51003694534302</v>
+        <v>2.5100371837616</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G255" t="n">
-        <v>2.27528548240662</v>
+        <v>2.27528524398804</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.5</v>
       </c>
       <c r="G259" t="n">
-        <v>2.25722742080688</v>
+        <v>2.25722765922546</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.5</v>
       </c>
       <c r="G261" t="n">
-        <v>2.25722742080688</v>
+        <v>2.25722765922546</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.5</v>
       </c>
       <c r="G262" t="n">
-        <v>2.25722742080688</v>
+        <v>2.25722765922546</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G263" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G264" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G265" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G268" t="n">
-        <v>2.47392153739929</v>
+        <v>2.47392129898071</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G269" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>2.27528548240662</v>
+        <v>2.27528524398804</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G275" t="n">
-        <v>2.30237221717834</v>
+        <v>2.30237197875977</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G276" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G277" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G281" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>2.15790939331055</v>
+        <v>2.15790963172913</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>2.12179398536682</v>
+        <v>2.12179374694824</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G292" t="n">
-        <v>2.05859160423279</v>
+        <v>2.05859136581421</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G299" t="n">
-        <v>1.9412157535553</v>
+        <v>1.94121563434601</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G300" t="n">
-        <v>1.87801313400269</v>
+        <v>1.87801325321198</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G301" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>1.9773313999176</v>
+        <v>1.97733116149902</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G303" t="n">
-        <v>1.9773313999176</v>
+        <v>1.97733116149902</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G304" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>1.95927345752716</v>
+        <v>1.95927357673645</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G306" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G311" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G312" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G313" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G316" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G318" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G319" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G320" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G321" t="n">
-        <v>1.95024466514587</v>
+        <v>1.95024478435516</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G322" t="n">
-        <v>1.95024466514587</v>
+        <v>1.95024478435516</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G323" t="n">
-        <v>1.95024466514587</v>
+        <v>1.95024478435516</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G324" t="n">
-        <v>1.95024466514587</v>
+        <v>1.95024478435516</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>2.04956269264221</v>
+        <v>2.04956245422363</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>1.84189772605896</v>
+        <v>1.84189760684967</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G338" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G339" t="n">
-        <v>2.05859160423279</v>
+        <v>2.05859136581421</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G340" t="n">
-        <v>2.00441789627075</v>
+        <v>2.00441813468933</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G341" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G342" t="n">
-        <v>2.00441789627075</v>
+        <v>2.00441813468933</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G344" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G350" t="n">
-        <v>1.87801313400269</v>
+        <v>1.87801325321198</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G364" t="n">
-        <v>1.73355054855347</v>
+        <v>1.73355066776276</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G370" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G371" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>1.7877242565155</v>
+        <v>1.78772413730621</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G382" t="n">
-        <v>1.71549296379089</v>
+        <v>1.7154928445816</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G383" t="n">
-        <v>1.71549296379089</v>
+        <v>1.7154928445816</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G386" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326179027557</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G387" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G391" t="n">
-        <v>1.71549296379089</v>
+        <v>1.7154928445816</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G394" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>1.75</v>
       </c>
       <c r="G395" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G399" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G400" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G405" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G407" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G408" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G409" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G410" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G411" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G416" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G420" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G425" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G426" t="n">
-        <v>1.28210520744324</v>
+        <v>1.28210508823395</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G428" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G429" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G430" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G431" t="n">
-        <v>1.28210520744324</v>
+        <v>1.28210508823395</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G443" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G449" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326179027557</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>1.75</v>
       </c>
       <c r="G451" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G467" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>1.75</v>
       </c>
       <c r="G476" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G477" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G478" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G480" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G483" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G499" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G501" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G502" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G503" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G504" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G509" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G515" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326179027557</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G519" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G521" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>1.75</v>
       </c>
       <c r="G523" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G525" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>1.75</v>
       </c>
       <c r="G526" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G536" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G537" t="n">
-        <v>1.29113399982452</v>
+        <v>1.29113411903381</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G539" t="n">
-        <v>1.25501847267151</v>
+        <v>1.2550185918808</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G543" t="n">
-        <v>1.29113399982452</v>
+        <v>1.29113411903381</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G545" t="n">
-        <v>1.25501847267151</v>
+        <v>1.2550185918808</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G547" t="n">
-        <v>1.20084500312805</v>
+        <v>1.20084512233734</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G548" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G549" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G550" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G554" t="n">
-        <v>1.08346915245056</v>
+        <v>1.08346927165985</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G556" t="n">
-        <v>1.02026689052582</v>
+        <v>1.02026677131653</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G557" t="n">
-        <v>1.02026689052582</v>
+        <v>1.02026677131653</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G561" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G565" t="n">
-        <v>0.939006567001343</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G568" t="n">
-        <v>0.803572952747345</v>
+        <v>0.80357301235199</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G571" t="n">
-        <v>0.875804305076599</v>
+        <v>0.875804245471954</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G573" t="n">
-        <v>0.866775274276733</v>
+        <v>0.866775333881378</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G578" t="n">
-        <v>0.975122332572937</v>
+        <v>0.975122392177582</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G580" t="n">
-        <v>1.00220894813538</v>
+        <v>1.00220906734467</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G582" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G585" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G586" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G589" t="n">
-        <v>1.00220894813538</v>
+        <v>1.00220906734467</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G590" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G591" t="n">
-        <v>0.952549934387207</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>0.939006567001343</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G598" t="n">
-        <v>0.952549934387207</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G602" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G603" t="n">
-        <v>0.939006567001343</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G604" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G606" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G608" t="n">
-        <v>0.934492170810699</v>
+        <v>0.934492230415344</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G609" t="n">
-        <v>0.925463199615479</v>
+        <v>0.925463259220123</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G611" t="n">
-        <v>0.925463199615479</v>
+        <v>0.925463259220123</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G617" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G619" t="n">
-        <v>0.893862128257751</v>
+        <v>0.893862068653107</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G628" t="n">
-        <v>0.988665699958801</v>
+        <v>0.988665580749512</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>0.997694551944733</v>
+        <v>0.997694611549377</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G634" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G635" t="n">
-        <v>1.02929580211639</v>
+        <v>1.0292956829071</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G637" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>0.97963672876358</v>
+        <v>0.979636788368225</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G642" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G644" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G645" t="n">
-        <v>0.925463199615479</v>
+        <v>0.925463259220123</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>0.939006567001343</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>0.939006567001343</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G648" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G650" t="n">
-        <v>0.934492170810699</v>
+        <v>0.934492230415344</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G651" t="n">
-        <v>0.975122332572937</v>
+        <v>0.975122392177582</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G654" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607817173004</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G655" t="n">
-        <v>1.00220894813538</v>
+        <v>1.00220906734467</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>0.97963672876358</v>
+        <v>0.979636788368225</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G657" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G659" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607817173004</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G660" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607817173004</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G664" t="n">
-        <v>0.952549934387207</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G666" t="n">
-        <v>0.934492170810699</v>
+        <v>0.934492230415344</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G670" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607817173004</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.988665699958801</v>
+        <v>0.988665580749512</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G674" t="n">
-        <v>0.988665699958801</v>
+        <v>0.988665580749512</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G677" t="n">
-        <v>0.975122332572937</v>
+        <v>0.975122392177582</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G679" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>0.939006567001343</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G684" t="n">
-        <v>0.907405436038971</v>
+        <v>0.907405495643616</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G687" t="n">
-        <v>0.952549934387207</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G688" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G692" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G693" t="n">
-        <v>0.925463199615479</v>
+        <v>0.925463259220123</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G694" t="n">
-        <v>0.925463199615479</v>
+        <v>0.925463259220123</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G695" t="n">
-        <v>0.934492170810699</v>
+        <v>0.934492230415344</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G696" t="n">
-        <v>0.952549934387207</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G697" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G698" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607817173004</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G705" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G706" t="n">
-        <v>0.843300223350525</v>
+        <v>0.84330016374588</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G707" t="n">
-        <v>0.852329134941101</v>
+        <v>0.852329075336456</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G712" t="n">
-        <v>0.787320971488953</v>
+        <v>0.787320911884308</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G714" t="n">
-        <v>0.776486337184906</v>
+        <v>0.776486277580261</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G724" t="n">
-        <v>0.749399483203888</v>
+        <v>0.749399542808533</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G725" t="n">
-        <v>0.749399483203888</v>
+        <v>0.749399542808533</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G730" t="n">
-        <v>0.662721991539001</v>
+        <v>0.662722051143646</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G734" t="n">
-        <v>0.65369313955307</v>
+        <v>0.653693079948425</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G736" t="n">
-        <v>0.678974032402039</v>
+        <v>0.678973972797394</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G738" t="n">
-        <v>0.641052603721619</v>
+        <v>0.641052544116974</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G741" t="n">
-        <v>0.657304584980011</v>
+        <v>0.657304704189301</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G743" t="n">
-        <v>0.662721991539001</v>
+        <v>0.662722051143646</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G744" t="n">
-        <v>0.675362467765808</v>
+        <v>0.675362527370453</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G745" t="n">
-        <v>0.69342029094696</v>
+        <v>0.693420350551605</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G752" t="n">
-        <v>0.675362467765808</v>
+        <v>0.675362527370453</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G754" t="n">
-        <v>0.675362467765808</v>
+        <v>0.675362527370453</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G756" t="n">
-        <v>0.69342029094696</v>
+        <v>0.693420350551605</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G762" t="n">
-        <v>0.700643479824066</v>
+        <v>0.700643420219421</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G768" t="n">
-        <v>0.798155605792999</v>
+        <v>0.798155665397644</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G769" t="n">
-        <v>0.787320971488953</v>
+        <v>0.787320911884308</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G772" t="n">
-        <v>0.798155605792999</v>
+        <v>0.798155665397644</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G773" t="n">
-        <v>0.776486337184906</v>
+        <v>0.776486277580261</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G775" t="n">
-        <v>0.776486337184906</v>
+        <v>0.776486277580261</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G776" t="n">
-        <v>0.80176717042923</v>
+        <v>0.801767230033875</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G777" t="n">
-        <v>0.787320971488953</v>
+        <v>0.787320911884308</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G778" t="n">
-        <v>0.792738318443298</v>
+        <v>0.792738258838654</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G779" t="n">
-        <v>0.792738318443298</v>
+        <v>0.792738258838654</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G781" t="n">
-        <v>0.803572952747345</v>
+        <v>0.80357301235199</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G782" t="n">
-        <v>0.80176717042923</v>
+        <v>0.801767230033875</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G783" t="n">
-        <v>0.794544041156769</v>
+        <v>0.794544100761414</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G785" t="n">
-        <v>0.803572952747345</v>
+        <v>0.80357301235199</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G786" t="n">
-        <v>0.792738318443298</v>
+        <v>0.792738258838654</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>0.769263088703156</v>
+        <v>0.7692631483078</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G798" t="n">
-        <v>0.798155605792999</v>
+        <v>0.798155665397644</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G802" t="n">
-        <v>0.827048122882843</v>
+        <v>0.827048182487488</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G804" t="n">
-        <v>0.857746481895447</v>
+        <v>0.857746422290802</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>0.893862128257751</v>
+        <v>0.893862068653107</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G808" t="n">
-        <v>0.890250504016876</v>
+        <v>0.890250563621521</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G811" t="n">
-        <v>0.857746481895447</v>
+        <v>0.857746422290802</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G812" t="n">
-        <v>0.873998463153839</v>
+        <v>0.873998522758484</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G819" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G820" t="n">
-        <v>0.925463199615479</v>
+        <v>0.925463259220123</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G822" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G828" t="n">
-        <v>0.872192680835724</v>
+        <v>0.872192740440369</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G829" t="n">
-        <v>0.87941575050354</v>
+        <v>0.879415810108185</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G831" t="n">
-        <v>0.875804305076599</v>
+        <v>0.875804245471954</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G832" t="n">
-        <v>0.893862128257751</v>
+        <v>0.893862068653107</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G835" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G836" t="n">
-        <v>0.925463199615479</v>
+        <v>0.925463259220123</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G838" t="n">
-        <v>0.907405436038971</v>
+        <v>0.907405495643616</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G840" t="n">
-        <v>0.907405436038971</v>
+        <v>0.907405495643616</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G842" t="n">
-        <v>0.890250504016876</v>
+        <v>0.890250563621521</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G844" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G847" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G848" t="n">
-        <v>0.97963672876358</v>
+        <v>0.979636788368225</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G849" t="n">
-        <v>1.02929580211639</v>
+        <v>1.0292956829071</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G852" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G854" t="n">
-        <v>1.02929580211639</v>
+        <v>1.0292956829071</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G856" t="n">
-        <v>1.13764274120331</v>
+        <v>1.13764262199402</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G857" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G858" t="n">
-        <v>1.11507046222687</v>
+        <v>1.11507034301758</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G861" t="n">
-        <v>1.06541132926941</v>
+        <v>1.06541121006012</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G863" t="n">
-        <v>1.06089699268341</v>
+        <v>1.06089687347412</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G865" t="n">
-        <v>1.09701251983643</v>
+        <v>1.09701263904572</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G866" t="n">
-        <v>1.07895469665527</v>
+        <v>1.07895481586456</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G867" t="n">
-        <v>1.08346915245056</v>
+        <v>1.08346927165985</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G871" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G874" t="n">
-        <v>1.15570056438446</v>
+        <v>1.15570044517517</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G877" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G880" t="n">
-        <v>1.31370651721954</v>
+        <v>1.31370639801025</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G881" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G884" t="n">
-        <v>1.25501847267151</v>
+        <v>1.2550185918808</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G885" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G887" t="n">
-        <v>1.23244631290436</v>
+        <v>1.23244607448578</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G888" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G890" t="n">
-        <v>1.23244631290436</v>
+        <v>1.23244607448578</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G892" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G893" t="n">
-        <v>1.23244631290436</v>
+        <v>1.23244607448578</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G894" t="n">
-        <v>1.23244631290436</v>
+        <v>1.23244607448578</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G895" t="n">
-        <v>1.23244631290436</v>
+        <v>1.23244607448578</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G896" t="n">
-        <v>1.1827871799469</v>
+        <v>1.18278729915619</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G899" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G900" t="n">
-        <v>1.17827272415161</v>
+        <v>1.1782728433609</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G901" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G902" t="n">
-        <v>1.19633066654205</v>
+        <v>1.19633054733276</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G903" t="n">
-        <v>1.20084500312805</v>
+        <v>1.20084512233734</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G904" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G905" t="n">
-        <v>1.1827871799469</v>
+        <v>1.18278729915619</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G907" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G911" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G912" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G916" t="n">
-        <v>1.07895469665527</v>
+        <v>1.07895481586456</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G920" t="n">
-        <v>1.16021478176117</v>
+        <v>1.16021490097046</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G921" t="n">
-        <v>1.16021478176117</v>
+        <v>1.16021490097046</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G924" t="n">
-        <v>1.15118610858917</v>
+        <v>1.15118598937988</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G926" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G927" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G928" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G929" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G931" t="n">
-        <v>1.25501847267151</v>
+        <v>1.2550185918808</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G932" t="n">
-        <v>1.25501847267151</v>
+        <v>1.2550185918808</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.875</v>
       </c>
       <c r="G936" t="n">
-        <v>1.69292056560516</v>
+        <v>1.69292068481445</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G937" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G938" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.75</v>
       </c>
       <c r="G939" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G946" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G947" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G949" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G952" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G960" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G965" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G966" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G967" t="n">
-        <v>1.35885095596313</v>
+        <v>1.35885083675385</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G968" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G972" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G974" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G975" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G977" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G978" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G981" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G982" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G984" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G987" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G989" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G994" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G996" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G998" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G999" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.26856195926666</v>
+        <v>1.26856184005737</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.30467748641968</v>
+        <v>1.30467760562897</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.28210520744324</v>
+        <v>1.28210508823395</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.28210520744324</v>
+        <v>1.28210508823395</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.3317643404007</v>
+        <v>1.33176422119141</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.29113399982452</v>
+        <v>1.29113411903381</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.28210520744324</v>
+        <v>1.28210508823395</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.23244631290436</v>
+        <v>1.23244607448578</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.1827871799469</v>
+        <v>1.18278729915619</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.17827272415161</v>
+        <v>1.1782728433609</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.18730175495148</v>
+        <v>1.18730163574219</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.1827871799469</v>
+        <v>1.18278729915619</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.1827871799469</v>
+        <v>1.18278729915619</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>1.75</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.35885095596313</v>
+        <v>1.35885083675385</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.44011116027832</v>
+        <v>1.44011127948761</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.50331354141235</v>
+        <v>1.50331342220306</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.53040027618408</v>
+        <v>1.53040015697479</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.53040027618408</v>
+        <v>1.53040015697479</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1193" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.53040027618408</v>
+        <v>1.53040015697479</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.44011116027832</v>
+        <v>1.44011127948761</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.44011116027832</v>
+        <v>1.44011127948761</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.35885095596313</v>
+        <v>1.35885083675385</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.34982204437256</v>
+        <v>1.34982216358185</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.60263156890869</v>
+        <v>1.6026314496994</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326179027557</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1410" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>1.75</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.60263156890869</v>
+        <v>1.6026314496994</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>1.75</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>1.75</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>1.75</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>1.75</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1463" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1469" t="n">
-        <v>1.53040027618408</v>
+        <v>1.53040015697479</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1470" t="n">
-        <v>1.44011116027832</v>
+        <v>1.44011127948761</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.60263156890869</v>
+        <v>1.6026314496994</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>1.75</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1488" t="n">
-        <v>1.53040027618408</v>
+        <v>1.53040015697479</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.50331354141235</v>
+        <v>1.50331342220306</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1494" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>1.75</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1503" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1505" t="n">
-        <v>1.53040027618408</v>
+        <v>1.53040015697479</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>1.75</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>1.75</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>1.75</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.71097850799561</v>
+        <v>1.71097838878632</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1546" t="n">
-        <v>1.62068939208984</v>
+        <v>1.62068927288055</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1555" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1562" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>1.875</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.69292056560516</v>
+        <v>1.69292068481445</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.75</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1573" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326179027557</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326179027557</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.62068939208984</v>
+        <v>1.62068927288055</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.62068939208984</v>
+        <v>1.62068927288055</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326179027557</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.84189772605896</v>
+        <v>1.84189760684967</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.88704216480255</v>
+        <v>1.88704204559326</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.04956269264221</v>
+        <v>2.04956245422363</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.12179398536682</v>
+        <v>2.12179374694824</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.12179398536682</v>
+        <v>2.12179374694824</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1606" t="n">
-        <v>2.05859160423279</v>
+        <v>2.05859136581421</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.04956269264221</v>
+        <v>2.04956245422363</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1611" t="n">
-        <v>1.99538910388947</v>
+        <v>1.99538922309875</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.95927345752716</v>
+        <v>1.95927357673645</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1615" t="n">
-        <v>1.95927345752716</v>
+        <v>1.95927357673645</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.01344680786133</v>
+        <v>2.01344704627991</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.01344680786133</v>
+        <v>2.01344704627991</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.00441789627075</v>
+        <v>2.00441813468933</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1623" t="n">
-        <v>2.00441789627075</v>
+        <v>2.00441813468933</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.01344680786133</v>
+        <v>2.01344704627991</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1625" t="n">
-        <v>2.00441789627075</v>
+        <v>2.00441813468933</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.10373592376709</v>
+        <v>2.10373616218567</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.5172746181488</v>
+        <v>2.51727485656738</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.59213781356812</v>
+        <v>2.59213805198669</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.13489580154419</v>
+        <v>3.13489603996277</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.87287497520447</v>
+        <v>2.87287473678589</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.81672763824463</v>
+        <v>2.81672739982605</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1697" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.87287497520447</v>
+        <v>2.87287473678589</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.92902255058289</v>
+        <v>2.92902231216431</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1709" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.87287497520447</v>
+        <v>2.87287473678589</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.92902255058289</v>
+        <v>2.92902231216431</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.92902255058289</v>
+        <v>2.92902231216431</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1732" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1738" t="n">
-        <v>2.35819053649902</v>
+        <v>2.35819029808044</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.35819053649902</v>
+        <v>2.35819029808044</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.35819053649902</v>
+        <v>2.35819029808044</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.36754846572876</v>
+        <v>2.36754822731018</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.47048544883728</v>
+        <v>2.4704852104187</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1759" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.64828515052795</v>
+        <v>2.64828538894653</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.65764331817627</v>
+        <v>2.65764307975769</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.69507479667664</v>
+        <v>2.69507503509521</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1787" t="n">
-        <v>2.69507479667664</v>
+        <v>2.69507503509521</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1788" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.64828515052795</v>
+        <v>2.64828538894653</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.64828515052795</v>
+        <v>2.64828538894653</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.69507479667664</v>
+        <v>2.69507503509521</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.65764331817627</v>
+        <v>2.65764307975769</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.19104337692261</v>
+        <v>3.19104361534119</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.29398012161255</v>
+        <v>3.29398036003113</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.29398012161255</v>
+        <v>3.29398036003113</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.31269598007202</v>
+        <v>3.3126962184906</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.31269598007202</v>
+        <v>3.3126962184906</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.54664373397827</v>
+        <v>3.54664349555969</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1870" t="n">
-        <v>3.65893840789795</v>
+        <v>3.65893864631653</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1877" t="n">
-        <v>3.69636988639832</v>
+        <v>3.69637012481689</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1879" t="n">
-        <v>3.75251746177673</v>
+        <v>3.75251770019531</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1881" t="n">
-        <v>3.75251746177673</v>
+        <v>3.75251770019531</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -58300,6 +58300,32 @@
         <v>4.73999977111816</v>
       </c>
       <c r="H2228" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2229" t="n">
+        <v>6900</v>
+      </c>
+      <c r="C2229" t="n">
+        <v>4.67999982833862</v>
+      </c>
+      <c r="D2229" t="n">
+        <v>4.59000015258789</v>
+      </c>
+      <c r="E2229" t="n">
+        <v>4.65999984741211</v>
+      </c>
+      <c r="F2229" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="G2229" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="H2229" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G3" t="n">
-        <v>3.66393160820007</v>
+        <v>3.66393184661865</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G6" t="n">
-        <v>3.59711766242981</v>
+        <v>3.59711790084839</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G14" t="n">
-        <v>3.64406776428223</v>
+        <v>3.64406800270081</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5989236831665</v>
+        <v>3.59892344474792</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>3.56641936302185</v>
+        <v>3.56641960144043</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G27" t="n">
-        <v>3.62059307098389</v>
+        <v>3.62059330940247</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G30" t="n">
-        <v>3.57544851303101</v>
+        <v>3.57544827461243</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>3.57544851303101</v>
+        <v>3.57544827461243</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G32" t="n">
-        <v>3.60253524780273</v>
+        <v>3.60253500938416</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G33" t="n">
-        <v>3.60253524780273</v>
+        <v>3.60253500938416</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G34" t="n">
-        <v>3.60253524780273</v>
+        <v>3.60253500938416</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G35" t="n">
-        <v>3.60253524780273</v>
+        <v>3.60253500938416</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G41" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>3.5032172203064</v>
+        <v>3.50321698188782</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>3.57544851303101</v>
+        <v>3.57544827461243</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G64" t="n">
-        <v>3.44001460075378</v>
+        <v>3.44001483917236</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G72" t="n">
-        <v>3.47613024711609</v>
+        <v>3.47613048553467</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G73" t="n">
-        <v>3.47613024711609</v>
+        <v>3.47613048553467</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G74" t="n">
-        <v>3.47613024711609</v>
+        <v>3.47613048553467</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G92" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>3.3587543964386</v>
+        <v>3.35875463485718</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G107" t="n">
-        <v>3.22332072257996</v>
+        <v>3.22332096099854</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G111" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G114" t="n">
-        <v>3.00662708282471</v>
+        <v>3.00662684440613</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>3.04274249076843</v>
+        <v>3.04274272918701</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>3.04274249076843</v>
+        <v>3.04274272918701</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G119" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G120" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G127" t="n">
-        <v>3.45807266235352</v>
+        <v>3.45807242393494</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>3.47613024711609</v>
+        <v>3.47613048553467</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G138" t="n">
-        <v>3.28652310371399</v>
+        <v>3.28652358055115</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G176" t="n">
-        <v>3.24137878417969</v>
+        <v>3.24137854576111</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G186" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>3.19623398780823</v>
+        <v>3.19623422622681</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G188" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G190" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.5</v>
       </c>
       <c r="G191" t="n">
-        <v>3.16011881828308</v>
+        <v>3.16011834144592</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.5</v>
       </c>
       <c r="G192" t="n">
-        <v>3.16011881828308</v>
+        <v>3.16011834144592</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>3.19623398780823</v>
+        <v>3.19623422622681</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G210" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G211" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G212" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G213" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G220" t="n">
-        <v>2.66352868080139</v>
+        <v>2.66352844238281</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G221" t="n">
-        <v>2.60032606124878</v>
+        <v>2.60032629966736</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G223" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G225" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G226" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G230" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G231" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G232" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489214897156</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489214897156</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489214897156</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G241" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489214897156</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489214897156</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G250" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G252" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G253" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G255" t="n">
-        <v>2.27528548240662</v>
+        <v>2.27528524398804</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.5</v>
       </c>
       <c r="G259" t="n">
-        <v>2.25722742080688</v>
+        <v>2.25722765922546</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.5</v>
       </c>
       <c r="G261" t="n">
-        <v>2.25722742080688</v>
+        <v>2.25722765922546</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.5</v>
       </c>
       <c r="G262" t="n">
-        <v>2.25722742080688</v>
+        <v>2.25722765922546</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G263" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G264" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G265" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>2.27528548240662</v>
+        <v>2.27528524398804</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>2.18499612808228</v>
+        <v>2.18499636650085</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G289" t="n">
-        <v>2.18499612808228</v>
+        <v>2.18499636650085</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>2.12179398536682</v>
+        <v>2.12179374694824</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G296" t="n">
-        <v>2.0224757194519</v>
+        <v>2.02247595787048</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G298" t="n">
-        <v>1.93218684196472</v>
+        <v>1.93218672275543</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G299" t="n">
-        <v>1.9412157535553</v>
+        <v>1.94121563434601</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G301" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>1.97733128070831</v>
+        <v>1.97733116149902</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G303" t="n">
-        <v>1.97733128070831</v>
+        <v>1.97733116149902</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G304" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>1.95927345752716</v>
+        <v>1.95927357673645</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G306" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G311" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G312" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G313" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G314" t="n">
-        <v>2.0224757194519</v>
+        <v>2.02247595787048</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G316" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G318" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G319" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G320" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>1.92315793037415</v>
+        <v>1.92315804958344</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>2.04956269264221</v>
+        <v>2.04956245422363</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>1.84189772605896</v>
+        <v>1.84189760684967</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G337" t="n">
-        <v>2.0224757194519</v>
+        <v>2.02247595787048</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G338" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G341" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G344" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G345" t="n">
-        <v>1.93218684196472</v>
+        <v>1.93218672275543</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2</v>
       </c>
       <c r="G354" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2</v>
       </c>
       <c r="G356" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2</v>
       </c>
       <c r="G357" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2</v>
       </c>
       <c r="G358" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2</v>
       </c>
       <c r="G359" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2</v>
       </c>
       <c r="G360" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2</v>
       </c>
       <c r="G361" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2</v>
       </c>
       <c r="G362" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2</v>
       </c>
       <c r="G363" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2</v>
       </c>
       <c r="G365" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2</v>
       </c>
       <c r="G366" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2</v>
       </c>
       <c r="G378" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2</v>
       </c>
       <c r="G379" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2</v>
       </c>
       <c r="G380" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>1.7877242565155</v>
+        <v>1.78772413730621</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G386" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326179027557</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G390" t="n">
-        <v>1.6793771982193</v>
+        <v>1.67937731742859</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G394" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>1.75</v>
       </c>
       <c r="G395" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G396" t="n">
-        <v>1.59811699390411</v>
+        <v>1.5981171131134</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G399" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G400" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G405" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G407" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G408" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G409" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G410" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G411" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G421" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G425" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G426" t="n">
-        <v>1.28210532665253</v>
+        <v>1.28210508823395</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G428" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G429" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G430" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G431" t="n">
-        <v>1.28210532665253</v>
+        <v>1.28210508823395</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G432" t="n">
-        <v>1.30016303062439</v>
+        <v>1.30016314983368</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G433" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>1.30016303062439</v>
+        <v>1.30016314983368</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G437" t="n">
-        <v>1.30016303062439</v>
+        <v>1.30016314983368</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G438" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G439" t="n">
-        <v>1.30016303062439</v>
+        <v>1.30016314983368</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G440" t="n">
-        <v>1.30016303062439</v>
+        <v>1.30016314983368</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G441" t="n">
-        <v>1.30016303062439</v>
+        <v>1.30016314983368</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G442" t="n">
-        <v>1.24598968029022</v>
+        <v>1.24598956108093</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G443" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G449" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326179027557</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>1.75</v>
       </c>
       <c r="G451" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G467" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G469" t="n">
-        <v>1.6793771982193</v>
+        <v>1.67937731742859</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G471" t="n">
-        <v>1.59811699390411</v>
+        <v>1.5981171131134</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>1.75</v>
       </c>
       <c r="G476" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G477" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G478" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G480" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G483" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G494" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G499" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>1.59811699390411</v>
+        <v>1.5981171131134</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G501" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G503" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G504" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G506" t="n">
-        <v>1.59811699390411</v>
+        <v>1.5981171131134</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G507" t="n">
-        <v>1.59811699390411</v>
+        <v>1.5981171131134</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G508" t="n">
-        <v>1.59811699390411</v>
+        <v>1.5981171131134</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G515" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326179027557</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G519" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G521" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>1.75</v>
       </c>
       <c r="G523" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G525" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>1.75</v>
       </c>
       <c r="G526" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G534" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G535" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G536" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G542" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G544" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G547" t="n">
-        <v>1.20084500312805</v>
+        <v>1.20084512233734</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G548" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G549" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G550" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G554" t="n">
-        <v>1.08346915245056</v>
+        <v>1.08346927165985</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G556" t="n">
-        <v>1.02026689052582</v>
+        <v>1.02026677131653</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G557" t="n">
-        <v>1.02026689052582</v>
+        <v>1.02026677131653</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G559" t="n">
-        <v>1.01123785972595</v>
+        <v>1.01123797893524</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G560" t="n">
-        <v>1.01123785972595</v>
+        <v>1.01123797893524</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G561" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G566" t="n">
-        <v>0.83968859910965</v>
+        <v>0.839688658714294</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G568" t="n">
-        <v>0.803572952747345</v>
+        <v>0.80357301235199</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>0.884833216667175</v>
+        <v>0.884833157062531</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G571" t="n">
-        <v>0.875804305076599</v>
+        <v>0.875804245471954</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G575" t="n">
-        <v>0.884833216667175</v>
+        <v>0.884833157062531</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G581" t="n">
-        <v>1.01123785972595</v>
+        <v>1.01123797893524</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G582" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G585" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G586" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G590" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G591" t="n">
-        <v>0.952549874782562</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G592" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G593" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G594" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G597" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G598" t="n">
-        <v>0.952549874782562</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G599" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G602" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G604" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G605" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G606" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G607" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G608" t="n">
-        <v>0.934492170810699</v>
+        <v>0.934492230415344</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G612" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G616" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G617" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G619" t="n">
-        <v>0.893862128257751</v>
+        <v>0.893862068653107</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G620" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G622" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>1</v>
       </c>
       <c r="G623" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G625" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G628" t="n">
-        <v>0.988665640354156</v>
+        <v>0.988665580749512</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G629" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G630" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G633" t="n">
-        <v>1.01123785972595</v>
+        <v>1.01123797893524</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G634" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G637" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>0.97963672876358</v>
+        <v>0.979636788368225</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G642" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G643" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G644" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G648" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G650" t="n">
-        <v>0.934492170810699</v>
+        <v>0.934492230415344</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G654" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607817173004</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>0.97963672876358</v>
+        <v>0.979636788368225</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G657" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G659" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607817173004</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G660" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607817173004</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G662" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G664" t="n">
-        <v>0.952549874782562</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G665" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G666" t="n">
-        <v>0.934492170810699</v>
+        <v>0.934492230415344</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G667" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G669" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G670" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607817173004</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G672" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.988665640354156</v>
+        <v>0.988665580749512</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G674" t="n">
-        <v>0.988665640354156</v>
+        <v>0.988665580749512</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G679" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G687" t="n">
-        <v>0.952549874782562</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G688" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G692" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G695" t="n">
-        <v>0.934492170810699</v>
+        <v>0.934492230415344</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G696" t="n">
-        <v>0.952549874782562</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G697" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G698" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607817173004</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>1</v>
       </c>
       <c r="G700" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>1</v>
       </c>
       <c r="G701" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G705" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G706" t="n">
-        <v>0.843300223350525</v>
+        <v>0.84330016374588</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G714" t="n">
-        <v>0.776486337184906</v>
+        <v>0.776486277580261</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G715" t="n">
-        <v>0.80718457698822</v>
+        <v>0.807184517383575</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G721" t="n">
-        <v>0.698837697505951</v>
+        <v>0.698837637901306</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G724" t="n">
-        <v>0.749399483203888</v>
+        <v>0.749399542808533</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G725" t="n">
-        <v>0.749399483203888</v>
+        <v>0.749399542808533</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G728" t="n">
-        <v>0.622994840145111</v>
+        <v>0.622994780540466</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G729" t="n">
-        <v>0.619383156299591</v>
+        <v>0.619383215904236</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G736" t="n">
-        <v>0.678974032402039</v>
+        <v>0.678973972797394</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G738" t="n">
-        <v>0.641052663326263</v>
+        <v>0.641052544116974</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G739" t="n">
-        <v>0.637440979480743</v>
+        <v>0.637441039085388</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G741" t="n">
-        <v>0.657304584980011</v>
+        <v>0.657304704189301</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G744" t="n">
-        <v>0.675362467765808</v>
+        <v>0.675362527370453</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G745" t="n">
-        <v>0.69342029094696</v>
+        <v>0.693420350551605</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G752" t="n">
-        <v>0.675362467765808</v>
+        <v>0.675362527370453</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G754" t="n">
-        <v>0.675362467765808</v>
+        <v>0.675362527370453</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G755" t="n">
-        <v>0.698837697505951</v>
+        <v>0.698837637901306</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G756" t="n">
-        <v>0.69342029094696</v>
+        <v>0.693420350551605</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G762" t="n">
-        <v>0.700643479824066</v>
+        <v>0.700643420219421</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G766" t="n">
-        <v>0.80718457698822</v>
+        <v>0.807184517383575</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G770" t="n">
-        <v>0.765651524066925</v>
+        <v>0.76565158367157</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G771" t="n">
-        <v>0.765651524066925</v>
+        <v>0.76565158367157</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G773" t="n">
-        <v>0.776486337184906</v>
+        <v>0.776486277580261</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G775" t="n">
-        <v>0.776486337184906</v>
+        <v>0.776486277580261</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G776" t="n">
-        <v>0.80176717042923</v>
+        <v>0.801767230033875</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G778" t="n">
-        <v>0.792738318443298</v>
+        <v>0.792738258838654</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G779" t="n">
-        <v>0.792738318443298</v>
+        <v>0.792738258838654</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G780" t="n">
-        <v>0.80899041891098</v>
+        <v>0.808990359306335</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G781" t="n">
-        <v>0.803572952747345</v>
+        <v>0.80357301235199</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G782" t="n">
-        <v>0.80176717042923</v>
+        <v>0.801767230033875</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G783" t="n">
-        <v>0.794544041156769</v>
+        <v>0.794544100761414</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G784" t="n">
-        <v>0.80899041891098</v>
+        <v>0.808990359306335</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G785" t="n">
-        <v>0.803572952747345</v>
+        <v>0.80357301235199</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G786" t="n">
-        <v>0.792738318443298</v>
+        <v>0.792738258838654</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>0.769263088703156</v>
+        <v>0.7692631483078</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G800" t="n">
-        <v>0.823436558246613</v>
+        <v>0.823436617851257</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G805" t="n">
-        <v>0.859552204608917</v>
+        <v>0.859552264213562</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>0.893862128257751</v>
+        <v>0.893862068653107</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G808" t="n">
-        <v>0.890250504016876</v>
+        <v>0.890250563621521</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G815" t="n">
-        <v>0.859552204608917</v>
+        <v>0.859552264213562</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1</v>
       </c>
       <c r="G817" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G819" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G822" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G827" t="n">
-        <v>0.88302743434906</v>
+        <v>0.883027374744415</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G829" t="n">
-        <v>0.87941575050354</v>
+        <v>0.879415810108185</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G830" t="n">
-        <v>0.88302743434906</v>
+        <v>0.883027374744415</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G831" t="n">
-        <v>0.875804305076599</v>
+        <v>0.875804245471954</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G832" t="n">
-        <v>0.893862128257751</v>
+        <v>0.893862068653107</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G833" t="n">
-        <v>0.88302743434906</v>
+        <v>0.883027374744415</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1</v>
       </c>
       <c r="G834" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G835" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G841" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G842" t="n">
-        <v>0.890250504016876</v>
+        <v>0.890250563621521</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G844" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G846" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G847" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G848" t="n">
-        <v>0.97963672876358</v>
+        <v>0.979636788368225</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G852" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G856" t="n">
-        <v>1.13764274120331</v>
+        <v>1.13764262199402</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G857" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G858" t="n">
-        <v>1.11507046222687</v>
+        <v>1.11507034301758</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G860" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G861" t="n">
-        <v>1.06541132926941</v>
+        <v>1.06541121006012</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G863" t="n">
-        <v>1.06089699268341</v>
+        <v>1.06089687347412</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G867" t="n">
-        <v>1.08346915245056</v>
+        <v>1.08346927165985</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G871" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G872" t="n">
-        <v>1.1421571969986</v>
+        <v>1.14215707778931</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G877" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>1.20535945892334</v>
+        <v>1.20535957813263</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G882" t="n">
-        <v>1.24598968029022</v>
+        <v>1.24598956108093</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G885" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G886" t="n">
-        <v>1.20535945892334</v>
+        <v>1.20535957813263</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G887" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244607448578</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G888" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G890" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244607448578</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G892" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G893" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244607448578</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G894" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244607448578</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G895" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244607448578</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G896" t="n">
-        <v>1.1827871799469</v>
+        <v>1.18278729915619</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G899" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G900" t="n">
-        <v>1.17827272415161</v>
+        <v>1.1782728433609</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G901" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G903" t="n">
-        <v>1.20084500312805</v>
+        <v>1.20084512233734</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G904" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G905" t="n">
-        <v>1.1827871799469</v>
+        <v>1.18278729915619</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G907" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G908" t="n">
-        <v>1.1421571969986</v>
+        <v>1.14215707778931</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G911" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G912" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G915" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G917" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G918" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G920" t="n">
-        <v>1.16021478176117</v>
+        <v>1.16021490097046</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G921" t="n">
-        <v>1.16021478176117</v>
+        <v>1.16021490097046</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G923" t="n">
-        <v>1.1421571969986</v>
+        <v>1.14215707778931</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G925" t="n">
-        <v>1.1421571969986</v>
+        <v>1.14215707778931</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G926" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G927" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G928" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G929" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G930" t="n">
-        <v>1.24598968029022</v>
+        <v>1.24598956108093</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G935" t="n">
-        <v>1.6793771982193</v>
+        <v>1.67937731742859</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G937" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G938" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.75</v>
       </c>
       <c r="G939" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G940" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G946" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G947" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G949" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G952" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G960" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G966" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G967" t="n">
-        <v>1.35885107517242</v>
+        <v>1.35885083675385</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G972" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G974" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G975" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G977" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G978" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G981" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G983" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G984" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G985" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G990" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G994" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G996" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G998" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G999" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.43108236789703</v>
+        <v>1.43108224868774</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.32273542881012</v>
+        <v>1.32273530960083</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.30467748641968</v>
+        <v>1.30467760562897</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.28210532665253</v>
+        <v>1.28210508823395</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.28210532665253</v>
+        <v>1.28210508823395</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.27759063243866</v>
+        <v>1.27759075164795</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.3317643404007</v>
+        <v>1.33176422119141</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.40399551391602</v>
+        <v>1.40399539470673</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.28210532665253</v>
+        <v>1.28210508823395</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244607448578</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.1827871799469</v>
+        <v>1.18278729915619</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.17827272415161</v>
+        <v>1.1782728433609</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.1827871799469</v>
+        <v>1.18278729915619</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.1827871799469</v>
+        <v>1.18278729915619</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>1.75</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.35885107517242</v>
+        <v>1.35885083675385</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1114" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.44011116027832</v>
+        <v>1.44011127948761</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.30016303062439</v>
+        <v>1.30016314983368</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.50331354141235</v>
+        <v>1.50331342220306</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.53040027618408</v>
+        <v>1.53040015697479</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.53040027618408</v>
+        <v>1.53040015697479</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1193" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.53040027618408</v>
+        <v>1.53040015697479</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.44011116027832</v>
+        <v>1.44011127948761</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.44011116027832</v>
+        <v>1.44011127948761</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.43108236789703</v>
+        <v>1.43108224868774</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.40399551391602</v>
+        <v>1.40399539470673</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.43108236789703</v>
+        <v>1.43108224868774</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.35885107517242</v>
+        <v>1.35885083675385</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.34982204437256</v>
+        <v>1.34982216358185</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.40399551391602</v>
+        <v>1.40399539470673</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.40399551391602</v>
+        <v>1.40399539470673</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.40399551391602</v>
+        <v>1.40399539470673</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.40399551391602</v>
+        <v>1.40399539470673</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.40399551391602</v>
+        <v>1.40399539470673</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326179027557</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1410" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>1.75</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>1.75</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>1.75</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.59811699390411</v>
+        <v>1.5981171131134</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>1.75</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>1.75</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1463" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.50782799720764</v>
+        <v>1.50782787799835</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1469" t="n">
-        <v>1.53040027618408</v>
+        <v>1.53040015697479</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1470" t="n">
-        <v>1.44011116027832</v>
+        <v>1.44011127948761</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>1.75</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1488" t="n">
-        <v>1.53040027618408</v>
+        <v>1.53040015697479</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1489" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.50331354141235</v>
+        <v>1.50331342220306</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1494" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>1.75</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1503" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1505" t="n">
-        <v>1.53040027618408</v>
+        <v>1.53040015697479</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>1.75</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>1.75</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>1.75</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.65680515766144</v>
+        <v>1.65680503845215</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.71097850799561</v>
+        <v>1.71097838878632</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1538" t="n">
-        <v>1.65680515766144</v>
+        <v>1.65680503845215</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1546" t="n">
-        <v>1.62068939208984</v>
+        <v>1.62068927288055</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1553" t="n">
-        <v>1.70194959640503</v>
+        <v>1.70194947719574</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1556" t="n">
-        <v>1.6793771982193</v>
+        <v>1.67937731742859</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.70194959640503</v>
+        <v>1.70194947719574</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1566" t="n">
-        <v>1.65680515766144</v>
+        <v>1.65680503845215</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.75</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1573" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326179027557</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326179027557</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.62068939208984</v>
+        <v>1.62068927288055</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.62068939208984</v>
+        <v>1.62068927288055</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326179027557</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.84189772605896</v>
+        <v>1.84189760684967</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.88704216480255</v>
+        <v>1.88704204559326</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.04956269264221</v>
+        <v>2.04956245422363</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.12179398536682</v>
+        <v>2.12179374694824</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.12179398536682</v>
+        <v>2.12179374694824</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.04956269264221</v>
+        <v>2.04956245422363</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.95927345752716</v>
+        <v>1.95927357673645</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1615" t="n">
-        <v>1.95927345752716</v>
+        <v>1.95927357673645</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.01344680786133</v>
+        <v>2.01344704627991</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.0224757194519</v>
+        <v>2.02247595787048</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1618" t="n">
-        <v>2.0224757194519</v>
+        <v>2.02247595787048</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.0224757194519</v>
+        <v>2.02247595787048</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.01344680786133</v>
+        <v>2.01344704627991</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.0224757194519</v>
+        <v>2.02247595787048</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.01344680786133</v>
+        <v>2.01344704627991</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.10373592376709</v>
+        <v>2.10373616218567</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.5172746181488</v>
+        <v>2.51727485656738</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.59213781356812</v>
+        <v>2.59213805198669</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.13489580154419</v>
+        <v>3.13489603996277</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.87287497520447</v>
+        <v>2.87287473678589</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.81672763824463</v>
+        <v>2.81672739982605</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1697" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.87287497520447</v>
+        <v>2.87287473678589</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.92902255058289</v>
+        <v>2.92902231216431</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1709" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.87287497520447</v>
+        <v>2.87287473678589</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.92902255058289</v>
+        <v>2.92902231216431</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.92902255058289</v>
+        <v>2.92902231216431</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1732" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1738" t="n">
-        <v>2.35819053649902</v>
+        <v>2.35819029808044</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.35819053649902</v>
+        <v>2.35819029808044</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.35819053649902</v>
+        <v>2.35819029808044</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.36754846572876</v>
+        <v>2.36754822731018</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.47048544883728</v>
+        <v>2.4704852104187</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1759" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.64828515052795</v>
+        <v>2.64828538894653</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.65764331817627</v>
+        <v>2.65764307975769</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.69507479667664</v>
+        <v>2.69507503509521</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1787" t="n">
-        <v>2.69507479667664</v>
+        <v>2.69507503509521</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1788" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.64828515052795</v>
+        <v>2.64828538894653</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.64828515052795</v>
+        <v>2.64828538894653</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.69507479667664</v>
+        <v>2.69507503509521</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.65764331817627</v>
+        <v>2.65764307975769</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.19104337692261</v>
+        <v>3.19104361534119</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.29398012161255</v>
+        <v>3.29398036003113</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.29398012161255</v>
+        <v>3.29398036003113</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.31269598007202</v>
+        <v>3.3126962184906</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.31269598007202</v>
+        <v>3.3126962184906</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.54664373397827</v>
+        <v>3.54664349555969</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1870" t="n">
-        <v>3.65893840789795</v>
+        <v>3.65893864631653</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1877" t="n">
-        <v>3.69636988639832</v>
+        <v>3.69637012481689</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1879" t="n">
-        <v>3.75251746177673</v>
+        <v>3.75251770019531</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1881" t="n">
-        <v>3.75251746177673</v>
+        <v>3.75251770019531</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -58378,6 +58378,32 @@
         <v>4.73000001907349</v>
       </c>
       <c r="H2231" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2232" t="n">
+        <v>3300</v>
+      </c>
+      <c r="C2232" t="n">
+        <v>4.65999984741211</v>
+      </c>
+      <c r="D2232" t="n">
+        <v>4.63000011444092</v>
+      </c>
+      <c r="E2232" t="n">
+        <v>4.65999984741211</v>
+      </c>
+      <c r="F2232" t="n">
+        <v>4.65000009536743</v>
+      </c>
+      <c r="G2232" t="n">
+        <v>4.65000009536743</v>
+      </c>
+      <c r="H2232" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -51770,8 +51770,31 @@
       <c r="E2235" t="n">
         <v>4.55000019073486</v>
       </c>
-      <c r="F2235"/>
+      <c r="F2235" t="n">
+        <v>4.44000005722046</v>
+      </c>
       <c r="G2235" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2236" t="n">
+        <v>6900</v>
+      </c>
+      <c r="C2236" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D2236" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="E2236" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="F2236"/>
+      <c r="G2236" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -51785,7 +51785,7 @@
         <v>6900</v>
       </c>
       <c r="C2236" t="n">
-        <v>4.5</v>
+        <v>4.53000020980835</v>
       </c>
       <c r="D2236" t="n">
         <v>4.40000009536743</v>
@@ -51793,8 +51793,31 @@
       <c r="E2236" t="n">
         <v>4.40000009536743</v>
       </c>
-      <c r="F2236"/>
+      <c r="F2236" t="n">
+        <v>4.53000020980835</v>
+      </c>
       <c r="G2236" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2237" t="n">
+        <v>8100</v>
+      </c>
+      <c r="C2237" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2237" t="n">
+        <v>4.44999980926514</v>
+      </c>
+      <c r="E2237" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2237"/>
+      <c r="G2237" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -51816,8 +51816,31 @@
       <c r="E2237" t="n">
         <v>4.57999992370605</v>
       </c>
-      <c r="F2237"/>
+      <c r="F2237" t="n">
+        <v>4.51000022888184</v>
+      </c>
       <c r="G2237" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2238" t="n">
+        <v>900</v>
+      </c>
+      <c r="C2238" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D2238" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E2238" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F2238"/>
+      <c r="G2238" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -51839,8 +51839,31 @@
       <c r="E2238" t="n">
         <v>4.5</v>
       </c>
-      <c r="F2238"/>
+      <c r="F2238" t="n">
+        <v>4.5</v>
+      </c>
       <c r="G2238" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2239" t="n">
+        <v>300</v>
+      </c>
+      <c r="C2239" t="n">
+        <v>4.55000019073486</v>
+      </c>
+      <c r="D2239" t="n">
+        <v>4.55000019073486</v>
+      </c>
+      <c r="E2239" t="n">
+        <v>4.55000019073486</v>
+      </c>
+      <c r="F2239"/>
+      <c r="G2239" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -51869,6 +51869,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2240">
+      <c r="A2240" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2240" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C2240" t="n">
+        <v>4.51999998092651</v>
+      </c>
+      <c r="D2240" t="n">
+        <v>4.40999984741211</v>
+      </c>
+      <c r="E2240" t="n">
+        <v>4.51999998092651</v>
+      </c>
+      <c r="F2240" t="n">
+        <v>4.46000003814697</v>
+      </c>
+      <c r="G2240" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G3" t="n">
-        <v>3.66393184661865</v>
+        <v>3.66393160820007</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G14" t="n">
-        <v>3.64406800270081</v>
+        <v>3.64406776428223</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G22" t="n">
-        <v>3.62962198257446</v>
+        <v>3.62962174415588</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>3.56641960144043</v>
+        <v>3.56641936302185</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>3.62962198257446</v>
+        <v>3.62962174415588</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G27" t="n">
-        <v>3.62059330940247</v>
+        <v>3.62059307098389</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G37" t="n">
-        <v>3.5303041934967</v>
+        <v>3.53030371665955</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>3.52127504348755</v>
+        <v>3.52127528190613</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G39" t="n">
-        <v>3.52127504348755</v>
+        <v>3.52127528190613</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G41" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.75</v>
       </c>
       <c r="G43" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.75</v>
       </c>
       <c r="G44" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G53" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G54" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G55" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G56" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G57" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G58" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G60" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G61" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G65" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G66" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G67" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G68" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G69" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G70" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G71" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G87" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G88" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G89" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>3.34972548484802</v>
+        <v>3.3497257232666</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.34972548484802</v>
+        <v>3.3497257232666</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G92" t="n">
-        <v>3.34972548484802</v>
+        <v>3.3497257232666</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>3.34972548484802</v>
+        <v>3.3497257232666</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>3.34972548484802</v>
+        <v>3.3497257232666</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.75</v>
       </c>
       <c r="G101" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.75</v>
       </c>
       <c r="G102" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.75</v>
       </c>
       <c r="G103" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.75</v>
       </c>
       <c r="G104" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>3.3587543964386</v>
+        <v>3.35875463485718</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>3.29555201530457</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>3.2052628993988</v>
+        <v>3.20526313781738</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G119" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G120" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>3.75</v>
       </c>
       <c r="G124" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.75</v>
       </c>
       <c r="G125" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G128" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G135" t="n">
-        <v>3.29555201530457</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>3.29555201530457</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G138" t="n">
-        <v>3.28652334213257</v>
+        <v>3.28652310371399</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G141" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G142" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G143" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G145" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G146" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G148" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G149" t="n">
-        <v>3.29555201530457</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>3.29555201530457</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G151" t="n">
-        <v>3.29555201530457</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G152" t="n">
-        <v>3.37681245803833</v>
+        <v>3.37681221961975</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G153" t="n">
-        <v>3.37681245803833</v>
+        <v>3.37681221961975</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G154" t="n">
-        <v>3.37681245803833</v>
+        <v>3.37681221961975</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G155" t="n">
-        <v>3.37681245803833</v>
+        <v>3.37681221961975</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G156" t="n">
-        <v>3.37681245803833</v>
+        <v>3.37681221961975</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G166" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G167" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G168" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G169" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G171" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G172" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G173" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G174" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G175" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G177" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.75</v>
       </c>
       <c r="G178" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G203" t="n">
-        <v>3.09691643714905</v>
+        <v>3.09691619873047</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G208" t="n">
-        <v>3.05177164077759</v>
+        <v>3.05177140235901</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G210" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G211" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G212" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G213" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G220" t="n">
-        <v>2.66352844238281</v>
+        <v>2.66352868080139</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G223" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G225" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G226" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G227" t="n">
-        <v>2.63644194602966</v>
+        <v>2.63644170761108</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G230" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G231" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G232" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G236" t="n">
-        <v>2.5100371837616</v>
+        <v>2.51003694534302</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G237" t="n">
-        <v>2.5100371837616</v>
+        <v>2.51003694534302</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489262580872</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489262580872</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489262580872</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G241" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489262580872</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489262580872</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>2.50100827217102</v>
+        <v>2.50100803375244</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G245" t="n">
-        <v>2.50100827217102</v>
+        <v>2.50100803375244</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G246" t="n">
-        <v>2.50100827217102</v>
+        <v>2.50100803375244</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G247" t="n">
-        <v>2.50100827217102</v>
+        <v>2.50100803375244</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G248" t="n">
-        <v>2.50100827217102</v>
+        <v>2.50100803375244</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G249" t="n">
-        <v>2.5100371837616</v>
+        <v>2.51003694534302</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G250" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G252" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G253" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G255" t="n">
-        <v>2.27528524398804</v>
+        <v>2.27528548240662</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>2.32945847511292</v>
+        <v>2.32945871353149</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>2.32945847511292</v>
+        <v>2.32945871353149</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G258" t="n">
-        <v>2.24819850921631</v>
+        <v>2.24819874763489</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G260" t="n">
-        <v>2.24819850921631</v>
+        <v>2.24819874763489</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G267" t="n">
-        <v>2.42877697944641</v>
+        <v>2.42877674102783</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G268" t="n">
-        <v>2.47392129898071</v>
+        <v>2.47392153739929</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G269" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>2.27528524398804</v>
+        <v>2.27528548240662</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G275" t="n">
-        <v>2.30237197875977</v>
+        <v>2.30237221717834</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G276" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G277" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G281" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>2.18499612808228</v>
+        <v>2.18499636650085</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G289" t="n">
-        <v>2.18499612808228</v>
+        <v>2.18499636650085</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>2.15790963172913</v>
+        <v>2.15790939331055</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G298" t="n">
-        <v>1.93218684196472</v>
+        <v>1.93218672275543</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G300" t="n">
-        <v>1.87801337242126</v>
+        <v>1.87801313400269</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>1.97733128070831</v>
+        <v>1.9773313999176</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G303" t="n">
-        <v>1.97733128070831</v>
+        <v>1.9773313999176</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>1.95927369594574</v>
+        <v>1.95927345752716</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G321" t="n">
-        <v>1.95024478435516</v>
+        <v>1.95024466514587</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G322" t="n">
-        <v>1.95024478435516</v>
+        <v>1.95024466514587</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G323" t="n">
-        <v>1.95024478435516</v>
+        <v>1.95024466514587</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G324" t="n">
-        <v>1.95024478435516</v>
+        <v>1.95024466514587</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G340" t="n">
-        <v>2.00441813468933</v>
+        <v>2.00441789627075</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G342" t="n">
-        <v>2.00441813468933</v>
+        <v>2.00441789627075</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G345" t="n">
-        <v>1.93218684196472</v>
+        <v>1.93218672275543</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G350" t="n">
-        <v>1.87801337242126</v>
+        <v>1.87801313400269</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2</v>
       </c>
       <c r="G354" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2</v>
       </c>
       <c r="G356" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2</v>
       </c>
       <c r="G357" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2</v>
       </c>
       <c r="G358" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2</v>
       </c>
       <c r="G359" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2</v>
       </c>
       <c r="G360" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2</v>
       </c>
       <c r="G361" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2</v>
       </c>
       <c r="G362" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2</v>
       </c>
       <c r="G363" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G364" t="n">
-        <v>1.73355066776276</v>
+        <v>1.73355054855347</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2</v>
       </c>
       <c r="G365" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2</v>
       </c>
       <c r="G366" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G370" t="n">
-        <v>1.68840622901917</v>
+        <v>1.68840610980988</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G371" t="n">
-        <v>1.68840622901917</v>
+        <v>1.68840610980988</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2</v>
       </c>
       <c r="G378" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2</v>
       </c>
       <c r="G379" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2</v>
       </c>
       <c r="G380" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G382" t="n">
-        <v>1.7154928445816</v>
+        <v>1.71549296379089</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G383" t="n">
-        <v>1.7154928445816</v>
+        <v>1.71549296379089</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G386" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G387" t="n">
-        <v>1.68840622901917</v>
+        <v>1.68840610980988</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G390" t="n">
-        <v>1.6793771982193</v>
+        <v>1.67937731742859</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G391" t="n">
-        <v>1.7154928445816</v>
+        <v>1.71549296379089</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G392" t="n">
-        <v>1.69743502140045</v>
+        <v>1.69743514060974</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G393" t="n">
-        <v>1.69743502140045</v>
+        <v>1.69743514060974</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>1.52588582038879</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G405" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G407" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G410" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>1.52588582038879</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G416" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G420" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G421" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G425" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G427" t="n">
-        <v>1.31822097301483</v>
+        <v>1.31822085380554</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G428" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G429" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G430" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G433" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G435" t="n">
-        <v>1.31822097301483</v>
+        <v>1.31822085380554</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G438" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G442" t="n">
-        <v>1.24598968029022</v>
+        <v>1.24598956108093</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G449" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>1.52588582038879</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G453" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>1.31822097301483</v>
+        <v>1.31822085380554</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G467" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G469" t="n">
-        <v>1.6793771982193</v>
+        <v>1.67937731742859</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>1.52588582038879</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G477" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G478" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>1.52588582038879</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G480" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G482" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G483" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G492" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G494" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G495" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G501" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G502" t="n">
-        <v>1.63423264026642</v>
+        <v>1.63423275947571</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G503" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G504" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G509" t="n">
-        <v>1.52588582038879</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G515" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G520" t="n">
-        <v>1.61617493629456</v>
+        <v>1.61617481708527</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G525" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G534" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G535" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G536" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G537" t="n">
-        <v>1.29113411903381</v>
+        <v>1.29113399982452</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G539" t="n">
-        <v>1.2550185918808</v>
+        <v>1.25501847267151</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G542" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G543" t="n">
-        <v>1.29113411903381</v>
+        <v>1.29113399982452</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G544" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G545" t="n">
-        <v>1.2550185918808</v>
+        <v>1.25501847267151</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G549" t="n">
-        <v>1.19181609153748</v>
+        <v>1.19181621074677</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G550" t="n">
-        <v>1.19181609153748</v>
+        <v>1.19181621074677</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G554" t="n">
-        <v>1.08346927165985</v>
+        <v>1.08346915245056</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G565" t="n">
-        <v>0.939006686210632</v>
+        <v>0.939006567001343</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G566" t="n">
-        <v>0.83968859910965</v>
+        <v>0.839688658714294</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>0.884833216667175</v>
+        <v>0.884833157062531</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G573" t="n">
-        <v>0.866775333881378</v>
+        <v>0.866775274276733</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G575" t="n">
-        <v>0.884833216667175</v>
+        <v>0.884833157062531</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G578" t="n">
-        <v>0.975122392177582</v>
+        <v>0.975122332572937</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G580" t="n">
-        <v>1.00220906734467</v>
+        <v>1.00220894813538</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G589" t="n">
-        <v>1.00220906734467</v>
+        <v>1.00220894813538</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G592" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>0.939006686210632</v>
+        <v>0.939006567001343</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G599" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G603" t="n">
-        <v>0.939006686210632</v>
+        <v>0.939006567001343</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G604" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G605" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G606" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G609" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G611" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G612" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G616" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G620" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G622" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>1</v>
       </c>
       <c r="G623" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G625" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G628" t="n">
-        <v>0.988665640354156</v>
+        <v>0.988665699958801</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G629" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>0.997694611549377</v>
+        <v>0.997694551944733</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>0.97963684797287</v>
+        <v>0.97963672876358</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G642" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G643" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G645" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>0.939006686210632</v>
+        <v>0.939006567001343</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>0.939006686210632</v>
+        <v>0.939006567001343</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G648" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G651" t="n">
-        <v>0.975122392177582</v>
+        <v>0.975122332572937</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G655" t="n">
-        <v>1.00220906734467</v>
+        <v>1.00220894813538</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>0.97963684797287</v>
+        <v>0.97963672876358</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G662" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.988665640354156</v>
+        <v>0.988665699958801</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G674" t="n">
-        <v>0.988665640354156</v>
+        <v>0.988665699958801</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G677" t="n">
-        <v>0.975122392177582</v>
+        <v>0.975122332572937</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G679" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>0.939006686210632</v>
+        <v>0.939006567001343</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G684" t="n">
-        <v>0.907405495643616</v>
+        <v>0.907405436038971</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G688" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G692" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G693" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G694" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G697" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>1</v>
       </c>
       <c r="G700" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>1</v>
       </c>
       <c r="G701" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G706" t="n">
-        <v>0.84330016374588</v>
+        <v>0.843300223350525</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G707" t="n">
-        <v>0.852329075336456</v>
+        <v>0.852329134941101</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G712" t="n">
-        <v>0.787320911884308</v>
+        <v>0.787320971488953</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G714" t="n">
-        <v>0.776486277580261</v>
+        <v>0.776486337184906</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G715" t="n">
-        <v>0.80718457698822</v>
+        <v>0.807184517383575</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G724" t="n">
-        <v>0.749399542808533</v>
+        <v>0.749399483203888</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G725" t="n">
-        <v>0.749399542808533</v>
+        <v>0.749399483203888</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G728" t="n">
-        <v>0.622994840145111</v>
+        <v>0.622994780540466</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G730" t="n">
-        <v>0.662722051143646</v>
+        <v>0.662721991539001</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G734" t="n">
-        <v>0.653693079948425</v>
+        <v>0.65369313955307</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G741" t="n">
-        <v>0.657304644584656</v>
+        <v>0.657304584980011</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G743" t="n">
-        <v>0.662722051143646</v>
+        <v>0.662721991539001</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G749" t="n">
-        <v>0.720506966114044</v>
+        <v>0.720507025718689</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G760" t="n">
-        <v>0.659110486507416</v>
+        <v>0.659110426902771</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G762" t="n">
-        <v>0.700643420219421</v>
+        <v>0.700643479824066</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G766" t="n">
-        <v>0.80718457698822</v>
+        <v>0.807184517383575</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G768" t="n">
-        <v>0.798155665397644</v>
+        <v>0.798155605792999</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G769" t="n">
-        <v>0.787320911884308</v>
+        <v>0.787320971488953</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G772" t="n">
-        <v>0.798155665397644</v>
+        <v>0.798155605792999</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G773" t="n">
-        <v>0.776486277580261</v>
+        <v>0.776486337184906</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G775" t="n">
-        <v>0.776486277580261</v>
+        <v>0.776486337184906</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G776" t="n">
-        <v>0.801767230033875</v>
+        <v>0.80176717042923</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G777" t="n">
-        <v>0.787320911884308</v>
+        <v>0.787320971488953</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G782" t="n">
-        <v>0.801767230033875</v>
+        <v>0.80176717042923</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G783" t="n">
-        <v>0.794544100761414</v>
+        <v>0.794544041156769</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G788" t="n">
-        <v>0.774680495262146</v>
+        <v>0.774680435657501</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G791" t="n">
-        <v>0.754816949367523</v>
+        <v>0.754816889762878</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>0.7692631483078</v>
+        <v>0.769263088703156</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G796" t="n">
-        <v>0.789126813411713</v>
+        <v>0.789126753807068</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G798" t="n">
-        <v>0.798155665397644</v>
+        <v>0.798155605792999</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G800" t="n">
-        <v>0.823436558246613</v>
+        <v>0.823436617851257</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G802" t="n">
-        <v>0.827048182487488</v>
+        <v>0.827048122882843</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G803" t="n">
-        <v>0.848717510700226</v>
+        <v>0.848717570304871</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G804" t="n">
-        <v>0.857746422290802</v>
+        <v>0.857746481895447</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G805" t="n">
-        <v>0.859552204608917</v>
+        <v>0.859552264213562</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G808" t="n">
-        <v>0.890250563621521</v>
+        <v>0.890250504016876</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G810" t="n">
-        <v>0.854134857654572</v>
+        <v>0.854134917259216</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G811" t="n">
-        <v>0.857746422290802</v>
+        <v>0.857746481895447</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G812" t="n">
-        <v>0.873998522758484</v>
+        <v>0.873998463153839</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G814" t="n">
-        <v>0.848717510700226</v>
+        <v>0.848717570304871</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G815" t="n">
-        <v>0.859552204608917</v>
+        <v>0.859552264213562</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G816" t="n">
-        <v>0.848717510700226</v>
+        <v>0.848717570304871</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1</v>
       </c>
       <c r="G817" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G820" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G822" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G827" t="n">
-        <v>0.88302743434906</v>
+        <v>0.883027374744415</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G828" t="n">
-        <v>0.872192740440369</v>
+        <v>0.872192680835724</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G829" t="n">
-        <v>0.879415810108185</v>
+        <v>0.87941575050354</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G830" t="n">
-        <v>0.88302743434906</v>
+        <v>0.883027374744415</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G833" t="n">
-        <v>0.88302743434906</v>
+        <v>0.883027374744415</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1</v>
       </c>
       <c r="G834" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G836" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G838" t="n">
-        <v>0.907405495643616</v>
+        <v>0.907405436038971</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G840" t="n">
-        <v>0.907405495643616</v>
+        <v>0.907405436038971</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G841" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G842" t="n">
-        <v>0.890250563621521</v>
+        <v>0.890250504016876</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G846" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G848" t="n">
-        <v>0.97963684797287</v>
+        <v>0.97963672876358</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G856" t="n">
-        <v>1.13764262199402</v>
+        <v>1.13764274120331</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G858" t="n">
-        <v>1.11507034301758</v>
+        <v>1.11507046222687</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G859" t="n">
-        <v>1.08798360824585</v>
+        <v>1.08798372745514</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G860" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G865" t="n">
-        <v>1.09701263904572</v>
+        <v>1.09701251983643</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G866" t="n">
-        <v>1.07895481586456</v>
+        <v>1.07895469665527</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G867" t="n">
-        <v>1.08346927165985</v>
+        <v>1.08346915245056</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G873" t="n">
-        <v>1.16472923755646</v>
+        <v>1.16472935676575</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G874" t="n">
-        <v>1.15570044517517</v>
+        <v>1.15570056438446</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>1.16472923755646</v>
+        <v>1.16472935676575</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G877" t="n">
-        <v>1.19181609153748</v>
+        <v>1.19181621074677</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>1.20535945892334</v>
+        <v>1.20535957813263</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G880" t="n">
-        <v>1.31370639801025</v>
+        <v>1.31370651721954</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G881" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G882" t="n">
-        <v>1.24598968029022</v>
+        <v>1.24598956108093</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G883" t="n">
-        <v>1.25050413608551</v>
+        <v>1.25050401687622</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G884" t="n">
-        <v>1.2550185918808</v>
+        <v>1.25501847267151</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G885" t="n">
-        <v>1.22341740131378</v>
+        <v>1.22341728210449</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G886" t="n">
-        <v>1.20535945892334</v>
+        <v>1.20535957813263</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G887" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244631290436</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G890" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244631290436</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G893" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244631290436</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G894" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244631290436</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G895" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244631290436</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G899" t="n">
-        <v>1.22341740131378</v>
+        <v>1.22341728210449</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G901" t="n">
-        <v>1.19181609153748</v>
+        <v>1.19181621074677</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G902" t="n">
-        <v>1.19633054733276</v>
+        <v>1.19633066654205</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G904" t="n">
-        <v>1.22341740131378</v>
+        <v>1.22341728210449</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G907" t="n">
-        <v>1.19181609153748</v>
+        <v>1.19181621074677</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G910" t="n">
-        <v>1.08798360824585</v>
+        <v>1.08798372745514</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G915" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G916" t="n">
-        <v>1.07895481586456</v>
+        <v>1.07895469665527</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G917" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G918" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>1.16472923755646</v>
+        <v>1.16472935676575</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G922" t="n">
-        <v>1.16472923755646</v>
+        <v>1.16472935676575</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G924" t="n">
-        <v>1.15118598937988</v>
+        <v>1.15118610858917</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G928" t="n">
-        <v>1.22341740131378</v>
+        <v>1.22341728210449</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G929" t="n">
-        <v>1.22341740131378</v>
+        <v>1.22341728210449</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G930" t="n">
-        <v>1.24598968029022</v>
+        <v>1.24598956108093</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G931" t="n">
-        <v>1.2550185918808</v>
+        <v>1.25501847267151</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G932" t="n">
-        <v>1.2550185918808</v>
+        <v>1.25501847267151</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G933" t="n">
-        <v>1.31822097301483</v>
+        <v>1.31822085380554</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G935" t="n">
-        <v>1.6793771982193</v>
+        <v>1.67937731742859</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.875</v>
       </c>
       <c r="G936" t="n">
-        <v>1.69292068481445</v>
+        <v>1.69292056560516</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G937" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G941" t="n">
-        <v>1.64777600765228</v>
+        <v>1.64777612686157</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G946" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G949" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G952" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G960" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G965" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G966" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G968" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G972" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G973" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G974" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G978" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G982" t="n">
-        <v>1.52588582038879</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G983" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G984" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G987" t="n">
-        <v>1.52588582038879</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G989" t="n">
-        <v>1.52588582038879</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G991" t="n">
-        <v>1.54845821857452</v>
+        <v>1.54845809936523</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G993" t="n">
-        <v>1.54845821857452</v>
+        <v>1.54845809936523</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G994" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G996" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G998" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G999" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.32273542881012</v>
+        <v>1.32273530960083</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.26856184005737</v>
+        <v>1.26856195926666</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.30467760562897</v>
+        <v>1.30467748641968</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.33176422119141</v>
+        <v>1.3317643404007</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.29113411903381</v>
+        <v>1.29113399982452</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244631290436</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.18730163574219</v>
+        <v>1.18730175495148</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.38593757152557</v>
+        <v>1.38593769073486</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.54845821857452</v>
+        <v>1.54845809936523</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.38593757152557</v>
+        <v>1.38593769073486</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.38593757152557</v>
+        <v>1.38593769073486</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1114" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1193" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.52588582038879</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.52588582038879</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.38593757152557</v>
+        <v>1.38593769073486</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.64777600765228</v>
+        <v>1.64777612686157</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.61617493629456</v>
+        <v>1.61617481708527</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.63423264026642</v>
+        <v>1.63423275947571</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.6026314496994</v>
+        <v>1.60263156890869</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.61617493629456</v>
+        <v>1.61617481708527</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.63423264026642</v>
+        <v>1.63423275947571</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1409" t="n">
-        <v>1.54845821857452</v>
+        <v>1.54845809936523</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.52588582038879</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.6026314496994</v>
+        <v>1.60263156890869</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.54845821857452</v>
+        <v>1.54845809936523</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1463" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.54845821857452</v>
+        <v>1.54845809936523</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.52588582038879</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.6026314496994</v>
+        <v>1.60263156890869</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1494" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1503" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.52588582038879</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>1.52588582038879</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.52588582038879</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.71097838878632</v>
+        <v>1.71097850799561</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.69743502140045</v>
+        <v>1.69743514060974</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.63423264026642</v>
+        <v>1.63423275947571</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1539" t="n">
-        <v>1.68389165401459</v>
+        <v>1.68389177322388</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1541" t="n">
-        <v>1.64777600765228</v>
+        <v>1.64777612686157</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.67486274242401</v>
+        <v>1.6748628616333</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.63423264026642</v>
+        <v>1.63423275947571</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.67486274242401</v>
+        <v>1.6748628616333</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.67486274242401</v>
+        <v>1.6748628616333</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1554" t="n">
-        <v>1.68389165401459</v>
+        <v>1.68389177322388</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1555" t="n">
-        <v>1.68840622901917</v>
+        <v>1.68840610980988</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1556" t="n">
-        <v>1.6793771982193</v>
+        <v>1.67937731742859</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.68840622901917</v>
+        <v>1.68840610980988</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1558" t="n">
-        <v>1.69743502140045</v>
+        <v>1.69743514060974</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1559" t="n">
-        <v>1.69743502140045</v>
+        <v>1.69743514060974</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.68840622901917</v>
+        <v>1.68840610980988</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1562" t="n">
-        <v>1.68840622901917</v>
+        <v>1.68840610980988</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>1.875</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.69292068481445</v>
+        <v>1.69292056560516</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.67486274242401</v>
+        <v>1.6748628616333</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.64777600765228</v>
+        <v>1.64777612686157</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.63423264026642</v>
+        <v>1.63423275947571</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1582" t="n">
-        <v>1.61617493629456</v>
+        <v>1.61617481708527</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.63423264026642</v>
+        <v>1.63423275947571</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.61617493629456</v>
+        <v>1.61617481708527</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.61617493629456</v>
+        <v>1.61617481708527</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.88704204559326</v>
+        <v>1.88704216480255</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1611" t="n">
-        <v>1.99538922309875</v>
+        <v>1.99538910388947</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.95927369594574</v>
+        <v>1.95927345752716</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1615" t="n">
-        <v>1.95927369594574</v>
+        <v>1.95927345752716</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.01344704627991</v>
+        <v>2.01344680786133</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.01344704627991</v>
+        <v>2.01344680786133</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.00441813468933</v>
+        <v>2.00441789627075</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1623" t="n">
-        <v>2.00441813468933</v>
+        <v>2.00441789627075</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.01344704627991</v>
+        <v>2.01344680786133</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1625" t="n">
-        <v>2.00441813468933</v>
+        <v>2.00441789627075</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.51727485656738</v>
+        <v>2.5172746181488</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.59213805198669</v>
+        <v>2.59213781356812</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.13489603996277</v>
+        <v>3.13489580154419</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.87287473678589</v>
+        <v>2.87287497520447</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.73250651359558</v>
+        <v>2.732506275177</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.81672739982605</v>
+        <v>2.81672763824463</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.73250651359558</v>
+        <v>2.732506275177</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.91030621528625</v>
+        <v>2.91030645370483</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1697" t="n">
-        <v>2.91030621528625</v>
+        <v>2.91030645370483</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.87287473678589</v>
+        <v>2.87287497520447</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.92902231216431</v>
+        <v>2.92902255058289</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1709" t="n">
-        <v>2.91030621528625</v>
+        <v>2.91030645370483</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.91030621528625</v>
+        <v>2.91030645370483</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.87287473678589</v>
+        <v>2.87287497520447</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.91030621528625</v>
+        <v>2.91030645370483</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.92902231216431</v>
+        <v>2.92902255058289</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.92902231216431</v>
+        <v>2.92902255058289</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1732" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1738" t="n">
-        <v>2.35819029808044</v>
+        <v>2.35819053649902</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.35819029808044</v>
+        <v>2.35819053649902</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.35819029808044</v>
+        <v>2.35819053649902</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.36754822731018</v>
+        <v>2.36754846572876</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.4704852104187</v>
+        <v>2.47048544883728</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1759" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.64828538894653</v>
+        <v>2.64828515052795</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.65764307975769</v>
+        <v>2.65764331817627</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.73250651359558</v>
+        <v>2.732506275177</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.73250651359558</v>
+        <v>2.732506275177</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.73250651359558</v>
+        <v>2.732506275177</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.69507503509521</v>
+        <v>2.69507479667664</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1787" t="n">
-        <v>2.69507503509521</v>
+        <v>2.69507479667664</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1788" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.64828538894653</v>
+        <v>2.64828515052795</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.64828538894653</v>
+        <v>2.64828515052795</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.69507503509521</v>
+        <v>2.69507479667664</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.65764307975769</v>
+        <v>2.65764331817627</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.19104361534119</v>
+        <v>3.19104337692261</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.29398036003113</v>
+        <v>3.29398012161255</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.29398036003113</v>
+        <v>3.29398012161255</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.3126962184906</v>
+        <v>3.31269598007202</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.3126962184906</v>
+        <v>3.31269598007202</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.54664349555969</v>
+        <v>3.54664373397827</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1870" t="n">
-        <v>3.65893864631653</v>
+        <v>3.65893840789795</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1877" t="n">
-        <v>3.69637012481689</v>
+        <v>3.69636988639832</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1879" t="n">
-        <v>3.75251770019531</v>
+        <v>3.75251746177673</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1881" t="n">
-        <v>3.75251770019531</v>
+        <v>3.75251746177673</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -58664,6 +58664,32 @@
         <v>4.44999980926514</v>
       </c>
       <c r="H2242" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2243" t="n">
+        <v>6900</v>
+      </c>
+      <c r="C2243" t="n">
+        <v>4.40999984741211</v>
+      </c>
+      <c r="D2243" t="n">
+        <v>4.34999990463257</v>
+      </c>
+      <c r="E2243" t="n">
+        <v>4.40999984741211</v>
+      </c>
+      <c r="F2243" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="G2243" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="H2243" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -447,7 +447,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G3" t="n">
-        <v>3.66393160820007</v>
+        <v>3.66393184661865</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G4" t="n">
-        <v>3.63684487342834</v>
+        <v>3.63684463500977</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G11" t="n">
-        <v>3.63684487342834</v>
+        <v>3.63684463500977</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G14" t="n">
-        <v>3.64406776428223</v>
+        <v>3.64406800270081</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G30" t="n">
-        <v>3.57544851303101</v>
+        <v>3.57544827461243</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>3.57544851303101</v>
+        <v>3.57544827461243</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.75</v>
       </c>
       <c r="G43" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.75</v>
       </c>
       <c r="G44" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>3.57544851303101</v>
+        <v>3.57544827461243</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G53" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G54" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G55" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G56" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G57" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G58" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G60" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G61" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G92" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.75</v>
       </c>
       <c r="G101" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.75</v>
       </c>
       <c r="G102" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.75</v>
       </c>
       <c r="G103" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.75</v>
       </c>
       <c r="G104" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>3.06982946395874</v>
+        <v>3.06982970237732</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>3.04274272918701</v>
+        <v>3.04274249076843</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>3.04274272918701</v>
+        <v>3.04274249076843</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G117" t="n">
-        <v>3.06982946395874</v>
+        <v>3.06982970237732</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>3.06982946395874</v>
+        <v>3.06982970237732</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G119" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G120" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>3.75</v>
       </c>
       <c r="G124" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.75</v>
       </c>
       <c r="G125" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G127" t="n">
-        <v>3.45807242393494</v>
+        <v>3.45807266235352</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G128" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G135" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G138" t="n">
-        <v>3.28652310371399</v>
+        <v>3.28652334213257</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G141" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G142" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G143" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G145" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G146" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G148" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G149" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G151" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G152" t="n">
-        <v>3.37681221961975</v>
+        <v>3.37681245803833</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G153" t="n">
-        <v>3.37681221961975</v>
+        <v>3.37681245803833</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G154" t="n">
-        <v>3.37681221961975</v>
+        <v>3.37681245803833</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G155" t="n">
-        <v>3.37681221961975</v>
+        <v>3.37681245803833</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G156" t="n">
-        <v>3.37681221961975</v>
+        <v>3.37681245803833</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G166" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G167" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G168" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G169" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G171" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G172" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G173" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G174" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G175" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G177" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.75</v>
       </c>
       <c r="G178" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G193" t="n">
-        <v>3.1240029335022</v>
+        <v>3.12400269508362</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G204" t="n">
-        <v>3.06982946395874</v>
+        <v>3.06982970237732</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>3.06982946395874</v>
+        <v>3.06982970237732</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>3.06982946395874</v>
+        <v>3.06982970237732</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>3.06982946395874</v>
+        <v>3.06982970237732</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G208" t="n">
-        <v>3.05177140235901</v>
+        <v>3.05177164077759</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G210" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G211" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G212" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G213" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G236" t="n">
-        <v>2.51003694534302</v>
+        <v>2.51003670692444</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G237" t="n">
-        <v>2.51003694534302</v>
+        <v>2.51003670692444</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>2.46489262580872</v>
+        <v>2.46489238739014</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>2.46489262580872</v>
+        <v>2.46489238739014</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>2.46489262580872</v>
+        <v>2.46489238739014</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G241" t="n">
-        <v>2.46489262580872</v>
+        <v>2.46489238739014</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>2.46489262580872</v>
+        <v>2.46489238739014</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>2.50100803375244</v>
+        <v>2.50100827217102</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G245" t="n">
-        <v>2.50100803375244</v>
+        <v>2.50100827217102</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G246" t="n">
-        <v>2.50100803375244</v>
+        <v>2.50100827217102</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G247" t="n">
-        <v>2.50100803375244</v>
+        <v>2.50100827217102</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G248" t="n">
-        <v>2.50100803375244</v>
+        <v>2.50100827217102</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G249" t="n">
-        <v>2.51003694534302</v>
+        <v>2.51003670692444</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G263" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G264" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G265" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G275" t="n">
-        <v>2.30237221717834</v>
+        <v>2.30237197875977</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>2.12179398536682</v>
+        <v>2.12179374694824</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G293" t="n">
-        <v>2.06762051582336</v>
+        <v>2.06762027740479</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G298" t="n">
-        <v>1.93218672275543</v>
+        <v>1.93218684196472</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G300" t="n">
-        <v>1.87801313400269</v>
+        <v>1.87801325321198</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>1.9773313999176</v>
+        <v>1.97733116149902</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G303" t="n">
-        <v>1.9773313999176</v>
+        <v>1.97733116149902</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G306" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G317" t="n">
-        <v>1.89607095718384</v>
+        <v>1.89607083797455</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G328" t="n">
-        <v>1.91412889957428</v>
+        <v>1.91412878036499</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G329" t="n">
-        <v>1.89607095718384</v>
+        <v>1.89607083797455</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G331" t="n">
-        <v>1.89607095718384</v>
+        <v>1.89607083797455</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G332" t="n">
-        <v>1.89607095718384</v>
+        <v>1.89607083797455</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G338" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G340" t="n">
-        <v>2.00441789627075</v>
+        <v>2.00441813468933</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G341" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G342" t="n">
-        <v>2.00441789627075</v>
+        <v>2.00441813468933</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G345" t="n">
-        <v>1.93218672275543</v>
+        <v>1.93218684196472</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>1.89607095718384</v>
+        <v>1.89607083797455</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G349" t="n">
-        <v>1.89607095718384</v>
+        <v>1.89607083797455</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G350" t="n">
-        <v>1.87801313400269</v>
+        <v>1.87801325321198</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G353" t="n">
-        <v>1.89607095718384</v>
+        <v>1.89607083797455</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G364" t="n">
-        <v>1.73355054855347</v>
+        <v>1.73355066776276</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G370" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G371" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>1.7877242565155</v>
+        <v>1.78772413730621</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G386" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G387" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G392" t="n">
-        <v>1.69743514060974</v>
+        <v>1.69743502140045</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G393" t="n">
-        <v>1.69743514060974</v>
+        <v>1.69743502140045</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G397" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G402" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G421" t="n">
-        <v>1.34530770778656</v>
+        <v>1.34530758857727</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>1.34530770778656</v>
+        <v>1.34530758857727</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G449" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G470" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G474" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G477" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G478" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G485" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G487" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G491" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G493" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G496" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G502" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G509" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G510" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G513" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G515" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G520" t="n">
-        <v>1.61617481708527</v>
+        <v>1.61617493629456</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G524" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G527" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G528" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G529" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G530" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G531" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G532" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G534" t="n">
-        <v>1.34530770778656</v>
+        <v>1.34530758857727</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G535" t="n">
-        <v>1.34530770778656</v>
+        <v>1.34530758857727</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G537" t="n">
-        <v>1.29113399982452</v>
+        <v>1.29113411903381</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G539" t="n">
-        <v>1.25501847267151</v>
+        <v>1.25501835346222</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G543" t="n">
-        <v>1.29113399982452</v>
+        <v>1.29113411903381</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G545" t="n">
-        <v>1.25501847267151</v>
+        <v>1.25501835346222</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G547" t="n">
-        <v>1.20084500312805</v>
+        <v>1.20084512233734</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G549" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G550" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G554" t="n">
-        <v>1.08346915245056</v>
+        <v>1.08346927165985</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G556" t="n">
-        <v>1.02026689052582</v>
+        <v>1.02026677131653</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G557" t="n">
-        <v>1.02026689052582</v>
+        <v>1.02026677131653</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G558" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G563" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G565" t="n">
-        <v>0.939006567001343</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G573" t="n">
-        <v>0.866775274276733</v>
+        <v>0.866775333881378</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G580" t="n">
-        <v>1.00220894813538</v>
+        <v>1.00220906734467</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>1.03381025791168</v>
+        <v>1.03381013870239</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G584" t="n">
-        <v>1.03381025791168</v>
+        <v>1.03381013870239</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G587" t="n">
-        <v>1.03381025791168</v>
+        <v>1.03381013870239</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G589" t="n">
-        <v>1.00220894813538</v>
+        <v>1.00220906734467</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G591" t="n">
-        <v>0.952549934387207</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G592" t="n">
-        <v>0.966093361377716</v>
+        <v>0.966093420982361</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>0.939006567001343</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G598" t="n">
-        <v>0.952549934387207</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G599" t="n">
-        <v>0.966093361377716</v>
+        <v>0.966093420982361</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G601" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G603" t="n">
-        <v>0.939006567001343</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G605" t="n">
-        <v>0.966093361377716</v>
+        <v>0.966093420982361</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G619" t="n">
-        <v>0.893862128257751</v>
+        <v>0.893862068653107</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G627" t="n">
-        <v>1.04283905029297</v>
+        <v>1.04283916950226</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G628" t="n">
-        <v>0.988665699958801</v>
+        <v>0.988665580749512</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G629" t="n">
-        <v>0.966093361377716</v>
+        <v>0.966093420982361</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G640" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G641" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G643" t="n">
-        <v>0.966093361377716</v>
+        <v>0.966093420982361</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>0.939006567001343</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>0.939006567001343</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G649" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G655" t="n">
-        <v>1.00220894813538</v>
+        <v>1.00220906734467</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G662" t="n">
-        <v>0.966093361377716</v>
+        <v>0.966093420982361</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G663" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G664" t="n">
-        <v>0.952549934387207</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G668" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G671" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.988665699958801</v>
+        <v>0.988665580749512</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G674" t="n">
-        <v>0.988665699958801</v>
+        <v>0.988665580749512</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G678" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G680" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G681" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G682" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>0.939006567001343</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G687" t="n">
-        <v>0.952549934387207</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G689" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G690" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G691" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G696" t="n">
-        <v>0.952549934387207</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G699" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>0.911919891834259</v>
+        <v>0.911919951438904</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G712" t="n">
-        <v>0.787320971488953</v>
+        <v>0.787320911884308</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G714" t="n">
-        <v>0.776486337184906</v>
+        <v>0.776486277580261</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G718" t="n">
-        <v>0.722312808036804</v>
+        <v>0.722312867641449</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G731" t="n">
-        <v>0.666333556175232</v>
+        <v>0.666333496570587</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G733" t="n">
-        <v>0.65188729763031</v>
+        <v>0.651887357234955</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G734" t="n">
-        <v>0.65369313955307</v>
+        <v>0.653693079948425</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G736" t="n">
-        <v>0.678974032402039</v>
+        <v>0.678973972797394</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G740" t="n">
-        <v>0.644664168357849</v>
+        <v>0.644664227962494</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G744" t="n">
-        <v>0.675362467765808</v>
+        <v>0.675362527370453</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G746" t="n">
-        <v>0.673556685447693</v>
+        <v>0.673556625843048</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G752" t="n">
-        <v>0.675362467765808</v>
+        <v>0.675362527370453</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G754" t="n">
-        <v>0.675362467765808</v>
+        <v>0.675362527370453</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G759" t="n">
-        <v>0.673556685447693</v>
+        <v>0.673556625843048</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G761" t="n">
-        <v>0.673556685447693</v>
+        <v>0.673556625843048</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G768" t="n">
-        <v>0.798155605792999</v>
+        <v>0.798155665397644</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G769" t="n">
-        <v>0.787320971488953</v>
+        <v>0.787320911884308</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G770" t="n">
-        <v>0.76565158367157</v>
+        <v>0.765651524066925</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G771" t="n">
-        <v>0.76565158367157</v>
+        <v>0.765651524066925</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G772" t="n">
-        <v>0.798155605792999</v>
+        <v>0.798155665397644</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G773" t="n">
-        <v>0.776486337184906</v>
+        <v>0.776486277580261</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G774" t="n">
-        <v>0.767457365989685</v>
+        <v>0.76745742559433</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G775" t="n">
-        <v>0.776486337184906</v>
+        <v>0.776486277580261</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G777" t="n">
-        <v>0.787320971488953</v>
+        <v>0.787320911884308</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G788" t="n">
-        <v>0.774680435657501</v>
+        <v>0.774680495262146</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G789" t="n">
-        <v>0.767457365989685</v>
+        <v>0.76745742559433</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G794" t="n">
-        <v>0.767457365989685</v>
+        <v>0.76745742559433</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>0.769263088703156</v>
+        <v>0.7692631483078</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G796" t="n">
-        <v>0.789126753807068</v>
+        <v>0.789126813411713</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G798" t="n">
-        <v>0.798155605792999</v>
+        <v>0.798155665397644</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G799" t="n">
-        <v>0.819824993610382</v>
+        <v>0.819825053215027</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G802" t="n">
-        <v>0.827048122882843</v>
+        <v>0.827048182487488</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G803" t="n">
-        <v>0.848717570304871</v>
+        <v>0.848717510700226</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G805" t="n">
-        <v>0.859552264213562</v>
+        <v>0.859552323818207</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G806" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>0.893862128257751</v>
+        <v>0.893862068653107</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G808" t="n">
-        <v>0.890250504016876</v>
+        <v>0.890250563621521</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G809" t="n">
-        <v>0.886638998985291</v>
+        <v>0.886638939380646</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G813" t="n">
-        <v>0.886638998985291</v>
+        <v>0.886638939380646</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G814" t="n">
-        <v>0.848717570304871</v>
+        <v>0.848717510700226</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G815" t="n">
-        <v>0.859552264213562</v>
+        <v>0.859552323818207</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G816" t="n">
-        <v>0.848717570304871</v>
+        <v>0.848717510700226</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G821" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G824" t="n">
-        <v>0.911919891834259</v>
+        <v>0.911919951438904</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G832" t="n">
-        <v>0.893862128257751</v>
+        <v>0.893862068653107</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G839" t="n">
-        <v>0.911919891834259</v>
+        <v>0.911919951438904</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G842" t="n">
-        <v>0.890250504016876</v>
+        <v>0.890250563621521</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G846" t="n">
-        <v>0.966093361377716</v>
+        <v>0.966093420982361</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G857" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G863" t="n">
-        <v>1.06089699268341</v>
+        <v>1.06089687347412</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G867" t="n">
-        <v>1.08346915245056</v>
+        <v>1.08346927165985</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G871" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G877" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G883" t="n">
-        <v>1.25050401687622</v>
+        <v>1.25050413608551</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G884" t="n">
-        <v>1.25501847267151</v>
+        <v>1.25501835346222</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G887" t="n">
-        <v>1.23244631290436</v>
+        <v>1.23244619369507</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G890" t="n">
-        <v>1.23244631290436</v>
+        <v>1.23244619369507</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G893" t="n">
-        <v>1.23244631290436</v>
+        <v>1.23244619369507</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G894" t="n">
-        <v>1.23244631290436</v>
+        <v>1.23244619369507</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G895" t="n">
-        <v>1.23244631290436</v>
+        <v>1.23244619369507</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G901" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G903" t="n">
-        <v>1.20084500312805</v>
+        <v>1.20084512233734</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G907" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G911" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G912" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G920" t="n">
-        <v>1.16021478176117</v>
+        <v>1.16021490097046</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G921" t="n">
-        <v>1.16021478176117</v>
+        <v>1.16021490097046</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G924" t="n">
-        <v>1.15118610858917</v>
+        <v>1.15118598937988</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G931" t="n">
-        <v>1.25501847267151</v>
+        <v>1.25501835346222</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G932" t="n">
-        <v>1.25501847267151</v>
+        <v>1.25501835346222</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.875</v>
       </c>
       <c r="G936" t="n">
-        <v>1.69292056560516</v>
+        <v>1.69292068481445</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G937" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G938" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G940" t="n">
-        <v>1.52137136459351</v>
+        <v>1.52137124538422</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G941" t="n">
-        <v>1.64777612686157</v>
+        <v>1.64777624607086</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G944" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G946" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G957" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G958" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G959" t="n">
-        <v>1.53942918777466</v>
+        <v>1.53942930698395</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G969" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G976" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G982" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G983" t="n">
-        <v>1.47622692584991</v>
+        <v>1.47622680664062</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G985" t="n">
-        <v>1.52137136459351</v>
+        <v>1.52137124538422</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G987" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G988" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G989" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G990" t="n">
-        <v>1.52137136459351</v>
+        <v>1.52137124538422</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G992" t="n">
-        <v>1.53942918777466</v>
+        <v>1.53942930698395</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G994" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G996" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G997" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G999" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.43108224868774</v>
+        <v>1.43108212947845</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.40399539470673</v>
+        <v>1.40399551391602</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.29113399982452</v>
+        <v>1.29113411903381</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.23244631290436</v>
+        <v>1.23244619369507</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.38593769073486</v>
+        <v>1.38593757152557</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.53942918777466</v>
+        <v>1.53942930698395</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.47622692584991</v>
+        <v>1.47622680664062</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.47622692584991</v>
+        <v>1.47622680664062</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.38593769073486</v>
+        <v>1.38593757152557</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.38593769073486</v>
+        <v>1.38593757152557</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1210" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.47622692584991</v>
+        <v>1.47622680664062</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1224" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1230" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1231" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.52137136459351</v>
+        <v>1.52137124538422</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.47622692584991</v>
+        <v>1.47622680664062</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.47622692584991</v>
+        <v>1.47622680664062</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.43108224868774</v>
+        <v>1.43108212947845</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.40399539470673</v>
+        <v>1.40399551391602</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.43108224868774</v>
+        <v>1.43108212947845</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.34530770778656</v>
+        <v>1.34530758857727</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.38593769073486</v>
+        <v>1.38593757152557</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.40399539470673</v>
+        <v>1.40399551391602</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.40399539470673</v>
+        <v>1.40399551391602</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.40399539470673</v>
+        <v>1.40399551391602</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.40399539470673</v>
+        <v>1.40399551391602</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.40399539470673</v>
+        <v>1.40399551391602</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.64777612686157</v>
+        <v>1.64777624607086</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.61617481708527</v>
+        <v>1.61617493629456</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.61617481708527</v>
+        <v>1.61617493629456</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1413" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.57554471492767</v>
+        <v>1.57554483413696</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1428" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.57554471492767</v>
+        <v>1.57554483413696</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1446" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1472" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1475" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1482" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1485" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1486" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1489" t="n">
-        <v>1.52137136459351</v>
+        <v>1.52137124538422</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1492" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1493" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1494" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1495" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1502" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1503" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1504" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1507" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1512" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.57554471492767</v>
+        <v>1.57554483413696</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1518" t="n">
-        <v>1.57554471492767</v>
+        <v>1.57554483413696</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1520" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G1523" t="n">
-        <v>1.53942918777466</v>
+        <v>1.53942930698395</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.65680503845215</v>
+        <v>1.65680491924286</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.69743514060974</v>
+        <v>1.69743502140045</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1538" t="n">
-        <v>1.65680503845215</v>
+        <v>1.65680491924286</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1541" t="n">
-        <v>1.64777612686157</v>
+        <v>1.64777624607086</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1555" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1558" t="n">
-        <v>1.69743514060974</v>
+        <v>1.69743502140045</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1559" t="n">
-        <v>1.69743514060974</v>
+        <v>1.69743502140045</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1562" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>1.875</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.69292056560516</v>
+        <v>1.69292068481445</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1566" t="n">
-        <v>1.65680503845215</v>
+        <v>1.65680491924286</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.64777612686157</v>
+        <v>1.64777624607086</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1582" t="n">
-        <v>1.61617481708527</v>
+        <v>1.61617493629456</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.61617481708527</v>
+        <v>1.61617493629456</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.61617481708527</v>
+        <v>1.61617493629456</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.89607095718384</v>
+        <v>1.89607083797455</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.12179398536682</v>
+        <v>2.12179374694824</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.12179398536682</v>
+        <v>2.12179374694824</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1607" t="n">
-        <v>2.06762051582336</v>
+        <v>2.06762027740479</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.06762051582336</v>
+        <v>2.06762027740479</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.01344680786133</v>
+        <v>2.01344704627991</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.01344680786133</v>
+        <v>2.01344704627991</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.00441789627075</v>
+        <v>2.00441813468933</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1623" t="n">
-        <v>2.00441789627075</v>
+        <v>2.00441813468933</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.01344680786133</v>
+        <v>2.01344704627991</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1625" t="n">
-        <v>2.00441789627075</v>
+        <v>2.00441813468933</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.10373592376709</v>
+        <v>2.10373616218567</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -58690,6 +58690,32 @@
         <v>4.40000009536743</v>
       </c>
       <c r="H2243" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2244" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C2244" t="n">
+        <v>4.3899998664856</v>
+      </c>
+      <c r="D2244" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="E2244" t="n">
+        <v>4.34999990463257</v>
+      </c>
+      <c r="F2244" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="G2244" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="H2244" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -65465,10 +65465,10 @@
         <v>4.32000017166138</v>
       </c>
       <c r="D2245" t="n">
-        <v>4.32000017166138</v>
+        <v>4.32999992370605</v>
       </c>
       <c r="E2245" t="n">
-        <v>4.25</v>
+        <v>4.23000001907349</v>
       </c>
       <c r="F2245" t="n">
         <v>4.32999992370605</v>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -456,7 +456,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G3" t="n">
-        <v>3.66393160820007</v>
+        <v>3.66393184661865</v>
       </c>
       <c r="H3" t="n">
         <v>35400</v>
@@ -775,7 +775,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G14" t="n">
-        <v>3.64406776428223</v>
+        <v>3.64406800270081</v>
       </c>
       <c r="H14" t="n">
         <v>10200</v>
@@ -862,7 +862,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5989236831665</v>
+        <v>3.59892344474792</v>
       </c>
       <c r="H17" t="n">
         <v>81900</v>
@@ -891,7 +891,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G18" t="n">
-        <v>3.6549026966095</v>
+        <v>3.65490245819092</v>
       </c>
       <c r="H18" t="n">
         <v>28200</v>
@@ -920,7 +920,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G19" t="n">
-        <v>3.65851426124573</v>
+        <v>3.65851449966431</v>
       </c>
       <c r="H19" t="n">
         <v>19500</v>
@@ -1007,7 +1007,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G22" t="n">
-        <v>3.62962174415588</v>
+        <v>3.62962198257446</v>
       </c>
       <c r="H22" t="n">
         <v>2700</v>
@@ -1094,7 +1094,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>3.56641936302185</v>
+        <v>3.56641960144043</v>
       </c>
       <c r="H25" t="n">
         <v>6600</v>
@@ -1123,7 +1123,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>3.62962174415588</v>
+        <v>3.62962198257446</v>
       </c>
       <c r="H26" t="n">
         <v>5100</v>
@@ -1239,7 +1239,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G30" t="n">
-        <v>3.57544851303101</v>
+        <v>3.57544827461243</v>
       </c>
       <c r="H30" t="n">
         <v>300</v>
@@ -1268,7 +1268,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>3.57544851303101</v>
+        <v>3.57544827461243</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G37" t="n">
-        <v>3.53030371665955</v>
+        <v>3.53030395507812</v>
       </c>
       <c r="H37" t="n">
         <v>10200</v>
@@ -1471,7 +1471,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>3.52127528190613</v>
+        <v>3.52127504348755</v>
       </c>
       <c r="H38" t="n">
         <v>3600</v>
@@ -1500,7 +1500,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G39" t="n">
-        <v>3.52127528190613</v>
+        <v>3.52127504348755</v>
       </c>
       <c r="H39" t="n">
         <v>600</v>
@@ -1529,7 +1529,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H40" t="n">
         <v>6300</v>
@@ -1558,7 +1558,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G41" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H42" t="n">
         <v>3900</v>
@@ -1616,7 +1616,7 @@
         <v>3.75</v>
       </c>
       <c r="G43" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H43" t="n">
         <v>300</v>
@@ -1645,7 +1645,7 @@
         <v>3.75</v>
       </c>
       <c r="G44" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H44" t="n">
         <v>300</v>
@@ -1790,7 +1790,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>3.57544851303101</v>
+        <v>3.57544827461243</v>
       </c>
       <c r="H49" t="n">
         <v>1800</v>
@@ -1848,7 +1848,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H51" t="n">
         <v>17400</v>
@@ -1906,7 +1906,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G53" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H53" t="n">
         <v>1500</v>
@@ -1935,7 +1935,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G54" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G55" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G56" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G57" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G58" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G60" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G61" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H62" t="n">
         <v>1200</v>
@@ -2196,7 +2196,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>3.33166790008545</v>
+        <v>3.33166766166687</v>
       </c>
       <c r="H63" t="n">
         <v>600</v>
@@ -2225,7 +2225,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G64" t="n">
-        <v>3.44001460075378</v>
+        <v>3.44001483917236</v>
       </c>
       <c r="H64" t="n">
         <v>900</v>
@@ -2254,7 +2254,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G65" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H65" t="n">
         <v>1500</v>
@@ -2283,7 +2283,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G66" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G67" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G68" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G69" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G70" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G71" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H85" t="n">
         <v>7500</v>
@@ -2863,7 +2863,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H86" t="n">
         <v>2400</v>
@@ -2892,7 +2892,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G87" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H87" t="n">
         <v>3300</v>
@@ -2921,7 +2921,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G88" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G89" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H90" t="n">
         <v>900</v>
@@ -3008,7 +3008,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G92" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H99" t="n">
         <v>3600</v>
@@ -3269,7 +3269,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H100" t="n">
         <v>300</v>
@@ -3298,7 +3298,7 @@
         <v>3.75</v>
       </c>
       <c r="G101" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H101" t="n">
         <v>2400</v>
@@ -3327,7 +3327,7 @@
         <v>3.75</v>
       </c>
       <c r="G102" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>3.75</v>
       </c>
       <c r="G103" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>3.75</v>
       </c>
       <c r="G104" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G107" t="n">
-        <v>3.22332072257996</v>
+        <v>3.22332096099854</v>
       </c>
       <c r="H107" t="n">
         <v>6300</v>
@@ -3559,7 +3559,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H110" t="n">
         <v>8100</v>
@@ -3588,7 +3588,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G111" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H111" t="n">
         <v>30300</v>
@@ -3704,7 +3704,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>3.04274272918701</v>
+        <v>3.04274249076843</v>
       </c>
       <c r="H115" t="n">
         <v>600</v>
@@ -3733,7 +3733,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>3.04274272918701</v>
+        <v>3.04274249076843</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G119" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H119" t="n">
         <v>30900</v>
@@ -3849,7 +3849,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G120" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H120" t="n">
         <v>2100</v>
@@ -3878,7 +3878,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G121" t="n">
-        <v>3.13303184509277</v>
+        <v>3.13303208351135</v>
       </c>
       <c r="H121" t="n">
         <v>30600</v>
@@ -3965,7 +3965,7 @@
         <v>3.75</v>
       </c>
       <c r="G124" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H124" t="n">
         <v>5700</v>
@@ -3994,7 +3994,7 @@
         <v>3.75</v>
       </c>
       <c r="G125" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H125" t="n">
         <v>11100</v>
@@ -4023,7 +4023,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H126" t="n">
         <v>1800</v>
@@ -4052,7 +4052,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G127" t="n">
-        <v>3.45807242393494</v>
+        <v>3.45807266235352</v>
       </c>
       <c r="H127" t="n">
         <v>30600</v>
@@ -4168,7 +4168,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H131" t="n">
         <v>1500</v>
@@ -4197,7 +4197,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H132" t="n">
         <v>2100</v>
@@ -4226,7 +4226,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G133" t="n">
-        <v>3.33166790008545</v>
+        <v>3.33166766166687</v>
       </c>
       <c r="H133" t="n">
         <v>300</v>
@@ -4255,7 +4255,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>3.33166790008545</v>
+        <v>3.33166766166687</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G135" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H135" t="n">
         <v>300</v>
@@ -4313,7 +4313,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G138" t="n">
-        <v>3.28652310371399</v>
+        <v>3.28652334213257</v>
       </c>
       <c r="H138" t="n">
         <v>900</v>
@@ -4429,7 +4429,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H140" t="n">
         <v>11700</v>
@@ -4458,7 +4458,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G141" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H141" t="n">
         <v>2100</v>
@@ -4487,7 +4487,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G142" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G143" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G145" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G146" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G148" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G149" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H149" t="n">
         <v>3900</v>
@@ -4719,7 +4719,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G151" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H151" t="n">
         <v>900</v>
@@ -4777,7 +4777,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G152" t="n">
-        <v>3.37681221961975</v>
+        <v>3.37681245803833</v>
       </c>
       <c r="H152" t="n">
         <v>300</v>
@@ -4806,7 +4806,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G153" t="n">
-        <v>3.37681221961975</v>
+        <v>3.37681245803833</v>
       </c>
       <c r="H153" t="n">
         <v>300</v>
@@ -4835,7 +4835,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G154" t="n">
-        <v>3.37681221961975</v>
+        <v>3.37681245803833</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G155" t="n">
-        <v>3.37681221961975</v>
+        <v>3.37681245803833</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G156" t="n">
-        <v>3.37681221961975</v>
+        <v>3.37681245803833</v>
       </c>
       <c r="H156" t="n">
         <v>300</v>
@@ -5473,7 +5473,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G176" t="n">
-        <v>3.24137878417969</v>
+        <v>3.24137854576111</v>
       </c>
       <c r="H176" t="n">
         <v>2400</v>
@@ -5531,7 +5531,7 @@
         <v>3.75</v>
       </c>
       <c r="G178" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H178" t="n">
         <v>1500</v>
@@ -5763,7 +5763,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G186" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H186" t="n">
         <v>60000</v>
@@ -5821,7 +5821,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G188" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H188" t="n">
         <v>600</v>
@@ -5850,7 +5850,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G190" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>3.5</v>
       </c>
       <c r="G191" t="n">
-        <v>3.1601185798645</v>
+        <v>3.16011834144592</v>
       </c>
       <c r="H191" t="n">
         <v>300</v>
@@ -5937,7 +5937,7 @@
         <v>3.5</v>
       </c>
       <c r="G192" t="n">
-        <v>3.1601185798645</v>
+        <v>3.16011834144592</v>
       </c>
       <c r="H192" t="n">
         <v>2400</v>
@@ -6401,7 +6401,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G208" t="n">
-        <v>3.05177140235901</v>
+        <v>3.05177187919617</v>
       </c>
       <c r="H208" t="n">
         <v>6600</v>
@@ -6430,7 +6430,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H209" t="n">
         <v>13500</v>
@@ -6459,7 +6459,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G210" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G211" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G212" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G213" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G215" t="n">
-        <v>2.87119340896606</v>
+        <v>2.87119364738464</v>
       </c>
       <c r="H215" t="n">
         <v>2100</v>
@@ -6633,7 +6633,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G216" t="n">
-        <v>2.87119340896606</v>
+        <v>2.87119364738464</v>
       </c>
       <c r="H216" t="n">
         <v>21000</v>
@@ -6662,7 +6662,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G217" t="n">
-        <v>2.87119340896606</v>
+        <v>2.87119364738464</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G220" t="n">
-        <v>2.66352868080139</v>
+        <v>2.66352844238281</v>
       </c>
       <c r="H220" t="n">
         <v>2100</v>
@@ -7271,7 +7271,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>2.46489262580872</v>
+        <v>2.46489238739014</v>
       </c>
       <c r="H238" t="n">
         <v>11100</v>
@@ -7300,7 +7300,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>2.46489262580872</v>
+        <v>2.46489238739014</v>
       </c>
       <c r="H239" t="n">
         <v>1200</v>
@@ -7329,7 +7329,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>2.46489262580872</v>
+        <v>2.46489238739014</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G241" t="n">
-        <v>2.46489262580872</v>
+        <v>2.46489238739014</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>2.46489262580872</v>
+        <v>2.46489238739014</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G250" t="n">
-        <v>2.41071915626526</v>
+        <v>2.41071891784668</v>
       </c>
       <c r="H250" t="n">
         <v>600</v>
@@ -7648,7 +7648,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>2.41071915626526</v>
+        <v>2.41071891784668</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G252" t="n">
-        <v>2.41071915626526</v>
+        <v>2.41071891784668</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G253" t="n">
-        <v>2.41071915626526</v>
+        <v>2.41071891784668</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>2.41071915626526</v>
+        <v>2.41071891784668</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>2.32945871353149</v>
+        <v>2.32945895195007</v>
       </c>
       <c r="H256" t="n">
         <v>1500</v>
@@ -7822,7 +7822,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>2.32945871353149</v>
+        <v>2.32945895195007</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>2.5</v>
       </c>
       <c r="G259" t="n">
-        <v>2.25722742080688</v>
+        <v>2.25722765922546</v>
       </c>
       <c r="H259" t="n">
         <v>9900</v>
@@ -7938,7 +7938,7 @@
         <v>2.5</v>
       </c>
       <c r="G261" t="n">
-        <v>2.25722742080688</v>
+        <v>2.25722765922546</v>
       </c>
       <c r="H261" t="n">
         <v>2400</v>
@@ -7967,7 +7967,7 @@
         <v>2.5</v>
       </c>
       <c r="G262" t="n">
-        <v>2.25722742080688</v>
+        <v>2.25722765922546</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G263" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H263" t="n">
         <v>2100</v>
@@ -8025,7 +8025,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G264" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G265" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G268" t="n">
-        <v>2.47392153739929</v>
+        <v>2.47392129898071</v>
       </c>
       <c r="H268" t="n">
         <v>1500</v>
@@ -8170,7 +8170,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G269" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H269" t="n">
         <v>2400</v>
@@ -8344,7 +8344,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G275" t="n">
-        <v>2.30237221717834</v>
+        <v>2.30237197875977</v>
       </c>
       <c r="H275" t="n">
         <v>2100</v>
@@ -8373,7 +8373,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G276" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H276" t="n">
         <v>1200</v>
@@ -8402,7 +8402,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G277" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H277" t="n">
         <v>3600</v>
@@ -8431,7 +8431,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G278" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H278" t="n">
         <v>3600</v>
@@ -8460,7 +8460,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H279" t="n">
         <v>4800</v>
@@ -8518,7 +8518,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G281" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H281" t="n">
         <v>21000</v>
@@ -8547,7 +8547,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G282" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H282" t="n">
         <v>900</v>
@@ -8576,7 +8576,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G283" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H283" t="n">
         <v>1500</v>
@@ -8605,7 +8605,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G284" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G285" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H285" t="n">
         <v>2100</v>
@@ -8663,7 +8663,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G286" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G287" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>2.15790939331055</v>
+        <v>2.15790963172913</v>
       </c>
       <c r="H290" t="n">
         <v>20700</v>
@@ -8808,7 +8808,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>2.12179398536682</v>
+        <v>2.12179350852966</v>
       </c>
       <c r="H291" t="n">
         <v>2400</v>
@@ -8837,7 +8837,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G292" t="n">
-        <v>2.05859160423279</v>
+        <v>2.05859136581421</v>
       </c>
       <c r="H292" t="n">
         <v>18900</v>
@@ -9011,7 +9011,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G298" t="n">
-        <v>1.93218672275543</v>
+        <v>1.93218684196472</v>
       </c>
       <c r="H298" t="n">
         <v>1500</v>
@@ -9040,7 +9040,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G299" t="n">
-        <v>1.9412157535553</v>
+        <v>1.94121587276459</v>
       </c>
       <c r="H299" t="n">
         <v>1200</v>
@@ -9069,7 +9069,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G300" t="n">
-        <v>1.87801313400269</v>
+        <v>1.87801325321198</v>
       </c>
       <c r="H300" t="n">
         <v>7200</v>
@@ -9098,7 +9098,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G301" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H301" t="n">
         <v>35700</v>
@@ -9127,7 +9127,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>1.9773313999176</v>
+        <v>1.97733116149902</v>
       </c>
       <c r="H302" t="n">
         <v>4200</v>
@@ -9156,7 +9156,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G303" t="n">
-        <v>1.9773313999176</v>
+        <v>1.97733116149902</v>
       </c>
       <c r="H303" t="n">
         <v>300</v>
@@ -9185,7 +9185,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G304" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H304" t="n">
         <v>600</v>
@@ -9243,7 +9243,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G306" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H306" t="n">
         <v>3600</v>
@@ -9359,7 +9359,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H310" t="n">
         <v>900</v>
@@ -9388,7 +9388,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G311" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H311" t="n">
         <v>1200</v>
@@ -9417,7 +9417,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G312" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G313" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H315" t="n">
         <v>300</v>
@@ -9533,7 +9533,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G316" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G318" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H318" t="n">
         <v>600</v>
@@ -9620,7 +9620,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G319" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G320" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G321" t="n">
-        <v>1.95024466514587</v>
+        <v>1.95024478435516</v>
       </c>
       <c r="H321" t="n">
         <v>600</v>
@@ -9707,7 +9707,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G322" t="n">
-        <v>1.95024466514587</v>
+        <v>1.95024478435516</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G323" t="n">
-        <v>1.95024466514587</v>
+        <v>1.95024478435516</v>
       </c>
       <c r="H323" t="n">
         <v>600</v>
@@ -9765,7 +9765,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G324" t="n">
-        <v>1.95024466514587</v>
+        <v>1.95024478435516</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>1.92315804958344</v>
+        <v>1.92315793037415</v>
       </c>
       <c r="H325" t="n">
         <v>600</v>
@@ -9823,7 +9823,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>2.04956269264221</v>
+        <v>2.04956245422363</v>
       </c>
       <c r="H326" t="n">
         <v>5700</v>
@@ -9881,7 +9881,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G328" t="n">
-        <v>1.91412889957428</v>
+        <v>1.91412878036499</v>
       </c>
       <c r="H328" t="n">
         <v>51000</v>
@@ -9939,7 +9939,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>1.84189772605896</v>
+        <v>1.84189760684967</v>
       </c>
       <c r="H330" t="n">
         <v>29100</v>
@@ -10171,7 +10171,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G338" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H338" t="n">
         <v>18000</v>
@@ -10200,7 +10200,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G339" t="n">
-        <v>2.05859160423279</v>
+        <v>2.05859136581421</v>
       </c>
       <c r="H339" t="n">
         <v>54900</v>
@@ -10229,7 +10229,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G340" t="n">
-        <v>2.00441789627075</v>
+        <v>2.00441813468933</v>
       </c>
       <c r="H340" t="n">
         <v>300</v>
@@ -10258,7 +10258,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G341" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H341" t="n">
         <v>1200</v>
@@ -10287,7 +10287,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G342" t="n">
-        <v>2.00441789627075</v>
+        <v>2.00441813468933</v>
       </c>
       <c r="H342" t="n">
         <v>2400</v>
@@ -10345,7 +10345,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G344" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H344" t="n">
         <v>13200</v>
@@ -10374,7 +10374,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G345" t="n">
-        <v>1.93218672275543</v>
+        <v>1.93218684196472</v>
       </c>
       <c r="H345" t="n">
         <v>5700</v>
@@ -10519,7 +10519,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G350" t="n">
-        <v>1.87801313400269</v>
+        <v>1.87801325321198</v>
       </c>
       <c r="H350" t="n">
         <v>2400</v>
@@ -10925,7 +10925,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G364" t="n">
-        <v>1.73355054855347</v>
+        <v>1.73355066776276</v>
       </c>
       <c r="H364" t="n">
         <v>2400</v>
@@ -11099,7 +11099,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G370" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H370" t="n">
         <v>2400</v>
@@ -11128,7 +11128,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G371" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>1.7877242565155</v>
+        <v>1.78772413730621</v>
       </c>
       <c r="H381" t="n">
         <v>98700</v>
@@ -11447,7 +11447,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G382" t="n">
-        <v>1.71549296379089</v>
+        <v>1.7154928445816</v>
       </c>
       <c r="H382" t="n">
         <v>9600</v>
@@ -11476,7 +11476,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G383" t="n">
-        <v>1.71549296379089</v>
+        <v>1.7154928445816</v>
       </c>
       <c r="H383" t="n">
         <v>23400</v>
@@ -11563,7 +11563,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G386" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H386" t="n">
         <v>5100</v>
@@ -11592,7 +11592,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G387" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H387" t="n">
         <v>6300</v>
@@ -11708,7 +11708,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G391" t="n">
-        <v>1.71549296379089</v>
+        <v>1.7154928445816</v>
       </c>
       <c r="H391" t="n">
         <v>4800</v>
@@ -11795,7 +11795,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G394" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H394" t="n">
         <v>5100</v>
@@ -11824,7 +11824,7 @@
         <v>1.75</v>
       </c>
       <c r="G395" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H395" t="n">
         <v>3900</v>
@@ -11911,7 +11911,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H398" t="n">
         <v>1200</v>
@@ -12085,7 +12085,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H404" t="n">
         <v>80700</v>
@@ -12317,7 +12317,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H412" t="n">
         <v>900</v>
@@ -12578,7 +12578,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G421" t="n">
-        <v>1.34530770778656</v>
+        <v>1.34530758857727</v>
       </c>
       <c r="H421" t="n">
         <v>1500</v>
@@ -12607,7 +12607,7 @@
         <v>1.5</v>
       </c>
       <c r="G422" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H422" t="n">
         <v>300</v>
@@ -12636,7 +12636,7 @@
         <v>1.5</v>
       </c>
       <c r="G423" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H423" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>1.5</v>
       </c>
       <c r="G424" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>1.34530770778656</v>
+        <v>1.34530758857727</v>
       </c>
       <c r="H434" t="n">
         <v>25500</v>
@@ -13216,7 +13216,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G443" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H443" t="n">
         <v>6000</v>
@@ -13390,7 +13390,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G449" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H449" t="n">
         <v>71700</v>
@@ -13448,7 +13448,7 @@
         <v>1.75</v>
       </c>
       <c r="G451" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H451" t="n">
         <v>17400</v>
@@ -13477,7 +13477,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H452" t="n">
         <v>5100</v>
@@ -13622,7 +13622,7 @@
         <v>1.5</v>
       </c>
       <c r="G457" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H457" t="n">
         <v>3000</v>
@@ -13651,7 +13651,7 @@
         <v>1.5</v>
       </c>
       <c r="G458" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H458" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>1.5</v>
       </c>
       <c r="G459" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H459" t="n">
         <v>9300</v>
@@ -13709,7 +13709,7 @@
         <v>1.5</v>
       </c>
       <c r="G460" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H460" t="n">
         <v>300</v>
@@ -13738,7 +13738,7 @@
         <v>1.5</v>
       </c>
       <c r="G461" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>1.5</v>
       </c>
       <c r="G462" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>1.5</v>
       </c>
       <c r="G463" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H463" t="n">
         <v>4200</v>
@@ -13854,7 +13854,7 @@
         <v>1.5</v>
       </c>
       <c r="G465" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H465" t="n">
         <v>20100</v>
@@ -13883,7 +13883,7 @@
         <v>1.5</v>
       </c>
       <c r="G466" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H466" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H475" t="n">
         <v>49500</v>
@@ -14173,7 +14173,7 @@
         <v>1.75</v>
       </c>
       <c r="G476" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H476" t="n">
         <v>21600</v>
@@ -14202,7 +14202,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G477" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H477" t="n">
         <v>18600</v>
@@ -14231,7 +14231,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G478" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H478" t="n">
         <v>31500</v>
@@ -14260,7 +14260,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H479" t="n">
         <v>39600</v>
@@ -14318,7 +14318,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G481" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H481" t="n">
         <v>30900</v>
@@ -14463,7 +14463,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G486" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H486" t="n">
         <v>16800</v>
@@ -14521,7 +14521,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G488" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H488" t="n">
         <v>6000</v>
@@ -14695,7 +14695,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G494" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H494" t="n">
         <v>7200</v>
@@ -14840,7 +14840,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G499" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H499" t="n">
         <v>42000</v>
@@ -14898,7 +14898,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G501" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H501" t="n">
         <v>9900</v>
@@ -14927,7 +14927,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G502" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H502" t="n">
         <v>19200</v>
@@ -14956,7 +14956,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G503" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H503" t="n">
         <v>44700</v>
@@ -14985,7 +14985,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G504" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H504" t="n">
         <v>5400</v>
@@ -15130,7 +15130,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G509" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H509" t="n">
         <v>3600</v>
@@ -15217,7 +15217,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H512" t="n">
         <v>36000</v>
@@ -15304,7 +15304,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G515" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H515" t="n">
         <v>7500</v>
@@ -15420,7 +15420,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G519" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H519" t="n">
         <v>4800</v>
@@ -15478,7 +15478,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G521" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H521" t="n">
         <v>600</v>
@@ -15507,7 +15507,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H522" t="n">
         <v>2400</v>
@@ -15536,7 +15536,7 @@
         <v>1.75</v>
       </c>
       <c r="G523" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H523" t="n">
         <v>9900</v>
@@ -15594,7 +15594,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G525" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H525" t="n">
         <v>37500</v>
@@ -15623,7 +15623,7 @@
         <v>1.75</v>
       </c>
       <c r="G526" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H526" t="n">
         <v>92100</v>
@@ -15826,7 +15826,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G533" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H533" t="n">
         <v>5400</v>
@@ -15855,7 +15855,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G534" t="n">
-        <v>1.34530770778656</v>
+        <v>1.34530758857727</v>
       </c>
       <c r="H534" t="n">
         <v>72000</v>
@@ -15884,7 +15884,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G535" t="n">
-        <v>1.34530770778656</v>
+        <v>1.34530758857727</v>
       </c>
       <c r="H535" t="n">
         <v>105300</v>
@@ -15942,7 +15942,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G537" t="n">
-        <v>1.29113399982452</v>
+        <v>1.29113411903381</v>
       </c>
       <c r="H537" t="n">
         <v>8700</v>
@@ -16116,7 +16116,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G543" t="n">
-        <v>1.29113399982452</v>
+        <v>1.29113411903381</v>
       </c>
       <c r="H543" t="n">
         <v>45600</v>
@@ -16261,7 +16261,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G548" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H548" t="n">
         <v>21900</v>
@@ -16290,7 +16290,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G549" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H549" t="n">
         <v>45900</v>
@@ -16319,7 +16319,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G550" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H550" t="n">
         <v>19800</v>
@@ -16435,7 +16435,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G554" t="n">
-        <v>1.08346915245056</v>
+        <v>1.08346927165985</v>
       </c>
       <c r="H554" t="n">
         <v>29100</v>
@@ -16493,7 +16493,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G556" t="n">
-        <v>1.02026689052582</v>
+        <v>1.02026677131653</v>
       </c>
       <c r="H556" t="n">
         <v>72900</v>
@@ -16522,7 +16522,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G557" t="n">
-        <v>1.02026689052582</v>
+        <v>1.02026677131653</v>
       </c>
       <c r="H557" t="n">
         <v>37800</v>
@@ -16551,7 +16551,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G558" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H558" t="n">
         <v>19500</v>
@@ -16638,7 +16638,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G561" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H561" t="n">
         <v>8100</v>
@@ -16725,7 +16725,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H564" t="n">
         <v>15300</v>
@@ -16754,7 +16754,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G565" t="n">
-        <v>0.939006567001343</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H565" t="n">
         <v>2400</v>
@@ -16841,7 +16841,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G568" t="n">
-        <v>0.803572952747345</v>
+        <v>0.80357301235199</v>
       </c>
       <c r="H568" t="n">
         <v>9600</v>
@@ -16986,7 +16986,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G573" t="n">
-        <v>0.866775274276733</v>
+        <v>0.866775333881378</v>
       </c>
       <c r="H573" t="n">
         <v>10800</v>
@@ -17131,7 +17131,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G578" t="n">
-        <v>0.975122332572937</v>
+        <v>0.975122392177582</v>
       </c>
       <c r="H578" t="n">
         <v>14700</v>
@@ -17189,7 +17189,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G580" t="n">
-        <v>1.00220894813538</v>
+        <v>1.00220906734467</v>
       </c>
       <c r="H580" t="n">
         <v>1500</v>
@@ -17247,7 +17247,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G582" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H582" t="n">
         <v>1200</v>
@@ -17334,7 +17334,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G585" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H585" t="n">
         <v>15600</v>
@@ -17363,7 +17363,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G586" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H586" t="n">
         <v>9600</v>
@@ -17450,7 +17450,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G589" t="n">
-        <v>1.00220894813538</v>
+        <v>1.00220906734467</v>
       </c>
       <c r="H589" t="n">
         <v>10800</v>
@@ -17479,7 +17479,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G590" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H590" t="n">
         <v>18000</v>
@@ -17508,7 +17508,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G591" t="n">
-        <v>0.952549934387207</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H591" t="n">
         <v>102000</v>
@@ -17537,7 +17537,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G592" t="n">
-        <v>0.966093361377716</v>
+        <v>0.966093420982361</v>
       </c>
       <c r="H592" t="n">
         <v>4200</v>
@@ -17566,7 +17566,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G593" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H593" t="n">
         <v>12900</v>
@@ -17595,7 +17595,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G594" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H594" t="n">
         <v>1500</v>
@@ -17624,7 +17624,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H595" t="n">
         <v>15900</v>
@@ -17653,7 +17653,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>0.939006567001343</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H596" t="n">
         <v>39300</v>
@@ -17682,7 +17682,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G597" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H597" t="n">
         <v>15000</v>
@@ -17711,7 +17711,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G598" t="n">
-        <v>0.952549934387207</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H598" t="n">
         <v>21600</v>
@@ -17740,7 +17740,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G599" t="n">
-        <v>0.966093361377716</v>
+        <v>0.966093420982361</v>
       </c>
       <c r="H599" t="n">
         <v>2700</v>
@@ -17798,7 +17798,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G601" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H601" t="n">
         <v>17100</v>
@@ -17827,7 +17827,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G602" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H602" t="n">
         <v>13200</v>
@@ -17856,7 +17856,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G603" t="n">
-        <v>0.939006567001343</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H603" t="n">
         <v>9600</v>
@@ -17914,7 +17914,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G605" t="n">
-        <v>0.966093361377716</v>
+        <v>0.966093420982361</v>
       </c>
       <c r="H605" t="n">
         <v>23400</v>
@@ -17972,7 +17972,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G607" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H607" t="n">
         <v>7800</v>
@@ -18030,7 +18030,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G609" t="n">
-        <v>0.925463199615479</v>
+        <v>0.925463259220123</v>
       </c>
       <c r="H609" t="n">
         <v>38400</v>
@@ -18059,7 +18059,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H610" t="n">
         <v>52200</v>
@@ -18088,7 +18088,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G611" t="n">
-        <v>0.925463199615479</v>
+        <v>0.925463259220123</v>
       </c>
       <c r="H611" t="n">
         <v>195300</v>
@@ -18262,7 +18262,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G617" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H617" t="n">
         <v>13200</v>
@@ -18320,7 +18320,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G619" t="n">
-        <v>0.893862128257751</v>
+        <v>0.893862068653107</v>
       </c>
       <c r="H619" t="n">
         <v>41100</v>
@@ -18552,7 +18552,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G627" t="n">
-        <v>1.04283905029297</v>
+        <v>1.04283916950226</v>
       </c>
       <c r="H627" t="n">
         <v>258300</v>
@@ -18581,7 +18581,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G628" t="n">
-        <v>0.988665699958801</v>
+        <v>0.988665580749512</v>
       </c>
       <c r="H628" t="n">
         <v>45600</v>
@@ -18610,7 +18610,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G629" t="n">
-        <v>0.966093361377716</v>
+        <v>0.966093420982361</v>
       </c>
       <c r="H629" t="n">
         <v>36000</v>
@@ -18639,7 +18639,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G630" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H630" t="n">
         <v>20400</v>
@@ -18668,7 +18668,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>0.997694551944733</v>
+        <v>0.997694611549377</v>
       </c>
       <c r="H631" t="n">
         <v>19200</v>
@@ -18755,7 +18755,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G634" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H634" t="n">
         <v>5700</v>
@@ -18784,7 +18784,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G635" t="n">
-        <v>1.02929580211639</v>
+        <v>1.0292956829071</v>
       </c>
       <c r="H635" t="n">
         <v>5700</v>
@@ -18842,7 +18842,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G637" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H637" t="n">
         <v>3900</v>
@@ -18900,7 +18900,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H639" t="n">
         <v>2400</v>
@@ -18929,7 +18929,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G640" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H640" t="n">
         <v>18600</v>
@@ -19016,7 +19016,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G643" t="n">
-        <v>0.966093361377716</v>
+        <v>0.966093420982361</v>
       </c>
       <c r="H643" t="n">
         <v>9000</v>
@@ -19045,7 +19045,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G644" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H644" t="n">
         <v>10800</v>
@@ -19074,7 +19074,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G645" t="n">
-        <v>0.925463199615479</v>
+        <v>0.925463259220123</v>
       </c>
       <c r="H645" t="n">
         <v>9000</v>
@@ -19103,7 +19103,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>0.939006567001343</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H646" t="n">
         <v>7200</v>
@@ -19132,7 +19132,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>0.939006567001343</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H647" t="n">
         <v>1500</v>
@@ -19190,7 +19190,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G649" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H649" t="n">
         <v>3000</v>
@@ -19248,7 +19248,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G651" t="n">
-        <v>0.975122332572937</v>
+        <v>0.975122392177582</v>
       </c>
       <c r="H651" t="n">
         <v>2700</v>
@@ -19335,7 +19335,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G654" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607936382294</v>
       </c>
       <c r="H654" t="n">
         <v>7500</v>
@@ -19364,7 +19364,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G655" t="n">
-        <v>1.00220894813538</v>
+        <v>1.00220906734467</v>
       </c>
       <c r="H655" t="n">
         <v>2400</v>
@@ -19422,7 +19422,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G657" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H657" t="n">
         <v>5400</v>
@@ -19480,7 +19480,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G659" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607936382294</v>
       </c>
       <c r="H659" t="n">
         <v>12300</v>
@@ -19509,7 +19509,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G660" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607936382294</v>
       </c>
       <c r="H660" t="n">
         <v>0</v>
@@ -19567,7 +19567,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G662" t="n">
-        <v>0.966093361377716</v>
+        <v>0.966093420982361</v>
       </c>
       <c r="H662" t="n">
         <v>300</v>
@@ -19625,7 +19625,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G664" t="n">
-        <v>0.952549934387207</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H664" t="n">
         <v>300</v>
@@ -19654,7 +19654,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G665" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H665" t="n">
         <v>1800</v>
@@ -19712,7 +19712,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G667" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H667" t="n">
         <v>3900</v>
@@ -19770,7 +19770,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G669" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H669" t="n">
         <v>300</v>
@@ -19799,7 +19799,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G670" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607936382294</v>
       </c>
       <c r="H670" t="n">
         <v>2100</v>
@@ -19857,7 +19857,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G672" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H672" t="n">
         <v>300</v>
@@ -19886,7 +19886,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.988665699958801</v>
+        <v>0.988665580749512</v>
       </c>
       <c r="H673" t="n">
         <v>3300</v>
@@ -19915,7 +19915,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G674" t="n">
-        <v>0.988665699958801</v>
+        <v>0.988665580749512</v>
       </c>
       <c r="H674" t="n">
         <v>300</v>
@@ -20002,7 +20002,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G677" t="n">
-        <v>0.975122332572937</v>
+        <v>0.975122392177582</v>
       </c>
       <c r="H677" t="n">
         <v>10500</v>
@@ -20031,7 +20031,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G678" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H678" t="n">
         <v>9300</v>
@@ -20176,7 +20176,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>0.939006567001343</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H683" t="n">
         <v>23100</v>
@@ -20205,7 +20205,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G684" t="n">
-        <v>0.907405436038971</v>
+        <v>0.907405495643616</v>
       </c>
       <c r="H684" t="n">
         <v>29700</v>
@@ -20263,7 +20263,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H686" t="n">
         <v>3000</v>
@@ -20292,7 +20292,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G687" t="n">
-        <v>0.952549934387207</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H687" t="n">
         <v>3600</v>
@@ -20379,7 +20379,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G690" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H690" t="n">
         <v>3600</v>
@@ -20408,7 +20408,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G691" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H691" t="n">
         <v>600</v>
@@ -20466,7 +20466,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G693" t="n">
-        <v>0.925463199615479</v>
+        <v>0.925463259220123</v>
       </c>
       <c r="H693" t="n">
         <v>15600</v>
@@ -20495,7 +20495,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G694" t="n">
-        <v>0.925463199615479</v>
+        <v>0.925463259220123</v>
       </c>
       <c r="H694" t="n">
         <v>29100</v>
@@ -20553,7 +20553,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G696" t="n">
-        <v>0.952549934387207</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H696" t="n">
         <v>12000</v>
@@ -20611,7 +20611,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G698" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607936382294</v>
       </c>
       <c r="H698" t="n">
         <v>21600</v>
@@ -20756,7 +20756,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>0.911919891834259</v>
+        <v>0.911919951438904</v>
       </c>
       <c r="H703" t="n">
         <v>11700</v>
@@ -20814,7 +20814,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G705" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H705" t="n">
         <v>900</v>
@@ -20843,7 +20843,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G706" t="n">
-        <v>0.843300223350525</v>
+        <v>0.84330016374588</v>
       </c>
       <c r="H706" t="n">
         <v>67500</v>
@@ -21017,7 +21017,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G712" t="n">
-        <v>0.787320971488953</v>
+        <v>0.787320911884308</v>
       </c>
       <c r="H712" t="n">
         <v>32100</v>
@@ -21075,7 +21075,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G714" t="n">
-        <v>0.776486337184906</v>
+        <v>0.776486277580261</v>
       </c>
       <c r="H714" t="n">
         <v>10800</v>
@@ -21278,7 +21278,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G721" t="n">
-        <v>0.698837637901306</v>
+        <v>0.698837578296661</v>
       </c>
       <c r="H721" t="n">
         <v>20700</v>
@@ -21510,7 +21510,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G729" t="n">
-        <v>0.619383215904236</v>
+        <v>0.619383275508881</v>
       </c>
       <c r="H729" t="n">
         <v>9600</v>
@@ -21539,7 +21539,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G730" t="n">
-        <v>0.662721991539001</v>
+        <v>0.662722051143646</v>
       </c>
       <c r="H730" t="n">
         <v>3900</v>
@@ -21626,7 +21626,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G733" t="n">
-        <v>0.65188729763031</v>
+        <v>0.651887357234955</v>
       </c>
       <c r="H733" t="n">
         <v>3600</v>
@@ -21655,7 +21655,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G734" t="n">
-        <v>0.65369313955307</v>
+        <v>0.653693020343781</v>
       </c>
       <c r="H734" t="n">
         <v>27900</v>
@@ -21713,7 +21713,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G736" t="n">
-        <v>0.678974032402039</v>
+        <v>0.678973972797394</v>
       </c>
       <c r="H736" t="n">
         <v>4200</v>
@@ -21742,7 +21742,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G737" t="n">
-        <v>0.684391379356384</v>
+        <v>0.68439131975174</v>
       </c>
       <c r="H737" t="n">
         <v>14700</v>
@@ -21829,7 +21829,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G740" t="n">
-        <v>0.644664168357849</v>
+        <v>0.644664227962494</v>
       </c>
       <c r="H740" t="n">
         <v>3600</v>
@@ -21858,7 +21858,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G741" t="n">
-        <v>0.657304584980011</v>
+        <v>0.657304644584656</v>
       </c>
       <c r="H741" t="n">
         <v>20100</v>
@@ -21916,7 +21916,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G743" t="n">
-        <v>0.662721991539001</v>
+        <v>0.662722051143646</v>
       </c>
       <c r="H743" t="n">
         <v>73200</v>
@@ -21945,7 +21945,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G744" t="n">
-        <v>0.675362467765808</v>
+        <v>0.675362527370453</v>
       </c>
       <c r="H744" t="n">
         <v>18000</v>
@@ -22090,7 +22090,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G749" t="n">
-        <v>0.720507025718689</v>
+        <v>0.720506966114044</v>
       </c>
       <c r="H749" t="n">
         <v>48300</v>
@@ -22119,7 +22119,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G750" t="n">
-        <v>0.709672331809998</v>
+        <v>0.709672272205353</v>
       </c>
       <c r="H750" t="n">
         <v>35100</v>
@@ -22177,7 +22177,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G752" t="n">
-        <v>0.675362467765808</v>
+        <v>0.675362527370453</v>
       </c>
       <c r="H752" t="n">
         <v>33600</v>
@@ -22206,7 +22206,7 @@
         <v>0.75</v>
       </c>
       <c r="G753" t="n">
-        <v>0.677168250083923</v>
+        <v>0.677168309688568</v>
       </c>
       <c r="H753" t="n">
         <v>36600</v>
@@ -22235,7 +22235,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G754" t="n">
-        <v>0.675362467765808</v>
+        <v>0.675362527370453</v>
       </c>
       <c r="H754" t="n">
         <v>27900</v>
@@ -22264,7 +22264,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G755" t="n">
-        <v>0.698837637901306</v>
+        <v>0.698837578296661</v>
       </c>
       <c r="H755" t="n">
         <v>134100</v>
@@ -22322,7 +22322,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G757" t="n">
-        <v>0.684391379356384</v>
+        <v>0.68439131975174</v>
       </c>
       <c r="H757" t="n">
         <v>34500</v>
@@ -22641,7 +22641,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G768" t="n">
-        <v>0.798155605792999</v>
+        <v>0.798155665397644</v>
       </c>
       <c r="H768" t="n">
         <v>107700</v>
@@ -22670,7 +22670,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G769" t="n">
-        <v>0.787320971488953</v>
+        <v>0.787320911884308</v>
       </c>
       <c r="H769" t="n">
         <v>28800</v>
@@ -22757,7 +22757,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G772" t="n">
-        <v>0.798155605792999</v>
+        <v>0.798155665397644</v>
       </c>
       <c r="H772" t="n">
         <v>56700</v>
@@ -22786,7 +22786,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G773" t="n">
-        <v>0.776486337184906</v>
+        <v>0.776486277580261</v>
       </c>
       <c r="H773" t="n">
         <v>17700</v>
@@ -22844,7 +22844,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G775" t="n">
-        <v>0.776486337184906</v>
+        <v>0.776486277580261</v>
       </c>
       <c r="H775" t="n">
         <v>10800</v>
@@ -22873,7 +22873,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G776" t="n">
-        <v>0.80176717042923</v>
+        <v>0.801767230033875</v>
       </c>
       <c r="H776" t="n">
         <v>99600</v>
@@ -22902,7 +22902,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G777" t="n">
-        <v>0.787320971488953</v>
+        <v>0.787320911884308</v>
       </c>
       <c r="H777" t="n">
         <v>15000</v>
@@ -22989,7 +22989,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G780" t="n">
-        <v>0.808990359306335</v>
+        <v>0.80899041891098</v>
       </c>
       <c r="H780" t="n">
         <v>34200</v>
@@ -23018,7 +23018,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G781" t="n">
-        <v>0.803572952747345</v>
+        <v>0.80357301235199</v>
       </c>
       <c r="H781" t="n">
         <v>27000</v>
@@ -23047,7 +23047,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G782" t="n">
-        <v>0.80176717042923</v>
+        <v>0.801767230033875</v>
       </c>
       <c r="H782" t="n">
         <v>21600</v>
@@ -23076,7 +23076,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G783" t="n">
-        <v>0.794544041156769</v>
+        <v>0.794544100761414</v>
       </c>
       <c r="H783" t="n">
         <v>92100</v>
@@ -23105,7 +23105,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G784" t="n">
-        <v>0.808990359306335</v>
+        <v>0.80899041891098</v>
       </c>
       <c r="H784" t="n">
         <v>44700</v>
@@ -23134,7 +23134,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G785" t="n">
-        <v>0.803572952747345</v>
+        <v>0.80357301235199</v>
       </c>
       <c r="H785" t="n">
         <v>7500</v>
@@ -23424,7 +23424,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>0.769263088703156</v>
+        <v>0.7692631483078</v>
       </c>
       <c r="H795" t="n">
         <v>9900</v>
@@ -23511,7 +23511,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G798" t="n">
-        <v>0.798155605792999</v>
+        <v>0.798155665397644</v>
       </c>
       <c r="H798" t="n">
         <v>40200</v>
@@ -23540,7 +23540,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G799" t="n">
-        <v>0.819824993610382</v>
+        <v>0.819825053215027</v>
       </c>
       <c r="H799" t="n">
         <v>312600</v>
@@ -23569,7 +23569,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G800" t="n">
-        <v>0.823436617851257</v>
+        <v>0.823436677455902</v>
       </c>
       <c r="H800" t="n">
         <v>87300</v>
@@ -23598,7 +23598,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G801" t="n">
-        <v>0.834271311759949</v>
+        <v>0.834271371364594</v>
       </c>
       <c r="H801" t="n">
         <v>39300</v>
@@ -23627,7 +23627,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G802" t="n">
-        <v>0.827048122882843</v>
+        <v>0.827048182487488</v>
       </c>
       <c r="H802" t="n">
         <v>36900</v>
@@ -23685,7 +23685,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G804" t="n">
-        <v>0.857746481895447</v>
+        <v>0.857746422290802</v>
       </c>
       <c r="H804" t="n">
         <v>87300</v>
@@ -23772,7 +23772,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>0.893862128257751</v>
+        <v>0.893862068653107</v>
       </c>
       <c r="H807" t="n">
         <v>214500</v>
@@ -23801,7 +23801,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G808" t="n">
-        <v>0.890250504016876</v>
+        <v>0.890250563621521</v>
       </c>
       <c r="H808" t="n">
         <v>21600</v>
@@ -23888,7 +23888,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G811" t="n">
-        <v>0.857746481895447</v>
+        <v>0.857746422290802</v>
       </c>
       <c r="H811" t="n">
         <v>22500</v>
@@ -24120,7 +24120,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G819" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H819" t="n">
         <v>47400</v>
@@ -24149,7 +24149,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G820" t="n">
-        <v>0.925463199615479</v>
+        <v>0.925463259220123</v>
       </c>
       <c r="H820" t="n">
         <v>38100</v>
@@ -24265,7 +24265,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G824" t="n">
-        <v>0.911919891834259</v>
+        <v>0.911919951438904</v>
       </c>
       <c r="H824" t="n">
         <v>29700</v>
@@ -24381,7 +24381,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G828" t="n">
-        <v>0.872192680835724</v>
+        <v>0.872192740440369</v>
       </c>
       <c r="H828" t="n">
         <v>37500</v>
@@ -24410,7 +24410,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G829" t="n">
-        <v>0.87941575050354</v>
+        <v>0.879415810108185</v>
       </c>
       <c r="H829" t="n">
         <v>30300</v>
@@ -24497,7 +24497,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G832" t="n">
-        <v>0.893862128257751</v>
+        <v>0.893862068653107</v>
       </c>
       <c r="H832" t="n">
         <v>12000</v>
@@ -24584,7 +24584,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G835" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H835" t="n">
         <v>30600</v>
@@ -24613,7 +24613,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G836" t="n">
-        <v>0.925463199615479</v>
+        <v>0.925463259220123</v>
       </c>
       <c r="H836" t="n">
         <v>18000</v>
@@ -24671,7 +24671,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G838" t="n">
-        <v>0.907405436038971</v>
+        <v>0.907405495643616</v>
       </c>
       <c r="H838" t="n">
         <v>3900</v>
@@ -24700,7 +24700,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G839" t="n">
-        <v>0.911919891834259</v>
+        <v>0.911919951438904</v>
       </c>
       <c r="H839" t="n">
         <v>300</v>
@@ -24729,7 +24729,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G840" t="n">
-        <v>0.907405436038971</v>
+        <v>0.907405495643616</v>
       </c>
       <c r="H840" t="n">
         <v>900</v>
@@ -24787,7 +24787,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G842" t="n">
-        <v>0.890250504016876</v>
+        <v>0.890250563621521</v>
       </c>
       <c r="H842" t="n">
         <v>21000</v>
@@ -24845,7 +24845,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G844" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H844" t="n">
         <v>35100</v>
@@ -24903,7 +24903,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G846" t="n">
-        <v>0.966093361377716</v>
+        <v>0.966093420982361</v>
       </c>
       <c r="H846" t="n">
         <v>119100</v>
@@ -24932,7 +24932,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G847" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H847" t="n">
         <v>6600</v>
@@ -24990,7 +24990,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G849" t="n">
-        <v>1.02929580211639</v>
+        <v>1.0292956829071</v>
       </c>
       <c r="H849" t="n">
         <v>90600</v>
@@ -25077,7 +25077,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G852" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H852" t="n">
         <v>109800</v>
@@ -25135,7 +25135,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G854" t="n">
-        <v>1.02929580211639</v>
+        <v>1.0292956829071</v>
       </c>
       <c r="H854" t="n">
         <v>5400</v>
@@ -25222,7 +25222,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G857" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H857" t="n">
         <v>135300</v>
@@ -25396,7 +25396,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G863" t="n">
-        <v>1.06089699268341</v>
+        <v>1.06089675426483</v>
       </c>
       <c r="H863" t="n">
         <v>3900</v>
@@ -25425,7 +25425,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G864" t="n">
-        <v>1.10604155063629</v>
+        <v>1.106041431427</v>
       </c>
       <c r="H864" t="n">
         <v>43500</v>
@@ -25454,7 +25454,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G865" t="n">
-        <v>1.09701251983643</v>
+        <v>1.09701263904572</v>
       </c>
       <c r="H865" t="n">
         <v>21600</v>
@@ -25483,7 +25483,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G866" t="n">
-        <v>1.07895469665527</v>
+        <v>1.07895481586456</v>
       </c>
       <c r="H866" t="n">
         <v>8100</v>
@@ -25512,7 +25512,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G867" t="n">
-        <v>1.08346915245056</v>
+        <v>1.08346927165985</v>
       </c>
       <c r="H867" t="n">
         <v>25800</v>
@@ -25628,7 +25628,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G871" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H871" t="n">
         <v>7500</v>
@@ -25657,7 +25657,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G872" t="n">
-        <v>1.14215707778931</v>
+        <v>1.14215695858002</v>
       </c>
       <c r="H872" t="n">
         <v>46800</v>
@@ -25686,7 +25686,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G873" t="n">
-        <v>1.16472935676575</v>
+        <v>1.16472947597504</v>
       </c>
       <c r="H873" t="n">
         <v>48300</v>
@@ -25715,7 +25715,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G874" t="n">
-        <v>1.15570056438446</v>
+        <v>1.15570044517517</v>
       </c>
       <c r="H874" t="n">
         <v>54300</v>
@@ -25744,7 +25744,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>1.16472935676575</v>
+        <v>1.16472947597504</v>
       </c>
       <c r="H875" t="n">
         <v>158700</v>
@@ -25802,7 +25802,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G877" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H877" t="n">
         <v>32400</v>
@@ -25831,7 +25831,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>1.20535957813263</v>
+        <v>1.20535945892334</v>
       </c>
       <c r="H878" t="n">
         <v>25200</v>
@@ -25860,7 +25860,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G879" t="n">
-        <v>1.27307629585266</v>
+        <v>1.27307617664337</v>
       </c>
       <c r="H879" t="n">
         <v>146400</v>
@@ -25889,7 +25889,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G880" t="n">
-        <v>1.31370651721954</v>
+        <v>1.31370639801025</v>
       </c>
       <c r="H880" t="n">
         <v>138600</v>
@@ -26034,7 +26034,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G885" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H885" t="n">
         <v>49200</v>
@@ -26063,7 +26063,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G886" t="n">
-        <v>1.20535957813263</v>
+        <v>1.20535945892334</v>
       </c>
       <c r="H886" t="n">
         <v>24000</v>
@@ -26092,7 +26092,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G887" t="n">
-        <v>1.23244631290436</v>
+        <v>1.23244619369507</v>
       </c>
       <c r="H887" t="n">
         <v>7800</v>
@@ -26121,7 +26121,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G888" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H888" t="n">
         <v>5100</v>
@@ -26179,7 +26179,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G890" t="n">
-        <v>1.23244631290436</v>
+        <v>1.23244619369507</v>
       </c>
       <c r="H890" t="n">
         <v>3000</v>
@@ -26237,7 +26237,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G892" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H892" t="n">
         <v>12600</v>
@@ -26266,7 +26266,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G893" t="n">
-        <v>1.23244631290436</v>
+        <v>1.23244619369507</v>
       </c>
       <c r="H893" t="n">
         <v>5100</v>
@@ -26295,7 +26295,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G894" t="n">
-        <v>1.23244631290436</v>
+        <v>1.23244619369507</v>
       </c>
       <c r="H894" t="n">
         <v>900</v>
@@ -26324,7 +26324,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G895" t="n">
-        <v>1.23244631290436</v>
+        <v>1.23244619369507</v>
       </c>
       <c r="H895" t="n">
         <v>3000</v>
@@ -26440,7 +26440,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G899" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H899" t="n">
         <v>11400</v>
@@ -26498,7 +26498,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G901" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H901" t="n">
         <v>68700</v>
@@ -26585,7 +26585,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G904" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H904" t="n">
         <v>900</v>
@@ -26672,7 +26672,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G907" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H907" t="n">
         <v>4500</v>
@@ -26701,7 +26701,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G908" t="n">
-        <v>1.14215707778931</v>
+        <v>1.14215695858002</v>
       </c>
       <c r="H908" t="n">
         <v>3600</v>
@@ -26788,7 +26788,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G911" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H911" t="n">
         <v>2100</v>
@@ -26817,7 +26817,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G912" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H912" t="n">
         <v>1200</v>
@@ -26875,7 +26875,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G914" t="n">
-        <v>1.10604155063629</v>
+        <v>1.106041431427</v>
       </c>
       <c r="H914" t="n">
         <v>900</v>
@@ -26933,7 +26933,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G916" t="n">
-        <v>1.07895469665527</v>
+        <v>1.07895481586456</v>
       </c>
       <c r="H916" t="n">
         <v>26100</v>
@@ -27020,7 +27020,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>1.16472935676575</v>
+        <v>1.16472947597504</v>
       </c>
       <c r="H919" t="n">
         <v>21000</v>
@@ -27049,7 +27049,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G920" t="n">
-        <v>1.16021478176117</v>
+        <v>1.16021490097046</v>
       </c>
       <c r="H920" t="n">
         <v>3900</v>
@@ -27078,7 +27078,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G921" t="n">
-        <v>1.16021478176117</v>
+        <v>1.16021490097046</v>
       </c>
       <c r="H921" t="n">
         <v>3000</v>
@@ -27107,7 +27107,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G922" t="n">
-        <v>1.16472935676575</v>
+        <v>1.16472947597504</v>
       </c>
       <c r="H922" t="n">
         <v>15000</v>
@@ -27136,7 +27136,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G923" t="n">
-        <v>1.14215707778931</v>
+        <v>1.14215695858002</v>
       </c>
       <c r="H923" t="n">
         <v>4200</v>
@@ -27165,7 +27165,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G924" t="n">
-        <v>1.15118610858917</v>
+        <v>1.15118598937988</v>
       </c>
       <c r="H924" t="n">
         <v>9600</v>
@@ -27194,7 +27194,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G925" t="n">
-        <v>1.14215707778931</v>
+        <v>1.14215695858002</v>
       </c>
       <c r="H925" t="n">
         <v>1200</v>
@@ -27223,7 +27223,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G926" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H926" t="n">
         <v>16500</v>
@@ -27252,7 +27252,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G927" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H927" t="n">
         <v>60300</v>
@@ -27281,7 +27281,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G928" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H928" t="n">
         <v>10200</v>
@@ -27310,7 +27310,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G929" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H929" t="n">
         <v>0</v>
@@ -27513,7 +27513,7 @@
         <v>1.875</v>
       </c>
       <c r="G936" t="n">
-        <v>1.69292056560516</v>
+        <v>1.69292068481445</v>
       </c>
       <c r="H936" t="n">
         <v>592500</v>
@@ -27542,7 +27542,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G937" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H937" t="n">
         <v>201600</v>
@@ -27571,7 +27571,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G938" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H938" t="n">
         <v>60000</v>
@@ -27600,7 +27600,7 @@
         <v>1.75</v>
       </c>
       <c r="G939" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H939" t="n">
         <v>30600</v>
@@ -27629,7 +27629,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G940" t="n">
-        <v>1.52137136459351</v>
+        <v>1.52137124538422</v>
       </c>
       <c r="H940" t="n">
         <v>57000</v>
@@ -27658,7 +27658,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G941" t="n">
-        <v>1.64777612686157</v>
+        <v>1.64777624607086</v>
       </c>
       <c r="H941" t="n">
         <v>159900</v>
@@ -27716,7 +27716,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H943" t="n">
         <v>35700</v>
@@ -27803,7 +27803,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G946" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H946" t="n">
         <v>20700</v>
@@ -28064,7 +28064,7 @@
         <v>1.5</v>
       </c>
       <c r="G955" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H955" t="n">
         <v>54600</v>
@@ -28093,7 +28093,7 @@
         <v>1.5</v>
       </c>
       <c r="G956" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H956" t="n">
         <v>15000</v>
@@ -28238,7 +28238,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G961" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H961" t="n">
         <v>116400</v>
@@ -28325,7 +28325,7 @@
         <v>1.5</v>
       </c>
       <c r="G964" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H964" t="n">
         <v>15900</v>
@@ -28412,7 +28412,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G967" t="n">
-        <v>1.35885095596313</v>
+        <v>1.35885083675385</v>
       </c>
       <c r="H967" t="n">
         <v>54900</v>
@@ -28499,7 +28499,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G970" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H970" t="n">
         <v>59100</v>
@@ -28847,7 +28847,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G982" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H982" t="n">
         <v>41400</v>
@@ -28876,7 +28876,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G983" t="n">
-        <v>1.47622692584991</v>
+        <v>1.47622680664062</v>
       </c>
       <c r="H983" t="n">
         <v>18900</v>
@@ -28934,7 +28934,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G985" t="n">
-        <v>1.52137136459351</v>
+        <v>1.52137124538422</v>
       </c>
       <c r="H985" t="n">
         <v>24000</v>
@@ -28992,7 +28992,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G987" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H987" t="n">
         <v>38700</v>
@@ -29050,7 +29050,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G989" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H989" t="n">
         <v>57300</v>
@@ -29079,7 +29079,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G990" t="n">
-        <v>1.52137136459351</v>
+        <v>1.52137124538422</v>
       </c>
       <c r="H990" t="n">
         <v>18300</v>
@@ -29195,7 +29195,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G994" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H994" t="n">
         <v>6600</v>
@@ -29224,7 +29224,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H995" t="n">
         <v>3300</v>
@@ -29253,7 +29253,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G996" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H996" t="n">
         <v>28800</v>
@@ -29340,7 +29340,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G999" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H999" t="n">
         <v>10500</v>
@@ -29572,7 +29572,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H1007" t="n">
         <v>3900</v>
@@ -29659,7 +29659,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1010" t="n">
         <v>4800</v>
@@ -29688,7 +29688,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1011" t="n">
         <v>900</v>
@@ -29862,7 +29862,7 @@
         <v>1.5</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1017" t="n">
         <v>26400</v>
@@ -30036,7 +30036,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.30467748641968</v>
+        <v>1.30467760562897</v>
       </c>
       <c r="H1023" t="n">
         <v>300</v>
@@ -30181,7 +30181,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.3317643404007</v>
+        <v>1.33176422119141</v>
       </c>
       <c r="H1028" t="n">
         <v>19200</v>
@@ -30268,7 +30268,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H1031" t="n">
         <v>16200</v>
@@ -30413,7 +30413,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1036" t="n">
         <v>27900</v>
@@ -30442,7 +30442,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1037" t="n">
         <v>2100</v>
@@ -30616,7 +30616,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1043" t="n">
         <v>4800</v>
@@ -31109,7 +31109,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1060" t="n">
         <v>5700</v>
@@ -31196,7 +31196,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.34079313278198</v>
+        <v>1.34079325199127</v>
       </c>
       <c r="H1063" t="n">
         <v>6000</v>
@@ -31254,7 +31254,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.27307629585266</v>
+        <v>1.27307617664337</v>
       </c>
       <c r="H1065" t="n">
         <v>64500</v>
@@ -31283,7 +31283,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.29113399982452</v>
+        <v>1.29113411903381</v>
       </c>
       <c r="H1066" t="n">
         <v>2700</v>
@@ -31341,7 +31341,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.2595329284668</v>
+        <v>1.25953304767609</v>
       </c>
       <c r="H1068" t="n">
         <v>2100</v>
@@ -31370,7 +31370,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.2595329284668</v>
+        <v>1.25953304767609</v>
       </c>
       <c r="H1069" t="n">
         <v>600</v>
@@ -31399,7 +31399,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.2595329284668</v>
+        <v>1.25953304767609</v>
       </c>
       <c r="H1070" t="n">
         <v>600</v>
@@ -31428,7 +31428,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.23244631290436</v>
+        <v>1.23244619369507</v>
       </c>
       <c r="H1071" t="n">
         <v>6900</v>
@@ -31602,7 +31602,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.2956485748291</v>
+        <v>1.29564845561981</v>
       </c>
       <c r="H1077" t="n">
         <v>52800</v>
@@ -31660,7 +31660,7 @@
         <v>1.5</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1079" t="n">
         <v>71400</v>
@@ -31747,7 +31747,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H1082" t="n">
         <v>25500</v>
@@ -31805,7 +31805,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1084" t="n">
         <v>15300</v>
@@ -31834,7 +31834,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1085" t="n">
         <v>9300</v>
@@ -31892,7 +31892,7 @@
         <v>1.75</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1087" t="n">
         <v>179400</v>
@@ -32008,7 +32008,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1091" t="n">
         <v>9000</v>
@@ -32066,7 +32066,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1093" t="n">
         <v>3600</v>
@@ -32095,7 +32095,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1094" t="n">
         <v>21000</v>
@@ -32182,7 +32182,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.47622692584991</v>
+        <v>1.47622680664062</v>
       </c>
       <c r="H1097" t="n">
         <v>1800</v>
@@ -32356,7 +32356,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1103" t="n">
         <v>9300</v>
@@ -32501,7 +32501,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.47622692584991</v>
+        <v>1.47622680664062</v>
       </c>
       <c r="H1108" t="n">
         <v>3600</v>
@@ -32530,7 +32530,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1109" t="n">
         <v>3300</v>
@@ -32617,7 +32617,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.35885095596313</v>
+        <v>1.35885083675385</v>
       </c>
       <c r="H1112" t="n">
         <v>9600</v>
@@ -32675,7 +32675,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1114" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1114" t="n">
         <v>11100</v>
@@ -33023,7 +33023,7 @@
         <v>1.5</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1126" t="n">
         <v>65700</v>
@@ -33081,7 +33081,7 @@
         <v>1.5</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1128" t="n">
         <v>42600</v>
@@ -33313,7 +33313,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H1136" t="n">
         <v>13200</v>
@@ -33429,7 +33429,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H1140" t="n">
         <v>6300</v>
@@ -33458,7 +33458,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1141" t="n">
         <v>5400</v>
@@ -33661,7 +33661,7 @@
         <v>1.5</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1148" t="n">
         <v>21900</v>
@@ -33922,7 +33922,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1157" t="n">
         <v>14100</v>
@@ -34763,7 +34763,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1186" t="n">
         <v>38400</v>
@@ -35024,7 +35024,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1195" t="n">
         <v>6600</v>
@@ -35053,7 +35053,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1196" t="n">
         <v>0</v>
@@ -35082,7 +35082,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1197" t="n">
         <v>600</v>
@@ -35111,7 +35111,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1198" t="n">
         <v>11400</v>
@@ -35140,7 +35140,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1199" t="n">
         <v>0</v>
@@ -35256,7 +35256,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1203" t="n">
         <v>2700</v>
@@ -35517,7 +35517,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.47622692584991</v>
+        <v>1.47622680664062</v>
       </c>
       <c r="H1212" t="n">
         <v>600</v>
@@ -35546,7 +35546,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1213" t="n">
         <v>23400</v>
@@ -35633,7 +35633,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1216" t="n">
         <v>6600</v>
@@ -35981,7 +35981,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1228" t="n">
         <v>21900</v>
@@ -36358,7 +36358,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1241" t="n">
         <v>2700</v>
@@ -36387,7 +36387,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.52137136459351</v>
+        <v>1.52137124538422</v>
       </c>
       <c r="H1242" t="n">
         <v>10500</v>
@@ -36677,7 +36677,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H1252" t="n">
         <v>8700</v>
@@ -36706,7 +36706,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H1253" t="n">
         <v>11100</v>
@@ -37025,7 +37025,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.47622692584991</v>
+        <v>1.47622680664062</v>
       </c>
       <c r="H1264" t="n">
         <v>6000</v>
@@ -37054,7 +37054,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.47622692584991</v>
+        <v>1.47622680664062</v>
       </c>
       <c r="H1265" t="n">
         <v>0</v>
@@ -37344,7 +37344,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1275" t="n">
         <v>4200</v>
@@ -37373,7 +37373,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1276" t="n">
         <v>8100</v>
@@ -37547,7 +37547,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1282" t="n">
         <v>4500</v>
@@ -37576,7 +37576,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1283" t="n">
         <v>0</v>
@@ -37634,7 +37634,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H1285" t="n">
         <v>28500</v>
@@ -37924,7 +37924,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1295" t="n">
         <v>3000</v>
@@ -37953,7 +37953,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1296" t="n">
         <v>1500</v>
@@ -37982,7 +37982,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H1297" t="n">
         <v>2400</v>
@@ -38011,7 +38011,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1298" t="n">
         <v>7200</v>
@@ -38069,7 +38069,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1300" t="n">
         <v>19800</v>
@@ -38098,7 +38098,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1301" t="n">
         <v>0</v>
@@ -38156,7 +38156,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1303" t="n">
         <v>1500</v>
@@ -38185,7 +38185,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1304" t="n">
         <v>7500</v>
@@ -38272,7 +38272,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1307" t="n">
         <v>8400</v>
@@ -38504,7 +38504,7 @@
         <v>1.5</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1315" t="n">
         <v>4200</v>
@@ -38794,7 +38794,7 @@
         <v>1.5</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1325" t="n">
         <v>12600</v>
@@ -38823,7 +38823,7 @@
         <v>1.5</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1326" t="n">
         <v>9300</v>
@@ -38852,7 +38852,7 @@
         <v>1.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1327" t="n">
         <v>10500</v>
@@ -38910,7 +38910,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.34530770778656</v>
+        <v>1.34530758857727</v>
       </c>
       <c r="H1329" t="n">
         <v>14400</v>
@@ -39055,7 +39055,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.35885095596313</v>
+        <v>1.35885083675385</v>
       </c>
       <c r="H1334" t="n">
         <v>31200</v>
@@ -39142,7 +39142,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.34982204437256</v>
+        <v>1.34982216358185</v>
       </c>
       <c r="H1337" t="n">
         <v>60300</v>
@@ -39374,7 +39374,7 @@
         <v>1.5</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1345" t="n">
         <v>22800</v>
@@ -39722,7 +39722,7 @@
         <v>1.5</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1357" t="n">
         <v>8100</v>
@@ -39751,7 +39751,7 @@
         <v>1.5</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1358" t="n">
         <v>3000</v>
@@ -40157,7 +40157,7 @@
         <v>1.5</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1372" t="n">
         <v>432000</v>
@@ -40186,7 +40186,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1373" t="n">
         <v>41100</v>
@@ -40215,7 +40215,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1374" t="n">
         <v>17400</v>
@@ -40244,7 +40244,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1375" t="n">
         <v>1500</v>
@@ -40273,7 +40273,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1376" t="n">
         <v>16500</v>
@@ -40302,7 +40302,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1377" t="n">
         <v>12300</v>
@@ -40331,7 +40331,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1378" t="n">
         <v>9300</v>
@@ -40360,7 +40360,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1379" t="n">
         <v>10200</v>
@@ -40389,7 +40389,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1380" t="n">
         <v>0</v>
@@ -40650,7 +40650,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1389" t="n">
         <v>13500</v>
@@ -40679,7 +40679,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1390" t="n">
         <v>0</v>
@@ -40737,7 +40737,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.64777612686157</v>
+        <v>1.64777624607086</v>
       </c>
       <c r="H1392" t="n">
         <v>238200</v>
@@ -40766,7 +40766,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1393" t="n">
         <v>120900</v>
@@ -40853,7 +40853,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H1396" t="n">
         <v>66000</v>
@@ -40940,7 +40940,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H1399" t="n">
         <v>21600</v>
@@ -41172,7 +41172,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H1407" t="n">
         <v>6600</v>
@@ -41201,7 +41201,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1408" t="n">
         <v>18000</v>
@@ -41288,7 +41288,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H1411" t="n">
         <v>9000</v>
@@ -41375,7 +41375,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.57554471492767</v>
+        <v>1.57554483413696</v>
       </c>
       <c r="H1414" t="n">
         <v>6600</v>
@@ -41404,7 +41404,7 @@
         <v>1.75</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1415" t="n">
         <v>1200</v>
@@ -41462,7 +41462,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1417" t="n">
         <v>17700</v>
@@ -41549,7 +41549,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1420" t="n">
         <v>6000</v>
@@ -41578,7 +41578,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1421" t="n">
         <v>16200</v>
@@ -41607,7 +41607,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1422" t="n">
         <v>28500</v>
@@ -41636,7 +41636,7 @@
         <v>1.75</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1423" t="n">
         <v>13500</v>
@@ -41665,7 +41665,7 @@
         <v>1.75</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1424" t="n">
         <v>0</v>
@@ -41694,7 +41694,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1425" t="n">
         <v>17400</v>
@@ -41723,7 +41723,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1426" t="n">
         <v>4800</v>
@@ -41752,7 +41752,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1427" t="n">
         <v>19500</v>
@@ -41839,7 +41839,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1430" t="n">
         <v>12300</v>
@@ -41868,7 +41868,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1431" t="n">
         <v>5100</v>
@@ -41897,7 +41897,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.57554471492767</v>
+        <v>1.57554483413696</v>
       </c>
       <c r="H1432" t="n">
         <v>12000</v>
@@ -41926,7 +41926,7 @@
         <v>1.75</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1433" t="n">
         <v>20100</v>
@@ -42071,7 +42071,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1438" t="n">
         <v>16800</v>
@@ -42100,7 +42100,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1439" t="n">
         <v>10800</v>
@@ -42187,7 +42187,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1442" t="n">
         <v>900</v>
@@ -42332,7 +42332,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1447" t="n">
         <v>31500</v>
@@ -42361,7 +42361,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1448" t="n">
         <v>49200</v>
@@ -42419,7 +42419,7 @@
         <v>1.75</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1450" t="n">
         <v>17100</v>
@@ -42477,7 +42477,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1452" t="n">
         <v>6600</v>
@@ -42506,7 +42506,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1453" t="n">
         <v>0</v>
@@ -42535,7 +42535,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1454" t="n">
         <v>3300</v>
@@ -42564,7 +42564,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1455" t="n">
         <v>300</v>
@@ -42883,7 +42883,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1466" t="n">
         <v>4200</v>
@@ -42912,7 +42912,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1467" t="n">
         <v>3000</v>
@@ -43028,7 +43028,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H1471" t="n">
         <v>23400</v>
@@ -43115,7 +43115,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1474" t="n">
         <v>50700</v>
@@ -43173,7 +43173,7 @@
         <v>1.75</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1476" t="n">
         <v>4500</v>
@@ -43231,7 +43231,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1478" t="n">
         <v>32700</v>
@@ -43260,7 +43260,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1479" t="n">
         <v>0</v>
@@ -43318,7 +43318,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1481" t="n">
         <v>6300</v>
@@ -43550,7 +43550,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1489" t="n">
-        <v>1.52137136459351</v>
+        <v>1.52137124538422</v>
       </c>
       <c r="H1489" t="n">
         <v>18300</v>
@@ -43695,7 +43695,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1494" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1494" t="n">
         <v>8100</v>
@@ -43753,7 +43753,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1496" t="n">
         <v>3300</v>
@@ -43782,7 +43782,7 @@
         <v>1.75</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1497" t="n">
         <v>22800</v>
@@ -43840,7 +43840,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1499" t="n">
         <v>3000</v>
@@ -43869,7 +43869,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1500" t="n">
         <v>0</v>
@@ -43956,7 +43956,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1503" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1503" t="n">
         <v>7500</v>
@@ -44043,7 +44043,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H1506" t="n">
         <v>10200</v>
@@ -44101,7 +44101,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H1508" t="n">
         <v>2700</v>
@@ -44130,7 +44130,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H1509" t="n">
         <v>11100</v>
@@ -44246,7 +44246,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.57554471492767</v>
+        <v>1.57554483413696</v>
       </c>
       <c r="H1513" t="n">
         <v>1200</v>
@@ -44275,7 +44275,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.56651592254639</v>
+        <v>1.56651604175568</v>
       </c>
       <c r="H1514" t="n">
         <v>3900</v>
@@ -44304,7 +44304,7 @@
         <v>1.75</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1515" t="n">
         <v>900</v>
@@ -44362,7 +44362,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1517" t="n">
         <v>10200</v>
@@ -44391,7 +44391,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1518" t="n">
-        <v>1.57554471492767</v>
+        <v>1.57554483413696</v>
       </c>
       <c r="H1518" t="n">
         <v>5400</v>
@@ -44478,7 +44478,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1521" t="n">
         <v>11100</v>
@@ -44507,7 +44507,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1522" t="n">
         <v>4200</v>
@@ -44565,7 +44565,7 @@
         <v>1.75</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1524" t="n">
         <v>44400</v>
@@ -44594,7 +44594,7 @@
         <v>1.75</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1525" t="n">
         <v>0</v>
@@ -44623,7 +44623,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1526" t="n">
         <v>1800</v>
@@ -44652,7 +44652,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1527" t="n">
         <v>2700</v>
@@ -44681,7 +44681,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1528" t="n">
         <v>12600</v>
@@ -44710,7 +44710,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1529" t="n">
         <v>7500</v>
@@ -44739,7 +44739,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1530" t="n">
         <v>5100</v>
@@ -44768,7 +44768,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1531" t="n">
         <v>0</v>
@@ -44797,7 +44797,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1532" t="n">
         <v>600</v>
@@ -44855,7 +44855,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.71097850799561</v>
+        <v>1.71097838878632</v>
       </c>
       <c r="H1534" t="n">
         <v>162900</v>
@@ -44942,7 +44942,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H1537" t="n">
         <v>64800</v>
@@ -45058,7 +45058,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1541" t="n">
-        <v>1.64777612686157</v>
+        <v>1.64777624607086</v>
       </c>
       <c r="H1541" t="n">
         <v>2700</v>
@@ -45087,7 +45087,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1542" t="n">
         <v>12600</v>
@@ -45116,7 +45116,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H1543" t="n">
         <v>51000</v>
@@ -45145,7 +45145,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1544" t="n">
         <v>6300</v>
@@ -45174,7 +45174,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1545" t="n">
         <v>600</v>
@@ -45203,7 +45203,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1546" t="n">
-        <v>1.62068939208984</v>
+        <v>1.62068927288055</v>
       </c>
       <c r="H1546" t="n">
         <v>3000</v>
@@ -45232,7 +45232,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1547" t="n">
         <v>6300</v>
@@ -45261,7 +45261,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1548" t="n">
         <v>4200</v>
@@ -45290,7 +45290,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1549" t="n">
         <v>10500</v>
@@ -45319,7 +45319,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1550" t="n">
-        <v>1.66583395004272</v>
+        <v>1.66583383083344</v>
       </c>
       <c r="H1550" t="n">
         <v>5100</v>
@@ -45348,7 +45348,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1551" t="n">
         <v>27000</v>
@@ -45377,7 +45377,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1552" t="n">
         <v>6300</v>
@@ -45464,7 +45464,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1555" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H1555" t="n">
         <v>7800</v>
@@ -45522,7 +45522,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H1557" t="n">
         <v>126300</v>
@@ -45638,7 +45638,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H1561" t="n">
         <v>26100</v>
@@ -45667,7 +45667,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1562" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H1562" t="n">
         <v>9900</v>
@@ -45696,7 +45696,7 @@
         <v>1.875</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.69292056560516</v>
+        <v>1.69292068481445</v>
       </c>
       <c r="H1563" t="n">
         <v>3000</v>
@@ -45725,7 +45725,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1564" t="n">
         <v>8700</v>
@@ -45754,7 +45754,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1565" t="n">
-        <v>1.66583395004272</v>
+        <v>1.66583383083344</v>
       </c>
       <c r="H1565" t="n">
         <v>8400</v>
@@ -45812,7 +45812,7 @@
         <v>1.75</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1567" t="n">
         <v>38700</v>
@@ -45957,7 +45957,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.64777612686157</v>
+        <v>1.64777624607086</v>
       </c>
       <c r="H1572" t="n">
         <v>13200</v>
@@ -45986,7 +45986,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1573" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1573" t="n">
         <v>8700</v>
@@ -46131,7 +46131,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H1578" t="n">
         <v>3300</v>
@@ -46218,7 +46218,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H1581" t="n">
         <v>8400</v>
@@ -46276,7 +46276,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H1583" t="n">
         <v>12600</v>
@@ -46305,7 +46305,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H1584" t="n">
         <v>7200</v>
@@ -46363,7 +46363,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1586" t="n">
         <v>7500</v>
@@ -46450,7 +46450,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.62068939208984</v>
+        <v>1.62068927288055</v>
       </c>
       <c r="H1589" t="n">
         <v>18900</v>
@@ -46508,7 +46508,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.62068939208984</v>
+        <v>1.62068927288055</v>
       </c>
       <c r="H1591" t="n">
         <v>11400</v>
@@ -46624,7 +46624,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H1595" t="n">
         <v>1500</v>
@@ -46740,7 +46740,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.84189772605896</v>
+        <v>1.84189760684967</v>
       </c>
       <c r="H1599" t="n">
         <v>343200</v>
@@ -46827,7 +46827,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.04956269264221</v>
+        <v>2.04956245422363</v>
       </c>
       <c r="H1602" t="n">
         <v>380700</v>
@@ -46856,7 +46856,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.12179398536682</v>
+        <v>2.12179350852966</v>
       </c>
       <c r="H1603" t="n">
         <v>147900</v>
@@ -46914,7 +46914,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.12179398536682</v>
+        <v>2.12179350852966</v>
       </c>
       <c r="H1605" t="n">
         <v>38100</v>
@@ -46943,7 +46943,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1606" t="n">
-        <v>2.05859160423279</v>
+        <v>2.05859136581421</v>
       </c>
       <c r="H1606" t="n">
         <v>98400</v>
@@ -47030,7 +47030,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.04956269264221</v>
+        <v>2.04956245422363</v>
       </c>
       <c r="H1609" t="n">
         <v>36000</v>
@@ -47088,7 +47088,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1611" t="n">
-        <v>1.99538910388947</v>
+        <v>1.99538922309875</v>
       </c>
       <c r="H1611" t="n">
         <v>20700</v>
@@ -47175,7 +47175,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H1614" t="n">
         <v>6300</v>
@@ -47233,7 +47233,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.01344680786133</v>
+        <v>2.01344704627991</v>
       </c>
       <c r="H1616" t="n">
         <v>28200</v>
@@ -47349,7 +47349,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.01344680786133</v>
+        <v>2.01344704627991</v>
       </c>
       <c r="H1620" t="n">
         <v>57900</v>
@@ -47378,7 +47378,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.00441789627075</v>
+        <v>2.00441813468933</v>
       </c>
       <c r="H1621" t="n">
         <v>34800</v>
@@ -47436,7 +47436,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1623" t="n">
-        <v>2.00441789627075</v>
+        <v>2.00441813468933</v>
       </c>
       <c r="H1623" t="n">
         <v>6000</v>
@@ -47465,7 +47465,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.01344680786133</v>
+        <v>2.01344704627991</v>
       </c>
       <c r="H1624" t="n">
         <v>25500</v>
@@ -47494,7 +47494,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1625" t="n">
-        <v>2.00441789627075</v>
+        <v>2.00441813468933</v>
       </c>
       <c r="H1625" t="n">
         <v>14100</v>
@@ -47523,7 +47523,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.10373592376709</v>
+        <v>2.10373616218567</v>
       </c>
       <c r="H1626" t="n">
         <v>31800</v>
@@ -47552,7 +47552,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H1627" t="n">
         <v>192000</v>
@@ -47668,7 +47668,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1631" t="n">
         <v>23100</v>
@@ -47697,7 +47697,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.5172746181488</v>
+        <v>2.51727485656738</v>
       </c>
       <c r="H1632" t="n">
         <v>41100</v>
@@ -47726,7 +47726,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.59213781356812</v>
+        <v>2.59213805198669</v>
       </c>
       <c r="H1633" t="n">
         <v>87600</v>
@@ -47871,7 +47871,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.13489580154419</v>
+        <v>3.13489603996277</v>
       </c>
       <c r="H1638" t="n">
         <v>112200</v>
@@ -47987,7 +47987,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1642" t="n">
         <v>209700</v>
@@ -48074,7 +48074,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.87287497520447</v>
+        <v>2.87287473678589</v>
       </c>
       <c r="H1645" t="n">
         <v>21300</v>
@@ -48190,7 +48190,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1649" t="n">
         <v>22800</v>
@@ -48248,7 +48248,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1651" t="n">
         <v>10500</v>
@@ -48306,7 +48306,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1653" t="n">
         <v>4800</v>
@@ -48364,7 +48364,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1655" t="n">
         <v>9000</v>
@@ -48451,7 +48451,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1658" t="n">
         <v>3900</v>
@@ -48567,7 +48567,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1662" t="n">
         <v>5400</v>
@@ -48625,7 +48625,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1664" t="n">
         <v>2400</v>
@@ -48654,7 +48654,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1665" t="n">
         <v>4500</v>
@@ -48683,7 +48683,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1666" t="n">
         <v>3900</v>
@@ -48712,7 +48712,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1667" t="n">
         <v>13800</v>
@@ -48741,7 +48741,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1668" t="n">
         <v>12600</v>
@@ -48915,7 +48915,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1674" t="n">
         <v>5700</v>
@@ -48973,7 +48973,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.81672763824463</v>
+        <v>2.81672739982605</v>
       </c>
       <c r="H1676" t="n">
         <v>5400</v>
@@ -49408,7 +49408,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1691" t="n">
         <v>3300</v>
@@ -49553,7 +49553,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1696" t="n">
         <v>7800</v>
@@ -49582,7 +49582,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1697" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1697" t="n">
         <v>16800</v>
@@ -49727,7 +49727,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.87287497520447</v>
+        <v>2.87287473678589</v>
       </c>
       <c r="H1702" t="n">
         <v>16500</v>
@@ -49843,7 +49843,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.92902255058289</v>
+        <v>2.92902231216431</v>
       </c>
       <c r="H1706" t="n">
         <v>13800</v>
@@ -49930,7 +49930,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1709" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1709" t="n">
         <v>300</v>
@@ -49959,7 +49959,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1710" t="n">
         <v>600</v>
@@ -49988,7 +49988,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.87287497520447</v>
+        <v>2.87287473678589</v>
       </c>
       <c r="H1711" t="n">
         <v>28800</v>
@@ -50075,7 +50075,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1714" t="n">
         <v>5100</v>
@@ -50249,7 +50249,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.92902255058289</v>
+        <v>2.92902231216431</v>
       </c>
       <c r="H1720" t="n">
         <v>29100</v>
@@ -50336,7 +50336,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.92902255058289</v>
+        <v>2.92902231216431</v>
       </c>
       <c r="H1723" t="n">
         <v>26700</v>
@@ -50597,7 +50597,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1732" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1732" t="n">
         <v>48000</v>
@@ -50626,7 +50626,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1733" t="n">
         <v>64500</v>
@@ -50771,7 +50771,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1738" t="n">
-        <v>2.35819053649902</v>
+        <v>2.35819029808044</v>
       </c>
       <c r="H1738" t="n">
         <v>38400</v>
@@ -50800,7 +50800,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.35819053649902</v>
+        <v>2.35819029808044</v>
       </c>
       <c r="H1739" t="n">
         <v>18300</v>
@@ -50829,7 +50829,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.35819053649902</v>
+        <v>2.35819029808044</v>
       </c>
       <c r="H1740" t="n">
         <v>19200</v>
@@ -50887,7 +50887,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.36754846572876</v>
+        <v>2.36754822731018</v>
       </c>
       <c r="H1742" t="n">
         <v>5100</v>
@@ -50974,7 +50974,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H1745" t="n">
         <v>174000</v>
@@ -51177,7 +51177,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.47048544883728</v>
+        <v>2.4704852104187</v>
       </c>
       <c r="H1752" t="n">
         <v>7500</v>
@@ -51380,7 +51380,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1759" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1759" t="n">
         <v>600</v>
@@ -51409,7 +51409,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1760" t="n">
         <v>9000</v>
@@ -51438,7 +51438,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1761" t="n">
         <v>6600</v>
@@ -51641,7 +51641,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1768" t="n">
         <v>30000</v>
@@ -51844,7 +51844,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.64828515052795</v>
+        <v>2.64828538894653</v>
       </c>
       <c r="H1775" t="n">
         <v>13200</v>
@@ -51960,7 +51960,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.65764331817627</v>
+        <v>2.65764307975769</v>
       </c>
       <c r="H1779" t="n">
         <v>22500</v>
@@ -51989,7 +51989,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1780" t="n">
         <v>26700</v>
@@ -52047,7 +52047,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1782" t="n">
         <v>14100</v>
@@ -52076,7 +52076,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1783" t="n">
         <v>46200</v>
@@ -52105,7 +52105,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1784" t="n">
         <v>15000</v>
@@ -52134,7 +52134,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.69507479667664</v>
+        <v>2.69507503509521</v>
       </c>
       <c r="H1785" t="n">
         <v>35700</v>
@@ -52163,7 +52163,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1786" t="n">
         <v>19800</v>
@@ -52192,7 +52192,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1787" t="n">
-        <v>2.69507479667664</v>
+        <v>2.69507503509521</v>
       </c>
       <c r="H1787" t="n">
         <v>7200</v>
@@ -52221,7 +52221,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1788" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1788" t="n">
         <v>4500</v>
@@ -52308,7 +52308,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1791" t="n">
         <v>3300</v>
@@ -52366,7 +52366,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1793" t="n">
         <v>7200</v>
@@ -52453,7 +52453,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1796" t="n">
         <v>7800</v>
@@ -52482,7 +52482,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1797" t="n">
         <v>600</v>
@@ -52511,7 +52511,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1798" t="n">
         <v>10500</v>
@@ -52569,7 +52569,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1800" t="n">
         <v>34500</v>
@@ -52627,7 +52627,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1802" t="n">
         <v>8100</v>
@@ -52656,7 +52656,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1803" t="n">
         <v>0</v>
@@ -52685,7 +52685,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1804" t="n">
         <v>2100</v>
@@ -52743,7 +52743,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1806" t="n">
         <v>13500</v>
@@ -52772,7 +52772,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.64828515052795</v>
+        <v>2.64828538894653</v>
       </c>
       <c r="H1807" t="n">
         <v>81600</v>
@@ -52801,7 +52801,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.64828515052795</v>
+        <v>2.64828538894653</v>
       </c>
       <c r="H1808" t="n">
         <v>0</v>
@@ -52830,7 +52830,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1809" t="n">
         <v>12000</v>
@@ -52859,7 +52859,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1810" t="n">
         <v>300</v>
@@ -53004,7 +53004,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1815" t="n">
         <v>5100</v>
@@ -53062,7 +53062,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1817" t="n">
         <v>4800</v>
@@ -53091,7 +53091,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1818" t="n">
         <v>4800</v>
@@ -53323,7 +53323,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.69507479667664</v>
+        <v>2.69507503509521</v>
       </c>
       <c r="H1826" t="n">
         <v>9900</v>
@@ -53352,7 +53352,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1827" t="n">
         <v>6300</v>
@@ -53381,7 +53381,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.65764331817627</v>
+        <v>2.65764307975769</v>
       </c>
       <c r="H1828" t="n">
         <v>6300</v>
@@ -53816,7 +53816,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.19104337692261</v>
+        <v>3.19104361534119</v>
       </c>
       <c r="H1843" t="n">
         <v>98100</v>
@@ -53961,7 +53961,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.29398012161255</v>
+        <v>3.29398036003113</v>
       </c>
       <c r="H1848" t="n">
         <v>28200</v>
@@ -53990,7 +53990,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.29398012161255</v>
+        <v>3.29398036003113</v>
       </c>
       <c r="H1849" t="n">
         <v>10800</v>
@@ -54077,7 +54077,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.31269598007202</v>
+        <v>3.3126962184906</v>
       </c>
       <c r="H1852" t="n">
         <v>62700</v>
@@ -54106,7 +54106,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.31269598007202</v>
+        <v>3.3126962184906</v>
       </c>
       <c r="H1853" t="n">
         <v>15900</v>
@@ -54338,7 +54338,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.54664373397827</v>
+        <v>3.54664349555969</v>
       </c>
       <c r="H1861" t="n">
         <v>3600</v>
@@ -54599,7 +54599,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1870" t="n">
-        <v>3.65893840789795</v>
+        <v>3.65893864631653</v>
       </c>
       <c r="H1870" t="n">
         <v>20400</v>
@@ -54802,7 +54802,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1877" t="n">
-        <v>3.69636988639832</v>
+        <v>3.69637012481689</v>
       </c>
       <c r="H1877" t="n">
         <v>2100</v>
@@ -54860,7 +54860,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1879" t="n">
-        <v>3.75251746177673</v>
+        <v>3.75251770019531</v>
       </c>
       <c r="H1879" t="n">
         <v>9900</v>
@@ -54918,7 +54918,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1881" t="n">
-        <v>3.75251746177673</v>
+        <v>3.75251770019531</v>
       </c>
       <c r="H1881" t="n">
         <v>15900</v>
@@ -65480,6 +65480,64 @@
         <v>8700</v>
       </c>
       <c r="I2245" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="A2246" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2246" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2246" t="n">
+        <v>4.32999992370605</v>
+      </c>
+      <c r="D2246" t="n">
+        <v>4.32999992370605</v>
+      </c>
+      <c r="E2246" t="n">
+        <v>4.32999992370605</v>
+      </c>
+      <c r="F2246" t="n">
+        <v>4.32999992370605</v>
+      </c>
+      <c r="G2246" t="n">
+        <v>4.32999992370605</v>
+      </c>
+      <c r="H2246" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2246" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2247" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2247" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="D2247" t="n">
+        <v>4.32999992370605</v>
+      </c>
+      <c r="E2247" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="F2247" t="n">
+        <v>4.32000017166138</v>
+      </c>
+      <c r="G2247" t="n">
+        <v>4.32000017166138</v>
+      </c>
+      <c r="H2247" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I2247" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -65541,6 +65541,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2248">
+      <c r="A2248" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2248" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2248" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="D2248" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E2248" t="n">
+        <v>4.19999980926514</v>
+      </c>
+      <c r="F2248" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="G2248" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="H2248" t="n">
+        <v>5400</v>
+      </c>
+      <c r="I2248" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H2" t="n">
         <v>326100</v>
@@ -514,7 +514,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H5" t="n">
         <v>14700</v>
@@ -630,7 +630,7 @@
         <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H9" t="n">
         <v>1200</v>
@@ -833,7 +833,7 @@
         <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H16" t="n">
         <v>600</v>
@@ -862,7 +862,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G17" t="n">
-        <v>3.59892344474792</v>
+        <v>3.5989236831665</v>
       </c>
       <c r="H17" t="n">
         <v>81900</v>
@@ -891,7 +891,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G18" t="n">
-        <v>3.65490245819092</v>
+        <v>3.6549026966095</v>
       </c>
       <c r="H18" t="n">
         <v>28200</v>
@@ -920,7 +920,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G19" t="n">
-        <v>3.65851449966431</v>
+        <v>3.65851426124573</v>
       </c>
       <c r="H19" t="n">
         <v>19500</v>
@@ -978,7 +978,7 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H21" t="n">
         <v>2100</v>
@@ -1036,7 +1036,7 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H23" t="n">
         <v>28500</v>
@@ -1065,7 +1065,7 @@
         <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G27" t="n">
-        <v>3.62059307098389</v>
+        <v>3.62059330940247</v>
       </c>
       <c r="H27" t="n">
         <v>1800</v>
@@ -1181,7 +1181,7 @@
         <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H28" t="n">
         <v>11400</v>
@@ -1210,7 +1210,7 @@
         <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H29" t="n">
         <v>4800</v>
@@ -1239,7 +1239,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G30" t="n">
-        <v>3.57544827461243</v>
+        <v>3.57544851303101</v>
       </c>
       <c r="H30" t="n">
         <v>300</v>
@@ -1268,7 +1268,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>3.57544827461243</v>
+        <v>3.57544851303101</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G37" t="n">
-        <v>3.53030395507812</v>
+        <v>3.5303041934967</v>
       </c>
       <c r="H37" t="n">
         <v>10200</v>
@@ -1790,7 +1790,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>3.57544827461243</v>
+        <v>3.57544851303101</v>
       </c>
       <c r="H49" t="n">
         <v>1800</v>
@@ -2196,7 +2196,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>3.33166766166687</v>
+        <v>3.33166790008545</v>
       </c>
       <c r="H63" t="n">
         <v>600</v>
@@ -2225,7 +2225,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G64" t="n">
-        <v>3.44001483917236</v>
+        <v>3.44001460075378</v>
       </c>
       <c r="H64" t="n">
         <v>900</v>
@@ -3414,7 +3414,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>3.35875463485718</v>
+        <v>3.3587543964386</v>
       </c>
       <c r="H105" t="n">
         <v>900</v>
@@ -3472,7 +3472,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G107" t="n">
-        <v>3.22332096099854</v>
+        <v>3.22332072257996</v>
       </c>
       <c r="H107" t="n">
         <v>6300</v>
@@ -3559,7 +3559,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555201530457</v>
       </c>
       <c r="H110" t="n">
         <v>8100</v>
@@ -3588,7 +3588,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G111" t="n">
-        <v>3.21429204940796</v>
+        <v>3.21429181098938</v>
       </c>
       <c r="H111" t="n">
         <v>30300</v>
@@ -3617,7 +3617,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>3.20526313781738</v>
+        <v>3.2052628993988</v>
       </c>
       <c r="H112" t="n">
         <v>900</v>
@@ -3704,7 +3704,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>3.04274249076843</v>
+        <v>3.04274272918701</v>
       </c>
       <c r="H115" t="n">
         <v>600</v>
@@ -3733,7 +3733,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>3.04274249076843</v>
+        <v>3.04274272918701</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G121" t="n">
-        <v>3.13303208351135</v>
+        <v>3.13303184509277</v>
       </c>
       <c r="H121" t="n">
         <v>30600</v>
@@ -4052,7 +4052,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G127" t="n">
-        <v>3.45807266235352</v>
+        <v>3.45807242393494</v>
       </c>
       <c r="H127" t="n">
         <v>30600</v>
@@ -4081,7 +4081,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G128" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H128" t="n">
         <v>600</v>
@@ -4226,7 +4226,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G133" t="n">
-        <v>3.33166766166687</v>
+        <v>3.33166790008545</v>
       </c>
       <c r="H133" t="n">
         <v>300</v>
@@ -4255,7 +4255,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>3.33166766166687</v>
+        <v>3.33166790008545</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G135" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555201530457</v>
       </c>
       <c r="H135" t="n">
         <v>300</v>
@@ -4313,7 +4313,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555201530457</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G149" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555201530457</v>
       </c>
       <c r="H149" t="n">
         <v>3900</v>
@@ -4719,7 +4719,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555201530457</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G151" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555201530457</v>
       </c>
       <c r="H151" t="n">
         <v>900</v>
@@ -5183,7 +5183,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G166" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H166" t="n">
         <v>2400</v>
@@ -5212,7 +5212,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G167" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G168" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G169" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G171" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G172" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G173" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G174" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G175" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G176" t="n">
-        <v>3.24137854576111</v>
+        <v>3.24137878417969</v>
       </c>
       <c r="H176" t="n">
         <v>2400</v>
@@ -5502,7 +5502,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G177" t="n">
-        <v>3.39487028121948</v>
+        <v>3.3948700428009</v>
       </c>
       <c r="H177" t="n">
         <v>2400</v>
@@ -5763,7 +5763,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G186" t="n">
-        <v>3.21429204940796</v>
+        <v>3.21429181098938</v>
       </c>
       <c r="H186" t="n">
         <v>60000</v>
@@ -5821,7 +5821,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G188" t="n">
-        <v>3.21429204940796</v>
+        <v>3.21429181098938</v>
       </c>
       <c r="H188" t="n">
         <v>600</v>
@@ -5850,7 +5850,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>3.21429204940796</v>
+        <v>3.21429181098938</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G190" t="n">
-        <v>3.21429204940796</v>
+        <v>3.21429181098938</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>3.5</v>
       </c>
       <c r="G191" t="n">
-        <v>3.16011834144592</v>
+        <v>3.1601185798645</v>
       </c>
       <c r="H191" t="n">
         <v>300</v>
@@ -5937,7 +5937,7 @@
         <v>3.5</v>
       </c>
       <c r="G192" t="n">
-        <v>3.16011834144592</v>
+        <v>3.1601185798645</v>
       </c>
       <c r="H192" t="n">
         <v>2400</v>
@@ -6256,7 +6256,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G203" t="n">
-        <v>3.09691619873047</v>
+        <v>3.09691643714905</v>
       </c>
       <c r="H203" t="n">
         <v>900</v>
@@ -6401,7 +6401,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G208" t="n">
-        <v>3.05177187919617</v>
+        <v>3.05177164077759</v>
       </c>
       <c r="H208" t="n">
         <v>6600</v>
@@ -6604,7 +6604,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G215" t="n">
-        <v>2.87119364738464</v>
+        <v>2.87119340896606</v>
       </c>
       <c r="H215" t="n">
         <v>2100</v>
@@ -6633,7 +6633,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G216" t="n">
-        <v>2.87119364738464</v>
+        <v>2.87119340896606</v>
       </c>
       <c r="H216" t="n">
         <v>21000</v>
@@ -6662,7 +6662,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G217" t="n">
-        <v>2.87119364738464</v>
+        <v>2.87119340896606</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H222" t="n">
         <v>3900</v>
@@ -6836,7 +6836,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G223" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G225" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H225" t="n">
         <v>1200</v>
@@ -6923,7 +6923,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G226" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G227" t="n">
-        <v>2.63644170761108</v>
+        <v>2.63644194602966</v>
       </c>
       <c r="H227" t="n">
         <v>6000</v>
@@ -6981,7 +6981,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H228" t="n">
         <v>2700</v>
@@ -7010,7 +7010,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G230" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G231" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G232" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G236" t="n">
-        <v>2.51003694534302</v>
+        <v>2.5100371837616</v>
       </c>
       <c r="H236" t="n">
         <v>2700</v>
@@ -7242,7 +7242,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G237" t="n">
-        <v>2.51003694534302</v>
+        <v>2.5100371837616</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>2.50100803375244</v>
+        <v>2.50100827217102</v>
       </c>
       <c r="H244" t="n">
         <v>22800</v>
@@ -7474,7 +7474,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G245" t="n">
-        <v>2.50100803375244</v>
+        <v>2.50100827217102</v>
       </c>
       <c r="H245" t="n">
         <v>2400</v>
@@ -7503,7 +7503,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G246" t="n">
-        <v>2.50100803375244</v>
+        <v>2.50100827217102</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G247" t="n">
-        <v>2.50100803375244</v>
+        <v>2.50100827217102</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G248" t="n">
-        <v>2.50100803375244</v>
+        <v>2.50100827217102</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G249" t="n">
-        <v>2.51003694534302</v>
+        <v>2.5100371837616</v>
       </c>
       <c r="H249" t="n">
         <v>2100</v>
@@ -7764,7 +7764,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G255" t="n">
-        <v>2.27528548240662</v>
+        <v>2.27528524398804</v>
       </c>
       <c r="H255" t="n">
         <v>2100</v>
@@ -7793,7 +7793,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>2.32945895195007</v>
+        <v>2.32945847511292</v>
       </c>
       <c r="H256" t="n">
         <v>1500</v>
@@ -7822,7 +7822,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>2.32945895195007</v>
+        <v>2.32945847511292</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G258" t="n">
-        <v>2.24819874763489</v>
+        <v>2.24819850921631</v>
       </c>
       <c r="H258" t="n">
         <v>1800</v>
@@ -7880,7 +7880,7 @@
         <v>2.5</v>
       </c>
       <c r="G259" t="n">
-        <v>2.25722765922546</v>
+        <v>2.25722742080688</v>
       </c>
       <c r="H259" t="n">
         <v>9900</v>
@@ -7909,7 +7909,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G260" t="n">
-        <v>2.24819874763489</v>
+        <v>2.24819850921631</v>
       </c>
       <c r="H260" t="n">
         <v>900</v>
@@ -7938,7 +7938,7 @@
         <v>2.5</v>
       </c>
       <c r="G261" t="n">
-        <v>2.25722765922546</v>
+        <v>2.25722742080688</v>
       </c>
       <c r="H261" t="n">
         <v>2400</v>
@@ -7967,7 +7967,7 @@
         <v>2.5</v>
       </c>
       <c r="G262" t="n">
-        <v>2.25722765922546</v>
+        <v>2.25722742080688</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G263" t="n">
-        <v>2.32042980194092</v>
+        <v>2.32042956352234</v>
       </c>
       <c r="H263" t="n">
         <v>2100</v>
@@ -8025,7 +8025,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G264" t="n">
-        <v>2.32042980194092</v>
+        <v>2.32042956352234</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G265" t="n">
-        <v>2.32042980194092</v>
+        <v>2.32042956352234</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.32042980194092</v>
+        <v>2.32042956352234</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G267" t="n">
-        <v>2.42877674102783</v>
+        <v>2.42877697944641</v>
       </c>
       <c r="H267" t="n">
         <v>2100</v>
@@ -8315,7 +8315,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>2.27528548240662</v>
+        <v>2.27528524398804</v>
       </c>
       <c r="H274" t="n">
         <v>7500</v>
@@ -8431,7 +8431,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G278" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H278" t="n">
         <v>3600</v>
@@ -8460,7 +8460,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H279" t="n">
         <v>4800</v>
@@ -8547,7 +8547,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G282" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H282" t="n">
         <v>900</v>
@@ -8576,7 +8576,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G283" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H283" t="n">
         <v>1500</v>
@@ -8605,7 +8605,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G284" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G285" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H285" t="n">
         <v>2100</v>
@@ -8663,7 +8663,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G286" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G287" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>2.18499636650085</v>
+        <v>2.18499612808228</v>
       </c>
       <c r="H288" t="n">
         <v>1200</v>
@@ -8750,7 +8750,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G289" t="n">
-        <v>2.18499636650085</v>
+        <v>2.18499612808228</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>2.12179350852966</v>
+        <v>2.12179398536682</v>
       </c>
       <c r="H291" t="n">
         <v>2400</v>
@@ -8837,7 +8837,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G292" t="n">
-        <v>2.05859136581421</v>
+        <v>2.05859160423279</v>
       </c>
       <c r="H292" t="n">
         <v>18900</v>
@@ -9040,7 +9040,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G299" t="n">
-        <v>1.94121587276459</v>
+        <v>1.9412157535553</v>
       </c>
       <c r="H299" t="n">
         <v>1200</v>
@@ -9069,7 +9069,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G300" t="n">
-        <v>1.87801325321198</v>
+        <v>1.87801337242126</v>
       </c>
       <c r="H300" t="n">
         <v>7200</v>
@@ -9098,7 +9098,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G301" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H301" t="n">
         <v>35700</v>
@@ -9127,7 +9127,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>1.97733116149902</v>
+        <v>1.97733128070831</v>
       </c>
       <c r="H302" t="n">
         <v>4200</v>
@@ -9156,7 +9156,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G303" t="n">
-        <v>1.97733116149902</v>
+        <v>1.97733128070831</v>
       </c>
       <c r="H303" t="n">
         <v>300</v>
@@ -9185,7 +9185,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G304" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H304" t="n">
         <v>600</v>
@@ -9214,7 +9214,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>1.95927345752716</v>
+        <v>1.95927369594574</v>
       </c>
       <c r="H305" t="n">
         <v>3900</v>
@@ -9243,7 +9243,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G306" t="n">
-        <v>2.04053354263306</v>
+        <v>2.04053378105164</v>
       </c>
       <c r="H306" t="n">
         <v>3600</v>
@@ -9359,7 +9359,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>2.04053354263306</v>
+        <v>2.04053378105164</v>
       </c>
       <c r="H310" t="n">
         <v>900</v>
@@ -9388,7 +9388,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G311" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H311" t="n">
         <v>1200</v>
@@ -9417,7 +9417,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G312" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G313" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H315" t="n">
         <v>300</v>
@@ -9533,7 +9533,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G316" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G318" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H318" t="n">
         <v>600</v>
@@ -9620,7 +9620,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G319" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G320" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>1.92315793037415</v>
+        <v>1.92315804958344</v>
       </c>
       <c r="H325" t="n">
         <v>600</v>
@@ -9823,7 +9823,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>2.04956245422363</v>
+        <v>2.04956269264221</v>
       </c>
       <c r="H326" t="n">
         <v>5700</v>
@@ -9881,7 +9881,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G328" t="n">
-        <v>1.91412878036499</v>
+        <v>1.91412889957428</v>
       </c>
       <c r="H328" t="n">
         <v>51000</v>
@@ -9939,7 +9939,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>1.84189760684967</v>
+        <v>1.84189772605896</v>
       </c>
       <c r="H330" t="n">
         <v>29100</v>
@@ -10171,7 +10171,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G338" t="n">
-        <v>2.04053354263306</v>
+        <v>2.04053378105164</v>
       </c>
       <c r="H338" t="n">
         <v>18000</v>
@@ -10200,7 +10200,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G339" t="n">
-        <v>2.05859136581421</v>
+        <v>2.05859160423279</v>
       </c>
       <c r="H339" t="n">
         <v>54900</v>
@@ -10258,7 +10258,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G341" t="n">
-        <v>2.04053354263306</v>
+        <v>2.04053378105164</v>
       </c>
       <c r="H341" t="n">
         <v>1200</v>
@@ -10345,7 +10345,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G344" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H344" t="n">
         <v>13200</v>
@@ -10519,7 +10519,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G350" t="n">
-        <v>1.87801325321198</v>
+        <v>1.87801337242126</v>
       </c>
       <c r="H350" t="n">
         <v>2400</v>
@@ -10635,7 +10635,7 @@
         <v>2</v>
       </c>
       <c r="G354" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H354" t="n">
         <v>21600</v>
@@ -10693,7 +10693,7 @@
         <v>2</v>
       </c>
       <c r="G356" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H356" t="n">
         <v>1500</v>
@@ -10722,7 +10722,7 @@
         <v>2</v>
       </c>
       <c r="G357" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>2</v>
       </c>
       <c r="G358" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
         <v>2</v>
       </c>
       <c r="G359" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>2</v>
       </c>
       <c r="G360" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>2</v>
       </c>
       <c r="G361" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>2</v>
       </c>
       <c r="G362" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>2</v>
       </c>
       <c r="G363" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>2</v>
       </c>
       <c r="G365" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H365" t="n">
         <v>3000</v>
@@ -10983,7 +10983,7 @@
         <v>2</v>
       </c>
       <c r="G366" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>2</v>
       </c>
       <c r="G378" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H378" t="n">
         <v>2100</v>
@@ -11360,7 +11360,7 @@
         <v>2</v>
       </c>
       <c r="G379" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>2</v>
       </c>
       <c r="G380" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>1.78772413730621</v>
+        <v>1.7877242565155</v>
       </c>
       <c r="H381" t="n">
         <v>98700</v>
@@ -11679,7 +11679,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G390" t="n">
-        <v>1.67937731742859</v>
+        <v>1.6793771982193</v>
       </c>
       <c r="H390" t="n">
         <v>2400</v>
@@ -11737,7 +11737,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G392" t="n">
-        <v>1.69743514060974</v>
+        <v>1.69743502140045</v>
       </c>
       <c r="H392" t="n">
         <v>2100</v>
@@ -11766,7 +11766,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G393" t="n">
-        <v>1.69743514060974</v>
+        <v>1.69743502140045</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G394" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H394" t="n">
         <v>5100</v>
@@ -11824,7 +11824,7 @@
         <v>1.75</v>
       </c>
       <c r="G395" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H395" t="n">
         <v>3900</v>
@@ -11911,7 +11911,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H398" t="n">
         <v>1200</v>
@@ -12085,7 +12085,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>1.52588593959808</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H404" t="n">
         <v>80700</v>
@@ -12114,7 +12114,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G405" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H405" t="n">
         <v>4200</v>
@@ -12172,7 +12172,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G407" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H407" t="n">
         <v>3300</v>
@@ -12259,7 +12259,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G410" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H410" t="n">
         <v>39900</v>
@@ -12317,7 +12317,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>1.52588593959808</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H412" t="n">
         <v>900</v>
@@ -12433,7 +12433,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G416" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H416" t="n">
         <v>2100</v>
@@ -12549,7 +12549,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G420" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H420" t="n">
         <v>300</v>
@@ -12607,7 +12607,7 @@
         <v>1.5</v>
       </c>
       <c r="G422" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H422" t="n">
         <v>300</v>
@@ -12636,7 +12636,7 @@
         <v>1.5</v>
       </c>
       <c r="G423" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H423" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>1.5</v>
       </c>
       <c r="G424" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12694,7 +12694,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G425" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H425" t="n">
         <v>1500</v>
@@ -12752,7 +12752,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G427" t="n">
-        <v>1.31822085380554</v>
+        <v>1.31822097301483</v>
       </c>
       <c r="H427" t="n">
         <v>3300</v>
@@ -12781,7 +12781,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G428" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H428" t="n">
         <v>1800</v>
@@ -12810,7 +12810,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G429" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12839,7 +12839,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G430" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G433" t="n">
-        <v>1.30919206142426</v>
+        <v>1.30919194221497</v>
       </c>
       <c r="H433" t="n">
         <v>300</v>
@@ -12984,7 +12984,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G435" t="n">
-        <v>1.31822085380554</v>
+        <v>1.31822097301483</v>
       </c>
       <c r="H435" t="n">
         <v>3600</v>
@@ -13071,7 +13071,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G438" t="n">
-        <v>1.30919206142426</v>
+        <v>1.30919194221497</v>
       </c>
       <c r="H438" t="n">
         <v>27900</v>
@@ -13187,7 +13187,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G442" t="n">
-        <v>1.24598956108093</v>
+        <v>1.24598968029022</v>
       </c>
       <c r="H442" t="n">
         <v>79500</v>
@@ -13216,7 +13216,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G443" t="n">
-        <v>1.22793173789978</v>
+        <v>1.22793185710907</v>
       </c>
       <c r="H443" t="n">
         <v>6000</v>
@@ -13448,7 +13448,7 @@
         <v>1.75</v>
       </c>
       <c r="G451" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H451" t="n">
         <v>17400</v>
@@ -13477,7 +13477,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>1.52588593959808</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H452" t="n">
         <v>5100</v>
@@ -13506,7 +13506,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G453" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H453" t="n">
         <v>42000</v>
@@ -13622,7 +13622,7 @@
         <v>1.5</v>
       </c>
       <c r="G457" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H457" t="n">
         <v>3000</v>
@@ -13651,7 +13651,7 @@
         <v>1.5</v>
       </c>
       <c r="G458" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H458" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>1.5</v>
       </c>
       <c r="G459" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H459" t="n">
         <v>9300</v>
@@ -13709,7 +13709,7 @@
         <v>1.5</v>
       </c>
       <c r="G460" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H460" t="n">
         <v>300</v>
@@ -13738,7 +13738,7 @@
         <v>1.5</v>
       </c>
       <c r="G461" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>1.5</v>
       </c>
       <c r="G462" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>1.5</v>
       </c>
       <c r="G463" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H463" t="n">
         <v>4200</v>
@@ -13825,7 +13825,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>1.31822085380554</v>
+        <v>1.31822097301483</v>
       </c>
       <c r="H464" t="n">
         <v>900</v>
@@ -13854,7 +13854,7 @@
         <v>1.5</v>
       </c>
       <c r="G465" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H465" t="n">
         <v>20100</v>
@@ -13883,7 +13883,7 @@
         <v>1.5</v>
       </c>
       <c r="G466" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H466" t="n">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G467" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H467" t="n">
         <v>3300</v>
@@ -13970,7 +13970,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G469" t="n">
-        <v>1.67937731742859</v>
+        <v>1.6793771982193</v>
       </c>
       <c r="H469" t="n">
         <v>347100</v>
@@ -14144,7 +14144,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>1.52588593959808</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H475" t="n">
         <v>49500</v>
@@ -14173,7 +14173,7 @@
         <v>1.75</v>
       </c>
       <c r="G476" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H476" t="n">
         <v>21600</v>
@@ -14260,7 +14260,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>1.52588593959808</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H479" t="n">
         <v>39600</v>
@@ -14289,7 +14289,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G480" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H480" t="n">
         <v>30000</v>
@@ -14318,7 +14318,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G481" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H481" t="n">
         <v>30900</v>
@@ -14347,7 +14347,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G482" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H482" t="n">
         <v>17100</v>
@@ -14376,7 +14376,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G483" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H483" t="n">
         <v>8400</v>
@@ -14463,7 +14463,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G486" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H486" t="n">
         <v>16800</v>
@@ -14521,7 +14521,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G488" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H488" t="n">
         <v>6000</v>
@@ -14637,7 +14637,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G492" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H492" t="n">
         <v>79200</v>
@@ -14724,7 +14724,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G495" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H495" t="n">
         <v>9900</v>
@@ -14840,7 +14840,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G499" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H499" t="n">
         <v>42000</v>
@@ -15130,7 +15130,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G509" t="n">
-        <v>1.52588593959808</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H509" t="n">
         <v>3600</v>
@@ -15217,7 +15217,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H512" t="n">
         <v>36000</v>
@@ -15420,7 +15420,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G519" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H519" t="n">
         <v>4800</v>
@@ -15449,7 +15449,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G520" t="n">
-        <v>1.61617481708527</v>
+        <v>1.61617493629456</v>
       </c>
       <c r="H520" t="n">
         <v>1500</v>
@@ -15478,7 +15478,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G521" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H521" t="n">
         <v>600</v>
@@ -15536,7 +15536,7 @@
         <v>1.75</v>
       </c>
       <c r="G523" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H523" t="n">
         <v>9900</v>
@@ -15623,7 +15623,7 @@
         <v>1.75</v>
       </c>
       <c r="G526" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H526" t="n">
         <v>92100</v>
@@ -15826,7 +15826,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G533" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H533" t="n">
         <v>5400</v>
@@ -15913,7 +15913,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G536" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H536" t="n">
         <v>51900</v>
@@ -16000,7 +16000,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G539" t="n">
-        <v>1.25501847267151</v>
+        <v>1.2550185918808</v>
       </c>
       <c r="H539" t="n">
         <v>51300</v>
@@ -16087,7 +16087,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G542" t="n">
-        <v>1.30919206142426</v>
+        <v>1.30919194221497</v>
       </c>
       <c r="H542" t="n">
         <v>21600</v>
@@ -16145,7 +16145,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G544" t="n">
-        <v>1.30919206142426</v>
+        <v>1.30919194221497</v>
       </c>
       <c r="H544" t="n">
         <v>11400</v>
@@ -16174,7 +16174,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G545" t="n">
-        <v>1.25501847267151</v>
+        <v>1.2550185918808</v>
       </c>
       <c r="H545" t="n">
         <v>70200</v>
@@ -16261,7 +16261,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G548" t="n">
-        <v>1.22793173789978</v>
+        <v>1.22793185710907</v>
       </c>
       <c r="H548" t="n">
         <v>21900</v>
@@ -16493,7 +16493,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G556" t="n">
-        <v>1.02026677131653</v>
+        <v>1.02026689052582</v>
       </c>
       <c r="H556" t="n">
         <v>72900</v>
@@ -16522,7 +16522,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G557" t="n">
-        <v>1.02026677131653</v>
+        <v>1.02026689052582</v>
       </c>
       <c r="H557" t="n">
         <v>37800</v>
@@ -16551,7 +16551,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G558" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H558" t="n">
         <v>19500</v>
@@ -16638,7 +16638,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G561" t="n">
-        <v>0.984151244163513</v>
+        <v>0.984151303768158</v>
       </c>
       <c r="H561" t="n">
         <v>8100</v>
@@ -16725,7 +16725,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H564" t="n">
         <v>15300</v>
@@ -16754,7 +16754,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G565" t="n">
-        <v>0.939006626605988</v>
+        <v>0.939006686210632</v>
       </c>
       <c r="H565" t="n">
         <v>2400</v>
@@ -16783,7 +16783,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G566" t="n">
-        <v>0.839688658714294</v>
+        <v>0.83968859910965</v>
       </c>
       <c r="H566" t="n">
         <v>3600</v>
@@ -16841,7 +16841,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G568" t="n">
-        <v>0.80357301235199</v>
+        <v>0.803572952747345</v>
       </c>
       <c r="H568" t="n">
         <v>9600</v>
@@ -16870,7 +16870,7 @@
         <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>0.902890980243683</v>
+        <v>0.902891039848328</v>
       </c>
       <c r="H569" t="n">
         <v>16200</v>
@@ -16899,7 +16899,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>0.884833157062531</v>
+        <v>0.884833216667175</v>
       </c>
       <c r="H570" t="n">
         <v>10800</v>
@@ -17044,7 +17044,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G575" t="n">
-        <v>0.884833157062531</v>
+        <v>0.884833216667175</v>
       </c>
       <c r="H575" t="n">
         <v>16200</v>
@@ -17247,7 +17247,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G582" t="n">
-        <v>1.02478122711182</v>
+        <v>1.02478134632111</v>
       </c>
       <c r="H582" t="n">
         <v>1200</v>
@@ -17334,7 +17334,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G585" t="n">
-        <v>1.02478122711182</v>
+        <v>1.02478134632111</v>
       </c>
       <c r="H585" t="n">
         <v>15600</v>
@@ -17363,7 +17363,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G586" t="n">
-        <v>1.02478122711182</v>
+        <v>1.02478134632111</v>
       </c>
       <c r="H586" t="n">
         <v>9600</v>
@@ -17479,7 +17479,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G590" t="n">
-        <v>0.984151244163513</v>
+        <v>0.984151303768158</v>
       </c>
       <c r="H590" t="n">
         <v>18000</v>
@@ -17508,7 +17508,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G591" t="n">
-        <v>0.952549993991852</v>
+        <v>0.952549934387207</v>
       </c>
       <c r="H591" t="n">
         <v>102000</v>
@@ -17566,7 +17566,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G593" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H593" t="n">
         <v>12900</v>
@@ -17595,7 +17595,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G594" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H594" t="n">
         <v>1500</v>
@@ -17624,7 +17624,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H595" t="n">
         <v>15900</v>
@@ -17653,7 +17653,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>0.939006626605988</v>
+        <v>0.939006686210632</v>
       </c>
       <c r="H596" t="n">
         <v>39300</v>
@@ -17682,7 +17682,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G597" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H597" t="n">
         <v>15000</v>
@@ -17711,7 +17711,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G598" t="n">
-        <v>0.952549993991852</v>
+        <v>0.952549934387207</v>
       </c>
       <c r="H598" t="n">
         <v>21600</v>
@@ -17798,7 +17798,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G601" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H601" t="n">
         <v>17100</v>
@@ -17827,7 +17827,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G602" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H602" t="n">
         <v>13200</v>
@@ -17856,7 +17856,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G603" t="n">
-        <v>0.939006626605988</v>
+        <v>0.939006686210632</v>
       </c>
       <c r="H603" t="n">
         <v>9600</v>
@@ -17885,7 +17885,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G604" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H604" t="n">
         <v>36600</v>
@@ -17943,7 +17943,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G606" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H606" t="n">
         <v>21600</v>
@@ -17972,7 +17972,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G607" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H607" t="n">
         <v>7800</v>
@@ -18059,7 +18059,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H610" t="n">
         <v>52200</v>
@@ -18117,7 +18117,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G612" t="n">
-        <v>0.901085257530212</v>
+        <v>0.901085317134857</v>
       </c>
       <c r="H612" t="n">
         <v>36000</v>
@@ -18204,7 +18204,7 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>0.902890980243683</v>
+        <v>0.902891039848328</v>
       </c>
       <c r="H615" t="n">
         <v>20700</v>
@@ -18233,7 +18233,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G616" t="n">
-        <v>0.901085257530212</v>
+        <v>0.901085317134857</v>
       </c>
       <c r="H616" t="n">
         <v>26700</v>
@@ -18262,7 +18262,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G617" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H617" t="n">
         <v>13200</v>
@@ -18320,7 +18320,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G619" t="n">
-        <v>0.893862068653107</v>
+        <v>0.893862128257751</v>
       </c>
       <c r="H619" t="n">
         <v>41100</v>
@@ -18349,7 +18349,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G620" t="n">
-        <v>0.901085257530212</v>
+        <v>0.901085317134857</v>
       </c>
       <c r="H620" t="n">
         <v>13500</v>
@@ -18378,7 +18378,7 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>0.902890980243683</v>
+        <v>0.902891039848328</v>
       </c>
       <c r="H621" t="n">
         <v>9900</v>
@@ -18407,7 +18407,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G622" t="n">
-        <v>0.901085257530212</v>
+        <v>0.901085317134857</v>
       </c>
       <c r="H622" t="n">
         <v>54000</v>
@@ -18436,7 +18436,7 @@
         <v>1</v>
       </c>
       <c r="G623" t="n">
-        <v>0.902890980243683</v>
+        <v>0.902891039848328</v>
       </c>
       <c r="H623" t="n">
         <v>20100</v>
@@ -18494,7 +18494,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G625" t="n">
-        <v>0.901085257530212</v>
+        <v>0.901085317134857</v>
       </c>
       <c r="H625" t="n">
         <v>47100</v>
@@ -18552,7 +18552,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G627" t="n">
-        <v>1.04283916950226</v>
+        <v>1.04283905029297</v>
       </c>
       <c r="H627" t="n">
         <v>258300</v>
@@ -18581,7 +18581,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G628" t="n">
-        <v>0.988665580749512</v>
+        <v>0.988665640354156</v>
       </c>
       <c r="H628" t="n">
         <v>45600</v>
@@ -18639,7 +18639,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G630" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H630" t="n">
         <v>20400</v>
@@ -18755,7 +18755,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G634" t="n">
-        <v>1.02478122711182</v>
+        <v>1.02478134632111</v>
       </c>
       <c r="H634" t="n">
         <v>5700</v>
@@ -18784,7 +18784,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G635" t="n">
-        <v>1.0292956829071</v>
+        <v>1.02929580211639</v>
       </c>
       <c r="H635" t="n">
         <v>5700</v>
@@ -18842,7 +18842,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G637" t="n">
-        <v>0.984151244163513</v>
+        <v>0.984151303768158</v>
       </c>
       <c r="H637" t="n">
         <v>3900</v>
@@ -18871,7 +18871,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>0.97963672876358</v>
+        <v>0.97963684797287</v>
       </c>
       <c r="H638" t="n">
         <v>6900</v>
@@ -18900,7 +18900,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H639" t="n">
         <v>2400</v>
@@ -18929,7 +18929,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G640" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H640" t="n">
         <v>18600</v>
@@ -18987,7 +18987,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G642" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H642" t="n">
         <v>3600</v>
@@ -19045,7 +19045,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G644" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H644" t="n">
         <v>10800</v>
@@ -19103,7 +19103,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>0.939006626605988</v>
+        <v>0.939006686210632</v>
       </c>
       <c r="H646" t="n">
         <v>7200</v>
@@ -19132,7 +19132,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>0.939006626605988</v>
+        <v>0.939006686210632</v>
       </c>
       <c r="H647" t="n">
         <v>1500</v>
@@ -19161,7 +19161,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G648" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H648" t="n">
         <v>900</v>
@@ -19190,7 +19190,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G649" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H649" t="n">
         <v>3000</v>
@@ -19335,7 +19335,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G654" t="n">
-        <v>0.970607936382294</v>
+        <v>0.970607876777649</v>
       </c>
       <c r="H654" t="n">
         <v>7500</v>
@@ -19393,7 +19393,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>0.97963672876358</v>
+        <v>0.97963684797287</v>
       </c>
       <c r="H656" t="n">
         <v>7200</v>
@@ -19422,7 +19422,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G657" t="n">
-        <v>0.984151244163513</v>
+        <v>0.984151303768158</v>
       </c>
       <c r="H657" t="n">
         <v>5400</v>
@@ -19480,7 +19480,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G659" t="n">
-        <v>0.970607936382294</v>
+        <v>0.970607876777649</v>
       </c>
       <c r="H659" t="n">
         <v>12300</v>
@@ -19509,7 +19509,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G660" t="n">
-        <v>0.970607936382294</v>
+        <v>0.970607876777649</v>
       </c>
       <c r="H660" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G664" t="n">
-        <v>0.952549993991852</v>
+        <v>0.952549934387207</v>
       </c>
       <c r="H664" t="n">
         <v>300</v>
@@ -19654,7 +19654,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G665" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H665" t="n">
         <v>1800</v>
@@ -19712,7 +19712,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G667" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H667" t="n">
         <v>3900</v>
@@ -19770,7 +19770,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G669" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H669" t="n">
         <v>300</v>
@@ -19799,7 +19799,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G670" t="n">
-        <v>0.970607936382294</v>
+        <v>0.970607876777649</v>
       </c>
       <c r="H670" t="n">
         <v>2100</v>
@@ -19857,7 +19857,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G672" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H672" t="n">
         <v>300</v>
@@ -19886,7 +19886,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.988665580749512</v>
+        <v>0.988665640354156</v>
       </c>
       <c r="H673" t="n">
         <v>3300</v>
@@ -19915,7 +19915,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G674" t="n">
-        <v>0.988665580749512</v>
+        <v>0.988665640354156</v>
       </c>
       <c r="H674" t="n">
         <v>300</v>
@@ -20031,7 +20031,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G678" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H678" t="n">
         <v>9300</v>
@@ -20060,7 +20060,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G679" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H679" t="n">
         <v>15300</v>
@@ -20176,7 +20176,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>0.939006626605988</v>
+        <v>0.939006686210632</v>
       </c>
       <c r="H683" t="n">
         <v>23100</v>
@@ -20263,7 +20263,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H686" t="n">
         <v>3000</v>
@@ -20292,7 +20292,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G687" t="n">
-        <v>0.952549993991852</v>
+        <v>0.952549934387207</v>
       </c>
       <c r="H687" t="n">
         <v>3600</v>
@@ -20321,7 +20321,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G688" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H688" t="n">
         <v>21900</v>
@@ -20379,7 +20379,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G690" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H690" t="n">
         <v>3600</v>
@@ -20408,7 +20408,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G691" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H691" t="n">
         <v>600</v>
@@ -20437,7 +20437,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G692" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H692" t="n">
         <v>9600</v>
@@ -20553,7 +20553,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G696" t="n">
-        <v>0.952549993991852</v>
+        <v>0.952549934387207</v>
       </c>
       <c r="H696" t="n">
         <v>12000</v>
@@ -20582,7 +20582,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G697" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H697" t="n">
         <v>7200</v>
@@ -20611,7 +20611,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G698" t="n">
-        <v>0.970607936382294</v>
+        <v>0.970607876777649</v>
       </c>
       <c r="H698" t="n">
         <v>21600</v>
@@ -20669,7 +20669,7 @@
         <v>1</v>
       </c>
       <c r="G700" t="n">
-        <v>0.902890980243683</v>
+        <v>0.902891039848328</v>
       </c>
       <c r="H700" t="n">
         <v>15000</v>
@@ -20698,7 +20698,7 @@
         <v>1</v>
       </c>
       <c r="G701" t="n">
-        <v>0.902890980243683</v>
+        <v>0.902891039848328</v>
       </c>
       <c r="H701" t="n">
         <v>14100</v>
@@ -20727,7 +20727,7 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>0.902890980243683</v>
+        <v>0.902891039848328</v>
       </c>
       <c r="H702" t="n">
         <v>5700</v>
@@ -20756,7 +20756,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>0.911919951438904</v>
+        <v>0.911919891834259</v>
       </c>
       <c r="H703" t="n">
         <v>11700</v>
@@ -20814,7 +20814,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G705" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H705" t="n">
         <v>900</v>
@@ -20872,7 +20872,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G707" t="n">
-        <v>0.852329134941101</v>
+        <v>0.852329075336456</v>
       </c>
       <c r="H707" t="n">
         <v>10200</v>
@@ -21104,7 +21104,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G715" t="n">
-        <v>0.807184517383575</v>
+        <v>0.80718457698822</v>
       </c>
       <c r="H715" t="n">
         <v>1500</v>
@@ -21278,7 +21278,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G721" t="n">
-        <v>0.698837578296661</v>
+        <v>0.698837637901306</v>
       </c>
       <c r="H721" t="n">
         <v>20700</v>
@@ -21365,7 +21365,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G724" t="n">
-        <v>0.749399483203888</v>
+        <v>0.749399542808533</v>
       </c>
       <c r="H724" t="n">
         <v>24900</v>
@@ -21394,7 +21394,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G725" t="n">
-        <v>0.749399483203888</v>
+        <v>0.749399542808533</v>
       </c>
       <c r="H725" t="n">
         <v>0</v>
@@ -21481,7 +21481,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G728" t="n">
-        <v>0.622994780540466</v>
+        <v>0.622994840145111</v>
       </c>
       <c r="H728" t="n">
         <v>15600</v>
@@ -21510,7 +21510,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G729" t="n">
-        <v>0.619383275508881</v>
+        <v>0.619383215904236</v>
       </c>
       <c r="H729" t="n">
         <v>9600</v>
@@ -21626,7 +21626,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G733" t="n">
-        <v>0.651887357234955</v>
+        <v>0.65188729763031</v>
       </c>
       <c r="H733" t="n">
         <v>3600</v>
@@ -21655,7 +21655,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G734" t="n">
-        <v>0.653693020343781</v>
+        <v>0.653693079948425</v>
       </c>
       <c r="H734" t="n">
         <v>27900</v>
@@ -21713,7 +21713,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G736" t="n">
-        <v>0.678973972797394</v>
+        <v>0.678974032402039</v>
       </c>
       <c r="H736" t="n">
         <v>4200</v>
@@ -21742,7 +21742,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G737" t="n">
-        <v>0.68439131975174</v>
+        <v>0.684391379356384</v>
       </c>
       <c r="H737" t="n">
         <v>14700</v>
@@ -21829,7 +21829,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G740" t="n">
-        <v>0.644664227962494</v>
+        <v>0.644664168357849</v>
       </c>
       <c r="H740" t="n">
         <v>3600</v>
@@ -21945,7 +21945,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G744" t="n">
-        <v>0.675362527370453</v>
+        <v>0.675362467765808</v>
       </c>
       <c r="H744" t="n">
         <v>18000</v>
@@ -22119,7 +22119,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G750" t="n">
-        <v>0.709672272205353</v>
+        <v>0.709672331809998</v>
       </c>
       <c r="H750" t="n">
         <v>35100</v>
@@ -22177,7 +22177,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G752" t="n">
-        <v>0.675362527370453</v>
+        <v>0.675362467765808</v>
       </c>
       <c r="H752" t="n">
         <v>33600</v>
@@ -22206,7 +22206,7 @@
         <v>0.75</v>
       </c>
       <c r="G753" t="n">
-        <v>0.677168309688568</v>
+        <v>0.677168250083923</v>
       </c>
       <c r="H753" t="n">
         <v>36600</v>
@@ -22235,7 +22235,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G754" t="n">
-        <v>0.675362527370453</v>
+        <v>0.675362467765808</v>
       </c>
       <c r="H754" t="n">
         <v>27900</v>
@@ -22264,7 +22264,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G755" t="n">
-        <v>0.698837578296661</v>
+        <v>0.698837637901306</v>
       </c>
       <c r="H755" t="n">
         <v>134100</v>
@@ -22322,7 +22322,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G757" t="n">
-        <v>0.68439131975174</v>
+        <v>0.684391379356384</v>
       </c>
       <c r="H757" t="n">
         <v>34500</v>
@@ -22409,7 +22409,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G760" t="n">
-        <v>0.659110426902771</v>
+        <v>0.659110486507416</v>
       </c>
       <c r="H760" t="n">
         <v>22500</v>
@@ -22467,7 +22467,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G762" t="n">
-        <v>0.700643479824066</v>
+        <v>0.700643420219421</v>
       </c>
       <c r="H762" t="n">
         <v>48300</v>
@@ -22583,7 +22583,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G766" t="n">
-        <v>0.807184517383575</v>
+        <v>0.80718457698822</v>
       </c>
       <c r="H766" t="n">
         <v>120300</v>
@@ -22989,7 +22989,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G780" t="n">
-        <v>0.80899041891098</v>
+        <v>0.808990359306335</v>
       </c>
       <c r="H780" t="n">
         <v>34200</v>
@@ -23018,7 +23018,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G781" t="n">
-        <v>0.80357301235199</v>
+        <v>0.803572952747345</v>
       </c>
       <c r="H781" t="n">
         <v>27000</v>
@@ -23105,7 +23105,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G784" t="n">
-        <v>0.80899041891098</v>
+        <v>0.808990359306335</v>
       </c>
       <c r="H784" t="n">
         <v>44700</v>
@@ -23134,7 +23134,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G785" t="n">
-        <v>0.80357301235199</v>
+        <v>0.803572952747345</v>
       </c>
       <c r="H785" t="n">
         <v>7500</v>
@@ -23221,7 +23221,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G788" t="n">
-        <v>0.774680435657501</v>
+        <v>0.774680495262146</v>
       </c>
       <c r="H788" t="n">
         <v>112500</v>
@@ -23308,7 +23308,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G791" t="n">
-        <v>0.754816889762878</v>
+        <v>0.754816949367523</v>
       </c>
       <c r="H791" t="n">
         <v>36000</v>
@@ -23453,7 +23453,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G796" t="n">
-        <v>0.789126753807068</v>
+        <v>0.789126813411713</v>
       </c>
       <c r="H796" t="n">
         <v>17400</v>
@@ -23540,7 +23540,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G799" t="n">
-        <v>0.819825053215027</v>
+        <v>0.819824993610382</v>
       </c>
       <c r="H799" t="n">
         <v>312600</v>
@@ -23569,7 +23569,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G800" t="n">
-        <v>0.823436677455902</v>
+        <v>0.823436558246613</v>
       </c>
       <c r="H800" t="n">
         <v>87300</v>
@@ -23598,7 +23598,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G801" t="n">
-        <v>0.834271371364594</v>
+        <v>0.834271311759949</v>
       </c>
       <c r="H801" t="n">
         <v>39300</v>
@@ -23656,7 +23656,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G803" t="n">
-        <v>0.848717570304871</v>
+        <v>0.848717510700226</v>
       </c>
       <c r="H803" t="n">
         <v>618600</v>
@@ -23714,7 +23714,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G805" t="n">
-        <v>0.859552264213562</v>
+        <v>0.859552204608917</v>
       </c>
       <c r="H805" t="n">
         <v>41700</v>
@@ -23772,7 +23772,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>0.893862068653107</v>
+        <v>0.893862128257751</v>
       </c>
       <c r="H807" t="n">
         <v>214500</v>
@@ -23859,7 +23859,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G810" t="n">
-        <v>0.854134917259216</v>
+        <v>0.854134857654572</v>
       </c>
       <c r="H810" t="n">
         <v>57000</v>
@@ -23917,7 +23917,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G812" t="n">
-        <v>0.873998463153839</v>
+        <v>0.873998522758484</v>
       </c>
       <c r="H812" t="n">
         <v>37200</v>
@@ -23975,7 +23975,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G814" t="n">
-        <v>0.848717570304871</v>
+        <v>0.848717510700226</v>
       </c>
       <c r="H814" t="n">
         <v>37800</v>
@@ -24004,7 +24004,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G815" t="n">
-        <v>0.859552264213562</v>
+        <v>0.859552204608917</v>
       </c>
       <c r="H815" t="n">
         <v>4800</v>
@@ -24033,7 +24033,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G816" t="n">
-        <v>0.848717570304871</v>
+        <v>0.848717510700226</v>
       </c>
       <c r="H816" t="n">
         <v>22500</v>
@@ -24062,7 +24062,7 @@
         <v>1</v>
       </c>
       <c r="G817" t="n">
-        <v>0.902890980243683</v>
+        <v>0.902891039848328</v>
       </c>
       <c r="H817" t="n">
         <v>158700</v>
@@ -24120,7 +24120,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G819" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H819" t="n">
         <v>47400</v>
@@ -24207,7 +24207,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G822" t="n">
-        <v>0.943521082401276</v>
+        <v>0.943521022796631</v>
       </c>
       <c r="H822" t="n">
         <v>21900</v>
@@ -24265,7 +24265,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G824" t="n">
-        <v>0.911919951438904</v>
+        <v>0.911919891834259</v>
       </c>
       <c r="H824" t="n">
         <v>29700</v>
@@ -24352,7 +24352,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G827" t="n">
-        <v>0.883027374744415</v>
+        <v>0.88302743434906</v>
       </c>
       <c r="H827" t="n">
         <v>58800</v>
@@ -24439,7 +24439,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G830" t="n">
-        <v>0.883027374744415</v>
+        <v>0.88302743434906</v>
       </c>
       <c r="H830" t="n">
         <v>2100</v>
@@ -24497,7 +24497,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G832" t="n">
-        <v>0.893862068653107</v>
+        <v>0.893862128257751</v>
       </c>
       <c r="H832" t="n">
         <v>12000</v>
@@ -24526,7 +24526,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G833" t="n">
-        <v>0.883027374744415</v>
+        <v>0.88302743434906</v>
       </c>
       <c r="H833" t="n">
         <v>8700</v>
@@ -24555,7 +24555,7 @@
         <v>1</v>
       </c>
       <c r="G834" t="n">
-        <v>0.902890980243683</v>
+        <v>0.902891039848328</v>
       </c>
       <c r="H834" t="n">
         <v>11400</v>
@@ -24584,7 +24584,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G835" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H835" t="n">
         <v>30600</v>
@@ -24700,7 +24700,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G839" t="n">
-        <v>0.911919951438904</v>
+        <v>0.911919891834259</v>
       </c>
       <c r="H839" t="n">
         <v>300</v>
@@ -24758,7 +24758,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G841" t="n">
-        <v>0.901085257530212</v>
+        <v>0.901085317134857</v>
       </c>
       <c r="H841" t="n">
         <v>45900</v>
@@ -24845,7 +24845,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G844" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H844" t="n">
         <v>35100</v>
@@ -24932,7 +24932,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G847" t="n">
-        <v>0.984151244163513</v>
+        <v>0.984151303768158</v>
       </c>
       <c r="H847" t="n">
         <v>6600</v>
@@ -24961,7 +24961,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G848" t="n">
-        <v>0.97963672876358</v>
+        <v>0.97963684797287</v>
       </c>
       <c r="H848" t="n">
         <v>13800</v>
@@ -24990,7 +24990,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G849" t="n">
-        <v>1.0292956829071</v>
+        <v>1.02929580211639</v>
       </c>
       <c r="H849" t="n">
         <v>90600</v>
@@ -25077,7 +25077,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G852" t="n">
-        <v>1.02478122711182</v>
+        <v>1.02478134632111</v>
       </c>
       <c r="H852" t="n">
         <v>109800</v>
@@ -25135,7 +25135,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G854" t="n">
-        <v>1.0292956829071</v>
+        <v>1.02929580211639</v>
       </c>
       <c r="H854" t="n">
         <v>5400</v>
@@ -25193,7 +25193,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G856" t="n">
-        <v>1.13764274120331</v>
+        <v>1.13764262199402</v>
       </c>
       <c r="H856" t="n">
         <v>330600</v>
@@ -25222,7 +25222,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G857" t="n">
-        <v>1.10152697563171</v>
+        <v>1.101527094841</v>
       </c>
       <c r="H857" t="n">
         <v>135300</v>
@@ -25251,7 +25251,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G858" t="n">
-        <v>1.11507046222687</v>
+        <v>1.11507034301758</v>
       </c>
       <c r="H858" t="n">
         <v>14700</v>
@@ -25280,7 +25280,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G859" t="n">
-        <v>1.08798372745514</v>
+        <v>1.08798360824585</v>
       </c>
       <c r="H859" t="n">
         <v>10800</v>
@@ -25309,7 +25309,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G860" t="n">
-        <v>1.09249818325043</v>
+        <v>1.09249806404114</v>
       </c>
       <c r="H860" t="n">
         <v>18000</v>
@@ -25396,7 +25396,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G863" t="n">
-        <v>1.06089675426483</v>
+        <v>1.06089699268341</v>
       </c>
       <c r="H863" t="n">
         <v>3900</v>
@@ -25425,7 +25425,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G864" t="n">
-        <v>1.106041431427</v>
+        <v>1.10604155063629</v>
       </c>
       <c r="H864" t="n">
         <v>43500</v>
@@ -25570,7 +25570,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>1.09249818325043</v>
+        <v>1.09249806404114</v>
       </c>
       <c r="H869" t="n">
         <v>38100</v>
@@ -25628,7 +25628,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G871" t="n">
-        <v>1.10152697563171</v>
+        <v>1.101527094841</v>
       </c>
       <c r="H871" t="n">
         <v>7500</v>
@@ -25657,7 +25657,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G872" t="n">
-        <v>1.14215695858002</v>
+        <v>1.14215707778931</v>
       </c>
       <c r="H872" t="n">
         <v>46800</v>
@@ -25686,7 +25686,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G873" t="n">
-        <v>1.16472947597504</v>
+        <v>1.16472923755646</v>
       </c>
       <c r="H873" t="n">
         <v>48300</v>
@@ -25744,7 +25744,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>1.16472947597504</v>
+        <v>1.16472923755646</v>
       </c>
       <c r="H875" t="n">
         <v>158700</v>
@@ -25860,7 +25860,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G879" t="n">
-        <v>1.27307617664337</v>
+        <v>1.27307629585266</v>
       </c>
       <c r="H879" t="n">
         <v>146400</v>
@@ -25918,7 +25918,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G881" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H881" t="n">
         <v>324000</v>
@@ -25947,7 +25947,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G882" t="n">
-        <v>1.24598956108093</v>
+        <v>1.24598968029022</v>
       </c>
       <c r="H882" t="n">
         <v>376800</v>
@@ -25976,7 +25976,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G883" t="n">
-        <v>1.25050401687622</v>
+        <v>1.25050413608551</v>
       </c>
       <c r="H883" t="n">
         <v>192900</v>
@@ -26005,7 +26005,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G884" t="n">
-        <v>1.25501847267151</v>
+        <v>1.2550185918808</v>
       </c>
       <c r="H884" t="n">
         <v>78600</v>
@@ -26121,7 +26121,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G888" t="n">
-        <v>1.22793173789978</v>
+        <v>1.22793185710907</v>
       </c>
       <c r="H888" t="n">
         <v>5100</v>
@@ -26237,7 +26237,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G892" t="n">
-        <v>1.22793173789978</v>
+        <v>1.22793185710907</v>
       </c>
       <c r="H892" t="n">
         <v>12600</v>
@@ -26527,7 +26527,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G902" t="n">
-        <v>1.19633066654205</v>
+        <v>1.19633054733276</v>
       </c>
       <c r="H902" t="n">
         <v>20400</v>
@@ -26701,7 +26701,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G908" t="n">
-        <v>1.14215695858002</v>
+        <v>1.14215707778931</v>
       </c>
       <c r="H908" t="n">
         <v>3600</v>
@@ -26759,7 +26759,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G910" t="n">
-        <v>1.08798372745514</v>
+        <v>1.08798360824585</v>
       </c>
       <c r="H910" t="n">
         <v>8100</v>
@@ -26788,7 +26788,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G911" t="n">
-        <v>1.10152697563171</v>
+        <v>1.101527094841</v>
       </c>
       <c r="H911" t="n">
         <v>2100</v>
@@ -26817,7 +26817,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G912" t="n">
-        <v>1.10152697563171</v>
+        <v>1.101527094841</v>
       </c>
       <c r="H912" t="n">
         <v>1200</v>
@@ -26875,7 +26875,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G914" t="n">
-        <v>1.106041431427</v>
+        <v>1.10604155063629</v>
       </c>
       <c r="H914" t="n">
         <v>900</v>
@@ -26904,7 +26904,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G915" t="n">
-        <v>1.09249818325043</v>
+        <v>1.09249806404114</v>
       </c>
       <c r="H915" t="n">
         <v>13500</v>
@@ -26962,7 +26962,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G917" t="n">
-        <v>1.09249818325043</v>
+        <v>1.09249806404114</v>
       </c>
       <c r="H917" t="n">
         <v>3300</v>
@@ -26991,7 +26991,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G918" t="n">
-        <v>1.09249818325043</v>
+        <v>1.09249806404114</v>
       </c>
       <c r="H918" t="n">
         <v>0</v>
@@ -27020,7 +27020,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>1.16472947597504</v>
+        <v>1.16472923755646</v>
       </c>
       <c r="H919" t="n">
         <v>21000</v>
@@ -27049,7 +27049,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G920" t="n">
-        <v>1.16021490097046</v>
+        <v>1.16021478176117</v>
       </c>
       <c r="H920" t="n">
         <v>3900</v>
@@ -27078,7 +27078,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G921" t="n">
-        <v>1.16021490097046</v>
+        <v>1.16021478176117</v>
       </c>
       <c r="H921" t="n">
         <v>3000</v>
@@ -27107,7 +27107,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G922" t="n">
-        <v>1.16472947597504</v>
+        <v>1.16472923755646</v>
       </c>
       <c r="H922" t="n">
         <v>15000</v>
@@ -27136,7 +27136,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G923" t="n">
-        <v>1.14215695858002</v>
+        <v>1.14215707778931</v>
       </c>
       <c r="H923" t="n">
         <v>4200</v>
@@ -27194,7 +27194,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G925" t="n">
-        <v>1.14215695858002</v>
+        <v>1.14215707778931</v>
       </c>
       <c r="H925" t="n">
         <v>1200</v>
@@ -27223,7 +27223,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G926" t="n">
-        <v>1.22793173789978</v>
+        <v>1.22793185710907</v>
       </c>
       <c r="H926" t="n">
         <v>16500</v>
@@ -27252,7 +27252,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G927" t="n">
-        <v>1.22793173789978</v>
+        <v>1.22793185710907</v>
       </c>
       <c r="H927" t="n">
         <v>60300</v>
@@ -27339,7 +27339,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G930" t="n">
-        <v>1.24598956108093</v>
+        <v>1.24598968029022</v>
       </c>
       <c r="H930" t="n">
         <v>8400</v>
@@ -27368,7 +27368,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G931" t="n">
-        <v>1.25501847267151</v>
+        <v>1.2550185918808</v>
       </c>
       <c r="H931" t="n">
         <v>17400</v>
@@ -27397,7 +27397,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G932" t="n">
-        <v>1.25501847267151</v>
+        <v>1.2550185918808</v>
       </c>
       <c r="H932" t="n">
         <v>0</v>
@@ -27426,7 +27426,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G933" t="n">
-        <v>1.31822085380554</v>
+        <v>1.31822097301483</v>
       </c>
       <c r="H933" t="n">
         <v>58200</v>
@@ -27484,7 +27484,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G935" t="n">
-        <v>1.67937731742859</v>
+        <v>1.6793771982193</v>
       </c>
       <c r="H935" t="n">
         <v>272400</v>
@@ -27571,7 +27571,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G938" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H938" t="n">
         <v>60000</v>
@@ -27600,7 +27600,7 @@
         <v>1.75</v>
       </c>
       <c r="G939" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H939" t="n">
         <v>30600</v>
@@ -27629,7 +27629,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G940" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H940" t="n">
         <v>57000</v>
@@ -27658,7 +27658,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G941" t="n">
-        <v>1.64777624607086</v>
+        <v>1.64777600765228</v>
       </c>
       <c r="H941" t="n">
         <v>159900</v>
@@ -27890,7 +27890,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G949" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H949" t="n">
         <v>36900</v>
@@ -27977,7 +27977,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G952" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H952" t="n">
         <v>20100</v>
@@ -28064,7 +28064,7 @@
         <v>1.5</v>
       </c>
       <c r="G955" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H955" t="n">
         <v>54600</v>
@@ -28093,7 +28093,7 @@
         <v>1.5</v>
       </c>
       <c r="G956" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H956" t="n">
         <v>15000</v>
@@ -28209,7 +28209,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G960" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H960" t="n">
         <v>121200</v>
@@ -28238,7 +28238,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G961" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H961" t="n">
         <v>116400</v>
@@ -28325,7 +28325,7 @@
         <v>1.5</v>
       </c>
       <c r="G964" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H964" t="n">
         <v>15900</v>
@@ -28354,7 +28354,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G965" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H965" t="n">
         <v>12900</v>
@@ -28383,7 +28383,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G966" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H966" t="n">
         <v>35400</v>
@@ -28412,7 +28412,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G967" t="n">
-        <v>1.35885083675385</v>
+        <v>1.35885095596313</v>
       </c>
       <c r="H967" t="n">
         <v>54900</v>
@@ -28441,7 +28441,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G968" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H968" t="n">
         <v>28500</v>
@@ -28499,7 +28499,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G970" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H970" t="n">
         <v>59100</v>
@@ -28557,7 +28557,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G972" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H972" t="n">
         <v>58800</v>
@@ -28586,7 +28586,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G973" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H973" t="n">
         <v>45600</v>
@@ -28615,7 +28615,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G974" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H974" t="n">
         <v>46200</v>
@@ -28731,7 +28731,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G978" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H978" t="n">
         <v>5700</v>
@@ -28847,7 +28847,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G982" t="n">
-        <v>1.52588593959808</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H982" t="n">
         <v>41400</v>
@@ -28905,7 +28905,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G984" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H984" t="n">
         <v>6300</v>
@@ -28934,7 +28934,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G985" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H985" t="n">
         <v>24000</v>
@@ -28992,7 +28992,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G987" t="n">
-        <v>1.52588593959808</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H987" t="n">
         <v>38700</v>
@@ -29050,7 +29050,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G989" t="n">
-        <v>1.52588593959808</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H989" t="n">
         <v>57300</v>
@@ -29079,7 +29079,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G990" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H990" t="n">
         <v>18300</v>
@@ -29108,7 +29108,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G991" t="n">
-        <v>1.54845809936523</v>
+        <v>1.54845821857452</v>
       </c>
       <c r="H991" t="n">
         <v>6000</v>
@@ -29166,7 +29166,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G993" t="n">
-        <v>1.54845809936523</v>
+        <v>1.54845821857452</v>
       </c>
       <c r="H993" t="n">
         <v>60300</v>
@@ -29224,7 +29224,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H995" t="n">
         <v>3300</v>
@@ -29311,7 +29311,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G998" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H998" t="n">
         <v>14400</v>
@@ -29456,7 +29456,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1003" t="n">
         <v>69900</v>
@@ -29485,7 +29485,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1004" t="n">
         <v>28800</v>
@@ -29572,7 +29572,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H1007" t="n">
         <v>3900</v>
@@ -29601,7 +29601,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1008" t="n">
         <v>4200</v>
@@ -29659,7 +29659,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.4897700548172</v>
+        <v>1.48977017402649</v>
       </c>
       <c r="H1010" t="n">
         <v>4800</v>
@@ -29862,7 +29862,7 @@
         <v>1.5</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1017" t="n">
         <v>26400</v>
@@ -29891,7 +29891,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.30919206142426</v>
+        <v>1.30919194221497</v>
       </c>
       <c r="H1018" t="n">
         <v>7200</v>
@@ -29949,7 +29949,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.32273530960083</v>
+        <v>1.32273542881012</v>
       </c>
       <c r="H1020" t="n">
         <v>10500</v>
@@ -29978,7 +29978,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.30919206142426</v>
+        <v>1.30919194221497</v>
       </c>
       <c r="H1021" t="n">
         <v>6900</v>
@@ -30007,7 +30007,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.26856195926666</v>
+        <v>1.26856184005737</v>
       </c>
       <c r="H1022" t="n">
         <v>40200</v>
@@ -30210,7 +30210,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1029" t="n">
         <v>8700</v>
@@ -30268,7 +30268,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H1031" t="n">
         <v>16200</v>
@@ -30326,7 +30326,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.45816898345947</v>
+        <v>1.45816886425018</v>
       </c>
       <c r="H1033" t="n">
         <v>9300</v>
@@ -30355,7 +30355,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.45816898345947</v>
+        <v>1.45816886425018</v>
       </c>
       <c r="H1034" t="n">
         <v>24000</v>
@@ -30442,7 +30442,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1037" t="n">
         <v>2100</v>
@@ -30500,7 +30500,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1039" t="n">
         <v>300</v>
@@ -30529,7 +30529,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H1040" t="n">
         <v>1500</v>
@@ -30558,7 +30558,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -30616,7 +30616,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1043" t="n">
         <v>4800</v>
@@ -30674,7 +30674,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1045" t="n">
         <v>20100</v>
@@ -30703,7 +30703,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1046" t="n">
         <v>3300</v>
@@ -30732,7 +30732,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1047" t="n">
         <v>3900</v>
@@ -30761,7 +30761,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1048" t="n">
         <v>300</v>
@@ -31109,7 +31109,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1060" t="n">
         <v>5700</v>
@@ -31167,7 +31167,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H1062" t="n">
         <v>7800</v>
@@ -31196,7 +31196,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.34079325199127</v>
+        <v>1.34079313278198</v>
       </c>
       <c r="H1063" t="n">
         <v>6000</v>
@@ -31254,7 +31254,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.27307617664337</v>
+        <v>1.27307629585266</v>
       </c>
       <c r="H1065" t="n">
         <v>64500</v>
@@ -31341,7 +31341,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.25953304767609</v>
+        <v>1.2595329284668</v>
       </c>
       <c r="H1068" t="n">
         <v>2100</v>
@@ -31370,7 +31370,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.25953304767609</v>
+        <v>1.2595329284668</v>
       </c>
       <c r="H1069" t="n">
         <v>600</v>
@@ -31399,7 +31399,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.25953304767609</v>
+        <v>1.2595329284668</v>
       </c>
       <c r="H1070" t="n">
         <v>600</v>
@@ -31515,7 +31515,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.18730175495148</v>
+        <v>1.18730163574219</v>
       </c>
       <c r="H1074" t="n">
         <v>1800</v>
@@ -31602,7 +31602,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.29564845561981</v>
+        <v>1.2956485748291</v>
       </c>
       <c r="H1077" t="n">
         <v>52800</v>
@@ -31631,7 +31631,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.38593769073486</v>
+        <v>1.38593757152557</v>
       </c>
       <c r="H1078" t="n">
         <v>40200</v>
@@ -31660,7 +31660,7 @@
         <v>1.5</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1079" t="n">
         <v>71400</v>
@@ -31718,7 +31718,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1081" t="n">
         <v>22200</v>
@@ -31747,7 +31747,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H1082" t="n">
         <v>25500</v>
@@ -31776,7 +31776,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1083" t="n">
         <v>15900</v>
@@ -31834,7 +31834,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1085" t="n">
         <v>9300</v>
@@ -31892,7 +31892,7 @@
         <v>1.75</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1087" t="n">
         <v>179400</v>
@@ -31979,7 +31979,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.54845809936523</v>
+        <v>1.54845821857452</v>
       </c>
       <c r="H1090" t="n">
         <v>3300</v>
@@ -32008,7 +32008,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H1091" t="n">
         <v>9000</v>
@@ -32211,7 +32211,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H1098" t="n">
         <v>3300</v>
@@ -32298,7 +32298,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H1101" t="n">
         <v>2700</v>
@@ -32414,7 +32414,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H1105" t="n">
         <v>12300</v>
@@ -32472,7 +32472,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.45816898345947</v>
+        <v>1.45816886425018</v>
       </c>
       <c r="H1107" t="n">
         <v>1200</v>
@@ -32588,7 +32588,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.38593769073486</v>
+        <v>1.38593757152557</v>
       </c>
       <c r="H1111" t="n">
         <v>56400</v>
@@ -32617,7 +32617,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.35885083675385</v>
+        <v>1.35885095596313</v>
       </c>
       <c r="H1112" t="n">
         <v>9600</v>
@@ -32646,7 +32646,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.38593769073486</v>
+        <v>1.38593757152557</v>
       </c>
       <c r="H1113" t="n">
         <v>5700</v>
@@ -32733,7 +32733,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1116" t="n">
         <v>300</v>
@@ -32791,7 +32791,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1118" t="n">
         <v>1200</v>
@@ -32820,7 +32820,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1119" t="n">
         <v>0</v>
@@ -33023,7 +33023,7 @@
         <v>1.5</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1126" t="n">
         <v>65700</v>
@@ -33081,7 +33081,7 @@
         <v>1.5</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1128" t="n">
         <v>42600</v>
@@ -33110,7 +33110,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H1129" t="n">
         <v>75900</v>
@@ -33197,7 +33197,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H1132" t="n">
         <v>5700</v>
@@ -33226,7 +33226,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H1133" t="n">
         <v>3000</v>
@@ -33313,7 +33313,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H1136" t="n">
         <v>13200</v>
@@ -33342,7 +33342,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1137" t="n">
         <v>600</v>
@@ -33400,7 +33400,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.45816898345947</v>
+        <v>1.45816886425018</v>
       </c>
       <c r="H1139" t="n">
         <v>4200</v>
@@ -33429,7 +33429,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H1140" t="n">
         <v>6300</v>
@@ -33458,7 +33458,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1141" t="n">
         <v>5400</v>
@@ -33661,7 +33661,7 @@
         <v>1.5</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1148" t="n">
         <v>21900</v>
@@ -33690,7 +33690,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1149" t="n">
         <v>75600</v>
@@ -33777,7 +33777,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1152" t="n">
         <v>51900</v>
@@ -33806,7 +33806,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1153" t="n">
         <v>64800</v>
@@ -34241,7 +34241,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1168" t="n">
         <v>4500</v>
@@ -34270,7 +34270,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1169" t="n">
         <v>0</v>
@@ -34560,7 +34560,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1179" t="n">
         <v>53400</v>
@@ -34821,7 +34821,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H1188" t="n">
         <v>9000</v>
@@ -34966,7 +34966,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1193" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H1193" t="n">
         <v>13200</v>
@@ -35169,7 +35169,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1200" t="n">
         <v>2100</v>
@@ -35198,7 +35198,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1201" t="n">
         <v>0</v>
@@ -35227,7 +35227,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1202" t="n">
         <v>0</v>
@@ -35256,7 +35256,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.4897700548172</v>
+        <v>1.48977017402649</v>
       </c>
       <c r="H1203" t="n">
         <v>2700</v>
@@ -35488,7 +35488,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.45816898345947</v>
+        <v>1.45816886425018</v>
       </c>
       <c r="H1211" t="n">
         <v>36000</v>
@@ -35546,7 +35546,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.4897700548172</v>
+        <v>1.48977017402649</v>
       </c>
       <c r="H1213" t="n">
         <v>23400</v>
@@ -35575,7 +35575,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.45816898345947</v>
+        <v>1.45816886425018</v>
       </c>
       <c r="H1214" t="n">
         <v>13200</v>
@@ -35604,7 +35604,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.45816898345947</v>
+        <v>1.45816886425018</v>
       </c>
       <c r="H1215" t="n">
         <v>0</v>
@@ -35633,7 +35633,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.4897700548172</v>
+        <v>1.48977017402649</v>
       </c>
       <c r="H1216" t="n">
         <v>6600</v>
@@ -35662,7 +35662,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H1217" t="n">
         <v>2400</v>
@@ -35691,7 +35691,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.45816898345947</v>
+        <v>1.45816886425018</v>
       </c>
       <c r="H1218" t="n">
         <v>5400</v>
@@ -35778,7 +35778,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H1221" t="n">
         <v>4500</v>
@@ -35807,7 +35807,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H1222" t="n">
         <v>0</v>
@@ -35836,7 +35836,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H1223" t="n">
         <v>0</v>
@@ -35981,7 +35981,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.4897700548172</v>
+        <v>1.48977017402649</v>
       </c>
       <c r="H1228" t="n">
         <v>21900</v>
@@ -36387,7 +36387,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H1242" t="n">
         <v>10500</v>
@@ -36677,7 +36677,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.52588593959808</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H1252" t="n">
         <v>8700</v>
@@ -36706,7 +36706,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.52588593959808</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H1253" t="n">
         <v>11100</v>
@@ -37083,7 +37083,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H1266" t="n">
         <v>6600</v>
@@ -37112,7 +37112,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H1267" t="n">
         <v>0</v>
@@ -37141,7 +37141,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1268" t="n">
         <v>3900</v>
@@ -37228,7 +37228,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1271" t="n">
         <v>4500</v>
@@ -37257,7 +37257,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1272" t="n">
         <v>2100</v>
@@ -37286,7 +37286,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1273" t="n">
         <v>0</v>
@@ -37315,7 +37315,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.45365452766418</v>
+        <v>1.4536544084549</v>
       </c>
       <c r="H1274" t="n">
         <v>0</v>
@@ -37373,7 +37373,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1276" t="n">
         <v>8100</v>
@@ -37460,7 +37460,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.45816898345947</v>
+        <v>1.45816886425018</v>
       </c>
       <c r="H1279" t="n">
         <v>1500</v>
@@ -37489,7 +37489,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.45816898345947</v>
+        <v>1.45816886425018</v>
       </c>
       <c r="H1280" t="n">
         <v>0</v>
@@ -37547,7 +37547,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1282" t="n">
         <v>4500</v>
@@ -37576,7 +37576,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1283" t="n">
         <v>0</v>
@@ -37605,7 +37605,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H1284" t="n">
         <v>7500</v>
@@ -37634,7 +37634,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H1285" t="n">
         <v>28500</v>
@@ -37692,7 +37692,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H1287" t="n">
         <v>600</v>
@@ -37721,7 +37721,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.46268343925476</v>
+        <v>1.46268332004547</v>
       </c>
       <c r="H1288" t="n">
         <v>14400</v>
@@ -37750,7 +37750,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.49879896640778</v>
+        <v>1.49879908561707</v>
       </c>
       <c r="H1289" t="n">
         <v>6900</v>
@@ -37953,7 +37953,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1296" t="n">
         <v>1500</v>
@@ -37982,7 +37982,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H1297" t="n">
         <v>2400</v>
@@ -38069,7 +38069,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1300" t="n">
         <v>19800</v>
@@ -38098,7 +38098,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1301" t="n">
         <v>0</v>
@@ -38156,7 +38156,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1303" t="n">
         <v>1500</v>
@@ -38185,7 +38185,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1304" t="n">
         <v>7500</v>
@@ -38272,7 +38272,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1307" t="n">
         <v>8400</v>
@@ -38504,7 +38504,7 @@
         <v>1.5</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1315" t="n">
         <v>4200</v>
@@ -38533,7 +38533,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H1316" t="n">
         <v>55800</v>
@@ -38765,7 +38765,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1324" t="n">
         <v>13800</v>
@@ -38794,7 +38794,7 @@
         <v>1.5</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1325" t="n">
         <v>12600</v>
@@ -38823,7 +38823,7 @@
         <v>1.5</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1326" t="n">
         <v>9300</v>
@@ -38852,7 +38852,7 @@
         <v>1.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1327" t="n">
         <v>10500</v>
@@ -38968,7 +38968,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H1331" t="n">
         <v>48900</v>
@@ -38997,7 +38997,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1332" t="n">
         <v>10500</v>
@@ -39026,7 +39026,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.38593769073486</v>
+        <v>1.38593757152557</v>
       </c>
       <c r="H1333" t="n">
         <v>7500</v>
@@ -39055,7 +39055,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.35885083675385</v>
+        <v>1.35885095596313</v>
       </c>
       <c r="H1334" t="n">
         <v>31200</v>
@@ -39142,7 +39142,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.34982216358185</v>
+        <v>1.34982204437256</v>
       </c>
       <c r="H1337" t="n">
         <v>60300</v>
@@ -39200,7 +39200,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1339" t="n">
         <v>6300</v>
@@ -39374,7 +39374,7 @@
         <v>1.5</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1345" t="n">
         <v>22800</v>
@@ -39693,7 +39693,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.32724976539612</v>
+        <v>1.32724988460541</v>
       </c>
       <c r="H1356" t="n">
         <v>28200</v>
@@ -39722,7 +39722,7 @@
         <v>1.5</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1357" t="n">
         <v>8100</v>
@@ -39751,7 +39751,7 @@
         <v>1.5</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1358" t="n">
         <v>3000</v>
@@ -39809,7 +39809,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H1360" t="n">
         <v>3600</v>
@@ -39983,7 +39983,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H1366" t="n">
         <v>4500</v>
@@ -40041,7 +40041,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H1368" t="n">
         <v>300</v>
@@ -40128,7 +40128,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H1371" t="n">
         <v>8100</v>
@@ -40157,7 +40157,7 @@
         <v>1.5</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1372" t="n">
         <v>432000</v>
@@ -40186,7 +40186,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1373" t="n">
         <v>41100</v>
@@ -40215,7 +40215,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1374" t="n">
         <v>17400</v>
@@ -40244,7 +40244,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1375" t="n">
         <v>1500</v>
@@ -40331,7 +40331,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1378" t="n">
         <v>9300</v>
@@ -40360,7 +40360,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1379" t="n">
         <v>10200</v>
@@ -40389,7 +40389,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1380" t="n">
         <v>0</v>
@@ -40737,7 +40737,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.64777624607086</v>
+        <v>1.64777600765228</v>
       </c>
       <c r="H1392" t="n">
         <v>238200</v>
@@ -40766,7 +40766,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H1393" t="n">
         <v>120900</v>
@@ -40824,7 +40824,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.61617481708527</v>
+        <v>1.61617493629456</v>
       </c>
       <c r="H1395" t="n">
         <v>23400</v>
@@ -40882,7 +40882,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.60263156890869</v>
+        <v>1.6026314496994</v>
       </c>
       <c r="H1397" t="n">
         <v>105900</v>
@@ -41056,7 +41056,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.61617481708527</v>
+        <v>1.61617493629456</v>
       </c>
       <c r="H1403" t="n">
         <v>21600</v>
@@ -41201,7 +41201,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1408" t="n">
         <v>18000</v>
@@ -41230,7 +41230,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1409" t="n">
-        <v>1.54845809936523</v>
+        <v>1.54845821857452</v>
       </c>
       <c r="H1409" t="n">
         <v>27900</v>
@@ -41288,7 +41288,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.52588593959808</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H1411" t="n">
         <v>9000</v>
@@ -41375,7 +41375,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.57554483413696</v>
+        <v>1.57554471492767</v>
       </c>
       <c r="H1414" t="n">
         <v>6600</v>
@@ -41404,7 +41404,7 @@
         <v>1.75</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1415" t="n">
         <v>1200</v>
@@ -41462,7 +41462,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1417" t="n">
         <v>17700</v>
@@ -41520,7 +41520,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.60263156890869</v>
+        <v>1.6026314496994</v>
       </c>
       <c r="H1419" t="n">
         <v>10500</v>
@@ -41549,7 +41549,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.61166048049927</v>
+        <v>1.61166036128998</v>
       </c>
       <c r="H1420" t="n">
         <v>6000</v>
@@ -41607,7 +41607,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1422" t="n">
         <v>28500</v>
@@ -41636,7 +41636,7 @@
         <v>1.75</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1423" t="n">
         <v>13500</v>
@@ -41665,7 +41665,7 @@
         <v>1.75</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1424" t="n">
         <v>0</v>
@@ -41694,7 +41694,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.61166048049927</v>
+        <v>1.61166036128998</v>
       </c>
       <c r="H1425" t="n">
         <v>17400</v>
@@ -41723,7 +41723,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.61166048049927</v>
+        <v>1.61166036128998</v>
       </c>
       <c r="H1426" t="n">
         <v>4800</v>
@@ -41752,7 +41752,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H1427" t="n">
         <v>19500</v>
@@ -41868,7 +41868,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H1431" t="n">
         <v>5100</v>
@@ -41897,7 +41897,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.57554483413696</v>
+        <v>1.57554471492767</v>
       </c>
       <c r="H1432" t="n">
         <v>12000</v>
@@ -41926,7 +41926,7 @@
         <v>1.75</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1433" t="n">
         <v>20100</v>
@@ -42013,7 +42013,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.54845809936523</v>
+        <v>1.54845821857452</v>
       </c>
       <c r="H1436" t="n">
         <v>26100</v>
@@ -42071,7 +42071,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1438" t="n">
         <v>16800</v>
@@ -42100,7 +42100,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1439" t="n">
         <v>10800</v>
@@ -42187,7 +42187,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1442" t="n">
         <v>900</v>
@@ -42419,7 +42419,7 @@
         <v>1.75</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1450" t="n">
         <v>17100</v>
@@ -42477,7 +42477,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H1452" t="n">
         <v>6600</v>
@@ -42506,7 +42506,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H1453" t="n">
         <v>0</v>
@@ -42796,7 +42796,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1463" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H1463" t="n">
         <v>4200</v>
@@ -42825,7 +42825,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.51234233379364</v>
+        <v>1.51234245300293</v>
       </c>
       <c r="H1464" t="n">
         <v>0</v>
@@ -42883,7 +42883,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H1466" t="n">
         <v>4200</v>
@@ -42912,7 +42912,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H1467" t="n">
         <v>3000</v>
@@ -42941,7 +42941,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.54845809936523</v>
+        <v>1.54845821857452</v>
       </c>
       <c r="H1468" t="n">
         <v>3000</v>
@@ -43028,7 +43028,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.52588593959808</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H1471" t="n">
         <v>23400</v>
@@ -43086,7 +43086,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.60263156890869</v>
+        <v>1.6026314496994</v>
       </c>
       <c r="H1473" t="n">
         <v>121200</v>
@@ -43115,7 +43115,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1474" t="n">
         <v>50700</v>
@@ -43173,7 +43173,7 @@
         <v>1.75</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1476" t="n">
         <v>4500</v>
@@ -43318,7 +43318,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H1481" t="n">
         <v>6300</v>
@@ -43550,7 +43550,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1489" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H1489" t="n">
         <v>18300</v>
@@ -43782,7 +43782,7 @@
         <v>1.75</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1497" t="n">
         <v>22800</v>
@@ -44043,7 +44043,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.52588593959808</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H1506" t="n">
         <v>10200</v>
@@ -44101,7 +44101,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>1.52588593959808</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H1508" t="n">
         <v>2700</v>
@@ -44130,7 +44130,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.52588593959808</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H1509" t="n">
         <v>11100</v>
@@ -44246,7 +44246,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.57554483413696</v>
+        <v>1.57554471492767</v>
       </c>
       <c r="H1513" t="n">
         <v>1200</v>
@@ -44275,7 +44275,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.56651604175568</v>
+        <v>1.56651592254639</v>
       </c>
       <c r="H1514" t="n">
         <v>3900</v>
@@ -44304,7 +44304,7 @@
         <v>1.75</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1515" t="n">
         <v>900</v>
@@ -44391,7 +44391,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1518" t="n">
-        <v>1.57554483413696</v>
+        <v>1.57554471492767</v>
       </c>
       <c r="H1518" t="n">
         <v>5400</v>
@@ -44478,7 +44478,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H1521" t="n">
         <v>11100</v>
@@ -44507,7 +44507,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H1522" t="n">
         <v>4200</v>
@@ -44565,7 +44565,7 @@
         <v>1.75</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1524" t="n">
         <v>44400</v>
@@ -44594,7 +44594,7 @@
         <v>1.75</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1525" t="n">
         <v>0</v>
@@ -44623,7 +44623,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1526" t="n">
         <v>1800</v>
@@ -44652,7 +44652,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1527" t="n">
         <v>2700</v>
@@ -44681,7 +44681,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.61166048049927</v>
+        <v>1.61166036128998</v>
       </c>
       <c r="H1528" t="n">
         <v>12600</v>
@@ -44710,7 +44710,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H1529" t="n">
         <v>7500</v>
@@ -44739,7 +44739,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1530" t="n">
         <v>5100</v>
@@ -44768,7 +44768,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1531" t="n">
         <v>0</v>
@@ -44913,7 +44913,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.69743514060974</v>
+        <v>1.69743502140045</v>
       </c>
       <c r="H1536" t="n">
         <v>46800</v>
@@ -45000,7 +45000,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1539" t="n">
-        <v>1.68389177322388</v>
+        <v>1.68389165401459</v>
       </c>
       <c r="H1539" t="n">
         <v>14700</v>
@@ -45058,7 +45058,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1541" t="n">
-        <v>1.64777624607086</v>
+        <v>1.64777600765228</v>
       </c>
       <c r="H1541" t="n">
         <v>2700</v>
@@ -45145,7 +45145,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H1544" t="n">
         <v>6300</v>
@@ -45174,7 +45174,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H1545" t="n">
         <v>600</v>
@@ -45203,7 +45203,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1546" t="n">
-        <v>1.62068927288055</v>
+        <v>1.62068939208984</v>
       </c>
       <c r="H1546" t="n">
         <v>3000</v>
@@ -45261,7 +45261,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1548" t="n">
         <v>4200</v>
@@ -45290,7 +45290,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H1549" t="n">
         <v>10500</v>
@@ -45319,7 +45319,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1550" t="n">
-        <v>1.66583383083344</v>
+        <v>1.66583395004272</v>
       </c>
       <c r="H1550" t="n">
         <v>5100</v>
@@ -45435,7 +45435,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1554" t="n">
-        <v>1.68389177322388</v>
+        <v>1.68389165401459</v>
       </c>
       <c r="H1554" t="n">
         <v>4500</v>
@@ -45493,7 +45493,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1556" t="n">
-        <v>1.67937731742859</v>
+        <v>1.6793771982193</v>
       </c>
       <c r="H1556" t="n">
         <v>3300</v>
@@ -45551,7 +45551,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1558" t="n">
-        <v>1.69743514060974</v>
+        <v>1.69743502140045</v>
       </c>
       <c r="H1558" t="n">
         <v>22200</v>
@@ -45580,7 +45580,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1559" t="n">
-        <v>1.69743514060974</v>
+        <v>1.69743502140045</v>
       </c>
       <c r="H1559" t="n">
         <v>1500</v>
@@ -45754,7 +45754,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1565" t="n">
-        <v>1.66583383083344</v>
+        <v>1.66583395004272</v>
       </c>
       <c r="H1565" t="n">
         <v>8400</v>
@@ -45812,7 +45812,7 @@
         <v>1.75</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1567" t="n">
         <v>38700</v>
@@ -45957,7 +45957,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.64777624607086</v>
+        <v>1.64777600765228</v>
       </c>
       <c r="H1572" t="n">
         <v>13200</v>
@@ -45986,7 +45986,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1573" t="n">
-        <v>1.61166048049927</v>
+        <v>1.61166036128998</v>
       </c>
       <c r="H1573" t="n">
         <v>8700</v>
@@ -46247,7 +46247,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1582" t="n">
-        <v>1.61617481708527</v>
+        <v>1.61617493629456</v>
       </c>
       <c r="H1582" t="n">
         <v>8100</v>
@@ -46363,7 +46363,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H1586" t="n">
         <v>7500</v>
@@ -46450,7 +46450,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.62068927288055</v>
+        <v>1.62068939208984</v>
       </c>
       <c r="H1589" t="n">
         <v>18900</v>
@@ -46508,7 +46508,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.62068927288055</v>
+        <v>1.62068939208984</v>
       </c>
       <c r="H1591" t="n">
         <v>11400</v>
@@ -46537,7 +46537,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.61617481708527</v>
+        <v>1.61617493629456</v>
       </c>
       <c r="H1592" t="n">
         <v>1200</v>
@@ -46566,7 +46566,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.61617481708527</v>
+        <v>1.61617493629456</v>
       </c>
       <c r="H1593" t="n">
         <v>6000</v>
@@ -46740,7 +46740,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.84189760684967</v>
+        <v>1.84189772605896</v>
       </c>
       <c r="H1599" t="n">
         <v>343200</v>
@@ -46769,7 +46769,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.88704216480255</v>
+        <v>1.88704204559326</v>
       </c>
       <c r="H1600" t="n">
         <v>381900</v>
@@ -46827,7 +46827,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.04956245422363</v>
+        <v>2.04956269264221</v>
       </c>
       <c r="H1602" t="n">
         <v>380700</v>
@@ -46856,7 +46856,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.12179350852966</v>
+        <v>2.12179398536682</v>
       </c>
       <c r="H1603" t="n">
         <v>147900</v>
@@ -46914,7 +46914,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.12179350852966</v>
+        <v>2.12179398536682</v>
       </c>
       <c r="H1605" t="n">
         <v>38100</v>
@@ -46943,7 +46943,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1606" t="n">
-        <v>2.05859136581421</v>
+        <v>2.05859160423279</v>
       </c>
       <c r="H1606" t="n">
         <v>98400</v>
@@ -47030,7 +47030,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.04956245422363</v>
+        <v>2.04956269264221</v>
       </c>
       <c r="H1609" t="n">
         <v>36000</v>
@@ -47146,7 +47146,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.95927345752716</v>
+        <v>1.95927369594574</v>
       </c>
       <c r="H1613" t="n">
         <v>45000</v>
@@ -47175,7 +47175,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H1614" t="n">
         <v>6300</v>
@@ -47204,7 +47204,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1615" t="n">
-        <v>1.95927345752716</v>
+        <v>1.95927369594574</v>
       </c>
       <c r="H1615" t="n">
         <v>12000</v>
@@ -47523,7 +47523,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.10373616218567</v>
+        <v>2.10373592376709</v>
       </c>
       <c r="H1626" t="n">
         <v>31800</v>
@@ -65567,6 +65567,35 @@
         <v>5400</v>
       </c>
       <c r="I2248" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2249" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2249" t="n">
+        <v>4.23000001907349</v>
+      </c>
+      <c r="D2249" t="n">
+        <v>4.23000001907349</v>
+      </c>
+      <c r="E2249" t="n">
+        <v>4.23000001907349</v>
+      </c>
+      <c r="F2249" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="G2249" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="H2249" t="n">
+        <v>600</v>
+      </c>
+      <c r="I2249" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H2" t="n">
         <v>326100</v>
@@ -485,7 +485,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G4" t="n">
-        <v>3.63684487342834</v>
+        <v>3.63684463500977</v>
       </c>
       <c r="H4" t="n">
         <v>17700</v>
@@ -514,7 +514,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H5" t="n">
         <v>14700</v>
@@ -630,7 +630,7 @@
         <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H9" t="n">
         <v>1200</v>
@@ -688,7 +688,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G11" t="n">
-        <v>3.63684487342834</v>
+        <v>3.63684463500977</v>
       </c>
       <c r="H11" t="n">
         <v>16500</v>
@@ -833,7 +833,7 @@
         <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H16" t="n">
         <v>600</v>
@@ -978,7 +978,7 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H21" t="n">
         <v>2100</v>
@@ -1007,7 +1007,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G22" t="n">
-        <v>3.62962198257446</v>
+        <v>3.62962174415588</v>
       </c>
       <c r="H22" t="n">
         <v>2700</v>
@@ -1036,7 +1036,7 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H23" t="n">
         <v>28500</v>
@@ -1065,7 +1065,7 @@
         <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>3.56641960144043</v>
+        <v>3.56641936302185</v>
       </c>
       <c r="H25" t="n">
         <v>6600</v>
@@ -1123,7 +1123,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>3.62962198257446</v>
+        <v>3.62962174415588</v>
       </c>
       <c r="H26" t="n">
         <v>5100</v>
@@ -1152,7 +1152,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G27" t="n">
-        <v>3.62059330940247</v>
+        <v>3.62059307098389</v>
       </c>
       <c r="H27" t="n">
         <v>1800</v>
@@ -1181,7 +1181,7 @@
         <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H28" t="n">
         <v>11400</v>
@@ -1210,7 +1210,7 @@
         <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H29" t="n">
         <v>4800</v>
@@ -1239,7 +1239,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G30" t="n">
-        <v>3.57544851303101</v>
+        <v>3.57544827461243</v>
       </c>
       <c r="H30" t="n">
         <v>300</v>
@@ -1268,7 +1268,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>3.57544851303101</v>
+        <v>3.57544827461243</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G37" t="n">
-        <v>3.5303041934967</v>
+        <v>3.53030371665955</v>
       </c>
       <c r="H37" t="n">
         <v>10200</v>
@@ -1471,7 +1471,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>3.52127504348755</v>
+        <v>3.52127528190613</v>
       </c>
       <c r="H38" t="n">
         <v>3600</v>
@@ -1500,7 +1500,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G39" t="n">
-        <v>3.52127504348755</v>
+        <v>3.52127528190613</v>
       </c>
       <c r="H39" t="n">
         <v>600</v>
@@ -1529,7 +1529,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H40" t="n">
         <v>6300</v>
@@ -1558,7 +1558,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G41" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H42" t="n">
         <v>3900</v>
@@ -1790,7 +1790,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>3.57544851303101</v>
+        <v>3.57544827461243</v>
       </c>
       <c r="H49" t="n">
         <v>1800</v>
@@ -1848,7 +1848,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H51" t="n">
         <v>17400</v>
@@ -2167,7 +2167,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H62" t="n">
         <v>1200</v>
@@ -2254,7 +2254,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G65" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H65" t="n">
         <v>1500</v>
@@ -2283,7 +2283,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G66" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G67" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G68" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G69" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G70" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G71" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H85" t="n">
         <v>7500</v>
@@ -2863,7 +2863,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H86" t="n">
         <v>2400</v>
@@ -2892,7 +2892,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G87" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H87" t="n">
         <v>3300</v>
@@ -2921,7 +2921,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G88" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G89" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>3.3587543964386</v>
+        <v>3.35875463485718</v>
       </c>
       <c r="H105" t="n">
         <v>900</v>
@@ -3559,7 +3559,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>3.29555201530457</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H110" t="n">
         <v>8100</v>
@@ -3617,7 +3617,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>3.2052628993988</v>
+        <v>3.20526313781738</v>
       </c>
       <c r="H112" t="n">
         <v>900</v>
@@ -3646,7 +3646,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>3.06982946395874</v>
+        <v>3.06982970237732</v>
       </c>
       <c r="H113" t="n">
         <v>5400</v>
@@ -3704,7 +3704,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>3.04274272918701</v>
+        <v>3.04274249076843</v>
       </c>
       <c r="H115" t="n">
         <v>600</v>
@@ -3733,7 +3733,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>3.04274272918701</v>
+        <v>3.04274249076843</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G117" t="n">
-        <v>3.06982946395874</v>
+        <v>3.06982970237732</v>
       </c>
       <c r="H117" t="n">
         <v>6900</v>
@@ -3791,7 +3791,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>3.06982946395874</v>
+        <v>3.06982970237732</v>
       </c>
       <c r="H118" t="n">
         <v>22800</v>
@@ -4023,7 +4023,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H126" t="n">
         <v>1800</v>
@@ -4052,7 +4052,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G127" t="n">
-        <v>3.45807242393494</v>
+        <v>3.45807266235352</v>
       </c>
       <c r="H127" t="n">
         <v>30600</v>
@@ -4168,7 +4168,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H131" t="n">
         <v>1500</v>
@@ -4197,7 +4197,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H132" t="n">
         <v>2100</v>
@@ -4284,7 +4284,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G135" t="n">
-        <v>3.29555201530457</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H135" t="n">
         <v>300</v>
@@ -4313,7 +4313,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>3.29555201530457</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G149" t="n">
-        <v>3.29555201530457</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H149" t="n">
         <v>3900</v>
@@ -4719,7 +4719,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>3.29555201530457</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G151" t="n">
-        <v>3.29555201530457</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H151" t="n">
         <v>900</v>
@@ -5966,7 +5966,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G193" t="n">
-        <v>3.1240029335022</v>
+        <v>3.12400269508362</v>
       </c>
       <c r="H193" t="n">
         <v>2100</v>
@@ -6256,7 +6256,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G203" t="n">
-        <v>3.09691643714905</v>
+        <v>3.09691619873047</v>
       </c>
       <c r="H203" t="n">
         <v>900</v>
@@ -6285,7 +6285,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G204" t="n">
-        <v>3.06982946395874</v>
+        <v>3.06982970237732</v>
       </c>
       <c r="H204" t="n">
         <v>1800</v>
@@ -6314,7 +6314,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>3.06982946395874</v>
+        <v>3.06982970237732</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>3.06982946395874</v>
+        <v>3.06982970237732</v>
       </c>
       <c r="H206" t="n">
         <v>1500</v>
@@ -6372,7 +6372,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>3.06982946395874</v>
+        <v>3.06982970237732</v>
       </c>
       <c r="H207" t="n">
         <v>300</v>
@@ -6749,7 +6749,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G220" t="n">
-        <v>2.66352844238281</v>
+        <v>2.66352868080139</v>
       </c>
       <c r="H220" t="n">
         <v>2100</v>
@@ -6807,7 +6807,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H222" t="n">
         <v>3900</v>
@@ -6836,7 +6836,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G223" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G225" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H225" t="n">
         <v>1200</v>
@@ -6923,7 +6923,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G226" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G227" t="n">
-        <v>2.63644194602966</v>
+        <v>2.63644170761108</v>
       </c>
       <c r="H227" t="n">
         <v>6000</v>
@@ -6981,7 +6981,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H228" t="n">
         <v>2700</v>
@@ -7010,7 +7010,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G230" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G231" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G232" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G236" t="n">
-        <v>2.5100371837616</v>
+        <v>2.51003670692444</v>
       </c>
       <c r="H236" t="n">
         <v>2700</v>
@@ -7242,7 +7242,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G237" t="n">
-        <v>2.5100371837616</v>
+        <v>2.51003670692444</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G249" t="n">
-        <v>2.5100371837616</v>
+        <v>2.51003670692444</v>
       </c>
       <c r="H249" t="n">
         <v>2100</v>
@@ -7619,7 +7619,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G250" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H250" t="n">
         <v>600</v>
@@ -7648,7 +7648,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G252" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G253" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G255" t="n">
-        <v>2.27528524398804</v>
+        <v>2.27528548240662</v>
       </c>
       <c r="H255" t="n">
         <v>2100</v>
@@ -7793,7 +7793,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>2.32945847511292</v>
+        <v>2.32945871353149</v>
       </c>
       <c r="H256" t="n">
         <v>1500</v>
@@ -7822,7 +7822,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>2.32945847511292</v>
+        <v>2.32945871353149</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G258" t="n">
-        <v>2.24819850921631</v>
+        <v>2.24819874763489</v>
       </c>
       <c r="H258" t="n">
         <v>1800</v>
@@ -7909,7 +7909,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G260" t="n">
-        <v>2.24819850921631</v>
+        <v>2.24819874763489</v>
       </c>
       <c r="H260" t="n">
         <v>900</v>
@@ -7996,7 +7996,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G263" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H263" t="n">
         <v>2100</v>
@@ -8025,7 +8025,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G264" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G265" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G267" t="n">
-        <v>2.42877697944641</v>
+        <v>2.42877674102783</v>
       </c>
       <c r="H267" t="n">
         <v>2100</v>
@@ -8141,7 +8141,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G268" t="n">
-        <v>2.47392129898071</v>
+        <v>2.47392153739929</v>
       </c>
       <c r="H268" t="n">
         <v>1500</v>
@@ -8170,7 +8170,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G269" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H269" t="n">
         <v>2400</v>
@@ -8315,7 +8315,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>2.27528524398804</v>
+        <v>2.27528548240662</v>
       </c>
       <c r="H274" t="n">
         <v>7500</v>
@@ -8373,7 +8373,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G276" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H276" t="n">
         <v>1200</v>
@@ -8402,7 +8402,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G277" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H277" t="n">
         <v>3600</v>
@@ -8518,7 +8518,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G281" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H281" t="n">
         <v>21000</v>
@@ -8721,7 +8721,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>2.18499612808228</v>
+        <v>2.18499636650085</v>
       </c>
       <c r="H288" t="n">
         <v>1200</v>
@@ -8750,7 +8750,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G289" t="n">
-        <v>2.18499612808228</v>
+        <v>2.18499636650085</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>2.15790963172913</v>
+        <v>2.15790939331055</v>
       </c>
       <c r="H290" t="n">
         <v>20700</v>
@@ -8808,7 +8808,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>2.12179398536682</v>
+        <v>2.12179374694824</v>
       </c>
       <c r="H291" t="n">
         <v>2400</v>
@@ -8866,7 +8866,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G293" t="n">
-        <v>2.06762051582336</v>
+        <v>2.06762027740479</v>
       </c>
       <c r="H293" t="n">
         <v>300</v>
@@ -9069,7 +9069,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G300" t="n">
-        <v>1.87801337242126</v>
+        <v>1.87801325321198</v>
       </c>
       <c r="H300" t="n">
         <v>7200</v>
@@ -9127,7 +9127,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>1.97733128070831</v>
+        <v>1.97733116149902</v>
       </c>
       <c r="H302" t="n">
         <v>4200</v>
@@ -9156,7 +9156,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G303" t="n">
-        <v>1.97733128070831</v>
+        <v>1.97733116149902</v>
       </c>
       <c r="H303" t="n">
         <v>300</v>
@@ -9214,7 +9214,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>1.95927369594574</v>
+        <v>1.95927345752716</v>
       </c>
       <c r="H305" t="n">
         <v>3900</v>
@@ -9243,7 +9243,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G306" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H306" t="n">
         <v>3600</v>
@@ -9359,7 +9359,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H310" t="n">
         <v>900</v>
@@ -9562,7 +9562,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G317" t="n">
-        <v>1.89607095718384</v>
+        <v>1.89607083797455</v>
       </c>
       <c r="H317" t="n">
         <v>6900</v>
@@ -9678,7 +9678,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G321" t="n">
-        <v>1.95024478435516</v>
+        <v>1.95024466514587</v>
       </c>
       <c r="H321" t="n">
         <v>600</v>
@@ -9707,7 +9707,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G322" t="n">
-        <v>1.95024478435516</v>
+        <v>1.95024466514587</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G323" t="n">
-        <v>1.95024478435516</v>
+        <v>1.95024466514587</v>
       </c>
       <c r="H323" t="n">
         <v>600</v>
@@ -9765,7 +9765,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G324" t="n">
-        <v>1.95024478435516</v>
+        <v>1.95024466514587</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G328" t="n">
-        <v>1.91412889957428</v>
+        <v>1.91412878036499</v>
       </c>
       <c r="H328" t="n">
         <v>51000</v>
@@ -9910,7 +9910,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G329" t="n">
-        <v>1.89607095718384</v>
+        <v>1.89607083797455</v>
       </c>
       <c r="H329" t="n">
         <v>3600</v>
@@ -9968,7 +9968,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G331" t="n">
-        <v>1.89607095718384</v>
+        <v>1.89607083797455</v>
       </c>
       <c r="H331" t="n">
         <v>27900</v>
@@ -9997,7 +9997,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G332" t="n">
-        <v>1.89607095718384</v>
+        <v>1.89607083797455</v>
       </c>
       <c r="H332" t="n">
         <v>4800</v>
@@ -10171,7 +10171,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G338" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H338" t="n">
         <v>18000</v>
@@ -10258,7 +10258,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G341" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H341" t="n">
         <v>1200</v>
@@ -10403,7 +10403,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>1.89607095718384</v>
+        <v>1.89607083797455</v>
       </c>
       <c r="H346" t="n">
         <v>29700</v>
@@ -10490,7 +10490,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G349" t="n">
-        <v>1.89607095718384</v>
+        <v>1.89607083797455</v>
       </c>
       <c r="H349" t="n">
         <v>5400</v>
@@ -10519,7 +10519,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G350" t="n">
-        <v>1.87801337242126</v>
+        <v>1.87801325321198</v>
       </c>
       <c r="H350" t="n">
         <v>2400</v>
@@ -10606,7 +10606,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G353" t="n">
-        <v>1.89607095718384</v>
+        <v>1.89607083797455</v>
       </c>
       <c r="H353" t="n">
         <v>1800</v>
@@ -10635,7 +10635,7 @@
         <v>2</v>
       </c>
       <c r="G354" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H354" t="n">
         <v>21600</v>
@@ -10693,7 +10693,7 @@
         <v>2</v>
       </c>
       <c r="G356" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H356" t="n">
         <v>1500</v>
@@ -10722,7 +10722,7 @@
         <v>2</v>
       </c>
       <c r="G357" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>2</v>
       </c>
       <c r="G358" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
         <v>2</v>
       </c>
       <c r="G359" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>2</v>
       </c>
       <c r="G360" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>2</v>
       </c>
       <c r="G361" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>2</v>
       </c>
       <c r="G362" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>2</v>
       </c>
       <c r="G363" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>2</v>
       </c>
       <c r="G365" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H365" t="n">
         <v>3000</v>
@@ -10983,7 +10983,7 @@
         <v>2</v>
       </c>
       <c r="G366" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>2</v>
       </c>
       <c r="G378" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H378" t="n">
         <v>2100</v>
@@ -11360,7 +11360,7 @@
         <v>2</v>
       </c>
       <c r="G379" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>2</v>
       </c>
       <c r="G380" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>1.7877242565155</v>
+        <v>1.78772413730621</v>
       </c>
       <c r="H381" t="n">
         <v>98700</v>
@@ -11447,7 +11447,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G382" t="n">
-        <v>1.7154928445816</v>
+        <v>1.71549296379089</v>
       </c>
       <c r="H382" t="n">
         <v>9600</v>
@@ -11476,7 +11476,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G383" t="n">
-        <v>1.7154928445816</v>
+        <v>1.71549296379089</v>
       </c>
       <c r="H383" t="n">
         <v>23400</v>
@@ -11679,7 +11679,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G390" t="n">
-        <v>1.6793771982193</v>
+        <v>1.67937731742859</v>
       </c>
       <c r="H390" t="n">
         <v>2400</v>
@@ -11708,7 +11708,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G391" t="n">
-        <v>1.7154928445816</v>
+        <v>1.71549296379089</v>
       </c>
       <c r="H391" t="n">
         <v>4800</v>
@@ -11882,7 +11882,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G397" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H397" t="n">
         <v>5400</v>
@@ -11911,7 +11911,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H398" t="n">
         <v>1200</v>
@@ -12027,7 +12027,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G402" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H402" t="n">
         <v>7800</v>
@@ -12114,7 +12114,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G405" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H405" t="n">
         <v>4200</v>
@@ -12172,7 +12172,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G407" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H407" t="n">
         <v>3300</v>
@@ -12259,7 +12259,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G410" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H410" t="n">
         <v>39900</v>
@@ -12433,7 +12433,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G416" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H416" t="n">
         <v>2100</v>
@@ -12549,7 +12549,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G420" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H420" t="n">
         <v>300</v>
@@ -12694,7 +12694,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G425" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H425" t="n">
         <v>1500</v>
@@ -12752,7 +12752,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G427" t="n">
-        <v>1.31822097301483</v>
+        <v>1.31822085380554</v>
       </c>
       <c r="H427" t="n">
         <v>3300</v>
@@ -12781,7 +12781,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G428" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H428" t="n">
         <v>1800</v>
@@ -12810,7 +12810,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G429" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12839,7 +12839,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G430" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G433" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H433" t="n">
         <v>300</v>
@@ -12984,7 +12984,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G435" t="n">
-        <v>1.31822097301483</v>
+        <v>1.31822085380554</v>
       </c>
       <c r="H435" t="n">
         <v>3600</v>
@@ -13071,7 +13071,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G438" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H438" t="n">
         <v>27900</v>
@@ -13187,7 +13187,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G442" t="n">
-        <v>1.24598968029022</v>
+        <v>1.24598956108093</v>
       </c>
       <c r="H442" t="n">
         <v>79500</v>
@@ -13419,7 +13419,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H450" t="n">
         <v>29700</v>
@@ -13506,7 +13506,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G453" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H453" t="n">
         <v>42000</v>
@@ -13825,7 +13825,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>1.31822097301483</v>
+        <v>1.31822085380554</v>
       </c>
       <c r="H464" t="n">
         <v>900</v>
@@ -13912,7 +13912,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G467" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H467" t="n">
         <v>3300</v>
@@ -13970,7 +13970,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G469" t="n">
-        <v>1.6793771982193</v>
+        <v>1.67937731742859</v>
       </c>
       <c r="H469" t="n">
         <v>347100</v>
@@ -13999,7 +13999,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G470" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H470" t="n">
         <v>92700</v>
@@ -14115,7 +14115,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G474" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H474" t="n">
         <v>12300</v>
@@ -14289,7 +14289,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G480" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H480" t="n">
         <v>30000</v>
@@ -14347,7 +14347,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G482" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H482" t="n">
         <v>17100</v>
@@ -14376,7 +14376,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G483" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H483" t="n">
         <v>8400</v>
@@ -14434,7 +14434,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G485" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H485" t="n">
         <v>4500</v>
@@ -14492,7 +14492,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G487" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H487" t="n">
         <v>4500</v>
@@ -14608,7 +14608,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G491" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H491" t="n">
         <v>5100</v>
@@ -14637,7 +14637,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G492" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H492" t="n">
         <v>79200</v>
@@ -14666,7 +14666,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G493" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H493" t="n">
         <v>50700</v>
@@ -14695,7 +14695,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G494" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H494" t="n">
         <v>7200</v>
@@ -14724,7 +14724,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G495" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H495" t="n">
         <v>9900</v>
@@ -14753,7 +14753,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G496" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H496" t="n">
         <v>100200</v>
@@ -14898,7 +14898,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G501" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H501" t="n">
         <v>9900</v>
@@ -14956,7 +14956,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G503" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H503" t="n">
         <v>44700</v>
@@ -14985,7 +14985,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G504" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H504" t="n">
         <v>5400</v>
@@ -15159,7 +15159,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G510" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H510" t="n">
         <v>14400</v>
@@ -15217,7 +15217,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H512" t="n">
         <v>36000</v>
@@ -15246,7 +15246,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G513" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H513" t="n">
         <v>8700</v>
@@ -15507,7 +15507,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H522" t="n">
         <v>2400</v>
@@ -15565,7 +15565,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G524" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H524" t="n">
         <v>6900</v>
@@ -15594,7 +15594,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G525" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H525" t="n">
         <v>37500</v>
@@ -15652,7 +15652,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G527" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H527" t="n">
         <v>43800</v>
@@ -15681,7 +15681,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G528" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H528" t="n">
         <v>18300</v>
@@ -15710,7 +15710,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G529" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H529" t="n">
         <v>24600</v>
@@ -15739,7 +15739,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G530" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H530" t="n">
         <v>83400</v>
@@ -15768,7 +15768,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G531" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H531" t="n">
         <v>13800</v>
@@ -15797,7 +15797,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G532" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H532" t="n">
         <v>65400</v>
@@ -15913,7 +15913,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G536" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H536" t="n">
         <v>51900</v>
@@ -16000,7 +16000,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G539" t="n">
-        <v>1.2550185918808</v>
+        <v>1.25501835346222</v>
       </c>
       <c r="H539" t="n">
         <v>51300</v>
@@ -16087,7 +16087,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G542" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H542" t="n">
         <v>21600</v>
@@ -16145,7 +16145,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G544" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H544" t="n">
         <v>11400</v>
@@ -16174,7 +16174,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G545" t="n">
-        <v>1.2550185918808</v>
+        <v>1.25501835346222</v>
       </c>
       <c r="H545" t="n">
         <v>70200</v>
@@ -16232,7 +16232,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G547" t="n">
-        <v>1.20084500312805</v>
+        <v>1.20084512233734</v>
       </c>
       <c r="H547" t="n">
         <v>76200</v>
@@ -16493,7 +16493,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G556" t="n">
-        <v>1.02026689052582</v>
+        <v>1.02026677131653</v>
       </c>
       <c r="H556" t="n">
         <v>72900</v>
@@ -16522,7 +16522,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G557" t="n">
-        <v>1.02026689052582</v>
+        <v>1.02026677131653</v>
       </c>
       <c r="H557" t="n">
         <v>37800</v>
@@ -16551,7 +16551,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G558" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H558" t="n">
         <v>19500</v>
@@ -16696,7 +16696,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G563" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H563" t="n">
         <v>45900</v>
@@ -16754,7 +16754,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G565" t="n">
-        <v>0.939006686210632</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H565" t="n">
         <v>2400</v>
@@ -16783,7 +16783,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G566" t="n">
-        <v>0.83968859910965</v>
+        <v>0.839688658714294</v>
       </c>
       <c r="H566" t="n">
         <v>3600</v>
@@ -16870,7 +16870,7 @@
         <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H569" t="n">
         <v>16200</v>
@@ -16899,7 +16899,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>0.884833216667175</v>
+        <v>0.884833157062531</v>
       </c>
       <c r="H570" t="n">
         <v>10800</v>
@@ -17044,7 +17044,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G575" t="n">
-        <v>0.884833216667175</v>
+        <v>0.884833157062531</v>
       </c>
       <c r="H575" t="n">
         <v>16200</v>
@@ -17131,7 +17131,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G578" t="n">
-        <v>0.975122392177582</v>
+        <v>0.975122332572937</v>
       </c>
       <c r="H578" t="n">
         <v>14700</v>
@@ -17276,7 +17276,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>1.03381025791168</v>
+        <v>1.03381013870239</v>
       </c>
       <c r="H583" t="n">
         <v>5400</v>
@@ -17305,7 +17305,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G584" t="n">
-        <v>1.03381025791168</v>
+        <v>1.03381013870239</v>
       </c>
       <c r="H584" t="n">
         <v>17400</v>
@@ -17392,7 +17392,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G587" t="n">
-        <v>1.03381025791168</v>
+        <v>1.03381013870239</v>
       </c>
       <c r="H587" t="n">
         <v>15000</v>
@@ -17508,7 +17508,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G591" t="n">
-        <v>0.952549934387207</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H591" t="n">
         <v>102000</v>
@@ -17624,7 +17624,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H595" t="n">
         <v>15900</v>
@@ -17653,7 +17653,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>0.939006686210632</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H596" t="n">
         <v>39300</v>
@@ -17711,7 +17711,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G598" t="n">
-        <v>0.952549934387207</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H598" t="n">
         <v>21600</v>
@@ -17798,7 +17798,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G601" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H601" t="n">
         <v>17100</v>
@@ -17856,7 +17856,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G603" t="n">
-        <v>0.939006686210632</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H603" t="n">
         <v>9600</v>
@@ -17885,7 +17885,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G604" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H604" t="n">
         <v>36600</v>
@@ -17943,7 +17943,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G606" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H606" t="n">
         <v>21600</v>
@@ -18030,7 +18030,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G609" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H609" t="n">
         <v>38400</v>
@@ -18088,7 +18088,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G611" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H611" t="n">
         <v>195300</v>
@@ -18117,7 +18117,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G612" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H612" t="n">
         <v>36000</v>
@@ -18204,7 +18204,7 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H615" t="n">
         <v>20700</v>
@@ -18233,7 +18233,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G616" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H616" t="n">
         <v>26700</v>
@@ -18320,7 +18320,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G619" t="n">
-        <v>0.893862128257751</v>
+        <v>0.893862068653107</v>
       </c>
       <c r="H619" t="n">
         <v>41100</v>
@@ -18349,7 +18349,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G620" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H620" t="n">
         <v>13500</v>
@@ -18378,7 +18378,7 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H621" t="n">
         <v>9900</v>
@@ -18407,7 +18407,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G622" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H622" t="n">
         <v>54000</v>
@@ -18436,7 +18436,7 @@
         <v>1</v>
       </c>
       <c r="G623" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H623" t="n">
         <v>20100</v>
@@ -18494,7 +18494,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G625" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H625" t="n">
         <v>47100</v>
@@ -18552,7 +18552,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G627" t="n">
-        <v>1.04283905029297</v>
+        <v>1.04283916950226</v>
       </c>
       <c r="H627" t="n">
         <v>258300</v>
@@ -18581,7 +18581,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G628" t="n">
-        <v>0.988665640354156</v>
+        <v>0.988665580749512</v>
       </c>
       <c r="H628" t="n">
         <v>45600</v>
@@ -18668,7 +18668,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>0.997694611549377</v>
+        <v>0.997694551944733</v>
       </c>
       <c r="H631" t="n">
         <v>19200</v>
@@ -18871,7 +18871,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>0.97963684797287</v>
+        <v>0.97963672876358</v>
       </c>
       <c r="H638" t="n">
         <v>6900</v>
@@ -18900,7 +18900,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H639" t="n">
         <v>2400</v>
@@ -18929,7 +18929,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G640" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H640" t="n">
         <v>18600</v>
@@ -18958,7 +18958,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G641" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H641" t="n">
         <v>3300</v>
@@ -18987,7 +18987,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G642" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H642" t="n">
         <v>3600</v>
@@ -19074,7 +19074,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G645" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H645" t="n">
         <v>9000</v>
@@ -19103,7 +19103,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>0.939006686210632</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H646" t="n">
         <v>7200</v>
@@ -19132,7 +19132,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>0.939006686210632</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H647" t="n">
         <v>1500</v>
@@ -19161,7 +19161,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G648" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H648" t="n">
         <v>900</v>
@@ -19190,7 +19190,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G649" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H649" t="n">
         <v>3000</v>
@@ -19248,7 +19248,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G651" t="n">
-        <v>0.975122392177582</v>
+        <v>0.975122332572937</v>
       </c>
       <c r="H651" t="n">
         <v>2700</v>
@@ -19393,7 +19393,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>0.97963684797287</v>
+        <v>0.97963672876358</v>
       </c>
       <c r="H656" t="n">
         <v>7200</v>
@@ -19596,7 +19596,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G663" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H663" t="n">
         <v>6900</v>
@@ -19625,7 +19625,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G664" t="n">
-        <v>0.952549934387207</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H664" t="n">
         <v>300</v>
@@ -19741,7 +19741,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G668" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H668" t="n">
         <v>5100</v>
@@ -19828,7 +19828,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G671" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H671" t="n">
         <v>4500</v>
@@ -19886,7 +19886,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.988665640354156</v>
+        <v>0.988665580749512</v>
       </c>
       <c r="H673" t="n">
         <v>3300</v>
@@ -19915,7 +19915,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G674" t="n">
-        <v>0.988665640354156</v>
+        <v>0.988665580749512</v>
       </c>
       <c r="H674" t="n">
         <v>300</v>
@@ -20002,7 +20002,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G677" t="n">
-        <v>0.975122392177582</v>
+        <v>0.975122332572937</v>
       </c>
       <c r="H677" t="n">
         <v>10500</v>
@@ -20031,7 +20031,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G678" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H678" t="n">
         <v>9300</v>
@@ -20060,7 +20060,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G679" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H679" t="n">
         <v>15300</v>
@@ -20089,7 +20089,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G680" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H680" t="n">
         <v>600</v>
@@ -20118,7 +20118,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G681" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H681" t="n">
         <v>12300</v>
@@ -20147,7 +20147,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G682" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H682" t="n">
         <v>600</v>
@@ -20176,7 +20176,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>0.939006686210632</v>
+        <v>0.939006626605988</v>
       </c>
       <c r="H683" t="n">
         <v>23100</v>
@@ -20205,7 +20205,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G684" t="n">
-        <v>0.907405495643616</v>
+        <v>0.907405436038971</v>
       </c>
       <c r="H684" t="n">
         <v>29700</v>
@@ -20292,7 +20292,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G687" t="n">
-        <v>0.952549934387207</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H687" t="n">
         <v>3600</v>
@@ -20321,7 +20321,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G688" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H688" t="n">
         <v>21900</v>
@@ -20350,7 +20350,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G689" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H689" t="n">
         <v>600</v>
@@ -20379,7 +20379,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G690" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H690" t="n">
         <v>3600</v>
@@ -20408,7 +20408,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G691" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H691" t="n">
         <v>600</v>
@@ -20437,7 +20437,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G692" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H692" t="n">
         <v>9600</v>
@@ -20466,7 +20466,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G693" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H693" t="n">
         <v>15600</v>
@@ -20495,7 +20495,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G694" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H694" t="n">
         <v>29100</v>
@@ -20553,7 +20553,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G696" t="n">
-        <v>0.952549934387207</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H696" t="n">
         <v>12000</v>
@@ -20582,7 +20582,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G697" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H697" t="n">
         <v>7200</v>
@@ -20640,7 +20640,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G699" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H699" t="n">
         <v>7500</v>
@@ -20669,7 +20669,7 @@
         <v>1</v>
       </c>
       <c r="G700" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H700" t="n">
         <v>15000</v>
@@ -20698,7 +20698,7 @@
         <v>1</v>
       </c>
       <c r="G701" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H701" t="n">
         <v>14100</v>
@@ -20727,7 +20727,7 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H702" t="n">
         <v>5700</v>
@@ -20756,7 +20756,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>0.911919891834259</v>
+        <v>0.911919951438904</v>
       </c>
       <c r="H703" t="n">
         <v>11700</v>
@@ -20843,7 +20843,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G706" t="n">
-        <v>0.84330016374588</v>
+        <v>0.843300223350525</v>
       </c>
       <c r="H706" t="n">
         <v>67500</v>
@@ -20872,7 +20872,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G707" t="n">
-        <v>0.852329075336456</v>
+        <v>0.852329134941101</v>
       </c>
       <c r="H707" t="n">
         <v>10200</v>
@@ -21104,7 +21104,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G715" t="n">
-        <v>0.80718457698822</v>
+        <v>0.807184517383575</v>
       </c>
       <c r="H715" t="n">
         <v>1500</v>
@@ -21191,7 +21191,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G718" t="n">
-        <v>0.722312808036804</v>
+        <v>0.722312867641449</v>
       </c>
       <c r="H718" t="n">
         <v>23400</v>
@@ -21365,7 +21365,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G724" t="n">
-        <v>0.749399542808533</v>
+        <v>0.749399483203888</v>
       </c>
       <c r="H724" t="n">
         <v>24900</v>
@@ -21394,7 +21394,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G725" t="n">
-        <v>0.749399542808533</v>
+        <v>0.749399483203888</v>
       </c>
       <c r="H725" t="n">
         <v>0</v>
@@ -21481,7 +21481,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G728" t="n">
-        <v>0.622994840145111</v>
+        <v>0.622994780540466</v>
       </c>
       <c r="H728" t="n">
         <v>15600</v>
@@ -21539,7 +21539,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G730" t="n">
-        <v>0.662722051143646</v>
+        <v>0.662721991539001</v>
       </c>
       <c r="H730" t="n">
         <v>3900</v>
@@ -21568,7 +21568,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G731" t="n">
-        <v>0.666333556175232</v>
+        <v>0.666333496570587</v>
       </c>
       <c r="H731" t="n">
         <v>12000</v>
@@ -21626,7 +21626,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G733" t="n">
-        <v>0.65188729763031</v>
+        <v>0.651887357234955</v>
       </c>
       <c r="H733" t="n">
         <v>3600</v>
@@ -21713,7 +21713,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G736" t="n">
-        <v>0.678974032402039</v>
+        <v>0.678973972797394</v>
       </c>
       <c r="H736" t="n">
         <v>4200</v>
@@ -21829,7 +21829,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G740" t="n">
-        <v>0.644664168357849</v>
+        <v>0.644664227962494</v>
       </c>
       <c r="H740" t="n">
         <v>3600</v>
@@ -21858,7 +21858,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G741" t="n">
-        <v>0.657304644584656</v>
+        <v>0.657304584980011</v>
       </c>
       <c r="H741" t="n">
         <v>20100</v>
@@ -21916,7 +21916,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G743" t="n">
-        <v>0.662722051143646</v>
+        <v>0.662721991539001</v>
       </c>
       <c r="H743" t="n">
         <v>73200</v>
@@ -21945,7 +21945,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G744" t="n">
-        <v>0.675362467765808</v>
+        <v>0.675362527370453</v>
       </c>
       <c r="H744" t="n">
         <v>18000</v>
@@ -22003,7 +22003,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G746" t="n">
-        <v>0.673556685447693</v>
+        <v>0.673556625843048</v>
       </c>
       <c r="H746" t="n">
         <v>53700</v>
@@ -22090,7 +22090,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G749" t="n">
-        <v>0.720506966114044</v>
+        <v>0.720507025718689</v>
       </c>
       <c r="H749" t="n">
         <v>48300</v>
@@ -22177,7 +22177,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G752" t="n">
-        <v>0.675362467765808</v>
+        <v>0.675362527370453</v>
       </c>
       <c r="H752" t="n">
         <v>33600</v>
@@ -22235,7 +22235,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G754" t="n">
-        <v>0.675362467765808</v>
+        <v>0.675362527370453</v>
       </c>
       <c r="H754" t="n">
         <v>27900</v>
@@ -22380,7 +22380,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G759" t="n">
-        <v>0.673556685447693</v>
+        <v>0.673556625843048</v>
       </c>
       <c r="H759" t="n">
         <v>17700</v>
@@ -22409,7 +22409,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G760" t="n">
-        <v>0.659110486507416</v>
+        <v>0.659110426902771</v>
       </c>
       <c r="H760" t="n">
         <v>22500</v>
@@ -22438,7 +22438,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G761" t="n">
-        <v>0.673556685447693</v>
+        <v>0.673556625843048</v>
       </c>
       <c r="H761" t="n">
         <v>8700</v>
@@ -22467,7 +22467,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G762" t="n">
-        <v>0.700643420219421</v>
+        <v>0.700643479824066</v>
       </c>
       <c r="H762" t="n">
         <v>48300</v>
@@ -22583,7 +22583,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G766" t="n">
-        <v>0.80718457698822</v>
+        <v>0.807184517383575</v>
       </c>
       <c r="H766" t="n">
         <v>120300</v>
@@ -22699,7 +22699,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G770" t="n">
-        <v>0.76565158367157</v>
+        <v>0.765651524066925</v>
       </c>
       <c r="H770" t="n">
         <v>44100</v>
@@ -22728,7 +22728,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G771" t="n">
-        <v>0.76565158367157</v>
+        <v>0.765651524066925</v>
       </c>
       <c r="H771" t="n">
         <v>9300</v>
@@ -22815,7 +22815,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G774" t="n">
-        <v>0.767457365989685</v>
+        <v>0.76745742559433</v>
       </c>
       <c r="H774" t="n">
         <v>50700</v>
@@ -22873,7 +22873,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G776" t="n">
-        <v>0.801767230033875</v>
+        <v>0.80176717042923</v>
       </c>
       <c r="H776" t="n">
         <v>99600</v>
@@ -23047,7 +23047,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G782" t="n">
-        <v>0.801767230033875</v>
+        <v>0.80176717042923</v>
       </c>
       <c r="H782" t="n">
         <v>21600</v>
@@ -23076,7 +23076,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G783" t="n">
-        <v>0.794544100761414</v>
+        <v>0.794544041156769</v>
       </c>
       <c r="H783" t="n">
         <v>92100</v>
@@ -23250,7 +23250,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G789" t="n">
-        <v>0.767457365989685</v>
+        <v>0.76745742559433</v>
       </c>
       <c r="H789" t="n">
         <v>72000</v>
@@ -23308,7 +23308,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G791" t="n">
-        <v>0.754816949367523</v>
+        <v>0.754816889762878</v>
       </c>
       <c r="H791" t="n">
         <v>36000</v>
@@ -23395,7 +23395,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G794" t="n">
-        <v>0.767457365989685</v>
+        <v>0.76745742559433</v>
       </c>
       <c r="H794" t="n">
         <v>23100</v>
@@ -23540,7 +23540,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G799" t="n">
-        <v>0.819824993610382</v>
+        <v>0.819825053215027</v>
       </c>
       <c r="H799" t="n">
         <v>312600</v>
@@ -23569,7 +23569,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G800" t="n">
-        <v>0.823436558246613</v>
+        <v>0.823436617851257</v>
       </c>
       <c r="H800" t="n">
         <v>87300</v>
@@ -23685,7 +23685,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G804" t="n">
-        <v>0.857746422290802</v>
+        <v>0.857746481895447</v>
       </c>
       <c r="H804" t="n">
         <v>87300</v>
@@ -23714,7 +23714,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G805" t="n">
-        <v>0.859552204608917</v>
+        <v>0.859552323818207</v>
       </c>
       <c r="H805" t="n">
         <v>41700</v>
@@ -23743,7 +23743,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G806" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H806" t="n">
         <v>362700</v>
@@ -23772,7 +23772,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>0.893862128257751</v>
+        <v>0.893862068653107</v>
       </c>
       <c r="H807" t="n">
         <v>214500</v>
@@ -23830,7 +23830,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G809" t="n">
-        <v>0.886638998985291</v>
+        <v>0.886638939380646</v>
       </c>
       <c r="H809" t="n">
         <v>36300</v>
@@ -23859,7 +23859,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G810" t="n">
-        <v>0.854134857654572</v>
+        <v>0.854134917259216</v>
       </c>
       <c r="H810" t="n">
         <v>57000</v>
@@ -23888,7 +23888,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G811" t="n">
-        <v>0.857746422290802</v>
+        <v>0.857746481895447</v>
       </c>
       <c r="H811" t="n">
         <v>22500</v>
@@ -23917,7 +23917,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G812" t="n">
-        <v>0.873998522758484</v>
+        <v>0.873998463153839</v>
       </c>
       <c r="H812" t="n">
         <v>37200</v>
@@ -23946,7 +23946,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G813" t="n">
-        <v>0.886638998985291</v>
+        <v>0.886638939380646</v>
       </c>
       <c r="H813" t="n">
         <v>24300</v>
@@ -24004,7 +24004,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G815" t="n">
-        <v>0.859552204608917</v>
+        <v>0.859552323818207</v>
       </c>
       <c r="H815" t="n">
         <v>4800</v>
@@ -24062,7 +24062,7 @@
         <v>1</v>
       </c>
       <c r="G817" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H817" t="n">
         <v>158700</v>
@@ -24149,7 +24149,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G820" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H820" t="n">
         <v>38100</v>
@@ -24178,7 +24178,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G821" t="n">
-        <v>0.948035478591919</v>
+        <v>0.948035418987274</v>
       </c>
       <c r="H821" t="n">
         <v>63900</v>
@@ -24207,7 +24207,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G822" t="n">
-        <v>0.943521022796631</v>
+        <v>0.943521082401276</v>
       </c>
       <c r="H822" t="n">
         <v>21900</v>
@@ -24265,7 +24265,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G824" t="n">
-        <v>0.911919891834259</v>
+        <v>0.911919951438904</v>
       </c>
       <c r="H824" t="n">
         <v>29700</v>
@@ -24352,7 +24352,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G827" t="n">
-        <v>0.88302743434906</v>
+        <v>0.883027374744415</v>
       </c>
       <c r="H827" t="n">
         <v>58800</v>
@@ -24381,7 +24381,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G828" t="n">
-        <v>0.872192740440369</v>
+        <v>0.872192680835724</v>
       </c>
       <c r="H828" t="n">
         <v>37500</v>
@@ -24410,7 +24410,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G829" t="n">
-        <v>0.879415810108185</v>
+        <v>0.87941575050354</v>
       </c>
       <c r="H829" t="n">
         <v>30300</v>
@@ -24439,7 +24439,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G830" t="n">
-        <v>0.88302743434906</v>
+        <v>0.883027374744415</v>
       </c>
       <c r="H830" t="n">
         <v>2100</v>
@@ -24497,7 +24497,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G832" t="n">
-        <v>0.893862128257751</v>
+        <v>0.893862068653107</v>
       </c>
       <c r="H832" t="n">
         <v>12000</v>
@@ -24526,7 +24526,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G833" t="n">
-        <v>0.88302743434906</v>
+        <v>0.883027374744415</v>
       </c>
       <c r="H833" t="n">
         <v>8700</v>
@@ -24555,7 +24555,7 @@
         <v>1</v>
       </c>
       <c r="G834" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H834" t="n">
         <v>11400</v>
@@ -24613,7 +24613,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G836" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H836" t="n">
         <v>18000</v>
@@ -24671,7 +24671,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G838" t="n">
-        <v>0.907405495643616</v>
+        <v>0.907405436038971</v>
       </c>
       <c r="H838" t="n">
         <v>3900</v>
@@ -24700,7 +24700,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G839" t="n">
-        <v>0.911919891834259</v>
+        <v>0.911919951438904</v>
       </c>
       <c r="H839" t="n">
         <v>300</v>
@@ -24729,7 +24729,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G840" t="n">
-        <v>0.907405495643616</v>
+        <v>0.907405436038971</v>
       </c>
       <c r="H840" t="n">
         <v>900</v>
@@ -24758,7 +24758,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G841" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H841" t="n">
         <v>45900</v>
@@ -24961,7 +24961,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G848" t="n">
-        <v>0.97963684797287</v>
+        <v>0.97963672876358</v>
       </c>
       <c r="H848" t="n">
         <v>13800</v>
@@ -25193,7 +25193,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G856" t="n">
-        <v>1.13764262199402</v>
+        <v>1.13764274120331</v>
       </c>
       <c r="H856" t="n">
         <v>330600</v>
@@ -25222,7 +25222,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G857" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H857" t="n">
         <v>135300</v>
@@ -25251,7 +25251,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G858" t="n">
-        <v>1.11507034301758</v>
+        <v>1.11507046222687</v>
       </c>
       <c r="H858" t="n">
         <v>14700</v>
@@ -25280,7 +25280,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G859" t="n">
-        <v>1.08798360824585</v>
+        <v>1.08798372745514</v>
       </c>
       <c r="H859" t="n">
         <v>10800</v>
@@ -25309,7 +25309,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G860" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H860" t="n">
         <v>18000</v>
@@ -25396,7 +25396,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G863" t="n">
-        <v>1.06089699268341</v>
+        <v>1.06089687347412</v>
       </c>
       <c r="H863" t="n">
         <v>3900</v>
@@ -25454,7 +25454,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G865" t="n">
-        <v>1.09701263904572</v>
+        <v>1.09701251983643</v>
       </c>
       <c r="H865" t="n">
         <v>21600</v>
@@ -25483,7 +25483,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G866" t="n">
-        <v>1.07895481586456</v>
+        <v>1.07895469665527</v>
       </c>
       <c r="H866" t="n">
         <v>8100</v>
@@ -25570,7 +25570,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H869" t="n">
         <v>38100</v>
@@ -25628,7 +25628,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G871" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H871" t="n">
         <v>7500</v>
@@ -25686,7 +25686,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G873" t="n">
-        <v>1.16472923755646</v>
+        <v>1.16472935676575</v>
       </c>
       <c r="H873" t="n">
         <v>48300</v>
@@ -25715,7 +25715,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G874" t="n">
-        <v>1.15570044517517</v>
+        <v>1.15570056438446</v>
       </c>
       <c r="H874" t="n">
         <v>54300</v>
@@ -25744,7 +25744,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>1.16472923755646</v>
+        <v>1.16472935676575</v>
       </c>
       <c r="H875" t="n">
         <v>158700</v>
@@ -25831,7 +25831,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>1.20535945892334</v>
+        <v>1.20535957813263</v>
       </c>
       <c r="H878" t="n">
         <v>25200</v>
@@ -25889,7 +25889,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G880" t="n">
-        <v>1.31370639801025</v>
+        <v>1.31370651721954</v>
       </c>
       <c r="H880" t="n">
         <v>138600</v>
@@ -25918,7 +25918,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G881" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H881" t="n">
         <v>324000</v>
@@ -25947,7 +25947,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G882" t="n">
-        <v>1.24598968029022</v>
+        <v>1.24598956108093</v>
       </c>
       <c r="H882" t="n">
         <v>376800</v>
@@ -26005,7 +26005,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G884" t="n">
-        <v>1.2550185918808</v>
+        <v>1.25501835346222</v>
       </c>
       <c r="H884" t="n">
         <v>78600</v>
@@ -26034,7 +26034,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G885" t="n">
-        <v>1.22341740131378</v>
+        <v>1.22341728210449</v>
       </c>
       <c r="H885" t="n">
         <v>49200</v>
@@ -26063,7 +26063,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G886" t="n">
-        <v>1.20535945892334</v>
+        <v>1.20535957813263</v>
       </c>
       <c r="H886" t="n">
         <v>24000</v>
@@ -26440,7 +26440,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G899" t="n">
-        <v>1.22341740131378</v>
+        <v>1.22341728210449</v>
       </c>
       <c r="H899" t="n">
         <v>11400</v>
@@ -26527,7 +26527,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G902" t="n">
-        <v>1.19633054733276</v>
+        <v>1.19633066654205</v>
       </c>
       <c r="H902" t="n">
         <v>20400</v>
@@ -26556,7 +26556,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G903" t="n">
-        <v>1.20084500312805</v>
+        <v>1.20084512233734</v>
       </c>
       <c r="H903" t="n">
         <v>3600</v>
@@ -26585,7 +26585,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G904" t="n">
-        <v>1.22341740131378</v>
+        <v>1.22341728210449</v>
       </c>
       <c r="H904" t="n">
         <v>900</v>
@@ -26759,7 +26759,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G910" t="n">
-        <v>1.08798360824585</v>
+        <v>1.08798372745514</v>
       </c>
       <c r="H910" t="n">
         <v>8100</v>
@@ -26788,7 +26788,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G911" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H911" t="n">
         <v>2100</v>
@@ -26817,7 +26817,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G912" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H912" t="n">
         <v>1200</v>
@@ -26904,7 +26904,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G915" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H915" t="n">
         <v>13500</v>
@@ -26933,7 +26933,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G916" t="n">
-        <v>1.07895481586456</v>
+        <v>1.07895469665527</v>
       </c>
       <c r="H916" t="n">
         <v>26100</v>
@@ -26962,7 +26962,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G917" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H917" t="n">
         <v>3300</v>
@@ -26991,7 +26991,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G918" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H918" t="n">
         <v>0</v>
@@ -27020,7 +27020,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>1.16472923755646</v>
+        <v>1.16472935676575</v>
       </c>
       <c r="H919" t="n">
         <v>21000</v>
@@ -27049,7 +27049,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G920" t="n">
-        <v>1.16021478176117</v>
+        <v>1.16021490097046</v>
       </c>
       <c r="H920" t="n">
         <v>3900</v>
@@ -27078,7 +27078,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G921" t="n">
-        <v>1.16021478176117</v>
+        <v>1.16021490097046</v>
       </c>
       <c r="H921" t="n">
         <v>3000</v>
@@ -27107,7 +27107,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G922" t="n">
-        <v>1.16472923755646</v>
+        <v>1.16472935676575</v>
       </c>
       <c r="H922" t="n">
         <v>15000</v>
@@ -27281,7 +27281,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G928" t="n">
-        <v>1.22341740131378</v>
+        <v>1.22341728210449</v>
       </c>
       <c r="H928" t="n">
         <v>10200</v>
@@ -27310,7 +27310,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G929" t="n">
-        <v>1.22341740131378</v>
+        <v>1.22341728210449</v>
       </c>
       <c r="H929" t="n">
         <v>0</v>
@@ -27339,7 +27339,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G930" t="n">
-        <v>1.24598968029022</v>
+        <v>1.24598956108093</v>
       </c>
       <c r="H930" t="n">
         <v>8400</v>
@@ -27368,7 +27368,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G931" t="n">
-        <v>1.2550185918808</v>
+        <v>1.25501835346222</v>
       </c>
       <c r="H931" t="n">
         <v>17400</v>
@@ -27397,7 +27397,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G932" t="n">
-        <v>1.2550185918808</v>
+        <v>1.25501835346222</v>
       </c>
       <c r="H932" t="n">
         <v>0</v>
@@ -27426,7 +27426,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G933" t="n">
-        <v>1.31822097301483</v>
+        <v>1.31822085380554</v>
       </c>
       <c r="H933" t="n">
         <v>58200</v>
@@ -27484,7 +27484,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G935" t="n">
-        <v>1.6793771982193</v>
+        <v>1.67937731742859</v>
       </c>
       <c r="H935" t="n">
         <v>272400</v>
@@ -27571,7 +27571,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G938" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H938" t="n">
         <v>60000</v>
@@ -27629,7 +27629,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G940" t="n">
-        <v>1.52137136459351</v>
+        <v>1.52137124538422</v>
       </c>
       <c r="H940" t="n">
         <v>57000</v>
@@ -27658,7 +27658,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G941" t="n">
-        <v>1.64777600765228</v>
+        <v>1.64777624607086</v>
       </c>
       <c r="H941" t="n">
         <v>159900</v>
@@ -27745,7 +27745,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G944" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H944" t="n">
         <v>12900</v>
@@ -27890,7 +27890,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G949" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H949" t="n">
         <v>36900</v>
@@ -27977,7 +27977,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G952" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H952" t="n">
         <v>20100</v>
@@ -28122,7 +28122,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G957" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H957" t="n">
         <v>27000</v>
@@ -28151,7 +28151,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G958" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H958" t="n">
         <v>19800</v>
@@ -28180,7 +28180,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G959" t="n">
-        <v>1.53942918777466</v>
+        <v>1.53942930698395</v>
       </c>
       <c r="H959" t="n">
         <v>32700</v>
@@ -28209,7 +28209,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G960" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H960" t="n">
         <v>121200</v>
@@ -28354,7 +28354,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G965" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H965" t="n">
         <v>12900</v>
@@ -28383,7 +28383,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G966" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H966" t="n">
         <v>35400</v>
@@ -28441,7 +28441,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G968" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H968" t="n">
         <v>28500</v>
@@ -28470,7 +28470,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G969" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H969" t="n">
         <v>8400</v>
@@ -28557,7 +28557,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G972" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H972" t="n">
         <v>58800</v>
@@ -28586,7 +28586,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G973" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H973" t="n">
         <v>45600</v>
@@ -28615,7 +28615,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G974" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H974" t="n">
         <v>46200</v>
@@ -28673,7 +28673,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G976" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H976" t="n">
         <v>27600</v>
@@ -28731,7 +28731,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G978" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H978" t="n">
         <v>5700</v>
@@ -28905,7 +28905,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G984" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H984" t="n">
         <v>6300</v>
@@ -28934,7 +28934,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G985" t="n">
-        <v>1.52137136459351</v>
+        <v>1.52137124538422</v>
       </c>
       <c r="H985" t="n">
         <v>24000</v>
@@ -29021,7 +29021,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G988" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H988" t="n">
         <v>41100</v>
@@ -29079,7 +29079,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G990" t="n">
-        <v>1.52137136459351</v>
+        <v>1.52137124538422</v>
       </c>
       <c r="H990" t="n">
         <v>18300</v>
@@ -29108,7 +29108,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G991" t="n">
-        <v>1.54845821857452</v>
+        <v>1.54845809936523</v>
       </c>
       <c r="H991" t="n">
         <v>6000</v>
@@ -29137,7 +29137,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G992" t="n">
-        <v>1.53942918777466</v>
+        <v>1.53942930698395</v>
       </c>
       <c r="H992" t="n">
         <v>5400</v>
@@ -29166,7 +29166,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G993" t="n">
-        <v>1.54845821857452</v>
+        <v>1.54845809936523</v>
       </c>
       <c r="H993" t="n">
         <v>60300</v>
@@ -29224,7 +29224,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H995" t="n">
         <v>3300</v>
@@ -29282,7 +29282,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G997" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H997" t="n">
         <v>21000</v>
@@ -29311,7 +29311,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G998" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H998" t="n">
         <v>14400</v>
@@ -29369,7 +29369,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1000" t="n">
         <v>19800</v>
@@ -29398,7 +29398,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1001" t="n">
         <v>1800</v>
@@ -29427,7 +29427,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1002" t="n">
         <v>6600</v>
@@ -29456,7 +29456,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1003" t="n">
         <v>69900</v>
@@ -29485,7 +29485,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1004" t="n">
         <v>28800</v>
@@ -29601,7 +29601,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1008" t="n">
         <v>4200</v>
@@ -29630,7 +29630,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1009" t="n">
         <v>1200</v>
@@ -29717,7 +29717,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.43108224868774</v>
+        <v>1.43108212947845</v>
       </c>
       <c r="H1012" t="n">
         <v>37800</v>
@@ -29891,7 +29891,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H1018" t="n">
         <v>7200</v>
@@ -29949,7 +29949,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.32273542881012</v>
+        <v>1.32273530960083</v>
       </c>
       <c r="H1020" t="n">
         <v>10500</v>
@@ -29978,7 +29978,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H1021" t="n">
         <v>6900</v>
@@ -30007,7 +30007,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.26856184005737</v>
+        <v>1.26856195926666</v>
       </c>
       <c r="H1022" t="n">
         <v>40200</v>
@@ -30036,7 +30036,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.30467760562897</v>
+        <v>1.30467748641968</v>
       </c>
       <c r="H1023" t="n">
         <v>300</v>
@@ -30181,7 +30181,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.33176422119141</v>
+        <v>1.3317643404007</v>
       </c>
       <c r="H1028" t="n">
         <v>19200</v>
@@ -30210,7 +30210,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1029" t="n">
         <v>8700</v>
@@ -30239,7 +30239,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H1030" t="n">
         <v>9600</v>
@@ -30297,7 +30297,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1032" t="n">
         <v>26400</v>
@@ -30326,7 +30326,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1033" t="n">
         <v>9300</v>
@@ -30355,7 +30355,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1034" t="n">
         <v>24000</v>
@@ -30384,7 +30384,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1035" t="n">
         <v>9600</v>
@@ -30413,7 +30413,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1036" t="n">
         <v>27900</v>
@@ -30442,7 +30442,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1037" t="n">
         <v>2100</v>
@@ -30500,7 +30500,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1039" t="n">
         <v>300</v>
@@ -30529,7 +30529,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1040" t="n">
         <v>1500</v>
@@ -30558,7 +30558,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -30587,7 +30587,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1042" t="n">
         <v>9900</v>
@@ -30616,7 +30616,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1043" t="n">
         <v>4800</v>
@@ -30645,7 +30645,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1044" t="n">
         <v>7500</v>
@@ -30674,7 +30674,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1045" t="n">
         <v>20100</v>
@@ -30703,7 +30703,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1046" t="n">
         <v>3300</v>
@@ -30732,7 +30732,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1047" t="n">
         <v>3900</v>
@@ -30761,7 +30761,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1048" t="n">
         <v>300</v>
@@ -30993,7 +30993,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.40399539470673</v>
+        <v>1.40399551391602</v>
       </c>
       <c r="H1056" t="n">
         <v>2100</v>
@@ -31022,7 +31022,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H1057" t="n">
         <v>42300</v>
@@ -31051,7 +31051,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H1058" t="n">
         <v>600</v>
@@ -31138,7 +31138,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H1061" t="n">
         <v>3000</v>
@@ -31167,7 +31167,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1062" t="n">
         <v>7800</v>
@@ -31515,7 +31515,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.18730163574219</v>
+        <v>1.18730175495148</v>
       </c>
       <c r="H1074" t="n">
         <v>1800</v>
@@ -31718,7 +31718,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1081" t="n">
         <v>22200</v>
@@ -31776,7 +31776,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1083" t="n">
         <v>15900</v>
@@ -31805,7 +31805,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1084" t="n">
         <v>15300</v>
@@ -31834,7 +31834,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1085" t="n">
         <v>9300</v>
@@ -31950,7 +31950,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.53942918777466</v>
+        <v>1.53942930698395</v>
       </c>
       <c r="H1089" t="n">
         <v>2400</v>
@@ -31979,7 +31979,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.54845821857452</v>
+        <v>1.54845809936523</v>
       </c>
       <c r="H1090" t="n">
         <v>3300</v>
@@ -32008,7 +32008,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1091" t="n">
         <v>9000</v>
@@ -32124,7 +32124,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1095" t="n">
         <v>3900</v>
@@ -32153,7 +32153,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1096" t="n">
         <v>12000</v>
@@ -32211,7 +32211,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1098" t="n">
         <v>3300</v>
@@ -32298,7 +32298,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1101" t="n">
         <v>2700</v>
@@ -32414,7 +32414,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1105" t="n">
         <v>12300</v>
@@ -32443,7 +32443,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1106" t="n">
         <v>8700</v>
@@ -32472,7 +32472,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1107" t="n">
         <v>1200</v>
@@ -32675,7 +32675,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1114" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1114" t="n">
         <v>11100</v>
@@ -32733,7 +32733,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1116" t="n">
         <v>300</v>
@@ -32791,7 +32791,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1118" t="n">
         <v>1200</v>
@@ -32820,7 +32820,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1119" t="n">
         <v>0</v>
@@ -32936,7 +32936,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H1123" t="n">
         <v>8100</v>
@@ -33110,7 +33110,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1129" t="n">
         <v>75900</v>
@@ -33168,7 +33168,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1131" t="n">
         <v>47700</v>
@@ -33197,7 +33197,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1132" t="n">
         <v>5700</v>
@@ -33226,7 +33226,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1133" t="n">
         <v>3000</v>
@@ -33255,7 +33255,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1134" t="n">
         <v>5700</v>
@@ -33284,7 +33284,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1135" t="n">
         <v>0</v>
@@ -33342,7 +33342,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1137" t="n">
         <v>600</v>
@@ -33371,7 +33371,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1138" t="n">
         <v>9900</v>
@@ -33400,7 +33400,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1139" t="n">
         <v>4200</v>
@@ -33458,7 +33458,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1141" t="n">
         <v>5400</v>
@@ -33690,7 +33690,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1149" t="n">
         <v>75600</v>
@@ -33719,7 +33719,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1150" t="n">
         <v>36900</v>
@@ -33777,7 +33777,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1152" t="n">
         <v>51900</v>
@@ -33806,7 +33806,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1153" t="n">
         <v>64800</v>
@@ -33835,7 +33835,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1154" t="n">
         <v>2700</v>
@@ -33864,7 +33864,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1155" t="n">
         <v>15900</v>
@@ -33893,7 +33893,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1156" t="n">
         <v>4800</v>
@@ -34038,7 +34038,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1161" t="n">
         <v>18900</v>
@@ -34067,7 +34067,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1162" t="n">
         <v>600</v>
@@ -34241,7 +34241,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H1168" t="n">
         <v>4500</v>
@@ -34270,7 +34270,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H1169" t="n">
         <v>0</v>
@@ -34502,7 +34502,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1177" t="n">
         <v>9900</v>
@@ -34531,7 +34531,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1178" t="n">
         <v>0</v>
@@ -34560,7 +34560,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H1179" t="n">
         <v>53400</v>
@@ -34647,7 +34647,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H1182" t="n">
         <v>26100</v>
@@ -34821,7 +34821,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H1188" t="n">
         <v>9000</v>
@@ -34966,7 +34966,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1193" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H1193" t="n">
         <v>13200</v>
@@ -35169,7 +35169,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H1200" t="n">
         <v>2100</v>
@@ -35198,7 +35198,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H1201" t="n">
         <v>0</v>
@@ -35227,7 +35227,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H1202" t="n">
         <v>0</v>
@@ -35459,7 +35459,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1210" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1210" t="n">
         <v>300</v>
@@ -35488,7 +35488,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1211" t="n">
         <v>36000</v>
@@ -35575,7 +35575,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1214" t="n">
         <v>13200</v>
@@ -35604,7 +35604,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1215" t="n">
         <v>0</v>
@@ -35662,7 +35662,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1217" t="n">
         <v>2400</v>
@@ -35691,7 +35691,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1218" t="n">
         <v>5400</v>
@@ -35749,7 +35749,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1220" t="n">
         <v>4800</v>
@@ -35778,7 +35778,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1221" t="n">
         <v>4500</v>
@@ -35807,7 +35807,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1222" t="n">
         <v>0</v>
@@ -35836,7 +35836,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1223" t="n">
         <v>0</v>
@@ -35865,7 +35865,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1224" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1224" t="n">
         <v>24300</v>
@@ -35894,7 +35894,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1225" t="n">
         <v>2700</v>
@@ -35923,7 +35923,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1226" t="n">
         <v>1500</v>
@@ -35952,7 +35952,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1227" t="n">
         <v>0</v>
@@ -36010,7 +36010,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1229" t="n">
         <v>5700</v>
@@ -36039,7 +36039,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1230" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1230" t="n">
         <v>0</v>
@@ -36068,7 +36068,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1231" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1231" t="n">
         <v>0</v>
@@ -36387,7 +36387,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.52137136459351</v>
+        <v>1.52137124538422</v>
       </c>
       <c r="H1242" t="n">
         <v>10500</v>
@@ -36735,7 +36735,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1254" t="n">
         <v>600</v>
@@ -36764,7 +36764,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1255" t="n">
         <v>0</v>
@@ -36793,7 +36793,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1256" t="n">
         <v>0</v>
@@ -36822,7 +36822,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1257" t="n">
         <v>0</v>
@@ -36967,7 +36967,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1262" t="n">
         <v>600</v>
@@ -36996,7 +36996,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1263" t="n">
         <v>0</v>
@@ -37083,7 +37083,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1266" t="n">
         <v>6600</v>
@@ -37112,7 +37112,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1267" t="n">
         <v>0</v>
@@ -37141,7 +37141,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1268" t="n">
         <v>3900</v>
@@ -37228,7 +37228,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1271" t="n">
         <v>4500</v>
@@ -37257,7 +37257,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1272" t="n">
         <v>2100</v>
@@ -37286,7 +37286,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1273" t="n">
         <v>0</v>
@@ -37315,7 +37315,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.4536544084549</v>
+        <v>1.45365452766418</v>
       </c>
       <c r="H1274" t="n">
         <v>0</v>
@@ -37344,7 +37344,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1275" t="n">
         <v>4200</v>
@@ -37373,7 +37373,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1276" t="n">
         <v>8100</v>
@@ -37402,7 +37402,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.43108224868774</v>
+        <v>1.43108212947845</v>
       </c>
       <c r="H1277" t="n">
         <v>300</v>
@@ -37431,7 +37431,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1278" t="n">
         <v>6300</v>
@@ -37460,7 +37460,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1279" t="n">
         <v>1500</v>
@@ -37489,7 +37489,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1280" t="n">
         <v>0</v>
@@ -37518,7 +37518,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1281" t="n">
         <v>373500</v>
@@ -37605,7 +37605,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1284" t="n">
         <v>7500</v>
@@ -37663,7 +37663,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.44462561607361</v>
+        <v>1.4446257352829</v>
       </c>
       <c r="H1286" t="n">
         <v>4200</v>
@@ -37692,7 +37692,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1287" t="n">
         <v>600</v>
@@ -37721,7 +37721,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.46268332004547</v>
+        <v>1.46268343925476</v>
       </c>
       <c r="H1288" t="n">
         <v>14400</v>
@@ -37750,7 +37750,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.49879908561707</v>
+        <v>1.49879896640778</v>
       </c>
       <c r="H1289" t="n">
         <v>6900</v>
@@ -37779,7 +37779,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1290" t="n">
         <v>26700</v>
@@ -37837,7 +37837,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.40399539470673</v>
+        <v>1.40399551391602</v>
       </c>
       <c r="H1292" t="n">
         <v>13500</v>
@@ -37924,7 +37924,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1295" t="n">
         <v>3000</v>
@@ -37953,7 +37953,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1296" t="n">
         <v>1500</v>
@@ -38011,7 +38011,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1298" t="n">
         <v>7200</v>
@@ -38069,7 +38069,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1300" t="n">
         <v>19800</v>
@@ -38098,7 +38098,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1301" t="n">
         <v>0</v>
@@ -38214,7 +38214,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H1305" t="n">
         <v>11700</v>
@@ -38359,7 +38359,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.43108224868774</v>
+        <v>1.43108212947845</v>
       </c>
       <c r="H1310" t="n">
         <v>1800</v>
@@ -38388,7 +38388,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H1311" t="n">
         <v>24300</v>
@@ -38533,7 +38533,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1316" t="n">
         <v>55800</v>
@@ -38765,7 +38765,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1324" t="n">
         <v>13800</v>
@@ -38968,7 +38968,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1331" t="n">
         <v>48900</v>
@@ -38997,7 +38997,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1332" t="n">
         <v>10500</v>
@@ -39113,7 +39113,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H1336" t="n">
         <v>16500</v>
@@ -39200,7 +39200,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1339" t="n">
         <v>6300</v>
@@ -39693,7 +39693,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.32724988460541</v>
+        <v>1.32724976539612</v>
       </c>
       <c r="H1356" t="n">
         <v>28200</v>
@@ -39809,7 +39809,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1360" t="n">
         <v>3600</v>
@@ -39983,7 +39983,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1366" t="n">
         <v>4500</v>
@@ -40041,7 +40041,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1368" t="n">
         <v>300</v>
@@ -40128,7 +40128,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1371" t="n">
         <v>8100</v>
@@ -40273,7 +40273,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1376" t="n">
         <v>16500</v>
@@ -40302,7 +40302,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1377" t="n">
         <v>12300</v>
@@ -40418,7 +40418,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H1381" t="n">
         <v>20700</v>
@@ -40476,7 +40476,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.39948105812073</v>
+        <v>1.39948093891144</v>
       </c>
       <c r="H1383" t="n">
         <v>1800</v>
@@ -40505,7 +40505,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.40399539470673</v>
+        <v>1.40399551391602</v>
       </c>
       <c r="H1384" t="n">
         <v>900</v>
@@ -40534,7 +40534,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.40399539470673</v>
+        <v>1.40399551391602</v>
       </c>
       <c r="H1385" t="n">
         <v>0</v>
@@ -40563,7 +40563,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.40399539470673</v>
+        <v>1.40399551391602</v>
       </c>
       <c r="H1386" t="n">
         <v>0</v>
@@ -40592,7 +40592,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.40399539470673</v>
+        <v>1.40399551391602</v>
       </c>
       <c r="H1387" t="n">
         <v>6000</v>
@@ -40621,7 +40621,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.40399539470673</v>
+        <v>1.40399551391602</v>
       </c>
       <c r="H1388" t="n">
         <v>14100</v>
@@ -40650,7 +40650,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1389" t="n">
         <v>13500</v>
@@ -40679,7 +40679,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1390" t="n">
         <v>0</v>
@@ -40708,7 +40708,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1391" t="n">
         <v>58800</v>
@@ -40737,7 +40737,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.64777600765228</v>
+        <v>1.64777624607086</v>
       </c>
       <c r="H1392" t="n">
         <v>238200</v>
@@ -40882,7 +40882,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.6026314496994</v>
+        <v>1.60263156890869</v>
       </c>
       <c r="H1397" t="n">
         <v>105900</v>
@@ -41201,7 +41201,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1408" t="n">
         <v>18000</v>
@@ -41230,7 +41230,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1409" t="n">
-        <v>1.54845821857452</v>
+        <v>1.54845809936523</v>
       </c>
       <c r="H1409" t="n">
         <v>27900</v>
@@ -41317,7 +41317,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1412" t="n">
         <v>7200</v>
@@ -41346,7 +41346,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1413" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H1413" t="n">
         <v>4800</v>
@@ -41375,7 +41375,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.57554471492767</v>
+        <v>1.57554483413696</v>
       </c>
       <c r="H1414" t="n">
         <v>6600</v>
@@ -41462,7 +41462,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1417" t="n">
         <v>17700</v>
@@ -41520,7 +41520,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.6026314496994</v>
+        <v>1.60263156890869</v>
       </c>
       <c r="H1419" t="n">
         <v>10500</v>
@@ -41578,7 +41578,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1421" t="n">
         <v>16200</v>
@@ -41607,7 +41607,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1422" t="n">
         <v>28500</v>
@@ -41781,7 +41781,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1428" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H1428" t="n">
         <v>12600</v>
@@ -41868,7 +41868,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1431" t="n">
         <v>5100</v>
@@ -41897,7 +41897,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.57554471492767</v>
+        <v>1.57554483413696</v>
       </c>
       <c r="H1432" t="n">
         <v>12000</v>
@@ -41984,7 +41984,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H1435" t="n">
         <v>600</v>
@@ -42013,7 +42013,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.54845821857452</v>
+        <v>1.54845809936523</v>
       </c>
       <c r="H1436" t="n">
         <v>26100</v>
@@ -42071,7 +42071,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1438" t="n">
         <v>16800</v>
@@ -42100,7 +42100,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1439" t="n">
         <v>10800</v>
@@ -42187,7 +42187,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1442" t="n">
         <v>900</v>
@@ -42274,7 +42274,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H1445" t="n">
         <v>1500</v>
@@ -42303,7 +42303,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1446" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H1446" t="n">
         <v>23700</v>
@@ -42390,7 +42390,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1449" t="n">
         <v>10500</v>
@@ -42477,7 +42477,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1452" t="n">
         <v>6600</v>
@@ -42506,7 +42506,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1453" t="n">
         <v>0</v>
@@ -42593,7 +42593,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1456" t="n">
         <v>3000</v>
@@ -42796,7 +42796,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1463" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H1463" t="n">
         <v>4200</v>
@@ -42825,7 +42825,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.51234245300293</v>
+        <v>1.51234233379364</v>
       </c>
       <c r="H1464" t="n">
         <v>0</v>
@@ -42883,7 +42883,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1466" t="n">
         <v>4200</v>
@@ -42912,7 +42912,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1467" t="n">
         <v>3000</v>
@@ -42941,7 +42941,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.54845821857452</v>
+        <v>1.54845809936523</v>
       </c>
       <c r="H1468" t="n">
         <v>3000</v>
@@ -43057,7 +43057,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1472" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H1472" t="n">
         <v>13500</v>
@@ -43086,7 +43086,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.6026314496994</v>
+        <v>1.60263156890869</v>
       </c>
       <c r="H1473" t="n">
         <v>121200</v>
@@ -43115,7 +43115,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1474" t="n">
         <v>50700</v>
@@ -43144,7 +43144,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1475" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H1475" t="n">
         <v>33300</v>
@@ -43318,7 +43318,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1481" t="n">
         <v>6300</v>
@@ -43347,7 +43347,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1482" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1482" t="n">
         <v>35100</v>
@@ -43434,7 +43434,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1485" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1485" t="n">
         <v>2400</v>
@@ -43463,7 +43463,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1486" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1486" t="n">
         <v>3300</v>
@@ -43492,7 +43492,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1487" t="n">
         <v>21600</v>
@@ -43550,7 +43550,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1489" t="n">
-        <v>1.52137136459351</v>
+        <v>1.52137124538422</v>
       </c>
       <c r="H1489" t="n">
         <v>18300</v>
@@ -43608,7 +43608,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1491" t="n">
         <v>18900</v>
@@ -43637,7 +43637,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1492" t="n">
-        <v>1.48074126243591</v>
+        <v>1.48074114322662</v>
       </c>
       <c r="H1492" t="n">
         <v>6900</v>
@@ -43666,7 +43666,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1493" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1493" t="n">
         <v>2100</v>
@@ -43724,7 +43724,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1495" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1495" t="n">
         <v>7200</v>
@@ -43840,7 +43840,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1499" t="n">
         <v>3000</v>
@@ -43869,7 +43869,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1500" t="n">
         <v>0</v>
@@ -43927,7 +43927,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1502" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H1502" t="n">
         <v>14400</v>
@@ -43985,7 +43985,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1504" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1504" t="n">
         <v>11100</v>
@@ -44072,7 +44072,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1507" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1507" t="n">
         <v>3600</v>
@@ -44217,7 +44217,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1512" t="n">
-        <v>1.5620014667511</v>
+        <v>1.56200134754181</v>
       </c>
       <c r="H1512" t="n">
         <v>300</v>
@@ -44246,7 +44246,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.57554471492767</v>
+        <v>1.57554483413696</v>
       </c>
       <c r="H1513" t="n">
         <v>1200</v>
@@ -44362,7 +44362,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1517" t="n">
         <v>10200</v>
@@ -44391,7 +44391,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1518" t="n">
-        <v>1.57554471492767</v>
+        <v>1.57554483413696</v>
       </c>
       <c r="H1518" t="n">
         <v>5400</v>
@@ -44449,7 +44449,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1520" t="n">
-        <v>1.53491473197937</v>
+        <v>1.53491485118866</v>
       </c>
       <c r="H1520" t="n">
         <v>14100</v>
@@ -44478,7 +44478,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1521" t="n">
         <v>11100</v>
@@ -44507,7 +44507,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1522" t="n">
         <v>4200</v>
@@ -44536,7 +44536,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G1523" t="n">
-        <v>1.53942918777466</v>
+        <v>1.53942930698395</v>
       </c>
       <c r="H1523" t="n">
         <v>30000</v>
@@ -44623,7 +44623,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1526" t="n">
         <v>1800</v>
@@ -44652,7 +44652,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1527" t="n">
         <v>2700</v>
@@ -44739,7 +44739,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1530" t="n">
         <v>5100</v>
@@ -44768,7 +44768,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1531" t="n">
         <v>0</v>
@@ -44797,7 +44797,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1532" t="n">
         <v>600</v>
@@ -44826,7 +44826,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.65680503845215</v>
+        <v>1.65680491924286</v>
       </c>
       <c r="H1533" t="n">
         <v>82800</v>
@@ -44855,7 +44855,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.71097838878632</v>
+        <v>1.71097850799561</v>
       </c>
       <c r="H1534" t="n">
         <v>162900</v>
@@ -44971,7 +44971,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1538" t="n">
-        <v>1.65680503845215</v>
+        <v>1.65680491924286</v>
       </c>
       <c r="H1538" t="n">
         <v>7500</v>
@@ -45000,7 +45000,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1539" t="n">
-        <v>1.68389165401459</v>
+        <v>1.68389177322388</v>
       </c>
       <c r="H1539" t="n">
         <v>14700</v>
@@ -45058,7 +45058,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1541" t="n">
-        <v>1.64777600765228</v>
+        <v>1.64777624607086</v>
       </c>
       <c r="H1541" t="n">
         <v>2700</v>
@@ -45232,7 +45232,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1547" t="n">
         <v>6300</v>
@@ -45261,7 +45261,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1548" t="n">
         <v>4200</v>
@@ -45435,7 +45435,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1554" t="n">
-        <v>1.68389165401459</v>
+        <v>1.68389177322388</v>
       </c>
       <c r="H1554" t="n">
         <v>4500</v>
@@ -45493,7 +45493,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1556" t="n">
-        <v>1.6793771982193</v>
+        <v>1.67937731742859</v>
       </c>
       <c r="H1556" t="n">
         <v>3300</v>
@@ -45783,7 +45783,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1566" t="n">
-        <v>1.65680503845215</v>
+        <v>1.65680491924286</v>
       </c>
       <c r="H1566" t="n">
         <v>2700</v>
@@ -45957,7 +45957,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.64777600765228</v>
+        <v>1.64777624607086</v>
       </c>
       <c r="H1572" t="n">
         <v>13200</v>
@@ -46769,7 +46769,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.88704204559326</v>
+        <v>1.88704216480255</v>
       </c>
       <c r="H1600" t="n">
         <v>381900</v>
@@ -46798,7 +46798,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.89607095718384</v>
+        <v>1.89607083797455</v>
       </c>
       <c r="H1601" t="n">
         <v>59400</v>
@@ -46856,7 +46856,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.12179398536682</v>
+        <v>2.12179374694824</v>
       </c>
       <c r="H1603" t="n">
         <v>147900</v>
@@ -46914,7 +46914,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.12179398536682</v>
+        <v>2.12179374694824</v>
       </c>
       <c r="H1605" t="n">
         <v>38100</v>
@@ -46972,7 +46972,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1607" t="n">
-        <v>2.06762051582336</v>
+        <v>2.06762027740479</v>
       </c>
       <c r="H1607" t="n">
         <v>18600</v>
@@ -47001,7 +47001,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.06762051582336</v>
+        <v>2.06762027740479</v>
       </c>
       <c r="H1608" t="n">
         <v>29100</v>
@@ -47088,7 +47088,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1611" t="n">
-        <v>1.99538922309875</v>
+        <v>1.99538910388947</v>
       </c>
       <c r="H1611" t="n">
         <v>20700</v>
@@ -47146,7 +47146,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.95927369594574</v>
+        <v>1.95927345752716</v>
       </c>
       <c r="H1613" t="n">
         <v>45000</v>
@@ -47204,7 +47204,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1615" t="n">
-        <v>1.95927369594574</v>
+        <v>1.95927345752716</v>
       </c>
       <c r="H1615" t="n">
         <v>12000</v>
@@ -47523,7 +47523,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.10373592376709</v>
+        <v>2.10373616218567</v>
       </c>
       <c r="H1626" t="n">
         <v>31800</v>
@@ -47552,7 +47552,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H1627" t="n">
         <v>192000</v>
@@ -47668,7 +47668,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1631" t="n">
         <v>23100</v>
@@ -47697,7 +47697,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.51727485656738</v>
+        <v>2.5172746181488</v>
       </c>
       <c r="H1632" t="n">
         <v>41100</v>
@@ -47726,7 +47726,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.59213805198669</v>
+        <v>2.59213781356812</v>
       </c>
       <c r="H1633" t="n">
         <v>87600</v>
@@ -47871,7 +47871,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.13489603996277</v>
+        <v>3.13489580154419</v>
       </c>
       <c r="H1638" t="n">
         <v>112200</v>
@@ -47987,7 +47987,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1642" t="n">
         <v>209700</v>
@@ -48074,7 +48074,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.87287473678589</v>
+        <v>2.87287497520447</v>
       </c>
       <c r="H1645" t="n">
         <v>21300</v>
@@ -48190,7 +48190,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1649" t="n">
         <v>22800</v>
@@ -48248,7 +48248,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1651" t="n">
         <v>10500</v>
@@ -48306,7 +48306,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1653" t="n">
         <v>4800</v>
@@ -48364,7 +48364,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1655" t="n">
         <v>9000</v>
@@ -48451,7 +48451,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1658" t="n">
         <v>3900</v>
@@ -48567,7 +48567,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1662" t="n">
         <v>5400</v>
@@ -48625,7 +48625,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.73250651359558</v>
+        <v>2.732506275177</v>
       </c>
       <c r="H1664" t="n">
         <v>2400</v>
@@ -48654,7 +48654,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1665" t="n">
         <v>4500</v>
@@ -48683,7 +48683,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1666" t="n">
         <v>3900</v>
@@ -48712,7 +48712,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1667" t="n">
         <v>13800</v>
@@ -48741,7 +48741,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1668" t="n">
         <v>12600</v>
@@ -48915,7 +48915,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1674" t="n">
         <v>5700</v>
@@ -48973,7 +48973,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.81672739982605</v>
+        <v>2.81672763824463</v>
       </c>
       <c r="H1676" t="n">
         <v>5400</v>
@@ -49408,7 +49408,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.73250651359558</v>
+        <v>2.732506275177</v>
       </c>
       <c r="H1691" t="n">
         <v>3300</v>
@@ -49553,7 +49553,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.91030621528625</v>
+        <v>2.91030645370483</v>
       </c>
       <c r="H1696" t="n">
         <v>7800</v>
@@ -49582,7 +49582,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1697" t="n">
-        <v>2.91030621528625</v>
+        <v>2.91030645370483</v>
       </c>
       <c r="H1697" t="n">
         <v>16800</v>
@@ -49727,7 +49727,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.87287473678589</v>
+        <v>2.87287497520447</v>
       </c>
       <c r="H1702" t="n">
         <v>16500</v>
@@ -49843,7 +49843,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.92902231216431</v>
+        <v>2.92902255058289</v>
       </c>
       <c r="H1706" t="n">
         <v>13800</v>
@@ -49930,7 +49930,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1709" t="n">
-        <v>2.91030621528625</v>
+        <v>2.91030645370483</v>
       </c>
       <c r="H1709" t="n">
         <v>300</v>
@@ -49959,7 +49959,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.91030621528625</v>
+        <v>2.91030645370483</v>
       </c>
       <c r="H1710" t="n">
         <v>600</v>
@@ -49988,7 +49988,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.87287473678589</v>
+        <v>2.87287497520447</v>
       </c>
       <c r="H1711" t="n">
         <v>28800</v>
@@ -50075,7 +50075,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.91030621528625</v>
+        <v>2.91030645370483</v>
       </c>
       <c r="H1714" t="n">
         <v>5100</v>
@@ -50249,7 +50249,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.92902231216431</v>
+        <v>2.92902255058289</v>
       </c>
       <c r="H1720" t="n">
         <v>29100</v>
@@ -50336,7 +50336,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.92902231216431</v>
+        <v>2.92902255058289</v>
       </c>
       <c r="H1723" t="n">
         <v>26700</v>
@@ -50597,7 +50597,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1732" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1732" t="n">
         <v>48000</v>
@@ -50626,7 +50626,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1733" t="n">
         <v>64500</v>
@@ -50771,7 +50771,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1738" t="n">
-        <v>2.35819029808044</v>
+        <v>2.35819053649902</v>
       </c>
       <c r="H1738" t="n">
         <v>38400</v>
@@ -50800,7 +50800,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.35819029808044</v>
+        <v>2.35819053649902</v>
       </c>
       <c r="H1739" t="n">
         <v>18300</v>
@@ -50829,7 +50829,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.35819029808044</v>
+        <v>2.35819053649902</v>
       </c>
       <c r="H1740" t="n">
         <v>19200</v>
@@ -50887,7 +50887,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.36754822731018</v>
+        <v>2.36754846572876</v>
       </c>
       <c r="H1742" t="n">
         <v>5100</v>
@@ -50974,7 +50974,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H1745" t="n">
         <v>174000</v>
@@ -51177,7 +51177,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.4704852104187</v>
+        <v>2.47048544883728</v>
       </c>
       <c r="H1752" t="n">
         <v>7500</v>
@@ -51380,7 +51380,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1759" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1759" t="n">
         <v>600</v>
@@ -51409,7 +51409,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1760" t="n">
         <v>9000</v>
@@ -51438,7 +51438,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1761" t="n">
         <v>6600</v>
@@ -51641,7 +51641,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1768" t="n">
         <v>30000</v>
@@ -51844,7 +51844,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.64828538894653</v>
+        <v>2.64828515052795</v>
       </c>
       <c r="H1775" t="n">
         <v>13200</v>
@@ -51960,7 +51960,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.65764307975769</v>
+        <v>2.65764331817627</v>
       </c>
       <c r="H1779" t="n">
         <v>22500</v>
@@ -51989,7 +51989,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.73250651359558</v>
+        <v>2.732506275177</v>
       </c>
       <c r="H1780" t="n">
         <v>26700</v>
@@ -52047,7 +52047,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1782" t="n">
         <v>14100</v>
@@ -52076,7 +52076,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.73250651359558</v>
+        <v>2.732506275177</v>
       </c>
       <c r="H1783" t="n">
         <v>46200</v>
@@ -52105,7 +52105,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.73250651359558</v>
+        <v>2.732506275177</v>
       </c>
       <c r="H1784" t="n">
         <v>15000</v>
@@ -52134,7 +52134,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.69507503509521</v>
+        <v>2.69507479667664</v>
       </c>
       <c r="H1785" t="n">
         <v>35700</v>
@@ -52163,7 +52163,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1786" t="n">
         <v>19800</v>
@@ -52192,7 +52192,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1787" t="n">
-        <v>2.69507503509521</v>
+        <v>2.69507479667664</v>
       </c>
       <c r="H1787" t="n">
         <v>7200</v>
@@ -52221,7 +52221,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1788" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1788" t="n">
         <v>4500</v>
@@ -52308,7 +52308,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1791" t="n">
         <v>3300</v>
@@ -52366,7 +52366,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1793" t="n">
         <v>7200</v>
@@ -52453,7 +52453,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1796" t="n">
         <v>7800</v>
@@ -52482,7 +52482,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1797" t="n">
         <v>600</v>
@@ -52511,7 +52511,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1798" t="n">
         <v>10500</v>
@@ -52569,7 +52569,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1800" t="n">
         <v>34500</v>
@@ -52627,7 +52627,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1802" t="n">
         <v>8100</v>
@@ -52656,7 +52656,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1803" t="n">
         <v>0</v>
@@ -52685,7 +52685,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1804" t="n">
         <v>2100</v>
@@ -52743,7 +52743,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1806" t="n">
         <v>13500</v>
@@ -52772,7 +52772,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.64828538894653</v>
+        <v>2.64828515052795</v>
       </c>
       <c r="H1807" t="n">
         <v>81600</v>
@@ -52801,7 +52801,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.64828538894653</v>
+        <v>2.64828515052795</v>
       </c>
       <c r="H1808" t="n">
         <v>0</v>
@@ -52830,7 +52830,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1809" t="n">
         <v>12000</v>
@@ -52859,7 +52859,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1810" t="n">
         <v>300</v>
@@ -53004,7 +53004,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1815" t="n">
         <v>5100</v>
@@ -53062,7 +53062,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1817" t="n">
         <v>4800</v>
@@ -53091,7 +53091,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1818" t="n">
         <v>4800</v>
@@ -53323,7 +53323,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.69507503509521</v>
+        <v>2.69507479667664</v>
       </c>
       <c r="H1826" t="n">
         <v>9900</v>
@@ -53352,7 +53352,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1827" t="n">
         <v>6300</v>
@@ -53381,7 +53381,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.65764307975769</v>
+        <v>2.65764331817627</v>
       </c>
       <c r="H1828" t="n">
         <v>6300</v>
@@ -53816,7 +53816,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.19104361534119</v>
+        <v>3.19104337692261</v>
       </c>
       <c r="H1843" t="n">
         <v>98100</v>
@@ -53961,7 +53961,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.29398036003113</v>
+        <v>3.29398012161255</v>
       </c>
       <c r="H1848" t="n">
         <v>28200</v>
@@ -53990,7 +53990,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.29398036003113</v>
+        <v>3.29398012161255</v>
       </c>
       <c r="H1849" t="n">
         <v>10800</v>
@@ -54077,7 +54077,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.3126962184906</v>
+        <v>3.31269598007202</v>
       </c>
       <c r="H1852" t="n">
         <v>62700</v>
@@ -54106,7 +54106,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.3126962184906</v>
+        <v>3.31269598007202</v>
       </c>
       <c r="H1853" t="n">
         <v>15900</v>
@@ -54338,7 +54338,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.54664349555969</v>
+        <v>3.54664373397827</v>
       </c>
       <c r="H1861" t="n">
         <v>3600</v>
@@ -54599,7 +54599,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1870" t="n">
-        <v>3.65893864631653</v>
+        <v>3.65893840789795</v>
       </c>
       <c r="H1870" t="n">
         <v>20400</v>
@@ -54802,7 +54802,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1877" t="n">
-        <v>3.69637012481689</v>
+        <v>3.69636988639832</v>
       </c>
       <c r="H1877" t="n">
         <v>2100</v>
@@ -54860,7 +54860,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1879" t="n">
-        <v>3.75251770019531</v>
+        <v>3.75251746177673</v>
       </c>
       <c r="H1879" t="n">
         <v>9900</v>
@@ -54918,7 +54918,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1881" t="n">
-        <v>3.75251770019531</v>
+        <v>3.75251746177673</v>
       </c>
       <c r="H1881" t="n">
         <v>15900</v>
@@ -65581,7 +65581,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="D2249" t="n">
-        <v>4.23000001907349</v>
+        <v>4.25</v>
       </c>
       <c r="E2249" t="n">
         <v>4.23000001907349</v>
@@ -65596,6 +65596,35 @@
         <v>600</v>
       </c>
       <c r="I2249" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="A2250" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2250" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2250" t="n">
+        <v>4.23000001907349</v>
+      </c>
+      <c r="D2250" t="n">
+        <v>4.23000001907349</v>
+      </c>
+      <c r="E2250" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="F2250" t="n">
+        <v>4.23000001907349</v>
+      </c>
+      <c r="G2250" t="n">
+        <v>4.23000001907349</v>
+      </c>
+      <c r="H2250" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I2250" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H2" t="n">
         <v>326100</v>
@@ -456,7 +456,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G3" t="n">
-        <v>3.66393184661865</v>
+        <v>3.66393160820007</v>
       </c>
       <c r="H3" t="n">
         <v>35400</v>
@@ -485,7 +485,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G4" t="n">
-        <v>3.63684463500977</v>
+        <v>3.63684487342834</v>
       </c>
       <c r="H4" t="n">
         <v>17700</v>
@@ -514,7 +514,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H5" t="n">
         <v>14700</v>
@@ -630,7 +630,7 @@
         <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H9" t="n">
         <v>1200</v>
@@ -688,7 +688,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G11" t="n">
-        <v>3.63684463500977</v>
+        <v>3.63684487342834</v>
       </c>
       <c r="H11" t="n">
         <v>16500</v>
@@ -775,7 +775,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G14" t="n">
-        <v>3.64406800270081</v>
+        <v>3.64406776428223</v>
       </c>
       <c r="H14" t="n">
         <v>10200</v>
@@ -833,7 +833,7 @@
         <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H16" t="n">
         <v>600</v>
@@ -978,7 +978,7 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H21" t="n">
         <v>2100</v>
@@ -1007,7 +1007,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G22" t="n">
-        <v>3.62962174415588</v>
+        <v>3.62962198257446</v>
       </c>
       <c r="H22" t="n">
         <v>2700</v>
@@ -1036,7 +1036,7 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H23" t="n">
         <v>28500</v>
@@ -1065,7 +1065,7 @@
         <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>3.62962174415588</v>
+        <v>3.62962198257446</v>
       </c>
       <c r="H26" t="n">
         <v>5100</v>
@@ -1181,7 +1181,7 @@
         <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H28" t="n">
         <v>11400</v>
@@ -1210,7 +1210,7 @@
         <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H29" t="n">
         <v>4800</v>
@@ -1239,7 +1239,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G30" t="n">
-        <v>3.57544827461243</v>
+        <v>3.57544851303101</v>
       </c>
       <c r="H30" t="n">
         <v>300</v>
@@ -1268,7 +1268,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>3.57544827461243</v>
+        <v>3.57544851303101</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G37" t="n">
-        <v>3.53030371665955</v>
+        <v>3.53030395507812</v>
       </c>
       <c r="H37" t="n">
         <v>10200</v>
@@ -1471,7 +1471,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>3.52127528190613</v>
+        <v>3.52127504348755</v>
       </c>
       <c r="H38" t="n">
         <v>3600</v>
@@ -1500,7 +1500,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G39" t="n">
-        <v>3.52127528190613</v>
+        <v>3.52127504348755</v>
       </c>
       <c r="H39" t="n">
         <v>600</v>
@@ -1790,7 +1790,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>3.57544827461243</v>
+        <v>3.57544851303101</v>
       </c>
       <c r="H49" t="n">
         <v>1800</v>
@@ -1848,7 +1848,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H51" t="n">
         <v>17400</v>
@@ -2254,7 +2254,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G65" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H65" t="n">
         <v>1500</v>
@@ -2283,7 +2283,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G66" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G67" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G68" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G69" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G70" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G71" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H85" t="n">
         <v>7500</v>
@@ -2863,7 +2863,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H86" t="n">
         <v>2400</v>
@@ -2892,7 +2892,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G87" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H87" t="n">
         <v>3300</v>
@@ -2921,7 +2921,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G88" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G89" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>3.34972548484802</v>
+        <v>3.3497257232666</v>
       </c>
       <c r="H90" t="n">
         <v>900</v>
@@ -3008,7 +3008,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.34972548484802</v>
+        <v>3.3497257232666</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G92" t="n">
-        <v>3.34972548484802</v>
+        <v>3.3497257232666</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>3.34972548484802</v>
+        <v>3.3497257232666</v>
       </c>
       <c r="H99" t="n">
         <v>3600</v>
@@ -3269,7 +3269,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>3.34972548484802</v>
+        <v>3.3497257232666</v>
       </c>
       <c r="H100" t="n">
         <v>300</v>
@@ -3414,7 +3414,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>3.35875463485718</v>
+        <v>3.3587543964386</v>
       </c>
       <c r="H105" t="n">
         <v>900</v>
@@ -3559,7 +3559,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H110" t="n">
         <v>8100</v>
@@ -3617,7 +3617,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>3.20526313781738</v>
+        <v>3.2052628993988</v>
       </c>
       <c r="H112" t="n">
         <v>900</v>
@@ -3646,7 +3646,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>3.06982970237732</v>
+        <v>3.06982946395874</v>
       </c>
       <c r="H113" t="n">
         <v>5400</v>
@@ -3762,7 +3762,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G117" t="n">
-        <v>3.06982970237732</v>
+        <v>3.06982946395874</v>
       </c>
       <c r="H117" t="n">
         <v>6900</v>
@@ -3791,7 +3791,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>3.06982970237732</v>
+        <v>3.06982946395874</v>
       </c>
       <c r="H118" t="n">
         <v>22800</v>
@@ -3820,7 +3820,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G119" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H119" t="n">
         <v>30900</v>
@@ -3849,7 +3849,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G120" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H120" t="n">
         <v>2100</v>
@@ -4081,7 +4081,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G128" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H128" t="n">
         <v>600</v>
@@ -4197,7 +4197,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H132" t="n">
         <v>2100</v>
@@ -4284,7 +4284,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G135" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H135" t="n">
         <v>300</v>
@@ -4313,7 +4313,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G138" t="n">
-        <v>3.28652334213257</v>
+        <v>3.28652310371399</v>
       </c>
       <c r="H138" t="n">
         <v>900</v>
@@ -4690,7 +4690,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G149" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H149" t="n">
         <v>3900</v>
@@ -4719,7 +4719,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G151" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H151" t="n">
         <v>900</v>
@@ -5183,7 +5183,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G166" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H166" t="n">
         <v>2400</v>
@@ -5212,7 +5212,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G167" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G168" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G169" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G171" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G172" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G173" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G174" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G175" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G177" t="n">
-        <v>3.3948700428009</v>
+        <v>3.39487028121948</v>
       </c>
       <c r="H177" t="n">
         <v>2400</v>
@@ -5792,7 +5792,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>3.19623422622681</v>
+        <v>3.19623398780823</v>
       </c>
       <c r="H187" t="n">
         <v>6600</v>
@@ -5908,7 +5908,7 @@
         <v>3.5</v>
       </c>
       <c r="G191" t="n">
-        <v>3.1601185798645</v>
+        <v>3.16011881828308</v>
       </c>
       <c r="H191" t="n">
         <v>300</v>
@@ -5937,7 +5937,7 @@
         <v>3.5</v>
       </c>
       <c r="G192" t="n">
-        <v>3.1601185798645</v>
+        <v>3.16011881828308</v>
       </c>
       <c r="H192" t="n">
         <v>2400</v>
@@ -5966,7 +5966,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G193" t="n">
-        <v>3.12400269508362</v>
+        <v>3.1240029335022</v>
       </c>
       <c r="H193" t="n">
         <v>2100</v>
@@ -5995,7 +5995,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>3.19623422622681</v>
+        <v>3.19623398780823</v>
       </c>
       <c r="H194" t="n">
         <v>600</v>
@@ -6285,7 +6285,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G204" t="n">
-        <v>3.06982970237732</v>
+        <v>3.06982946395874</v>
       </c>
       <c r="H204" t="n">
         <v>1800</v>
@@ -6314,7 +6314,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>3.06982970237732</v>
+        <v>3.06982946395874</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>3.06982970237732</v>
+        <v>3.06982946395874</v>
       </c>
       <c r="H206" t="n">
         <v>1500</v>
@@ -6372,7 +6372,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>3.06982970237732</v>
+        <v>3.06982946395874</v>
       </c>
       <c r="H207" t="n">
         <v>300</v>
@@ -6430,7 +6430,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H209" t="n">
         <v>13500</v>
@@ -6459,7 +6459,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G210" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G211" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G212" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G213" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G221" t="n">
-        <v>2.60032629966736</v>
+        <v>2.60032606124878</v>
       </c>
       <c r="H221" t="n">
         <v>900</v>
@@ -6807,7 +6807,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H222" t="n">
         <v>3900</v>
@@ -6836,7 +6836,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G223" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G225" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H225" t="n">
         <v>1200</v>
@@ -6923,7 +6923,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G226" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H228" t="n">
         <v>2700</v>
@@ -7010,7 +7010,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G230" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G231" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G232" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G236" t="n">
-        <v>2.51003670692444</v>
+        <v>2.5100371837616</v>
       </c>
       <c r="H236" t="n">
         <v>2700</v>
@@ -7242,7 +7242,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G237" t="n">
-        <v>2.51003670692444</v>
+        <v>2.5100371837616</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>2.50100827217102</v>
+        <v>2.50100803375244</v>
       </c>
       <c r="H244" t="n">
         <v>22800</v>
@@ -7474,7 +7474,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G245" t="n">
-        <v>2.50100827217102</v>
+        <v>2.50100803375244</v>
       </c>
       <c r="H245" t="n">
         <v>2400</v>
@@ -7503,7 +7503,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G246" t="n">
-        <v>2.50100827217102</v>
+        <v>2.50100803375244</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G247" t="n">
-        <v>2.50100827217102</v>
+        <v>2.50100803375244</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G248" t="n">
-        <v>2.50100827217102</v>
+        <v>2.50100803375244</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G249" t="n">
-        <v>2.51003670692444</v>
+        <v>2.5100371837616</v>
       </c>
       <c r="H249" t="n">
         <v>2100</v>
@@ -7619,7 +7619,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G250" t="n">
-        <v>2.41071915626526</v>
+        <v>2.41071891784668</v>
       </c>
       <c r="H250" t="n">
         <v>600</v>
@@ -7648,7 +7648,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>2.41071915626526</v>
+        <v>2.41071891784668</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G252" t="n">
-        <v>2.41071915626526</v>
+        <v>2.41071891784668</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G253" t="n">
-        <v>2.41071915626526</v>
+        <v>2.41071891784668</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>2.41071915626526</v>
+        <v>2.41071891784668</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G263" t="n">
-        <v>2.32042980194092</v>
+        <v>2.32042956352234</v>
       </c>
       <c r="H263" t="n">
         <v>2100</v>
@@ -8025,7 +8025,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G264" t="n">
-        <v>2.32042980194092</v>
+        <v>2.32042956352234</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G265" t="n">
-        <v>2.32042980194092</v>
+        <v>2.32042956352234</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.32042980194092</v>
+        <v>2.32042956352234</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G268" t="n">
-        <v>2.47392153739929</v>
+        <v>2.47392129898071</v>
       </c>
       <c r="H268" t="n">
         <v>1500</v>
@@ -8170,7 +8170,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G269" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H269" t="n">
         <v>2400</v>
@@ -8373,7 +8373,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G276" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H276" t="n">
         <v>1200</v>
@@ -8402,7 +8402,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G277" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H277" t="n">
         <v>3600</v>
@@ -8518,7 +8518,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G281" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H281" t="n">
         <v>21000</v>
@@ -8721,7 +8721,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>2.18499636650085</v>
+        <v>2.18499612808228</v>
       </c>
       <c r="H288" t="n">
         <v>1200</v>
@@ -8750,7 +8750,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G289" t="n">
-        <v>2.18499636650085</v>
+        <v>2.18499612808228</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>2.15790939331055</v>
+        <v>2.15790963172913</v>
       </c>
       <c r="H290" t="n">
         <v>20700</v>
@@ -8808,7 +8808,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>2.12179374694824</v>
+        <v>2.12179398536682</v>
       </c>
       <c r="H291" t="n">
         <v>2400</v>
@@ -8837,7 +8837,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G292" t="n">
-        <v>2.05859160423279</v>
+        <v>2.05859136581421</v>
       </c>
       <c r="H292" t="n">
         <v>18900</v>
@@ -8866,7 +8866,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G293" t="n">
-        <v>2.06762027740479</v>
+        <v>2.06762051582336</v>
       </c>
       <c r="H293" t="n">
         <v>300</v>
@@ -8953,7 +8953,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G296" t="n">
-        <v>2.02247595787048</v>
+        <v>2.0224757194519</v>
       </c>
       <c r="H296" t="n">
         <v>1800</v>
@@ -9127,7 +9127,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>1.97733116149902</v>
+        <v>1.97733128070831</v>
       </c>
       <c r="H302" t="n">
         <v>4200</v>
@@ -9156,7 +9156,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G303" t="n">
-        <v>1.97733116149902</v>
+        <v>1.97733128070831</v>
       </c>
       <c r="H303" t="n">
         <v>300</v>
@@ -9243,7 +9243,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G306" t="n">
-        <v>2.04053354263306</v>
+        <v>2.04053378105164</v>
       </c>
       <c r="H306" t="n">
         <v>3600</v>
@@ -9359,7 +9359,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>2.04053354263306</v>
+        <v>2.04053378105164</v>
       </c>
       <c r="H310" t="n">
         <v>900</v>
@@ -9475,7 +9475,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G314" t="n">
-        <v>2.02247595787048</v>
+        <v>2.0224757194519</v>
       </c>
       <c r="H314" t="n">
         <v>1800</v>
@@ -9562,7 +9562,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G317" t="n">
-        <v>1.89607083797455</v>
+        <v>1.89607095718384</v>
       </c>
       <c r="H317" t="n">
         <v>6900</v>
@@ -9678,7 +9678,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G321" t="n">
-        <v>1.95024466514587</v>
+        <v>1.95024478435516</v>
       </c>
       <c r="H321" t="n">
         <v>600</v>
@@ -9707,7 +9707,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G322" t="n">
-        <v>1.95024466514587</v>
+        <v>1.95024478435516</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G323" t="n">
-        <v>1.95024466514587</v>
+        <v>1.95024478435516</v>
       </c>
       <c r="H323" t="n">
         <v>600</v>
@@ -9765,7 +9765,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G324" t="n">
-        <v>1.95024466514587</v>
+        <v>1.95024478435516</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>1.92315804958344</v>
+        <v>1.92315793037415</v>
       </c>
       <c r="H325" t="n">
         <v>600</v>
@@ -9881,7 +9881,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G328" t="n">
-        <v>1.91412878036499</v>
+        <v>1.91412889957428</v>
       </c>
       <c r="H328" t="n">
         <v>51000</v>
@@ -9910,7 +9910,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G329" t="n">
-        <v>1.89607083797455</v>
+        <v>1.89607095718384</v>
       </c>
       <c r="H329" t="n">
         <v>3600</v>
@@ -9968,7 +9968,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G331" t="n">
-        <v>1.89607083797455</v>
+        <v>1.89607095718384</v>
       </c>
       <c r="H331" t="n">
         <v>27900</v>
@@ -9997,7 +9997,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G332" t="n">
-        <v>1.89607083797455</v>
+        <v>1.89607095718384</v>
       </c>
       <c r="H332" t="n">
         <v>4800</v>
@@ -10142,7 +10142,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G337" t="n">
-        <v>2.02247595787048</v>
+        <v>2.0224757194519</v>
       </c>
       <c r="H337" t="n">
         <v>300</v>
@@ -10171,7 +10171,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G338" t="n">
-        <v>2.04053354263306</v>
+        <v>2.04053378105164</v>
       </c>
       <c r="H338" t="n">
         <v>18000</v>
@@ -10200,7 +10200,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G339" t="n">
-        <v>2.05859160423279</v>
+        <v>2.05859136581421</v>
       </c>
       <c r="H339" t="n">
         <v>54900</v>
@@ -10258,7 +10258,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G341" t="n">
-        <v>2.04053354263306</v>
+        <v>2.04053378105164</v>
       </c>
       <c r="H341" t="n">
         <v>1200</v>
@@ -10403,7 +10403,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>1.89607083797455</v>
+        <v>1.89607095718384</v>
       </c>
       <c r="H346" t="n">
         <v>29700</v>
@@ -10490,7 +10490,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G349" t="n">
-        <v>1.89607083797455</v>
+        <v>1.89607095718384</v>
       </c>
       <c r="H349" t="n">
         <v>5400</v>
@@ -10606,7 +10606,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G353" t="n">
-        <v>1.89607083797455</v>
+        <v>1.89607095718384</v>
       </c>
       <c r="H353" t="n">
         <v>1800</v>
@@ -10635,7 +10635,7 @@
         <v>2</v>
       </c>
       <c r="G354" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H354" t="n">
         <v>21600</v>
@@ -10693,7 +10693,7 @@
         <v>2</v>
       </c>
       <c r="G356" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H356" t="n">
         <v>1500</v>
@@ -10722,7 +10722,7 @@
         <v>2</v>
       </c>
       <c r="G357" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>2</v>
       </c>
       <c r="G358" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
         <v>2</v>
       </c>
       <c r="G359" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>2</v>
       </c>
       <c r="G360" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>2</v>
       </c>
       <c r="G361" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>2</v>
       </c>
       <c r="G362" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>2</v>
       </c>
       <c r="G363" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>2</v>
       </c>
       <c r="G365" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H365" t="n">
         <v>3000</v>
@@ -10983,7 +10983,7 @@
         <v>2</v>
       </c>
       <c r="G366" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>2</v>
       </c>
       <c r="G378" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H378" t="n">
         <v>2100</v>
@@ -11360,7 +11360,7 @@
         <v>2</v>
       </c>
       <c r="G379" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>2</v>
       </c>
       <c r="G380" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>1.78772413730621</v>
+        <v>1.7877242565155</v>
       </c>
       <c r="H381" t="n">
         <v>98700</v>
@@ -11447,7 +11447,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G382" t="n">
-        <v>1.71549296379089</v>
+        <v>1.7154928445816</v>
       </c>
       <c r="H382" t="n">
         <v>9600</v>
@@ -11476,7 +11476,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G383" t="n">
-        <v>1.71549296379089</v>
+        <v>1.7154928445816</v>
       </c>
       <c r="H383" t="n">
         <v>23400</v>
@@ -11563,7 +11563,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G386" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H386" t="n">
         <v>5100</v>
@@ -11679,7 +11679,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G390" t="n">
-        <v>1.67937731742859</v>
+        <v>1.6793771982193</v>
       </c>
       <c r="H390" t="n">
         <v>2400</v>
@@ -11708,7 +11708,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G391" t="n">
-        <v>1.71549296379089</v>
+        <v>1.7154928445816</v>
       </c>
       <c r="H391" t="n">
         <v>4800</v>
@@ -11737,7 +11737,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G392" t="n">
-        <v>1.69743502140045</v>
+        <v>1.69743514060974</v>
       </c>
       <c r="H392" t="n">
         <v>2100</v>
@@ -11766,7 +11766,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G393" t="n">
-        <v>1.69743502140045</v>
+        <v>1.69743514060974</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -11824,7 +11824,7 @@
         <v>1.75</v>
       </c>
       <c r="G395" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H395" t="n">
         <v>3900</v>
@@ -11853,7 +11853,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G396" t="n">
-        <v>1.5981171131134</v>
+        <v>1.59811699390411</v>
       </c>
       <c r="H396" t="n">
         <v>12600</v>
@@ -11882,7 +11882,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G397" t="n">
-        <v>1.56200134754181</v>
+        <v>1.5620014667511</v>
       </c>
       <c r="H397" t="n">
         <v>5400</v>
@@ -11911,7 +11911,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H398" t="n">
         <v>1200</v>
@@ -12027,7 +12027,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G402" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H402" t="n">
         <v>7800</v>
@@ -12433,7 +12433,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G416" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H416" t="n">
         <v>2100</v>
@@ -12549,7 +12549,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G420" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H420" t="n">
         <v>300</v>
@@ -12723,7 +12723,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G426" t="n">
-        <v>1.28210520744324</v>
+        <v>1.28210532665253</v>
       </c>
       <c r="H426" t="n">
         <v>5100</v>
@@ -12868,7 +12868,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G431" t="n">
-        <v>1.28210520744324</v>
+        <v>1.28210532665253</v>
       </c>
       <c r="H431" t="n">
         <v>11700</v>
@@ -12897,7 +12897,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G432" t="n">
-        <v>1.30016314983368</v>
+        <v>1.30016303062439</v>
       </c>
       <c r="H432" t="n">
         <v>900</v>
@@ -12926,7 +12926,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G433" t="n">
-        <v>1.30919206142426</v>
+        <v>1.30919194221497</v>
       </c>
       <c r="H433" t="n">
         <v>300</v>
@@ -13013,7 +13013,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>1.30016314983368</v>
+        <v>1.30016303062439</v>
       </c>
       <c r="H436" t="n">
         <v>4200</v>
@@ -13042,7 +13042,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G437" t="n">
-        <v>1.30016314983368</v>
+        <v>1.30016303062439</v>
       </c>
       <c r="H437" t="n">
         <v>39900</v>
@@ -13071,7 +13071,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G438" t="n">
-        <v>1.30919206142426</v>
+        <v>1.30919194221497</v>
       </c>
       <c r="H438" t="n">
         <v>27900</v>
@@ -13100,7 +13100,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G439" t="n">
-        <v>1.30016314983368</v>
+        <v>1.30016303062439</v>
       </c>
       <c r="H439" t="n">
         <v>6000</v>
@@ -13129,7 +13129,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G440" t="n">
-        <v>1.30016314983368</v>
+        <v>1.30016303062439</v>
       </c>
       <c r="H440" t="n">
         <v>1500</v>
@@ -13158,7 +13158,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G441" t="n">
-        <v>1.30016314983368</v>
+        <v>1.30016303062439</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G442" t="n">
-        <v>1.24598956108093</v>
+        <v>1.24598968029022</v>
       </c>
       <c r="H442" t="n">
         <v>79500</v>
@@ -13390,7 +13390,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G449" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H449" t="n">
         <v>71700</v>
@@ -13419,7 +13419,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>1.56200134754181</v>
+        <v>1.5620014667511</v>
       </c>
       <c r="H450" t="n">
         <v>29700</v>
@@ -13448,7 +13448,7 @@
         <v>1.75</v>
       </c>
       <c r="G451" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H451" t="n">
         <v>17400</v>
@@ -13970,7 +13970,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G469" t="n">
-        <v>1.67937731742859</v>
+        <v>1.6793771982193</v>
       </c>
       <c r="H469" t="n">
         <v>347100</v>
@@ -13999,7 +13999,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G470" t="n">
-        <v>1.53491485118866</v>
+        <v>1.53491473197937</v>
       </c>
       <c r="H470" t="n">
         <v>92700</v>
@@ -14028,7 +14028,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G471" t="n">
-        <v>1.5981171131134</v>
+        <v>1.59811699390411</v>
       </c>
       <c r="H471" t="n">
         <v>32400</v>
@@ -14115,7 +14115,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G474" t="n">
-        <v>1.53491485118866</v>
+        <v>1.53491473197937</v>
       </c>
       <c r="H474" t="n">
         <v>12300</v>
@@ -14173,7 +14173,7 @@
         <v>1.75</v>
       </c>
       <c r="G476" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H476" t="n">
         <v>21600</v>
@@ -14202,7 +14202,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G477" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H477" t="n">
         <v>18600</v>
@@ -14231,7 +14231,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G478" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H478" t="n">
         <v>31500</v>
@@ -14434,7 +14434,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G485" t="n">
-        <v>1.39948093891144</v>
+        <v>1.39948105812073</v>
       </c>
       <c r="H485" t="n">
         <v>4500</v>
@@ -14492,7 +14492,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G487" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H487" t="n">
         <v>4500</v>
@@ -14608,7 +14608,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G491" t="n">
-        <v>1.39948093891144</v>
+        <v>1.39948105812073</v>
       </c>
       <c r="H491" t="n">
         <v>5100</v>
@@ -14666,7 +14666,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G493" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H493" t="n">
         <v>50700</v>
@@ -14695,7 +14695,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G494" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H494" t="n">
         <v>7200</v>
@@ -14753,7 +14753,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G496" t="n">
-        <v>1.53491485118866</v>
+        <v>1.53491473197937</v>
       </c>
       <c r="H496" t="n">
         <v>100200</v>
@@ -14869,7 +14869,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>1.5981171131134</v>
+        <v>1.59811699390411</v>
       </c>
       <c r="H500" t="n">
         <v>22200</v>
@@ -15043,7 +15043,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G506" t="n">
-        <v>1.5981171131134</v>
+        <v>1.59811699390411</v>
       </c>
       <c r="H506" t="n">
         <v>8700</v>
@@ -15072,7 +15072,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G507" t="n">
-        <v>1.5981171131134</v>
+        <v>1.59811699390411</v>
       </c>
       <c r="H507" t="n">
         <v>10500</v>
@@ -15101,7 +15101,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G508" t="n">
-        <v>1.5981171131134</v>
+        <v>1.59811699390411</v>
       </c>
       <c r="H508" t="n">
         <v>12600</v>
@@ -15159,7 +15159,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G510" t="n">
-        <v>1.56200134754181</v>
+        <v>1.5620014667511</v>
       </c>
       <c r="H510" t="n">
         <v>14400</v>
@@ -15217,7 +15217,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H512" t="n">
         <v>36000</v>
@@ -15246,7 +15246,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G513" t="n">
-        <v>1.56200134754181</v>
+        <v>1.5620014667511</v>
       </c>
       <c r="H513" t="n">
         <v>8700</v>
@@ -15304,7 +15304,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G515" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H515" t="n">
         <v>7500</v>
@@ -15449,7 +15449,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G520" t="n">
-        <v>1.61617493629456</v>
+        <v>1.61617481708527</v>
       </c>
       <c r="H520" t="n">
         <v>1500</v>
@@ -15536,7 +15536,7 @@
         <v>1.75</v>
       </c>
       <c r="G523" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H523" t="n">
         <v>9900</v>
@@ -15565,7 +15565,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G524" t="n">
-        <v>1.56200134754181</v>
+        <v>1.5620014667511</v>
       </c>
       <c r="H524" t="n">
         <v>6900</v>
@@ -15623,7 +15623,7 @@
         <v>1.75</v>
       </c>
       <c r="G526" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H526" t="n">
         <v>92100</v>
@@ -15652,7 +15652,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G527" t="n">
-        <v>1.53491485118866</v>
+        <v>1.53491473197937</v>
       </c>
       <c r="H527" t="n">
         <v>43800</v>
@@ -15681,7 +15681,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G528" t="n">
-        <v>1.53491485118866</v>
+        <v>1.53491473197937</v>
       </c>
       <c r="H528" t="n">
         <v>18300</v>
@@ -15710,7 +15710,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G529" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H529" t="n">
         <v>24600</v>
@@ -15739,7 +15739,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G530" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H530" t="n">
         <v>83400</v>
@@ -15768,7 +15768,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G531" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H531" t="n">
         <v>13800</v>
@@ -15797,7 +15797,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G532" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H532" t="n">
         <v>65400</v>
@@ -16000,7 +16000,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G539" t="n">
-        <v>1.25501835346222</v>
+        <v>1.2550185918808</v>
       </c>
       <c r="H539" t="n">
         <v>51300</v>
@@ -16087,7 +16087,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G542" t="n">
-        <v>1.30919206142426</v>
+        <v>1.30919194221497</v>
       </c>
       <c r="H542" t="n">
         <v>21600</v>
@@ -16145,7 +16145,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G544" t="n">
-        <v>1.30919206142426</v>
+        <v>1.30919194221497</v>
       </c>
       <c r="H544" t="n">
         <v>11400</v>
@@ -16174,7 +16174,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G545" t="n">
-        <v>1.25501835346222</v>
+        <v>1.2550185918808</v>
       </c>
       <c r="H545" t="n">
         <v>70200</v>
@@ -16232,7 +16232,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G547" t="n">
-        <v>1.20084512233734</v>
+        <v>1.20084500312805</v>
       </c>
       <c r="H547" t="n">
         <v>76200</v>
@@ -16290,7 +16290,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G549" t="n">
-        <v>1.19181609153748</v>
+        <v>1.19181621074677</v>
       </c>
       <c r="H549" t="n">
         <v>45900</v>
@@ -16319,7 +16319,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G550" t="n">
-        <v>1.19181609153748</v>
+        <v>1.19181621074677</v>
       </c>
       <c r="H550" t="n">
         <v>19800</v>
@@ -16435,7 +16435,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G554" t="n">
-        <v>1.08346927165985</v>
+        <v>1.08346915245056</v>
       </c>
       <c r="H554" t="n">
         <v>29100</v>
@@ -16493,7 +16493,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G556" t="n">
-        <v>1.02026677131653</v>
+        <v>1.02026689052582</v>
       </c>
       <c r="H556" t="n">
         <v>72900</v>
@@ -16522,7 +16522,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G557" t="n">
-        <v>1.02026677131653</v>
+        <v>1.02026689052582</v>
       </c>
       <c r="H557" t="n">
         <v>37800</v>
@@ -16551,7 +16551,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G558" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H558" t="n">
         <v>19500</v>
@@ -16580,7 +16580,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G559" t="n">
-        <v>1.01123797893524</v>
+        <v>1.01123785972595</v>
       </c>
       <c r="H559" t="n">
         <v>22800</v>
@@ -16609,7 +16609,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G560" t="n">
-        <v>1.01123797893524</v>
+        <v>1.01123785972595</v>
       </c>
       <c r="H560" t="n">
         <v>13800</v>
@@ -16696,7 +16696,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G563" t="n">
-        <v>0.948035418987274</v>
+        <v>0.948035478591919</v>
       </c>
       <c r="H563" t="n">
         <v>45900</v>
@@ -16783,7 +16783,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G566" t="n">
-        <v>0.839688658714294</v>
+        <v>0.83968859910965</v>
       </c>
       <c r="H566" t="n">
         <v>3600</v>
@@ -16870,7 +16870,7 @@
         <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>0.902890980243683</v>
+        <v>0.902891039848328</v>
       </c>
       <c r="H569" t="n">
         <v>16200</v>
@@ -16899,7 +16899,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>0.884833157062531</v>
+        <v>0.884833216667175</v>
       </c>
       <c r="H570" t="n">
         <v>10800</v>
@@ -17044,7 +17044,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G575" t="n">
-        <v>0.884833157062531</v>
+        <v>0.884833216667175</v>
       </c>
       <c r="H575" t="n">
         <v>16200</v>
@@ -17131,7 +17131,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G578" t="n">
-        <v>0.975122332572937</v>
+        <v>0.975122392177582</v>
       </c>
       <c r="H578" t="n">
         <v>14700</v>
@@ -17218,7 +17218,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G581" t="n">
-        <v>1.01123797893524</v>
+        <v>1.01123785972595</v>
       </c>
       <c r="H581" t="n">
         <v>24300</v>
@@ -17276,7 +17276,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>1.03381013870239</v>
+        <v>1.03381025791168</v>
       </c>
       <c r="H583" t="n">
         <v>5400</v>
@@ -17305,7 +17305,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G584" t="n">
-        <v>1.03381013870239</v>
+        <v>1.03381025791168</v>
       </c>
       <c r="H584" t="n">
         <v>17400</v>
@@ -17392,7 +17392,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G587" t="n">
-        <v>1.03381013870239</v>
+        <v>1.03381025791168</v>
       </c>
       <c r="H587" t="n">
         <v>15000</v>
@@ -17508,7 +17508,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G591" t="n">
-        <v>0.952549993991852</v>
+        <v>0.952549874782562</v>
       </c>
       <c r="H591" t="n">
         <v>102000</v>
@@ -17566,7 +17566,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G593" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H593" t="n">
         <v>12900</v>
@@ -17595,7 +17595,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G594" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H594" t="n">
         <v>1500</v>
@@ -17624,7 +17624,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H595" t="n">
         <v>15900</v>
@@ -17682,7 +17682,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G597" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H597" t="n">
         <v>15000</v>
@@ -17711,7 +17711,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G598" t="n">
-        <v>0.952549993991852</v>
+        <v>0.952549874782562</v>
       </c>
       <c r="H598" t="n">
         <v>21600</v>
@@ -17798,7 +17798,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G601" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H601" t="n">
         <v>17100</v>
@@ -17972,7 +17972,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G607" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H607" t="n">
         <v>7800</v>
@@ -18030,7 +18030,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G609" t="n">
-        <v>0.925463199615479</v>
+        <v>0.925463259220123</v>
       </c>
       <c r="H609" t="n">
         <v>38400</v>
@@ -18088,7 +18088,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G611" t="n">
-        <v>0.925463199615479</v>
+        <v>0.925463259220123</v>
       </c>
       <c r="H611" t="n">
         <v>195300</v>
@@ -18117,7 +18117,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G612" t="n">
-        <v>0.901085257530212</v>
+        <v>0.901085317134857</v>
       </c>
       <c r="H612" t="n">
         <v>36000</v>
@@ -18204,7 +18204,7 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>0.902890980243683</v>
+        <v>0.902891039848328</v>
       </c>
       <c r="H615" t="n">
         <v>20700</v>
@@ -18233,7 +18233,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G616" t="n">
-        <v>0.901085257530212</v>
+        <v>0.901085317134857</v>
       </c>
       <c r="H616" t="n">
         <v>26700</v>
@@ -18320,7 +18320,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G619" t="n">
-        <v>0.893862068653107</v>
+        <v>0.893862128257751</v>
       </c>
       <c r="H619" t="n">
         <v>41100</v>
@@ -18349,7 +18349,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G620" t="n">
-        <v>0.901085257530212</v>
+        <v>0.901085317134857</v>
       </c>
       <c r="H620" t="n">
         <v>13500</v>
@@ -18378,7 +18378,7 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>0.902890980243683</v>
+        <v>0.902891039848328</v>
       </c>
       <c r="H621" t="n">
         <v>9900</v>
@@ -18407,7 +18407,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G622" t="n">
-        <v>0.901085257530212</v>
+        <v>0.901085317134857</v>
       </c>
       <c r="H622" t="n">
         <v>54000</v>
@@ -18436,7 +18436,7 @@
         <v>1</v>
       </c>
       <c r="G623" t="n">
-        <v>0.902890980243683</v>
+        <v>0.902891039848328</v>
       </c>
       <c r="H623" t="n">
         <v>20100</v>
@@ -18494,7 +18494,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G625" t="n">
-        <v>0.901085257530212</v>
+        <v>0.901085317134857</v>
       </c>
       <c r="H625" t="n">
         <v>47100</v>
@@ -18552,7 +18552,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G627" t="n">
-        <v>1.04283916950226</v>
+        <v>1.04283905029297</v>
       </c>
       <c r="H627" t="n">
         <v>258300</v>
@@ -18581,7 +18581,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G628" t="n">
-        <v>0.988665580749512</v>
+        <v>0.988665640354156</v>
       </c>
       <c r="H628" t="n">
         <v>45600</v>
@@ -18639,7 +18639,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G630" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H630" t="n">
         <v>20400</v>
@@ -18668,7 +18668,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>0.997694551944733</v>
+        <v>0.997694611549377</v>
       </c>
       <c r="H631" t="n">
         <v>19200</v>
@@ -18726,7 +18726,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G633" t="n">
-        <v>1.01123797893524</v>
+        <v>1.01123785972595</v>
       </c>
       <c r="H633" t="n">
         <v>12000</v>
@@ -18784,7 +18784,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G635" t="n">
-        <v>1.02929580211639</v>
+        <v>1.0292956829071</v>
       </c>
       <c r="H635" t="n">
         <v>5700</v>
@@ -18900,7 +18900,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H639" t="n">
         <v>2400</v>
@@ -18929,7 +18929,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G640" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H640" t="n">
         <v>18600</v>
@@ -18958,7 +18958,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G641" t="n">
-        <v>0.948035418987274</v>
+        <v>0.948035478591919</v>
       </c>
       <c r="H641" t="n">
         <v>3300</v>
@@ -19074,7 +19074,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G645" t="n">
-        <v>0.925463199615479</v>
+        <v>0.925463259220123</v>
       </c>
       <c r="H645" t="n">
         <v>9000</v>
@@ -19190,7 +19190,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G649" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H649" t="n">
         <v>3000</v>
@@ -19248,7 +19248,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G651" t="n">
-        <v>0.975122332572937</v>
+        <v>0.975122392177582</v>
       </c>
       <c r="H651" t="n">
         <v>2700</v>
@@ -19596,7 +19596,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G663" t="n">
-        <v>0.948035418987274</v>
+        <v>0.948035478591919</v>
       </c>
       <c r="H663" t="n">
         <v>6900</v>
@@ -19625,7 +19625,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G664" t="n">
-        <v>0.952549993991852</v>
+        <v>0.952549874782562</v>
       </c>
       <c r="H664" t="n">
         <v>300</v>
@@ -19654,7 +19654,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G665" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H665" t="n">
         <v>1800</v>
@@ -19712,7 +19712,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G667" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H667" t="n">
         <v>3900</v>
@@ -19741,7 +19741,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G668" t="n">
-        <v>0.948035418987274</v>
+        <v>0.948035478591919</v>
       </c>
       <c r="H668" t="n">
         <v>5100</v>
@@ -19770,7 +19770,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G669" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H669" t="n">
         <v>300</v>
@@ -19828,7 +19828,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G671" t="n">
-        <v>0.948035418987274</v>
+        <v>0.948035478591919</v>
       </c>
       <c r="H671" t="n">
         <v>4500</v>
@@ -19857,7 +19857,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G672" t="n">
-        <v>0.961579024791718</v>
+        <v>0.961578965187073</v>
       </c>
       <c r="H672" t="n">
         <v>300</v>
@@ -19886,7 +19886,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.988665580749512</v>
+        <v>0.988665640354156</v>
       </c>
       <c r="H673" t="n">
         <v>3300</v>
@@ -19915,7 +19915,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G674" t="n">
-        <v>0.988665580749512</v>
+        <v>0.988665640354156</v>
       </c>
       <c r="H674" t="n">
         <v>300</v>
@@ -20002,7 +20002,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G677" t="n">
-        <v>0.975122332572937</v>
+        <v>0.975122392177582</v>
       </c>
       <c r="H677" t="n">
         <v>10500</v>
@@ -20031,7 +20031,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G678" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H678" t="n">
         <v>9300</v>
@@ -20089,7 +20089,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G680" t="n">
-        <v>0.948035418987274</v>
+        <v>0.948035478591919</v>
       </c>
       <c r="H680" t="n">
         <v>600</v>
@@ -20118,7 +20118,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G681" t="n">
-        <v>0.948035418987274</v>
+        <v>0.948035478591919</v>
       </c>
       <c r="H681" t="n">
         <v>12300</v>
@@ -20147,7 +20147,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G682" t="n">
-        <v>0.948035418987274</v>
+        <v>0.948035478591919</v>
       </c>
       <c r="H682" t="n">
         <v>600</v>
@@ -20205,7 +20205,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G684" t="n">
-        <v>0.907405436038971</v>
+        <v>0.907405495643616</v>
       </c>
       <c r="H684" t="n">
         <v>29700</v>
@@ -20292,7 +20292,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G687" t="n">
-        <v>0.952549993991852</v>
+        <v>0.952549874782562</v>
       </c>
       <c r="H687" t="n">
         <v>3600</v>
@@ -20350,7 +20350,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G689" t="n">
-        <v>0.948035418987274</v>
+        <v>0.948035478591919</v>
       </c>
       <c r="H689" t="n">
         <v>600</v>
@@ -20379,7 +20379,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G690" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H690" t="n">
         <v>3600</v>
@@ -20408,7 +20408,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G691" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H691" t="n">
         <v>600</v>
@@ -20466,7 +20466,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G693" t="n">
-        <v>0.925463199615479</v>
+        <v>0.925463259220123</v>
       </c>
       <c r="H693" t="n">
         <v>15600</v>
@@ -20495,7 +20495,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G694" t="n">
-        <v>0.925463199615479</v>
+        <v>0.925463259220123</v>
       </c>
       <c r="H694" t="n">
         <v>29100</v>
@@ -20553,7 +20553,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G696" t="n">
-        <v>0.952549993991852</v>
+        <v>0.952549874782562</v>
       </c>
       <c r="H696" t="n">
         <v>12000</v>
@@ -20640,7 +20640,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G699" t="n">
-        <v>0.948035418987274</v>
+        <v>0.948035478591919</v>
       </c>
       <c r="H699" t="n">
         <v>7500</v>
@@ -20669,7 +20669,7 @@
         <v>1</v>
       </c>
       <c r="G700" t="n">
-        <v>0.902890980243683</v>
+        <v>0.902891039848328</v>
       </c>
       <c r="H700" t="n">
         <v>15000</v>
@@ -20698,7 +20698,7 @@
         <v>1</v>
       </c>
       <c r="G701" t="n">
-        <v>0.902890980243683</v>
+        <v>0.902891039848328</v>
       </c>
       <c r="H701" t="n">
         <v>14100</v>
@@ -20727,7 +20727,7 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>0.902890980243683</v>
+        <v>0.902891039848328</v>
       </c>
       <c r="H702" t="n">
         <v>5700</v>
@@ -20756,7 +20756,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>0.911919951438904</v>
+        <v>0.911919891834259</v>
       </c>
       <c r="H703" t="n">
         <v>11700</v>
@@ -20872,7 +20872,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G707" t="n">
-        <v>0.852329134941101</v>
+        <v>0.852329075336456</v>
       </c>
       <c r="H707" t="n">
         <v>10200</v>
@@ -21075,7 +21075,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G714" t="n">
-        <v>0.776486277580261</v>
+        <v>0.776486337184906</v>
       </c>
       <c r="H714" t="n">
         <v>10800</v>
@@ -21104,7 +21104,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G715" t="n">
-        <v>0.807184517383575</v>
+        <v>0.80718457698822</v>
       </c>
       <c r="H715" t="n">
         <v>1500</v>
@@ -21191,7 +21191,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G718" t="n">
-        <v>0.722312867641449</v>
+        <v>0.722312808036804</v>
       </c>
       <c r="H718" t="n">
         <v>23400</v>
@@ -21278,7 +21278,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G721" t="n">
-        <v>0.698837637901306</v>
+        <v>0.698837697505951</v>
       </c>
       <c r="H721" t="n">
         <v>20700</v>
@@ -21481,7 +21481,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G728" t="n">
-        <v>0.622994780540466</v>
+        <v>0.622994840145111</v>
       </c>
       <c r="H728" t="n">
         <v>15600</v>
@@ -21510,7 +21510,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G729" t="n">
-        <v>0.619383215904236</v>
+        <v>0.619383156299591</v>
       </c>
       <c r="H729" t="n">
         <v>9600</v>
@@ -21539,7 +21539,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G730" t="n">
-        <v>0.662721991539001</v>
+        <v>0.662722051143646</v>
       </c>
       <c r="H730" t="n">
         <v>3900</v>
@@ -21568,7 +21568,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G731" t="n">
-        <v>0.666333496570587</v>
+        <v>0.666333556175232</v>
       </c>
       <c r="H731" t="n">
         <v>12000</v>
@@ -21626,7 +21626,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G733" t="n">
-        <v>0.651887357234955</v>
+        <v>0.65188729763031</v>
       </c>
       <c r="H733" t="n">
         <v>3600</v>
@@ -21713,7 +21713,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G736" t="n">
-        <v>0.678973972797394</v>
+        <v>0.678974032402039</v>
       </c>
       <c r="H736" t="n">
         <v>4200</v>
@@ -21771,7 +21771,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G738" t="n">
-        <v>0.641052603721619</v>
+        <v>0.641052663326263</v>
       </c>
       <c r="H738" t="n">
         <v>42000</v>
@@ -21800,7 +21800,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G739" t="n">
-        <v>0.637441039085388</v>
+        <v>0.637440979480743</v>
       </c>
       <c r="H739" t="n">
         <v>24000</v>
@@ -21829,7 +21829,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G740" t="n">
-        <v>0.644664227962494</v>
+        <v>0.644664168357849</v>
       </c>
       <c r="H740" t="n">
         <v>3600</v>
@@ -21916,7 +21916,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G743" t="n">
-        <v>0.662721991539001</v>
+        <v>0.662722051143646</v>
       </c>
       <c r="H743" t="n">
         <v>73200</v>
@@ -21945,7 +21945,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G744" t="n">
-        <v>0.675362527370453</v>
+        <v>0.675362467765808</v>
       </c>
       <c r="H744" t="n">
         <v>18000</v>
@@ -22003,7 +22003,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G746" t="n">
-        <v>0.673556625843048</v>
+        <v>0.673556685447693</v>
       </c>
       <c r="H746" t="n">
         <v>53700</v>
@@ -22177,7 +22177,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G752" t="n">
-        <v>0.675362527370453</v>
+        <v>0.675362467765808</v>
       </c>
       <c r="H752" t="n">
         <v>33600</v>
@@ -22235,7 +22235,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G754" t="n">
-        <v>0.675362527370453</v>
+        <v>0.675362467765808</v>
       </c>
       <c r="H754" t="n">
         <v>27900</v>
@@ -22264,7 +22264,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G755" t="n">
-        <v>0.698837637901306</v>
+        <v>0.698837697505951</v>
       </c>
       <c r="H755" t="n">
         <v>134100</v>
@@ -22380,7 +22380,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G759" t="n">
-        <v>0.673556625843048</v>
+        <v>0.673556685447693</v>
       </c>
       <c r="H759" t="n">
         <v>17700</v>
@@ -22438,7 +22438,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G761" t="n">
-        <v>0.673556625843048</v>
+        <v>0.673556685447693</v>
       </c>
       <c r="H761" t="n">
         <v>8700</v>
@@ -22583,7 +22583,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G766" t="n">
-        <v>0.807184517383575</v>
+        <v>0.80718457698822</v>
       </c>
       <c r="H766" t="n">
         <v>120300</v>
@@ -22786,7 +22786,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G773" t="n">
-        <v>0.776486277580261</v>
+        <v>0.776486337184906</v>
       </c>
       <c r="H773" t="n">
         <v>17700</v>
@@ -22815,7 +22815,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G774" t="n">
-        <v>0.76745742559433</v>
+        <v>0.767457365989685</v>
       </c>
       <c r="H774" t="n">
         <v>50700</v>
@@ -22844,7 +22844,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G775" t="n">
-        <v>0.776486277580261</v>
+        <v>0.776486337184906</v>
       </c>
       <c r="H775" t="n">
         <v>10800</v>
@@ -22989,7 +22989,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G780" t="n">
-        <v>0.808990359306335</v>
+        <v>0.80899041891098</v>
       </c>
       <c r="H780" t="n">
         <v>34200</v>
@@ -23105,7 +23105,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G784" t="n">
-        <v>0.808990359306335</v>
+        <v>0.80899041891098</v>
       </c>
       <c r="H784" t="n">
         <v>44700</v>
@@ -23221,7 +23221,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G788" t="n">
-        <v>0.774680495262146</v>
+        <v>0.774680435657501</v>
       </c>
       <c r="H788" t="n">
         <v>112500</v>
@@ -23250,7 +23250,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G789" t="n">
-        <v>0.76745742559433</v>
+        <v>0.767457365989685</v>
       </c>
       <c r="H789" t="n">
         <v>72000</v>
@@ -23395,7 +23395,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G794" t="n">
-        <v>0.76745742559433</v>
+        <v>0.767457365989685</v>
       </c>
       <c r="H794" t="n">
         <v>23100</v>
@@ -23424,7 +23424,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>0.7692631483078</v>
+        <v>0.769263088703156</v>
       </c>
       <c r="H795" t="n">
         <v>9900</v>
@@ -23453,7 +23453,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G796" t="n">
-        <v>0.789126813411713</v>
+        <v>0.789126753807068</v>
       </c>
       <c r="H796" t="n">
         <v>17400</v>
@@ -23540,7 +23540,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G799" t="n">
-        <v>0.819825053215027</v>
+        <v>0.819824993610382</v>
       </c>
       <c r="H799" t="n">
         <v>312600</v>
@@ -23569,7 +23569,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G800" t="n">
-        <v>0.823436617851257</v>
+        <v>0.823436558246613</v>
       </c>
       <c r="H800" t="n">
         <v>87300</v>
@@ -23656,7 +23656,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G803" t="n">
-        <v>0.848717510700226</v>
+        <v>0.848717570304871</v>
       </c>
       <c r="H803" t="n">
         <v>618600</v>
@@ -23685,7 +23685,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G804" t="n">
-        <v>0.857746481895447</v>
+        <v>0.857746422290802</v>
       </c>
       <c r="H804" t="n">
         <v>87300</v>
@@ -23714,7 +23714,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G805" t="n">
-        <v>0.859552323818207</v>
+        <v>0.859552204608917</v>
       </c>
       <c r="H805" t="n">
         <v>41700</v>
@@ -23743,7 +23743,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G806" t="n">
-        <v>0.948035418987274</v>
+        <v>0.948035478591919</v>
       </c>
       <c r="H806" t="n">
         <v>362700</v>
@@ -23772,7 +23772,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>0.893862068653107</v>
+        <v>0.893862128257751</v>
       </c>
       <c r="H807" t="n">
         <v>214500</v>
@@ -23801,7 +23801,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G808" t="n">
-        <v>0.890250563621521</v>
+        <v>0.890250504016876</v>
       </c>
       <c r="H808" t="n">
         <v>21600</v>
@@ -23830,7 +23830,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G809" t="n">
-        <v>0.886638939380646</v>
+        <v>0.886638998985291</v>
       </c>
       <c r="H809" t="n">
         <v>36300</v>
@@ -23888,7 +23888,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G811" t="n">
-        <v>0.857746481895447</v>
+        <v>0.857746422290802</v>
       </c>
       <c r="H811" t="n">
         <v>22500</v>
@@ -23917,7 +23917,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G812" t="n">
-        <v>0.873998463153839</v>
+        <v>0.873998522758484</v>
       </c>
       <c r="H812" t="n">
         <v>37200</v>
@@ -23946,7 +23946,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G813" t="n">
-        <v>0.886638939380646</v>
+        <v>0.886638998985291</v>
       </c>
       <c r="H813" t="n">
         <v>24300</v>
@@ -23975,7 +23975,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G814" t="n">
-        <v>0.848717510700226</v>
+        <v>0.848717570304871</v>
       </c>
       <c r="H814" t="n">
         <v>37800</v>
@@ -24004,7 +24004,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G815" t="n">
-        <v>0.859552323818207</v>
+        <v>0.859552204608917</v>
       </c>
       <c r="H815" t="n">
         <v>4800</v>
@@ -24033,7 +24033,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G816" t="n">
-        <v>0.848717510700226</v>
+        <v>0.848717570304871</v>
       </c>
       <c r="H816" t="n">
         <v>22500</v>
@@ -24062,7 +24062,7 @@
         <v>1</v>
       </c>
       <c r="G817" t="n">
-        <v>0.902890980243683</v>
+        <v>0.902891039848328</v>
       </c>
       <c r="H817" t="n">
         <v>158700</v>
@@ -24149,7 +24149,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G820" t="n">
-        <v>0.925463199615479</v>
+        <v>0.925463259220123</v>
       </c>
       <c r="H820" t="n">
         <v>38100</v>
@@ -24178,7 +24178,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G821" t="n">
-        <v>0.948035418987274</v>
+        <v>0.948035478591919</v>
       </c>
       <c r="H821" t="n">
         <v>63900</v>
@@ -24265,7 +24265,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G824" t="n">
-        <v>0.911919951438904</v>
+        <v>0.911919891834259</v>
       </c>
       <c r="H824" t="n">
         <v>29700</v>
@@ -24352,7 +24352,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G827" t="n">
-        <v>0.883027374744415</v>
+        <v>0.88302743434906</v>
       </c>
       <c r="H827" t="n">
         <v>58800</v>
@@ -24381,7 +24381,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G828" t="n">
-        <v>0.872192680835724</v>
+        <v>0.872192740440369</v>
       </c>
       <c r="H828" t="n">
         <v>37500</v>
@@ -24439,7 +24439,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G830" t="n">
-        <v>0.883027374744415</v>
+        <v>0.88302743434906</v>
       </c>
       <c r="H830" t="n">
         <v>2100</v>
@@ -24497,7 +24497,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G832" t="n">
-        <v>0.893862068653107</v>
+        <v>0.893862128257751</v>
       </c>
       <c r="H832" t="n">
         <v>12000</v>
@@ -24526,7 +24526,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G833" t="n">
-        <v>0.883027374744415</v>
+        <v>0.88302743434906</v>
       </c>
       <c r="H833" t="n">
         <v>8700</v>
@@ -24555,7 +24555,7 @@
         <v>1</v>
       </c>
       <c r="G834" t="n">
-        <v>0.902890980243683</v>
+        <v>0.902891039848328</v>
       </c>
       <c r="H834" t="n">
         <v>11400</v>
@@ -24613,7 +24613,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G836" t="n">
-        <v>0.925463199615479</v>
+        <v>0.925463259220123</v>
       </c>
       <c r="H836" t="n">
         <v>18000</v>
@@ -24671,7 +24671,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G838" t="n">
-        <v>0.907405436038971</v>
+        <v>0.907405495643616</v>
       </c>
       <c r="H838" t="n">
         <v>3900</v>
@@ -24700,7 +24700,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G839" t="n">
-        <v>0.911919951438904</v>
+        <v>0.911919891834259</v>
       </c>
       <c r="H839" t="n">
         <v>300</v>
@@ -24729,7 +24729,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G840" t="n">
-        <v>0.907405436038971</v>
+        <v>0.907405495643616</v>
       </c>
       <c r="H840" t="n">
         <v>900</v>
@@ -24758,7 +24758,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G841" t="n">
-        <v>0.901085257530212</v>
+        <v>0.901085317134857</v>
       </c>
       <c r="H841" t="n">
         <v>45900</v>
@@ -24787,7 +24787,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G842" t="n">
-        <v>0.890250563621521</v>
+        <v>0.890250504016876</v>
       </c>
       <c r="H842" t="n">
         <v>21000</v>
@@ -24990,7 +24990,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G849" t="n">
-        <v>1.02929580211639</v>
+        <v>1.0292956829071</v>
       </c>
       <c r="H849" t="n">
         <v>90600</v>
@@ -25135,7 +25135,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G854" t="n">
-        <v>1.02929580211639</v>
+        <v>1.0292956829071</v>
       </c>
       <c r="H854" t="n">
         <v>5400</v>
@@ -25222,7 +25222,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G857" t="n">
-        <v>1.10152697563171</v>
+        <v>1.101527094841</v>
       </c>
       <c r="H857" t="n">
         <v>135300</v>
@@ -25309,7 +25309,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G860" t="n">
-        <v>1.09249818325043</v>
+        <v>1.09249806404114</v>
       </c>
       <c r="H860" t="n">
         <v>18000</v>
@@ -25396,7 +25396,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G863" t="n">
-        <v>1.06089687347412</v>
+        <v>1.06089699268341</v>
       </c>
       <c r="H863" t="n">
         <v>3900</v>
@@ -25454,7 +25454,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G865" t="n">
-        <v>1.09701251983643</v>
+        <v>1.09701263904572</v>
       </c>
       <c r="H865" t="n">
         <v>21600</v>
@@ -25483,7 +25483,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G866" t="n">
-        <v>1.07895469665527</v>
+        <v>1.07895481586456</v>
       </c>
       <c r="H866" t="n">
         <v>8100</v>
@@ -25512,7 +25512,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G867" t="n">
-        <v>1.08346927165985</v>
+        <v>1.08346915245056</v>
       </c>
       <c r="H867" t="n">
         <v>25800</v>
@@ -25570,7 +25570,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>1.09249818325043</v>
+        <v>1.09249806404114</v>
       </c>
       <c r="H869" t="n">
         <v>38100</v>
@@ -25628,7 +25628,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G871" t="n">
-        <v>1.10152697563171</v>
+        <v>1.101527094841</v>
       </c>
       <c r="H871" t="n">
         <v>7500</v>
@@ -25657,7 +25657,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G872" t="n">
-        <v>1.14215707778931</v>
+        <v>1.1421571969986</v>
       </c>
       <c r="H872" t="n">
         <v>46800</v>
@@ -25715,7 +25715,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G874" t="n">
-        <v>1.15570056438446</v>
+        <v>1.15570044517517</v>
       </c>
       <c r="H874" t="n">
         <v>54300</v>
@@ -25802,7 +25802,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G877" t="n">
-        <v>1.19181609153748</v>
+        <v>1.19181621074677</v>
       </c>
       <c r="H877" t="n">
         <v>32400</v>
@@ -25831,7 +25831,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>1.20535957813263</v>
+        <v>1.20535945892334</v>
       </c>
       <c r="H878" t="n">
         <v>25200</v>
@@ -25889,7 +25889,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G880" t="n">
-        <v>1.31370651721954</v>
+        <v>1.31370639801025</v>
       </c>
       <c r="H880" t="n">
         <v>138600</v>
@@ -25918,7 +25918,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G881" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H881" t="n">
         <v>324000</v>
@@ -25947,7 +25947,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G882" t="n">
-        <v>1.24598956108093</v>
+        <v>1.24598968029022</v>
       </c>
       <c r="H882" t="n">
         <v>376800</v>
@@ -25976,7 +25976,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G883" t="n">
-        <v>1.25050413608551</v>
+        <v>1.25050401687622</v>
       </c>
       <c r="H883" t="n">
         <v>192900</v>
@@ -26005,7 +26005,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G884" t="n">
-        <v>1.25501835346222</v>
+        <v>1.2550185918808</v>
       </c>
       <c r="H884" t="n">
         <v>78600</v>
@@ -26063,7 +26063,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G886" t="n">
-        <v>1.20535957813263</v>
+        <v>1.20535945892334</v>
       </c>
       <c r="H886" t="n">
         <v>24000</v>
@@ -26498,7 +26498,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G901" t="n">
-        <v>1.19181609153748</v>
+        <v>1.19181621074677</v>
       </c>
       <c r="H901" t="n">
         <v>68700</v>
@@ -26527,7 +26527,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G902" t="n">
-        <v>1.19633066654205</v>
+        <v>1.19633054733276</v>
       </c>
       <c r="H902" t="n">
         <v>20400</v>
@@ -26556,7 +26556,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G903" t="n">
-        <v>1.20084512233734</v>
+        <v>1.20084500312805</v>
       </c>
       <c r="H903" t="n">
         <v>3600</v>
@@ -26672,7 +26672,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G907" t="n">
-        <v>1.19181609153748</v>
+        <v>1.19181621074677</v>
       </c>
       <c r="H907" t="n">
         <v>4500</v>
@@ -26701,7 +26701,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G908" t="n">
-        <v>1.14215707778931</v>
+        <v>1.1421571969986</v>
       </c>
       <c r="H908" t="n">
         <v>3600</v>
@@ -26788,7 +26788,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G911" t="n">
-        <v>1.10152697563171</v>
+        <v>1.101527094841</v>
       </c>
       <c r="H911" t="n">
         <v>2100</v>
@@ -26817,7 +26817,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G912" t="n">
-        <v>1.10152697563171</v>
+        <v>1.101527094841</v>
       </c>
       <c r="H912" t="n">
         <v>1200</v>
@@ -26904,7 +26904,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G915" t="n">
-        <v>1.09249818325043</v>
+        <v>1.09249806404114</v>
       </c>
       <c r="H915" t="n">
         <v>13500</v>
@@ -26933,7 +26933,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G916" t="n">
-        <v>1.07895469665527</v>
+        <v>1.07895481586456</v>
       </c>
       <c r="H916" t="n">
         <v>26100</v>
@@ -26962,7 +26962,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G917" t="n">
-        <v>1.09249818325043</v>
+        <v>1.09249806404114</v>
       </c>
       <c r="H917" t="n">
         <v>3300</v>
@@ -26991,7 +26991,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G918" t="n">
-        <v>1.09249818325043</v>
+        <v>1.09249806404114</v>
       </c>
       <c r="H918" t="n">
         <v>0</v>
@@ -27049,7 +27049,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G920" t="n">
-        <v>1.16021490097046</v>
+        <v>1.16021478176117</v>
       </c>
       <c r="H920" t="n">
         <v>3900</v>
@@ -27078,7 +27078,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G921" t="n">
-        <v>1.16021490097046</v>
+        <v>1.16021478176117</v>
       </c>
       <c r="H921" t="n">
         <v>3000</v>
@@ -27136,7 +27136,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G923" t="n">
-        <v>1.14215707778931</v>
+        <v>1.1421571969986</v>
       </c>
       <c r="H923" t="n">
         <v>4200</v>
@@ -27194,7 +27194,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G925" t="n">
-        <v>1.14215707778931</v>
+        <v>1.1421571969986</v>
       </c>
       <c r="H925" t="n">
         <v>1200</v>
@@ -27339,7 +27339,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G930" t="n">
-        <v>1.24598956108093</v>
+        <v>1.24598968029022</v>
       </c>
       <c r="H930" t="n">
         <v>8400</v>
@@ -27368,7 +27368,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G931" t="n">
-        <v>1.25501835346222</v>
+        <v>1.2550185918808</v>
       </c>
       <c r="H931" t="n">
         <v>17400</v>
@@ -27397,7 +27397,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G932" t="n">
-        <v>1.25501835346222</v>
+        <v>1.2550185918808</v>
       </c>
       <c r="H932" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G935" t="n">
-        <v>1.67937731742859</v>
+        <v>1.6793771982193</v>
       </c>
       <c r="H935" t="n">
         <v>272400</v>
@@ -27542,7 +27542,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G937" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H937" t="n">
         <v>201600</v>
@@ -27571,7 +27571,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G938" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H938" t="n">
         <v>60000</v>
@@ -27600,7 +27600,7 @@
         <v>1.75</v>
       </c>
       <c r="G939" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H939" t="n">
         <v>30600</v>
@@ -27658,7 +27658,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G941" t="n">
-        <v>1.64777624607086</v>
+        <v>1.64777612686157</v>
       </c>
       <c r="H941" t="n">
         <v>159900</v>
@@ -27716,7 +27716,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H943" t="n">
         <v>35700</v>
@@ -27745,7 +27745,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G944" t="n">
-        <v>1.56200134754181</v>
+        <v>1.5620014667511</v>
       </c>
       <c r="H944" t="n">
         <v>12900</v>
@@ -27803,7 +27803,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G946" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H946" t="n">
         <v>20700</v>
@@ -28122,7 +28122,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G957" t="n">
-        <v>1.39948093891144</v>
+        <v>1.39948105812073</v>
       </c>
       <c r="H957" t="n">
         <v>27000</v>
@@ -28151,7 +28151,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G958" t="n">
-        <v>1.39948093891144</v>
+        <v>1.39948105812073</v>
       </c>
       <c r="H958" t="n">
         <v>19800</v>
@@ -28180,7 +28180,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G959" t="n">
-        <v>1.53942930698395</v>
+        <v>1.53942918777466</v>
       </c>
       <c r="H959" t="n">
         <v>32700</v>
@@ -28354,7 +28354,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G965" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H965" t="n">
         <v>12900</v>
@@ -28412,7 +28412,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G967" t="n">
-        <v>1.35885095596313</v>
+        <v>1.35885107517242</v>
       </c>
       <c r="H967" t="n">
         <v>54900</v>
@@ -28441,7 +28441,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G968" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H968" t="n">
         <v>28500</v>
@@ -28470,7 +28470,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G969" t="n">
-        <v>1.39948093891144</v>
+        <v>1.39948105812073</v>
       </c>
       <c r="H969" t="n">
         <v>8400</v>
@@ -28673,7 +28673,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G976" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H976" t="n">
         <v>27600</v>
@@ -29021,7 +29021,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G988" t="n">
-        <v>1.53491485118866</v>
+        <v>1.53491473197937</v>
       </c>
       <c r="H988" t="n">
         <v>41100</v>
@@ -29137,7 +29137,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G992" t="n">
-        <v>1.53942930698395</v>
+        <v>1.53942918777466</v>
       </c>
       <c r="H992" t="n">
         <v>5400</v>
@@ -29195,7 +29195,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G994" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H994" t="n">
         <v>6600</v>
@@ -29224,7 +29224,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H995" t="n">
         <v>3300</v>
@@ -29253,7 +29253,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G996" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H996" t="n">
         <v>28800</v>
@@ -29282,7 +29282,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G997" t="n">
-        <v>1.56200134754181</v>
+        <v>1.5620014667511</v>
       </c>
       <c r="H997" t="n">
         <v>21000</v>
@@ -29340,7 +29340,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G999" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H999" t="n">
         <v>10500</v>
@@ -29369,7 +29369,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H1000" t="n">
         <v>19800</v>
@@ -29398,7 +29398,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H1001" t="n">
         <v>1800</v>
@@ -29427,7 +29427,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H1002" t="n">
         <v>6600</v>
@@ -29630,7 +29630,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H1009" t="n">
         <v>1200</v>
@@ -29688,7 +29688,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1011" t="n">
         <v>900</v>
@@ -29717,7 +29717,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.43108212947845</v>
+        <v>1.43108236789703</v>
       </c>
       <c r="H1012" t="n">
         <v>37800</v>
@@ -29891,7 +29891,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.30919206142426</v>
+        <v>1.30919194221497</v>
       </c>
       <c r="H1018" t="n">
         <v>7200</v>
@@ -29949,7 +29949,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.32273530960083</v>
+        <v>1.32273542881012</v>
       </c>
       <c r="H1020" t="n">
         <v>10500</v>
@@ -29978,7 +29978,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.30919206142426</v>
+        <v>1.30919194221497</v>
       </c>
       <c r="H1021" t="n">
         <v>6900</v>
@@ -30007,7 +30007,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.26856195926666</v>
+        <v>1.26856184005737</v>
       </c>
       <c r="H1022" t="n">
         <v>40200</v>
@@ -30065,7 +30065,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.28210520744324</v>
+        <v>1.28210532665253</v>
       </c>
       <c r="H1024" t="n">
         <v>8100</v>
@@ -30094,7 +30094,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.28210520744324</v>
+        <v>1.28210532665253</v>
       </c>
       <c r="H1025" t="n">
         <v>7800</v>
@@ -30123,7 +30123,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.27759075164795</v>
+        <v>1.27759063243866</v>
       </c>
       <c r="H1026" t="n">
         <v>12600</v>
@@ -30210,7 +30210,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1029" t="n">
         <v>8700</v>
@@ -30239,7 +30239,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.39948093891144</v>
+        <v>1.39948105812073</v>
       </c>
       <c r="H1030" t="n">
         <v>9600</v>
@@ -30297,7 +30297,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H1032" t="n">
         <v>26400</v>
@@ -30326,7 +30326,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.45816898345947</v>
+        <v>1.45816886425018</v>
       </c>
       <c r="H1033" t="n">
         <v>9300</v>
@@ -30355,7 +30355,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.45816898345947</v>
+        <v>1.45816886425018</v>
       </c>
       <c r="H1034" t="n">
         <v>24000</v>
@@ -30384,7 +30384,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H1035" t="n">
         <v>9600</v>
@@ -30413,7 +30413,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1036" t="n">
         <v>27900</v>
@@ -30442,7 +30442,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1037" t="n">
         <v>2100</v>
@@ -30587,7 +30587,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H1042" t="n">
         <v>9900</v>
@@ -30616,7 +30616,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1043" t="n">
         <v>4800</v>
@@ -30645,7 +30645,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H1044" t="n">
         <v>7500</v>
@@ -31022,7 +31022,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.39948093891144</v>
+        <v>1.39948105812073</v>
       </c>
       <c r="H1057" t="n">
         <v>42300</v>
@@ -31051,7 +31051,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.39948093891144</v>
+        <v>1.39948105812073</v>
       </c>
       <c r="H1058" t="n">
         <v>600</v>
@@ -31109,7 +31109,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1060" t="n">
         <v>5700</v>
@@ -31138,7 +31138,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.39948093891144</v>
+        <v>1.39948105812073</v>
       </c>
       <c r="H1061" t="n">
         <v>3000</v>
@@ -31167,7 +31167,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H1062" t="n">
         <v>7800</v>
@@ -31312,7 +31312,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.28210520744324</v>
+        <v>1.28210532665253</v>
       </c>
       <c r="H1067" t="n">
         <v>4200</v>
@@ -31515,7 +31515,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.18730175495148</v>
+        <v>1.18730163574219</v>
       </c>
       <c r="H1074" t="n">
         <v>1800</v>
@@ -31631,7 +31631,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.38593757152557</v>
+        <v>1.38593769073486</v>
       </c>
       <c r="H1078" t="n">
         <v>40200</v>
@@ -31718,7 +31718,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1081" t="n">
         <v>22200</v>
@@ -31805,7 +31805,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1084" t="n">
         <v>15300</v>
@@ -31834,7 +31834,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1085" t="n">
         <v>9300</v>
@@ -31892,7 +31892,7 @@
         <v>1.75</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H1087" t="n">
         <v>179400</v>
@@ -31950,7 +31950,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.53942930698395</v>
+        <v>1.53942918777466</v>
       </c>
       <c r="H1089" t="n">
         <v>2400</v>
@@ -32008,7 +32008,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H1091" t="n">
         <v>9000</v>
@@ -32066,7 +32066,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1093" t="n">
         <v>3600</v>
@@ -32095,7 +32095,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1094" t="n">
         <v>21000</v>
@@ -32124,7 +32124,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1095" t="n">
         <v>3900</v>
@@ -32153,7 +32153,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1096" t="n">
         <v>12000</v>
@@ -32356,7 +32356,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1103" t="n">
         <v>9300</v>
@@ -32443,7 +32443,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1106" t="n">
         <v>8700</v>
@@ -32472,7 +32472,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.45816898345947</v>
+        <v>1.45816886425018</v>
       </c>
       <c r="H1107" t="n">
         <v>1200</v>
@@ -32530,7 +32530,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1109" t="n">
         <v>3300</v>
@@ -32588,7 +32588,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.38593757152557</v>
+        <v>1.38593769073486</v>
       </c>
       <c r="H1111" t="n">
         <v>56400</v>
@@ -32617,7 +32617,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.35885095596313</v>
+        <v>1.35885107517242</v>
       </c>
       <c r="H1112" t="n">
         <v>9600</v>
@@ -32646,7 +32646,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.38593757152557</v>
+        <v>1.38593769073486</v>
       </c>
       <c r="H1113" t="n">
         <v>5700</v>
@@ -32675,7 +32675,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1114" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1114" t="n">
         <v>11100</v>
@@ -32733,7 +32733,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1116" t="n">
         <v>300</v>
@@ -32791,7 +32791,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1118" t="n">
         <v>1200</v>
@@ -32820,7 +32820,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1119" t="n">
         <v>0</v>
@@ -32936,7 +32936,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.39948093891144</v>
+        <v>1.39948105812073</v>
       </c>
       <c r="H1123" t="n">
         <v>8100</v>
@@ -33052,7 +33052,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.30016314983368</v>
+        <v>1.30016303062439</v>
       </c>
       <c r="H1127" t="n">
         <v>50400</v>
@@ -33168,7 +33168,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1131" t="n">
         <v>47700</v>
@@ -33255,7 +33255,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H1134" t="n">
         <v>5700</v>
@@ -33284,7 +33284,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H1135" t="n">
         <v>0</v>
@@ -33371,7 +33371,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1138" t="n">
         <v>9900</v>
@@ -33400,7 +33400,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.45816898345947</v>
+        <v>1.45816886425018</v>
       </c>
       <c r="H1139" t="n">
         <v>4200</v>
@@ -33458,7 +33458,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1141" t="n">
         <v>5400</v>
@@ -33719,7 +33719,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H1150" t="n">
         <v>36900</v>
@@ -33835,7 +33835,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H1154" t="n">
         <v>2700</v>
@@ -33864,7 +33864,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H1155" t="n">
         <v>15900</v>
@@ -33893,7 +33893,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H1156" t="n">
         <v>4800</v>
@@ -33922,7 +33922,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1157" t="n">
         <v>14100</v>
@@ -34038,7 +34038,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1161" t="n">
         <v>18900</v>
@@ -34067,7 +34067,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1162" t="n">
         <v>600</v>
@@ -34502,7 +34502,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H1177" t="n">
         <v>9900</v>
@@ -34531,7 +34531,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H1178" t="n">
         <v>0</v>
@@ -34647,7 +34647,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.56200134754181</v>
+        <v>1.5620014667511</v>
       </c>
       <c r="H1182" t="n">
         <v>26100</v>
@@ -34763,7 +34763,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1186" t="n">
         <v>38400</v>
@@ -35024,7 +35024,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1195" t="n">
         <v>6600</v>
@@ -35053,7 +35053,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1196" t="n">
         <v>0</v>
@@ -35082,7 +35082,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1197" t="n">
         <v>600</v>
@@ -35111,7 +35111,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1198" t="n">
         <v>11400</v>
@@ -35140,7 +35140,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1199" t="n">
         <v>0</v>
@@ -35459,7 +35459,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1210" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1210" t="n">
         <v>300</v>
@@ -35488,7 +35488,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.45816898345947</v>
+        <v>1.45816886425018</v>
       </c>
       <c r="H1211" t="n">
         <v>36000</v>
@@ -35575,7 +35575,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.45816898345947</v>
+        <v>1.45816886425018</v>
       </c>
       <c r="H1214" t="n">
         <v>13200</v>
@@ -35604,7 +35604,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.45816898345947</v>
+        <v>1.45816886425018</v>
       </c>
       <c r="H1215" t="n">
         <v>0</v>
@@ -35691,7 +35691,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.45816898345947</v>
+        <v>1.45816886425018</v>
       </c>
       <c r="H1218" t="n">
         <v>5400</v>
@@ -35749,7 +35749,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1220" t="n">
         <v>4800</v>
@@ -35865,7 +35865,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1224" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1224" t="n">
         <v>24300</v>
@@ -35894,7 +35894,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1225" t="n">
         <v>2700</v>
@@ -35923,7 +35923,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1226" t="n">
         <v>1500</v>
@@ -35952,7 +35952,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1227" t="n">
         <v>0</v>
@@ -36010,7 +36010,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1229" t="n">
         <v>5700</v>
@@ -36039,7 +36039,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1230" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1230" t="n">
         <v>0</v>
@@ -36068,7 +36068,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1231" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1231" t="n">
         <v>0</v>
@@ -36358,7 +36358,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1241" t="n">
         <v>2700</v>
@@ -36735,7 +36735,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.53491485118866</v>
+        <v>1.53491473197937</v>
       </c>
       <c r="H1254" t="n">
         <v>600</v>
@@ -36764,7 +36764,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.53491485118866</v>
+        <v>1.53491473197937</v>
       </c>
       <c r="H1255" t="n">
         <v>0</v>
@@ -36793,7 +36793,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.53491485118866</v>
+        <v>1.53491473197937</v>
       </c>
       <c r="H1256" t="n">
         <v>0</v>
@@ -36822,7 +36822,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.53491485118866</v>
+        <v>1.53491473197937</v>
       </c>
       <c r="H1257" t="n">
         <v>0</v>
@@ -36967,7 +36967,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1262" t="n">
         <v>600</v>
@@ -36996,7 +36996,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1263" t="n">
         <v>0</v>
@@ -37344,7 +37344,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1275" t="n">
         <v>4200</v>
@@ -37373,7 +37373,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1276" t="n">
         <v>8100</v>
@@ -37402,7 +37402,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.43108212947845</v>
+        <v>1.43108236789703</v>
       </c>
       <c r="H1277" t="n">
         <v>300</v>
@@ -37431,7 +37431,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H1278" t="n">
         <v>6300</v>
@@ -37460,7 +37460,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.45816898345947</v>
+        <v>1.45816886425018</v>
       </c>
       <c r="H1279" t="n">
         <v>1500</v>
@@ -37489,7 +37489,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.45816898345947</v>
+        <v>1.45816886425018</v>
       </c>
       <c r="H1280" t="n">
         <v>0</v>
@@ -37518,7 +37518,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H1281" t="n">
         <v>373500</v>
@@ -37547,7 +37547,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1282" t="n">
         <v>4500</v>
@@ -37576,7 +37576,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1283" t="n">
         <v>0</v>
@@ -37663,7 +37663,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.4446257352829</v>
+        <v>1.44462561607361</v>
       </c>
       <c r="H1286" t="n">
         <v>4200</v>
@@ -37779,7 +37779,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1290" t="n">
         <v>26700</v>
@@ -37924,7 +37924,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1295" t="n">
         <v>3000</v>
@@ -37953,7 +37953,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1296" t="n">
         <v>1500</v>
@@ -38011,7 +38011,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1298" t="n">
         <v>7200</v>
@@ -38069,7 +38069,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1300" t="n">
         <v>19800</v>
@@ -38098,7 +38098,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1301" t="n">
         <v>0</v>
@@ -38156,7 +38156,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1303" t="n">
         <v>1500</v>
@@ -38185,7 +38185,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1304" t="n">
         <v>7500</v>
@@ -38214,7 +38214,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.39948093891144</v>
+        <v>1.39948105812073</v>
       </c>
       <c r="H1305" t="n">
         <v>11700</v>
@@ -38272,7 +38272,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1307" t="n">
         <v>8400</v>
@@ -38359,7 +38359,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.43108212947845</v>
+        <v>1.43108236789703</v>
       </c>
       <c r="H1310" t="n">
         <v>1800</v>
@@ -38388,7 +38388,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.39948093891144</v>
+        <v>1.39948105812073</v>
       </c>
       <c r="H1311" t="n">
         <v>24300</v>
@@ -38533,7 +38533,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H1316" t="n">
         <v>55800</v>
@@ -38765,7 +38765,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1324" t="n">
         <v>13800</v>
@@ -38968,7 +38968,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H1331" t="n">
         <v>48900</v>
@@ -38997,7 +38997,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1332" t="n">
         <v>10500</v>
@@ -39026,7 +39026,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.38593757152557</v>
+        <v>1.38593769073486</v>
       </c>
       <c r="H1333" t="n">
         <v>7500</v>
@@ -39055,7 +39055,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.35885095596313</v>
+        <v>1.35885107517242</v>
       </c>
       <c r="H1334" t="n">
         <v>31200</v>
@@ -39113,7 +39113,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.39948093891144</v>
+        <v>1.39948105812073</v>
       </c>
       <c r="H1336" t="n">
         <v>16500</v>
@@ -39200,7 +39200,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H1339" t="n">
         <v>6300</v>
@@ -39809,7 +39809,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H1360" t="n">
         <v>3600</v>
@@ -39983,7 +39983,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H1366" t="n">
         <v>4500</v>
@@ -40041,7 +40041,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H1368" t="n">
         <v>300</v>
@@ -40128,7 +40128,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.36787974834442</v>
+        <v>1.36787986755371</v>
       </c>
       <c r="H1371" t="n">
         <v>8100</v>
@@ -40186,7 +40186,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1373" t="n">
         <v>41100</v>
@@ -40215,7 +40215,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1374" t="n">
         <v>17400</v>
@@ -40244,7 +40244,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1375" t="n">
         <v>1500</v>
@@ -40273,7 +40273,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1376" t="n">
         <v>16500</v>
@@ -40302,7 +40302,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1377" t="n">
         <v>12300</v>
@@ -40331,7 +40331,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1378" t="n">
         <v>9300</v>
@@ -40360,7 +40360,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1379" t="n">
         <v>10200</v>
@@ -40389,7 +40389,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.41302442550659</v>
+        <v>1.41302454471588</v>
       </c>
       <c r="H1380" t="n">
         <v>0</v>
@@ -40418,7 +40418,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.39948093891144</v>
+        <v>1.39948105812073</v>
       </c>
       <c r="H1381" t="n">
         <v>20700</v>
@@ -40476,7 +40476,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.39948093891144</v>
+        <v>1.39948105812073</v>
       </c>
       <c r="H1383" t="n">
         <v>1800</v>
@@ -40650,7 +40650,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1389" t="n">
         <v>13500</v>
@@ -40679,7 +40679,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H1390" t="n">
         <v>0</v>
@@ -40708,7 +40708,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1391" t="n">
         <v>58800</v>
@@ -40737,7 +40737,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.64777624607086</v>
+        <v>1.64777612686157</v>
       </c>
       <c r="H1392" t="n">
         <v>238200</v>
@@ -40824,7 +40824,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.61617493629456</v>
+        <v>1.61617481708527</v>
       </c>
       <c r="H1395" t="n">
         <v>23400</v>
@@ -40882,7 +40882,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.60263156890869</v>
+        <v>1.6026314496994</v>
       </c>
       <c r="H1397" t="n">
         <v>105900</v>
@@ -40940,7 +40940,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H1399" t="n">
         <v>21600</v>
@@ -41056,7 +41056,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.61617493629456</v>
+        <v>1.61617481708527</v>
       </c>
       <c r="H1403" t="n">
         <v>21600</v>
@@ -41201,7 +41201,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1408" t="n">
         <v>18000</v>
@@ -41317,7 +41317,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.53491485118866</v>
+        <v>1.53491473197937</v>
       </c>
       <c r="H1412" t="n">
         <v>7200</v>
@@ -41346,7 +41346,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1413" t="n">
-        <v>1.56200134754181</v>
+        <v>1.5620014667511</v>
       </c>
       <c r="H1413" t="n">
         <v>4800</v>
@@ -41375,7 +41375,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.57554483413696</v>
+        <v>1.57554471492767</v>
       </c>
       <c r="H1414" t="n">
         <v>6600</v>
@@ -41404,7 +41404,7 @@
         <v>1.75</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H1415" t="n">
         <v>1200</v>
@@ -41462,7 +41462,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1417" t="n">
         <v>17700</v>
@@ -41520,7 +41520,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.60263156890869</v>
+        <v>1.6026314496994</v>
       </c>
       <c r="H1419" t="n">
         <v>10500</v>
@@ -41607,7 +41607,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1422" t="n">
         <v>28500</v>
@@ -41636,7 +41636,7 @@
         <v>1.75</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H1423" t="n">
         <v>13500</v>
@@ -41665,7 +41665,7 @@
         <v>1.75</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H1424" t="n">
         <v>0</v>
@@ -41781,7 +41781,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1428" t="n">
-        <v>1.56200134754181</v>
+        <v>1.5620014667511</v>
       </c>
       <c r="H1428" t="n">
         <v>12600</v>
@@ -41810,7 +41810,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.5981171131134</v>
+        <v>1.59811699390411</v>
       </c>
       <c r="H1429" t="n">
         <v>8100</v>
@@ -41839,7 +41839,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1430" t="n">
         <v>12300</v>
@@ -41868,7 +41868,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H1431" t="n">
         <v>5100</v>
@@ -41897,7 +41897,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.57554483413696</v>
+        <v>1.57554471492767</v>
       </c>
       <c r="H1432" t="n">
         <v>12000</v>
@@ -41926,7 +41926,7 @@
         <v>1.75</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H1433" t="n">
         <v>20100</v>
@@ -41984,7 +41984,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.56200134754181</v>
+        <v>1.5620014667511</v>
       </c>
       <c r="H1435" t="n">
         <v>600</v>
@@ -42071,7 +42071,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1438" t="n">
         <v>16800</v>
@@ -42100,7 +42100,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1439" t="n">
         <v>10800</v>
@@ -42187,7 +42187,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1442" t="n">
         <v>900</v>
@@ -42274,7 +42274,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.56200134754181</v>
+        <v>1.5620014667511</v>
       </c>
       <c r="H1445" t="n">
         <v>1500</v>
@@ -42303,7 +42303,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1446" t="n">
-        <v>1.56200134754181</v>
+        <v>1.5620014667511</v>
       </c>
       <c r="H1446" t="n">
         <v>23700</v>
@@ -42332,7 +42332,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1447" t="n">
         <v>31500</v>
@@ -42361,7 +42361,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1448" t="n">
         <v>49200</v>
@@ -42390,7 +42390,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1449" t="n">
         <v>10500</v>
@@ -42419,7 +42419,7 @@
         <v>1.75</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H1450" t="n">
         <v>17100</v>
@@ -42477,7 +42477,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H1452" t="n">
         <v>6600</v>
@@ -42506,7 +42506,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H1453" t="n">
         <v>0</v>
@@ -42535,7 +42535,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1454" t="n">
         <v>3300</v>
@@ -42564,7 +42564,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1455" t="n">
         <v>300</v>
@@ -42593,7 +42593,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.53491485118866</v>
+        <v>1.53491473197937</v>
       </c>
       <c r="H1456" t="n">
         <v>3000</v>
@@ -42883,7 +42883,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H1466" t="n">
         <v>4200</v>
@@ -42912,7 +42912,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H1467" t="n">
         <v>3000</v>
@@ -43057,7 +43057,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1472" t="n">
-        <v>1.56200134754181</v>
+        <v>1.5620014667511</v>
       </c>
       <c r="H1472" t="n">
         <v>13500</v>
@@ -43086,7 +43086,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.60263156890869</v>
+        <v>1.6026314496994</v>
       </c>
       <c r="H1473" t="n">
         <v>121200</v>
@@ -43115,7 +43115,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1474" t="n">
         <v>50700</v>
@@ -43144,7 +43144,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1475" t="n">
-        <v>1.56200134754181</v>
+        <v>1.5620014667511</v>
       </c>
       <c r="H1475" t="n">
         <v>33300</v>
@@ -43173,7 +43173,7 @@
         <v>1.75</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H1476" t="n">
         <v>4500</v>
@@ -43231,7 +43231,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1478" t="n">
         <v>32700</v>
@@ -43260,7 +43260,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1479" t="n">
         <v>0</v>
@@ -43318,7 +43318,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H1481" t="n">
         <v>6300</v>
@@ -43347,7 +43347,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1482" t="n">
-        <v>1.53491485118866</v>
+        <v>1.53491473197937</v>
       </c>
       <c r="H1482" t="n">
         <v>35100</v>
@@ -43434,7 +43434,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1485" t="n">
-        <v>1.53491485118866</v>
+        <v>1.53491473197937</v>
       </c>
       <c r="H1485" t="n">
         <v>2400</v>
@@ -43463,7 +43463,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1486" t="n">
-        <v>1.53491485118866</v>
+        <v>1.53491473197937</v>
       </c>
       <c r="H1486" t="n">
         <v>3300</v>
@@ -43492,7 +43492,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.53491485118866</v>
+        <v>1.53491473197937</v>
       </c>
       <c r="H1487" t="n">
         <v>21600</v>
@@ -43608,7 +43608,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1491" t="n">
         <v>18900</v>
@@ -43637,7 +43637,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1492" t="n">
-        <v>1.48074114322662</v>
+        <v>1.48074126243591</v>
       </c>
       <c r="H1492" t="n">
         <v>6900</v>
@@ -43666,7 +43666,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1493" t="n">
-        <v>1.53491485118866</v>
+        <v>1.53491473197937</v>
       </c>
       <c r="H1493" t="n">
         <v>2100</v>
@@ -43695,7 +43695,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1494" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1494" t="n">
         <v>8100</v>
@@ -43724,7 +43724,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1495" t="n">
-        <v>1.53491485118866</v>
+        <v>1.53491473197937</v>
       </c>
       <c r="H1495" t="n">
         <v>7200</v>
@@ -43753,7 +43753,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1496" t="n">
         <v>3300</v>
@@ -43782,7 +43782,7 @@
         <v>1.75</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H1497" t="n">
         <v>22800</v>
@@ -43927,7 +43927,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1502" t="n">
-        <v>1.56200134754181</v>
+        <v>1.5620014667511</v>
       </c>
       <c r="H1502" t="n">
         <v>14400</v>
@@ -43956,7 +43956,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1503" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1503" t="n">
         <v>7500</v>
@@ -43985,7 +43985,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1504" t="n">
-        <v>1.53491485118866</v>
+        <v>1.53491473197937</v>
       </c>
       <c r="H1504" t="n">
         <v>11100</v>
@@ -44072,7 +44072,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1507" t="n">
-        <v>1.53491485118866</v>
+        <v>1.53491473197937</v>
       </c>
       <c r="H1507" t="n">
         <v>3600</v>
@@ -44217,7 +44217,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1512" t="n">
-        <v>1.56200134754181</v>
+        <v>1.5620014667511</v>
       </c>
       <c r="H1512" t="n">
         <v>300</v>
@@ -44246,7 +44246,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.57554483413696</v>
+        <v>1.57554471492767</v>
       </c>
       <c r="H1513" t="n">
         <v>1200</v>
@@ -44304,7 +44304,7 @@
         <v>1.75</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H1515" t="n">
         <v>900</v>
@@ -44391,7 +44391,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1518" t="n">
-        <v>1.57554483413696</v>
+        <v>1.57554471492767</v>
       </c>
       <c r="H1518" t="n">
         <v>5400</v>
@@ -44449,7 +44449,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1520" t="n">
-        <v>1.53491485118866</v>
+        <v>1.53491473197937</v>
       </c>
       <c r="H1520" t="n">
         <v>14100</v>
@@ -44478,7 +44478,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H1521" t="n">
         <v>11100</v>
@@ -44507,7 +44507,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H1522" t="n">
         <v>4200</v>
@@ -44536,7 +44536,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G1523" t="n">
-        <v>1.53942930698395</v>
+        <v>1.53942918777466</v>
       </c>
       <c r="H1523" t="n">
         <v>30000</v>
@@ -44565,7 +44565,7 @@
         <v>1.75</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H1524" t="n">
         <v>44400</v>
@@ -44594,7 +44594,7 @@
         <v>1.75</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H1525" t="n">
         <v>0</v>
@@ -44623,7 +44623,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1526" t="n">
         <v>1800</v>
@@ -44652,7 +44652,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1527" t="n">
         <v>2700</v>
@@ -44739,7 +44739,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1530" t="n">
         <v>5100</v>
@@ -44768,7 +44768,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1531" t="n">
         <v>0</v>
@@ -44826,7 +44826,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.65680491924286</v>
+        <v>1.65680515766144</v>
       </c>
       <c r="H1533" t="n">
         <v>82800</v>
@@ -44913,7 +44913,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.69743502140045</v>
+        <v>1.69743514060974</v>
       </c>
       <c r="H1536" t="n">
         <v>46800</v>
@@ -44971,7 +44971,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1538" t="n">
-        <v>1.65680491924286</v>
+        <v>1.65680515766144</v>
       </c>
       <c r="H1538" t="n">
         <v>7500</v>
@@ -45058,7 +45058,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1541" t="n">
-        <v>1.64777624607086</v>
+        <v>1.64777612686157</v>
       </c>
       <c r="H1541" t="n">
         <v>2700</v>
@@ -45087,7 +45087,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.67486274242401</v>
+        <v>1.6748628616333</v>
       </c>
       <c r="H1542" t="n">
         <v>12600</v>
@@ -45261,7 +45261,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1548" t="n">
         <v>4200</v>
@@ -45348,7 +45348,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.67486274242401</v>
+        <v>1.6748628616333</v>
       </c>
       <c r="H1551" t="n">
         <v>27000</v>
@@ -45377,7 +45377,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.67486274242401</v>
+        <v>1.6748628616333</v>
       </c>
       <c r="H1552" t="n">
         <v>6300</v>
@@ -45406,7 +45406,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1553" t="n">
-        <v>1.70194947719574</v>
+        <v>1.70194959640503</v>
       </c>
       <c r="H1553" t="n">
         <v>44400</v>
@@ -45493,7 +45493,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1556" t="n">
-        <v>1.67937731742859</v>
+        <v>1.6793771982193</v>
       </c>
       <c r="H1556" t="n">
         <v>3300</v>
@@ -45551,7 +45551,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1558" t="n">
-        <v>1.69743502140045</v>
+        <v>1.69743514060974</v>
       </c>
       <c r="H1558" t="n">
         <v>22200</v>
@@ -45580,7 +45580,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1559" t="n">
-        <v>1.69743502140045</v>
+        <v>1.69743514060974</v>
       </c>
       <c r="H1559" t="n">
         <v>1500</v>
@@ -45609,7 +45609,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.70194947719574</v>
+        <v>1.70194959640503</v>
       </c>
       <c r="H1560" t="n">
         <v>2400</v>
@@ -45725,7 +45725,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.67486274242401</v>
+        <v>1.6748628616333</v>
       </c>
       <c r="H1564" t="n">
         <v>8700</v>
@@ -45783,7 +45783,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1566" t="n">
-        <v>1.65680491924286</v>
+        <v>1.65680515766144</v>
       </c>
       <c r="H1566" t="n">
         <v>2700</v>
@@ -45812,7 +45812,7 @@
         <v>1.75</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H1567" t="n">
         <v>38700</v>
@@ -45957,7 +45957,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.64777624607086</v>
+        <v>1.64777612686157</v>
       </c>
       <c r="H1572" t="n">
         <v>13200</v>
@@ -46218,7 +46218,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H1581" t="n">
         <v>8400</v>
@@ -46247,7 +46247,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1582" t="n">
-        <v>1.61617493629456</v>
+        <v>1.61617481708527</v>
       </c>
       <c r="H1582" t="n">
         <v>8100</v>
@@ -46305,7 +46305,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H1584" t="n">
         <v>7200</v>
@@ -46537,7 +46537,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.61617493629456</v>
+        <v>1.61617481708527</v>
       </c>
       <c r="H1592" t="n">
         <v>1200</v>
@@ -46566,7 +46566,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.61617493629456</v>
+        <v>1.61617481708527</v>
       </c>
       <c r="H1593" t="n">
         <v>6000</v>
@@ -46624,7 +46624,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H1595" t="n">
         <v>1500</v>
@@ -46798,7 +46798,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.89607083797455</v>
+        <v>1.89607095718384</v>
       </c>
       <c r="H1601" t="n">
         <v>59400</v>
@@ -46856,7 +46856,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.12179374694824</v>
+        <v>2.12179398536682</v>
       </c>
       <c r="H1603" t="n">
         <v>147900</v>
@@ -46914,7 +46914,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.12179374694824</v>
+        <v>2.12179398536682</v>
       </c>
       <c r="H1605" t="n">
         <v>38100</v>
@@ -46943,7 +46943,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1606" t="n">
-        <v>2.05859160423279</v>
+        <v>2.05859136581421</v>
       </c>
       <c r="H1606" t="n">
         <v>98400</v>
@@ -46972,7 +46972,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1607" t="n">
-        <v>2.06762027740479</v>
+        <v>2.06762051582336</v>
       </c>
       <c r="H1607" t="n">
         <v>18600</v>
@@ -47001,7 +47001,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.06762027740479</v>
+        <v>2.06762051582336</v>
       </c>
       <c r="H1608" t="n">
         <v>29100</v>
@@ -47088,7 +47088,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1611" t="n">
-        <v>1.99538910388947</v>
+        <v>1.99538922309875</v>
       </c>
       <c r="H1611" t="n">
         <v>20700</v>
@@ -47233,7 +47233,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.01344704627991</v>
+        <v>2.01344680786133</v>
       </c>
       <c r="H1616" t="n">
         <v>28200</v>
@@ -47262,7 +47262,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.02247595787048</v>
+        <v>2.0224757194519</v>
       </c>
       <c r="H1617" t="n">
         <v>12600</v>
@@ -47291,7 +47291,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1618" t="n">
-        <v>2.02247595787048</v>
+        <v>2.0224757194519</v>
       </c>
       <c r="H1618" t="n">
         <v>73200</v>
@@ -47320,7 +47320,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.02247595787048</v>
+        <v>2.0224757194519</v>
       </c>
       <c r="H1619" t="n">
         <v>2100</v>
@@ -47349,7 +47349,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.01344704627991</v>
+        <v>2.01344680786133</v>
       </c>
       <c r="H1620" t="n">
         <v>57900</v>
@@ -47407,7 +47407,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.02247595787048</v>
+        <v>2.0224757194519</v>
       </c>
       <c r="H1622" t="n">
         <v>100200</v>
@@ -47465,7 +47465,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.01344704627991</v>
+        <v>2.01344680786133</v>
       </c>
       <c r="H1624" t="n">
         <v>25500</v>
@@ -47523,7 +47523,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.10373616218567</v>
+        <v>2.10373592376709</v>
       </c>
       <c r="H1626" t="n">
         <v>31800</v>
@@ -47552,7 +47552,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H1627" t="n">
         <v>192000</v>
@@ -65625,6 +65625,35 @@
         <v>2700</v>
       </c>
       <c r="I2250" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2251" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2251" t="n">
+        <v>4.23000001907349</v>
+      </c>
+      <c r="D2251" t="n">
+        <v>4.26999998092651</v>
+      </c>
+      <c r="E2251" t="n">
+        <v>4.19000005722046</v>
+      </c>
+      <c r="F2251" t="n">
+        <v>4.19000005722046</v>
+      </c>
+      <c r="G2251" t="n">
+        <v>4.19000005722046</v>
+      </c>
+      <c r="H2251" t="n">
+        <v>15900</v>
+      </c>
+      <c r="I2251" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H2" t="n">
         <v>326100</v>
@@ -456,7 +456,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G3" t="n">
-        <v>3.66393160820007</v>
+        <v>3.66393184661865</v>
       </c>
       <c r="H3" t="n">
         <v>35400</v>
@@ -514,7 +514,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H5" t="n">
         <v>14700</v>
@@ -630,7 +630,7 @@
         <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H9" t="n">
         <v>1200</v>
@@ -775,7 +775,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G14" t="n">
-        <v>3.64406776428223</v>
+        <v>3.64406800270081</v>
       </c>
       <c r="H14" t="n">
         <v>10200</v>
@@ -833,7 +833,7 @@
         <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H16" t="n">
         <v>600</v>
@@ -862,7 +862,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5989236831665</v>
+        <v>3.59892344474792</v>
       </c>
       <c r="H17" t="n">
         <v>81900</v>
@@ -891,7 +891,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G18" t="n">
-        <v>3.6549026966095</v>
+        <v>3.65490245819092</v>
       </c>
       <c r="H18" t="n">
         <v>28200</v>
@@ -920,7 +920,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G19" t="n">
-        <v>3.65851426124573</v>
+        <v>3.65851449966431</v>
       </c>
       <c r="H19" t="n">
         <v>19500</v>
@@ -978,7 +978,7 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H21" t="n">
         <v>2100</v>
@@ -1036,7 +1036,7 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H23" t="n">
         <v>28500</v>
@@ -1065,7 +1065,7 @@
         <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>3.56641936302185</v>
+        <v>3.56641960144043</v>
       </c>
       <c r="H25" t="n">
         <v>6600</v>
@@ -1181,7 +1181,7 @@
         <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H28" t="n">
         <v>11400</v>
@@ -1210,7 +1210,7 @@
         <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>3.61156415939331</v>
+        <v>3.61156392097473</v>
       </c>
       <c r="H29" t="n">
         <v>4800</v>
@@ -1239,7 +1239,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G30" t="n">
-        <v>3.57544851303101</v>
+        <v>3.57544827461243</v>
       </c>
       <c r="H30" t="n">
         <v>300</v>
@@ -1268,7 +1268,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>3.57544851303101</v>
+        <v>3.57544827461243</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H40" t="n">
         <v>6300</v>
@@ -1558,7 +1558,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G41" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H42" t="n">
         <v>3900</v>
@@ -1790,7 +1790,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>3.57544851303101</v>
+        <v>3.57544827461243</v>
       </c>
       <c r="H49" t="n">
         <v>1800</v>
@@ -2167,7 +2167,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H62" t="n">
         <v>1200</v>
@@ -2196,7 +2196,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>3.33166790008545</v>
+        <v>3.33166766166687</v>
       </c>
       <c r="H63" t="n">
         <v>600</v>
@@ -2225,7 +2225,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G64" t="n">
-        <v>3.44001460075378</v>
+        <v>3.44001483917236</v>
       </c>
       <c r="H64" t="n">
         <v>900</v>
@@ -2979,7 +2979,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H90" t="n">
         <v>900</v>
@@ -3008,7 +3008,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G92" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H99" t="n">
         <v>3600</v>
@@ -3269,7 +3269,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>3.3497257232666</v>
+        <v>3.34972548484802</v>
       </c>
       <c r="H100" t="n">
         <v>300</v>
@@ -3414,7 +3414,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>3.3587543964386</v>
+        <v>3.35875463485718</v>
       </c>
       <c r="H105" t="n">
         <v>900</v>
@@ -3472,7 +3472,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G107" t="n">
-        <v>3.22332072257996</v>
+        <v>3.22332096099854</v>
       </c>
       <c r="H107" t="n">
         <v>6300</v>
@@ -3559,7 +3559,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H110" t="n">
         <v>8100</v>
@@ -3588,7 +3588,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G111" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H111" t="n">
         <v>30300</v>
@@ -3617,7 +3617,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>3.2052628993988</v>
+        <v>3.20526313781738</v>
       </c>
       <c r="H112" t="n">
         <v>900</v>
@@ -3820,7 +3820,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G119" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H119" t="n">
         <v>30900</v>
@@ -3849,7 +3849,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G120" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H120" t="n">
         <v>2100</v>
@@ -3878,7 +3878,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G121" t="n">
-        <v>3.13303184509277</v>
+        <v>3.13303208351135</v>
       </c>
       <c r="H121" t="n">
         <v>30600</v>
@@ -4023,7 +4023,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H126" t="n">
         <v>1800</v>
@@ -4168,7 +4168,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>3.42195701599121</v>
+        <v>3.42195677757263</v>
       </c>
       <c r="H131" t="n">
         <v>1500</v>
@@ -4226,7 +4226,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G133" t="n">
-        <v>3.33166790008545</v>
+        <v>3.33166766166687</v>
       </c>
       <c r="H133" t="n">
         <v>300</v>
@@ -4255,7 +4255,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>3.33166790008545</v>
+        <v>3.33166766166687</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G135" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H135" t="n">
         <v>300</v>
@@ -4313,7 +4313,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G138" t="n">
-        <v>3.28652310371399</v>
+        <v>3.28652334213257</v>
       </c>
       <c r="H138" t="n">
         <v>900</v>
@@ -4690,7 +4690,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G149" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H149" t="n">
         <v>3900</v>
@@ -4719,7 +4719,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G151" t="n">
-        <v>3.29555225372314</v>
+        <v>3.29555249214172</v>
       </c>
       <c r="H151" t="n">
         <v>900</v>
@@ -5473,7 +5473,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G176" t="n">
-        <v>3.24137878417969</v>
+        <v>3.24137854576111</v>
       </c>
       <c r="H176" t="n">
         <v>2400</v>
@@ -5763,7 +5763,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G186" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H186" t="n">
         <v>60000</v>
@@ -5792,7 +5792,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>3.19623398780823</v>
+        <v>3.19623422622681</v>
       </c>
       <c r="H187" t="n">
         <v>6600</v>
@@ -5821,7 +5821,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G188" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H188" t="n">
         <v>600</v>
@@ -5850,7 +5850,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G190" t="n">
-        <v>3.21429181098938</v>
+        <v>3.21429204940796</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>3.5</v>
       </c>
       <c r="G191" t="n">
-        <v>3.16011881828308</v>
+        <v>3.16011834144592</v>
       </c>
       <c r="H191" t="n">
         <v>300</v>
@@ -5937,7 +5937,7 @@
         <v>3.5</v>
       </c>
       <c r="G192" t="n">
-        <v>3.16011881828308</v>
+        <v>3.16011834144592</v>
       </c>
       <c r="H192" t="n">
         <v>2400</v>
@@ -5995,7 +5995,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>3.19623398780823</v>
+        <v>3.19623422622681</v>
       </c>
       <c r="H194" t="n">
         <v>600</v>
@@ -6401,7 +6401,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G208" t="n">
-        <v>3.05177164077759</v>
+        <v>3.05177187919617</v>
       </c>
       <c r="H208" t="n">
         <v>6600</v>
@@ -6430,7 +6430,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H209" t="n">
         <v>13500</v>
@@ -6459,7 +6459,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G210" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G211" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G212" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G213" t="n">
-        <v>3.10594534873962</v>
+        <v>3.10594511032104</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G215" t="n">
-        <v>2.87119340896606</v>
+        <v>2.87119364738464</v>
       </c>
       <c r="H215" t="n">
         <v>2100</v>
@@ -6633,7 +6633,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G216" t="n">
-        <v>2.87119340896606</v>
+        <v>2.87119364738464</v>
       </c>
       <c r="H216" t="n">
         <v>21000</v>
@@ -6662,7 +6662,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G217" t="n">
-        <v>2.87119340896606</v>
+        <v>2.87119364738464</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G220" t="n">
-        <v>2.66352868080139</v>
+        <v>2.66352844238281</v>
       </c>
       <c r="H220" t="n">
         <v>2100</v>
@@ -6778,7 +6778,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G221" t="n">
-        <v>2.60032606124878</v>
+        <v>2.60032629966736</v>
       </c>
       <c r="H221" t="n">
         <v>900</v>
@@ -6807,7 +6807,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H222" t="n">
         <v>3900</v>
@@ -6836,7 +6836,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G223" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G225" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H225" t="n">
         <v>1200</v>
@@ -6923,7 +6923,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G226" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H228" t="n">
         <v>2700</v>
@@ -7010,7 +7010,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G230" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G231" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G232" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>2.61838388442993</v>
+        <v>2.61838412284851</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G236" t="n">
-        <v>2.5100371837616</v>
+        <v>2.51003694534302</v>
       </c>
       <c r="H236" t="n">
         <v>2700</v>
@@ -7242,7 +7242,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G237" t="n">
-        <v>2.5100371837616</v>
+        <v>2.51003694534302</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G249" t="n">
-        <v>2.5100371837616</v>
+        <v>2.51003694534302</v>
       </c>
       <c r="H249" t="n">
         <v>2100</v>
@@ -7793,7 +7793,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>2.32945871353149</v>
+        <v>2.32945895195007</v>
       </c>
       <c r="H256" t="n">
         <v>1500</v>
@@ -7822,7 +7822,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>2.32945871353149</v>
+        <v>2.32945895195007</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>2.5</v>
       </c>
       <c r="G259" t="n">
-        <v>2.25722742080688</v>
+        <v>2.25722765922546</v>
       </c>
       <c r="H259" t="n">
         <v>9900</v>
@@ -7938,7 +7938,7 @@
         <v>2.5</v>
       </c>
       <c r="G261" t="n">
-        <v>2.25722742080688</v>
+        <v>2.25722765922546</v>
       </c>
       <c r="H261" t="n">
         <v>2400</v>
@@ -7967,7 +7967,7 @@
         <v>2.5</v>
       </c>
       <c r="G262" t="n">
-        <v>2.25722742080688</v>
+        <v>2.25722765922546</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G263" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H263" t="n">
         <v>2100</v>
@@ -8025,7 +8025,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G264" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G265" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.32042956352234</v>
+        <v>2.32042980194092</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G278" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H278" t="n">
         <v>3600</v>
@@ -8460,7 +8460,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H279" t="n">
         <v>4800</v>
@@ -8547,7 +8547,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G282" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H282" t="n">
         <v>900</v>
@@ -8576,7 +8576,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G283" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H283" t="n">
         <v>1500</v>
@@ -8605,7 +8605,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G284" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G285" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H285" t="n">
         <v>2100</v>
@@ -8663,7 +8663,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G286" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G287" t="n">
-        <v>2.21208310127258</v>
+        <v>2.212082862854</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>2.18499612808228</v>
+        <v>2.18499636650085</v>
       </c>
       <c r="H288" t="n">
         <v>1200</v>
@@ -8750,7 +8750,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G289" t="n">
-        <v>2.18499612808228</v>
+        <v>2.18499636650085</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>2.12179398536682</v>
+        <v>2.12179350852966</v>
       </c>
       <c r="H291" t="n">
         <v>2400</v>
@@ -8953,7 +8953,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G296" t="n">
-        <v>2.0224757194519</v>
+        <v>2.02247595787048</v>
       </c>
       <c r="H296" t="n">
         <v>1800</v>
@@ -9040,7 +9040,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G299" t="n">
-        <v>1.9412157535553</v>
+        <v>1.94121587276459</v>
       </c>
       <c r="H299" t="n">
         <v>1200</v>
@@ -9098,7 +9098,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G301" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H301" t="n">
         <v>35700</v>
@@ -9127,7 +9127,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>1.97733128070831</v>
+        <v>1.97733116149902</v>
       </c>
       <c r="H302" t="n">
         <v>4200</v>
@@ -9156,7 +9156,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G303" t="n">
-        <v>1.97733128070831</v>
+        <v>1.97733116149902</v>
       </c>
       <c r="H303" t="n">
         <v>300</v>
@@ -9185,7 +9185,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G304" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H304" t="n">
         <v>600</v>
@@ -9243,7 +9243,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G306" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H306" t="n">
         <v>3600</v>
@@ -9359,7 +9359,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H310" t="n">
         <v>900</v>
@@ -9388,7 +9388,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G311" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H311" t="n">
         <v>1200</v>
@@ -9417,7 +9417,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G312" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G313" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9475,7 +9475,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G314" t="n">
-        <v>2.0224757194519</v>
+        <v>2.02247595787048</v>
       </c>
       <c r="H314" t="n">
         <v>1800</v>
@@ -9504,7 +9504,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H315" t="n">
         <v>300</v>
@@ -9533,7 +9533,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G316" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G318" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H318" t="n">
         <v>600</v>
@@ -9620,7 +9620,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G319" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G320" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>2.04956269264221</v>
+        <v>2.04956245422363</v>
       </c>
       <c r="H326" t="n">
         <v>5700</v>
@@ -9881,7 +9881,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G328" t="n">
-        <v>1.91412889957428</v>
+        <v>1.91412878036499</v>
       </c>
       <c r="H328" t="n">
         <v>51000</v>
@@ -9939,7 +9939,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>1.84189772605896</v>
+        <v>1.84189760684967</v>
       </c>
       <c r="H330" t="n">
         <v>29100</v>
@@ -10142,7 +10142,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G337" t="n">
-        <v>2.0224757194519</v>
+        <v>2.02247595787048</v>
       </c>
       <c r="H337" t="n">
         <v>300</v>
@@ -10171,7 +10171,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G338" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H338" t="n">
         <v>18000</v>
@@ -10258,7 +10258,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G341" t="n">
-        <v>2.04053378105164</v>
+        <v>2.04053354263306</v>
       </c>
       <c r="H341" t="n">
         <v>1200</v>
@@ -10345,7 +10345,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G344" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H344" t="n">
         <v>13200</v>
@@ -10635,7 +10635,7 @@
         <v>2</v>
       </c>
       <c r="G354" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H354" t="n">
         <v>21600</v>
@@ -10693,7 +10693,7 @@
         <v>2</v>
       </c>
       <c r="G356" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H356" t="n">
         <v>1500</v>
@@ -10722,7 +10722,7 @@
         <v>2</v>
       </c>
       <c r="G357" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>2</v>
       </c>
       <c r="G358" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
         <v>2</v>
       </c>
       <c r="G359" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>2</v>
       </c>
       <c r="G360" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>2</v>
       </c>
       <c r="G361" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>2</v>
       </c>
       <c r="G362" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>2</v>
       </c>
       <c r="G363" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>2</v>
       </c>
       <c r="G365" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H365" t="n">
         <v>3000</v>
@@ -10983,7 +10983,7 @@
         <v>2</v>
       </c>
       <c r="G366" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>2</v>
       </c>
       <c r="G378" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H378" t="n">
         <v>2100</v>
@@ -11360,7 +11360,7 @@
         <v>2</v>
       </c>
       <c r="G379" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>2</v>
       </c>
       <c r="G380" t="n">
-        <v>1.80578207969666</v>
+        <v>1.80578196048737</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>1.7877242565155</v>
+        <v>1.78772413730621</v>
       </c>
       <c r="H381" t="n">
         <v>98700</v>
@@ -11563,7 +11563,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G386" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H386" t="n">
         <v>5100</v>
@@ -11679,7 +11679,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G390" t="n">
-        <v>1.6793771982193</v>
+        <v>1.67937731742859</v>
       </c>
       <c r="H390" t="n">
         <v>2400</v>
@@ -11795,7 +11795,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G394" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H394" t="n">
         <v>5100</v>
@@ -11824,7 +11824,7 @@
         <v>1.75</v>
       </c>
       <c r="G395" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H395" t="n">
         <v>3900</v>
@@ -11853,7 +11853,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G396" t="n">
-        <v>1.59811699390411</v>
+        <v>1.5981171131134</v>
       </c>
       <c r="H396" t="n">
         <v>12600</v>
@@ -11911,7 +11911,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H398" t="n">
         <v>1200</v>
@@ -12085,7 +12085,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H404" t="n">
         <v>80700</v>
@@ -12317,7 +12317,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H412" t="n">
         <v>900</v>
@@ -12433,7 +12433,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G416" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H416" t="n">
         <v>2100</v>
@@ -12549,7 +12549,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G420" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H420" t="n">
         <v>300</v>
@@ -12607,7 +12607,7 @@
         <v>1.5</v>
       </c>
       <c r="G422" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H422" t="n">
         <v>300</v>
@@ -12636,7 +12636,7 @@
         <v>1.5</v>
       </c>
       <c r="G423" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H423" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>1.5</v>
       </c>
       <c r="G424" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G426" t="n">
-        <v>1.28210532665253</v>
+        <v>1.28210520744324</v>
       </c>
       <c r="H426" t="n">
         <v>5100</v>
@@ -12868,7 +12868,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G431" t="n">
-        <v>1.28210532665253</v>
+        <v>1.28210520744324</v>
       </c>
       <c r="H431" t="n">
         <v>11700</v>
@@ -12897,7 +12897,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G432" t="n">
-        <v>1.30016303062439</v>
+        <v>1.30016314983368</v>
       </c>
       <c r="H432" t="n">
         <v>900</v>
@@ -12926,7 +12926,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G433" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H433" t="n">
         <v>300</v>
@@ -13013,7 +13013,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>1.30016303062439</v>
+        <v>1.30016314983368</v>
       </c>
       <c r="H436" t="n">
         <v>4200</v>
@@ -13042,7 +13042,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G437" t="n">
-        <v>1.30016303062439</v>
+        <v>1.30016314983368</v>
       </c>
       <c r="H437" t="n">
         <v>39900</v>
@@ -13071,7 +13071,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G438" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H438" t="n">
         <v>27900</v>
@@ -13100,7 +13100,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G439" t="n">
-        <v>1.30016303062439</v>
+        <v>1.30016314983368</v>
       </c>
       <c r="H439" t="n">
         <v>6000</v>
@@ -13129,7 +13129,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G440" t="n">
-        <v>1.30016303062439</v>
+        <v>1.30016314983368</v>
       </c>
       <c r="H440" t="n">
         <v>1500</v>
@@ -13158,7 +13158,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G441" t="n">
-        <v>1.30016303062439</v>
+        <v>1.30016314983368</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G442" t="n">
-        <v>1.24598968029022</v>
+        <v>1.24598956108093</v>
       </c>
       <c r="H442" t="n">
         <v>79500</v>
@@ -13216,7 +13216,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G443" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H443" t="n">
         <v>6000</v>
@@ -13390,7 +13390,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G449" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H449" t="n">
         <v>71700</v>
@@ -13448,7 +13448,7 @@
         <v>1.75</v>
       </c>
       <c r="G451" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H451" t="n">
         <v>17400</v>
@@ -13477,7 +13477,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H452" t="n">
         <v>5100</v>
@@ -13622,7 +13622,7 @@
         <v>1.5</v>
       </c>
       <c r="G457" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H457" t="n">
         <v>3000</v>
@@ -13651,7 +13651,7 @@
         <v>1.5</v>
       </c>
       <c r="G458" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H458" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>1.5</v>
       </c>
       <c r="G459" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H459" t="n">
         <v>9300</v>
@@ -13709,7 +13709,7 @@
         <v>1.5</v>
       </c>
       <c r="G460" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H460" t="n">
         <v>300</v>
@@ -13738,7 +13738,7 @@
         <v>1.5</v>
       </c>
       <c r="G461" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>1.5</v>
       </c>
       <c r="G462" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>1.5</v>
       </c>
       <c r="G463" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H463" t="n">
         <v>4200</v>
@@ -13854,7 +13854,7 @@
         <v>1.5</v>
       </c>
       <c r="G465" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H465" t="n">
         <v>20100</v>
@@ -13883,7 +13883,7 @@
         <v>1.5</v>
       </c>
       <c r="G466" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H466" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G469" t="n">
-        <v>1.6793771982193</v>
+        <v>1.67937731742859</v>
       </c>
       <c r="H469" t="n">
         <v>347100</v>
@@ -14028,7 +14028,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G471" t="n">
-        <v>1.59811699390411</v>
+        <v>1.5981171131134</v>
       </c>
       <c r="H471" t="n">
         <v>32400</v>
@@ -14144,7 +14144,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H475" t="n">
         <v>49500</v>
@@ -14173,7 +14173,7 @@
         <v>1.75</v>
       </c>
       <c r="G476" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H476" t="n">
         <v>21600</v>
@@ -14202,7 +14202,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G477" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H477" t="n">
         <v>18600</v>
@@ -14231,7 +14231,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G478" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H478" t="n">
         <v>31500</v>
@@ -14260,7 +14260,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H479" t="n">
         <v>39600</v>
@@ -14318,7 +14318,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G481" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H481" t="n">
         <v>30900</v>
@@ -14463,7 +14463,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G486" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H486" t="n">
         <v>16800</v>
@@ -14521,7 +14521,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G488" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H488" t="n">
         <v>6000</v>
@@ -14840,7 +14840,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G499" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H499" t="n">
         <v>42000</v>
@@ -14869,7 +14869,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>1.59811699390411</v>
+        <v>1.5981171131134</v>
       </c>
       <c r="H500" t="n">
         <v>22200</v>
@@ -14898,7 +14898,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G501" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H501" t="n">
         <v>9900</v>
@@ -14956,7 +14956,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G503" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H503" t="n">
         <v>44700</v>
@@ -14985,7 +14985,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G504" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H504" t="n">
         <v>5400</v>
@@ -15043,7 +15043,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G506" t="n">
-        <v>1.59811699390411</v>
+        <v>1.5981171131134</v>
       </c>
       <c r="H506" t="n">
         <v>8700</v>
@@ -15072,7 +15072,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G507" t="n">
-        <v>1.59811699390411</v>
+        <v>1.5981171131134</v>
       </c>
       <c r="H507" t="n">
         <v>10500</v>
@@ -15101,7 +15101,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G508" t="n">
-        <v>1.59811699390411</v>
+        <v>1.5981171131134</v>
       </c>
       <c r="H508" t="n">
         <v>12600</v>
@@ -15130,7 +15130,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G509" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H509" t="n">
         <v>3600</v>
@@ -15217,7 +15217,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H512" t="n">
         <v>36000</v>
@@ -15304,7 +15304,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G515" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H515" t="n">
         <v>7500</v>
@@ -15420,7 +15420,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G519" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H519" t="n">
         <v>4800</v>
@@ -15478,7 +15478,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G521" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H521" t="n">
         <v>600</v>
@@ -15507,7 +15507,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H522" t="n">
         <v>2400</v>
@@ -15536,7 +15536,7 @@
         <v>1.75</v>
       </c>
       <c r="G523" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H523" t="n">
         <v>9900</v>
@@ -15594,7 +15594,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G525" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H525" t="n">
         <v>37500</v>
@@ -15623,7 +15623,7 @@
         <v>1.75</v>
       </c>
       <c r="G526" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H526" t="n">
         <v>92100</v>
@@ -15826,7 +15826,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G533" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H533" t="n">
         <v>5400</v>
@@ -16000,7 +16000,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G539" t="n">
-        <v>1.2550185918808</v>
+        <v>1.25501847267151</v>
       </c>
       <c r="H539" t="n">
         <v>51300</v>
@@ -16087,7 +16087,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G542" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H542" t="n">
         <v>21600</v>
@@ -16145,7 +16145,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G544" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H544" t="n">
         <v>11400</v>
@@ -16174,7 +16174,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G545" t="n">
-        <v>1.2550185918808</v>
+        <v>1.25501847267151</v>
       </c>
       <c r="H545" t="n">
         <v>70200</v>
@@ -16261,7 +16261,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G548" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H548" t="n">
         <v>21900</v>
@@ -16290,7 +16290,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G549" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H549" t="n">
         <v>45900</v>
@@ -16319,7 +16319,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G550" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H550" t="n">
         <v>19800</v>
@@ -16435,7 +16435,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G554" t="n">
-        <v>1.08346915245056</v>
+        <v>1.08346927165985</v>
       </c>
       <c r="H554" t="n">
         <v>29100</v>
@@ -16493,7 +16493,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G556" t="n">
-        <v>1.02026689052582</v>
+        <v>1.02026677131653</v>
       </c>
       <c r="H556" t="n">
         <v>72900</v>
@@ -16522,7 +16522,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G557" t="n">
-        <v>1.02026689052582</v>
+        <v>1.02026677131653</v>
       </c>
       <c r="H557" t="n">
         <v>37800</v>
@@ -16551,7 +16551,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G558" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H558" t="n">
         <v>19500</v>
@@ -16580,7 +16580,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G559" t="n">
-        <v>1.01123785972595</v>
+        <v>1.01123797893524</v>
       </c>
       <c r="H559" t="n">
         <v>22800</v>
@@ -16609,7 +16609,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G560" t="n">
-        <v>1.01123785972595</v>
+        <v>1.01123797893524</v>
       </c>
       <c r="H560" t="n">
         <v>13800</v>
@@ -16638,7 +16638,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G561" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H561" t="n">
         <v>8100</v>
@@ -16725,7 +16725,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H564" t="n">
         <v>15300</v>
@@ -16783,7 +16783,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G566" t="n">
-        <v>0.83968859910965</v>
+        <v>0.839688658714294</v>
       </c>
       <c r="H566" t="n">
         <v>3600</v>
@@ -16841,7 +16841,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G568" t="n">
-        <v>0.803572952747345</v>
+        <v>0.80357301235199</v>
       </c>
       <c r="H568" t="n">
         <v>9600</v>
@@ -16870,7 +16870,7 @@
         <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H569" t="n">
         <v>16200</v>
@@ -16899,7 +16899,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>0.884833216667175</v>
+        <v>0.884833157062531</v>
       </c>
       <c r="H570" t="n">
         <v>10800</v>
@@ -17044,7 +17044,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G575" t="n">
-        <v>0.884833216667175</v>
+        <v>0.884833157062531</v>
       </c>
       <c r="H575" t="n">
         <v>16200</v>
@@ -17218,7 +17218,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G581" t="n">
-        <v>1.01123785972595</v>
+        <v>1.01123797893524</v>
       </c>
       <c r="H581" t="n">
         <v>24300</v>
@@ -17247,7 +17247,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G582" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H582" t="n">
         <v>1200</v>
@@ -17334,7 +17334,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G585" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H585" t="n">
         <v>15600</v>
@@ -17363,7 +17363,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G586" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H586" t="n">
         <v>9600</v>
@@ -17479,7 +17479,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G590" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H590" t="n">
         <v>18000</v>
@@ -17508,7 +17508,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G591" t="n">
-        <v>0.952549874782562</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H591" t="n">
         <v>102000</v>
@@ -17624,7 +17624,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H595" t="n">
         <v>15900</v>
@@ -17711,7 +17711,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G598" t="n">
-        <v>0.952549874782562</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H598" t="n">
         <v>21600</v>
@@ -17798,7 +17798,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G601" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H601" t="n">
         <v>17100</v>
@@ -17827,7 +17827,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G602" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H602" t="n">
         <v>13200</v>
@@ -18059,7 +18059,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H610" t="n">
         <v>52200</v>
@@ -18117,7 +18117,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G612" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H612" t="n">
         <v>36000</v>
@@ -18204,7 +18204,7 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H615" t="n">
         <v>20700</v>
@@ -18233,7 +18233,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G616" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H616" t="n">
         <v>26700</v>
@@ -18262,7 +18262,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G617" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H617" t="n">
         <v>13200</v>
@@ -18320,7 +18320,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G619" t="n">
-        <v>0.893862128257751</v>
+        <v>0.893862068653107</v>
       </c>
       <c r="H619" t="n">
         <v>41100</v>
@@ -18349,7 +18349,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G620" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H620" t="n">
         <v>13500</v>
@@ -18378,7 +18378,7 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H621" t="n">
         <v>9900</v>
@@ -18407,7 +18407,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G622" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H622" t="n">
         <v>54000</v>
@@ -18436,7 +18436,7 @@
         <v>1</v>
       </c>
       <c r="G623" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H623" t="n">
         <v>20100</v>
@@ -18494,7 +18494,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G625" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H625" t="n">
         <v>47100</v>
@@ -18552,7 +18552,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G627" t="n">
-        <v>1.04283905029297</v>
+        <v>1.04283916950226</v>
       </c>
       <c r="H627" t="n">
         <v>258300</v>
@@ -18581,7 +18581,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G628" t="n">
-        <v>0.988665640354156</v>
+        <v>0.988665580749512</v>
       </c>
       <c r="H628" t="n">
         <v>45600</v>
@@ -18726,7 +18726,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G633" t="n">
-        <v>1.01123785972595</v>
+        <v>1.01123797893524</v>
       </c>
       <c r="H633" t="n">
         <v>12000</v>
@@ -18755,7 +18755,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G634" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H634" t="n">
         <v>5700</v>
@@ -18842,7 +18842,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G637" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H637" t="n">
         <v>3900</v>
@@ -18900,7 +18900,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H639" t="n">
         <v>2400</v>
@@ -18929,7 +18929,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G640" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H640" t="n">
         <v>18600</v>
@@ -19045,7 +19045,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G644" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H644" t="n">
         <v>10800</v>
@@ -19190,7 +19190,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G649" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H649" t="n">
         <v>3000</v>
@@ -19335,7 +19335,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G654" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607936382294</v>
       </c>
       <c r="H654" t="n">
         <v>7500</v>
@@ -19422,7 +19422,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G657" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H657" t="n">
         <v>5400</v>
@@ -19480,7 +19480,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G659" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607936382294</v>
       </c>
       <c r="H659" t="n">
         <v>12300</v>
@@ -19509,7 +19509,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G660" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607936382294</v>
       </c>
       <c r="H660" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G664" t="n">
-        <v>0.952549874782562</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H664" t="n">
         <v>300</v>
@@ -19799,7 +19799,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G670" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607936382294</v>
       </c>
       <c r="H670" t="n">
         <v>2100</v>
@@ -19886,7 +19886,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.988665640354156</v>
+        <v>0.988665580749512</v>
       </c>
       <c r="H673" t="n">
         <v>3300</v>
@@ -19915,7 +19915,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G674" t="n">
-        <v>0.988665640354156</v>
+        <v>0.988665580749512</v>
       </c>
       <c r="H674" t="n">
         <v>300</v>
@@ -20031,7 +20031,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G678" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H678" t="n">
         <v>9300</v>
@@ -20263,7 +20263,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H686" t="n">
         <v>3000</v>
@@ -20292,7 +20292,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G687" t="n">
-        <v>0.952549874782562</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H687" t="n">
         <v>3600</v>
@@ -20379,7 +20379,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G690" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H690" t="n">
         <v>3600</v>
@@ -20408,7 +20408,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G691" t="n">
-        <v>0.95706444978714</v>
+        <v>0.957064390182495</v>
       </c>
       <c r="H691" t="n">
         <v>600</v>
@@ -20553,7 +20553,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G696" t="n">
-        <v>0.952549874782562</v>
+        <v>0.952549993991852</v>
       </c>
       <c r="H696" t="n">
         <v>12000</v>
@@ -20611,7 +20611,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G698" t="n">
-        <v>0.970607876777649</v>
+        <v>0.970607936382294</v>
       </c>
       <c r="H698" t="n">
         <v>21600</v>
@@ -20669,7 +20669,7 @@
         <v>1</v>
       </c>
       <c r="G700" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H700" t="n">
         <v>15000</v>
@@ -20698,7 +20698,7 @@
         <v>1</v>
       </c>
       <c r="G701" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H701" t="n">
         <v>14100</v>
@@ -20727,7 +20727,7 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H702" t="n">
         <v>5700</v>
@@ -20756,7 +20756,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>0.911919891834259</v>
+        <v>0.911919951438904</v>
       </c>
       <c r="H703" t="n">
         <v>11700</v>
@@ -20814,7 +20814,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G705" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H705" t="n">
         <v>900</v>
@@ -20843,7 +20843,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G706" t="n">
-        <v>0.843300223350525</v>
+        <v>0.84330016374588</v>
       </c>
       <c r="H706" t="n">
         <v>67500</v>
@@ -20872,7 +20872,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G707" t="n">
-        <v>0.852329075336456</v>
+        <v>0.852329134941101</v>
       </c>
       <c r="H707" t="n">
         <v>10200</v>
@@ -21075,7 +21075,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G714" t="n">
-        <v>0.776486337184906</v>
+        <v>0.776486277580261</v>
       </c>
       <c r="H714" t="n">
         <v>10800</v>
@@ -21104,7 +21104,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G715" t="n">
-        <v>0.80718457698822</v>
+        <v>0.807184517383575</v>
       </c>
       <c r="H715" t="n">
         <v>1500</v>
@@ -21278,7 +21278,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G721" t="n">
-        <v>0.698837697505951</v>
+        <v>0.698837578296661</v>
       </c>
       <c r="H721" t="n">
         <v>20700</v>
@@ -21481,7 +21481,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G728" t="n">
-        <v>0.622994840145111</v>
+        <v>0.622994780540466</v>
       </c>
       <c r="H728" t="n">
         <v>15600</v>
@@ -21510,7 +21510,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G729" t="n">
-        <v>0.619383156299591</v>
+        <v>0.619383275508881</v>
       </c>
       <c r="H729" t="n">
         <v>9600</v>
@@ -21626,7 +21626,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G733" t="n">
-        <v>0.65188729763031</v>
+        <v>0.651887357234955</v>
       </c>
       <c r="H733" t="n">
         <v>3600</v>
@@ -21655,7 +21655,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G734" t="n">
-        <v>0.653693079948425</v>
+        <v>0.653693020343781</v>
       </c>
       <c r="H734" t="n">
         <v>27900</v>
@@ -21713,7 +21713,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G736" t="n">
-        <v>0.678974032402039</v>
+        <v>0.678973972797394</v>
       </c>
       <c r="H736" t="n">
         <v>4200</v>
@@ -21742,7 +21742,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G737" t="n">
-        <v>0.684391379356384</v>
+        <v>0.68439131975174</v>
       </c>
       <c r="H737" t="n">
         <v>14700</v>
@@ -21771,7 +21771,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G738" t="n">
-        <v>0.641052663326263</v>
+        <v>0.641052603721619</v>
       </c>
       <c r="H738" t="n">
         <v>42000</v>
@@ -21800,7 +21800,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G739" t="n">
-        <v>0.637440979480743</v>
+        <v>0.637441039085388</v>
       </c>
       <c r="H739" t="n">
         <v>24000</v>
@@ -21829,7 +21829,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G740" t="n">
-        <v>0.644664168357849</v>
+        <v>0.644664227962494</v>
       </c>
       <c r="H740" t="n">
         <v>3600</v>
@@ -21858,7 +21858,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G741" t="n">
-        <v>0.657304584980011</v>
+        <v>0.657304644584656</v>
       </c>
       <c r="H741" t="n">
         <v>20100</v>
@@ -21945,7 +21945,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G744" t="n">
-        <v>0.675362467765808</v>
+        <v>0.675362527370453</v>
       </c>
       <c r="H744" t="n">
         <v>18000</v>
@@ -22090,7 +22090,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G749" t="n">
-        <v>0.720507025718689</v>
+        <v>0.720506966114044</v>
       </c>
       <c r="H749" t="n">
         <v>48300</v>
@@ -22119,7 +22119,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G750" t="n">
-        <v>0.709672331809998</v>
+        <v>0.709672272205353</v>
       </c>
       <c r="H750" t="n">
         <v>35100</v>
@@ -22177,7 +22177,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G752" t="n">
-        <v>0.675362467765808</v>
+        <v>0.675362527370453</v>
       </c>
       <c r="H752" t="n">
         <v>33600</v>
@@ -22206,7 +22206,7 @@
         <v>0.75</v>
       </c>
       <c r="G753" t="n">
-        <v>0.677168250083923</v>
+        <v>0.677168309688568</v>
       </c>
       <c r="H753" t="n">
         <v>36600</v>
@@ -22235,7 +22235,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G754" t="n">
-        <v>0.675362467765808</v>
+        <v>0.675362527370453</v>
       </c>
       <c r="H754" t="n">
         <v>27900</v>
@@ -22264,7 +22264,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G755" t="n">
-        <v>0.698837697505951</v>
+        <v>0.698837578296661</v>
       </c>
       <c r="H755" t="n">
         <v>134100</v>
@@ -22322,7 +22322,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G757" t="n">
-        <v>0.684391379356384</v>
+        <v>0.68439131975174</v>
       </c>
       <c r="H757" t="n">
         <v>34500</v>
@@ -22583,7 +22583,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G766" t="n">
-        <v>0.80718457698822</v>
+        <v>0.807184517383575</v>
       </c>
       <c r="H766" t="n">
         <v>120300</v>
@@ -22699,7 +22699,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G770" t="n">
-        <v>0.765651524066925</v>
+        <v>0.76565158367157</v>
       </c>
       <c r="H770" t="n">
         <v>44100</v>
@@ -22728,7 +22728,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G771" t="n">
-        <v>0.765651524066925</v>
+        <v>0.76565158367157</v>
       </c>
       <c r="H771" t="n">
         <v>9300</v>
@@ -22786,7 +22786,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G773" t="n">
-        <v>0.776486337184906</v>
+        <v>0.776486277580261</v>
       </c>
       <c r="H773" t="n">
         <v>17700</v>
@@ -22844,7 +22844,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G775" t="n">
-        <v>0.776486337184906</v>
+        <v>0.776486277580261</v>
       </c>
       <c r="H775" t="n">
         <v>10800</v>
@@ -22873,7 +22873,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G776" t="n">
-        <v>0.80176717042923</v>
+        <v>0.801767230033875</v>
       </c>
       <c r="H776" t="n">
         <v>99600</v>
@@ -23018,7 +23018,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G781" t="n">
-        <v>0.803572952747345</v>
+        <v>0.80357301235199</v>
       </c>
       <c r="H781" t="n">
         <v>27000</v>
@@ -23047,7 +23047,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G782" t="n">
-        <v>0.80176717042923</v>
+        <v>0.801767230033875</v>
       </c>
       <c r="H782" t="n">
         <v>21600</v>
@@ -23076,7 +23076,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G783" t="n">
-        <v>0.794544041156769</v>
+        <v>0.794544100761414</v>
       </c>
       <c r="H783" t="n">
         <v>92100</v>
@@ -23134,7 +23134,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G785" t="n">
-        <v>0.803572952747345</v>
+        <v>0.80357301235199</v>
       </c>
       <c r="H785" t="n">
         <v>7500</v>
@@ -23424,7 +23424,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>0.769263088703156</v>
+        <v>0.7692631483078</v>
       </c>
       <c r="H795" t="n">
         <v>9900</v>
@@ -23540,7 +23540,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G799" t="n">
-        <v>0.819824993610382</v>
+        <v>0.819825053215027</v>
       </c>
       <c r="H799" t="n">
         <v>312600</v>
@@ -23569,7 +23569,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G800" t="n">
-        <v>0.823436558246613</v>
+        <v>0.823436677455902</v>
       </c>
       <c r="H800" t="n">
         <v>87300</v>
@@ -23598,7 +23598,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G801" t="n">
-        <v>0.834271311759949</v>
+        <v>0.834271371364594</v>
       </c>
       <c r="H801" t="n">
         <v>39300</v>
@@ -23714,7 +23714,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G805" t="n">
-        <v>0.859552204608917</v>
+        <v>0.859552264213562</v>
       </c>
       <c r="H805" t="n">
         <v>41700</v>
@@ -23772,7 +23772,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>0.893862128257751</v>
+        <v>0.893862068653107</v>
       </c>
       <c r="H807" t="n">
         <v>214500</v>
@@ -23801,7 +23801,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G808" t="n">
-        <v>0.890250504016876</v>
+        <v>0.890250563621521</v>
       </c>
       <c r="H808" t="n">
         <v>21600</v>
@@ -23917,7 +23917,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G812" t="n">
-        <v>0.873998522758484</v>
+        <v>0.873998463153839</v>
       </c>
       <c r="H812" t="n">
         <v>37200</v>
@@ -24004,7 +24004,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G815" t="n">
-        <v>0.859552204608917</v>
+        <v>0.859552264213562</v>
       </c>
       <c r="H815" t="n">
         <v>4800</v>
@@ -24062,7 +24062,7 @@
         <v>1</v>
       </c>
       <c r="G817" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H817" t="n">
         <v>158700</v>
@@ -24120,7 +24120,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G819" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H819" t="n">
         <v>47400</v>
@@ -24265,7 +24265,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G824" t="n">
-        <v>0.911919891834259</v>
+        <v>0.911919951438904</v>
       </c>
       <c r="H824" t="n">
         <v>29700</v>
@@ -24352,7 +24352,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G827" t="n">
-        <v>0.88302743434906</v>
+        <v>0.883027374744415</v>
       </c>
       <c r="H827" t="n">
         <v>58800</v>
@@ -24410,7 +24410,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G829" t="n">
-        <v>0.87941575050354</v>
+        <v>0.879415810108185</v>
       </c>
       <c r="H829" t="n">
         <v>30300</v>
@@ -24439,7 +24439,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G830" t="n">
-        <v>0.88302743434906</v>
+        <v>0.883027374744415</v>
       </c>
       <c r="H830" t="n">
         <v>2100</v>
@@ -24497,7 +24497,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G832" t="n">
-        <v>0.893862128257751</v>
+        <v>0.893862068653107</v>
       </c>
       <c r="H832" t="n">
         <v>12000</v>
@@ -24526,7 +24526,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G833" t="n">
-        <v>0.88302743434906</v>
+        <v>0.883027374744415</v>
       </c>
       <c r="H833" t="n">
         <v>8700</v>
@@ -24555,7 +24555,7 @@
         <v>1</v>
       </c>
       <c r="G834" t="n">
-        <v>0.902891039848328</v>
+        <v>0.902890980243683</v>
       </c>
       <c r="H834" t="n">
         <v>11400</v>
@@ -24584,7 +24584,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G835" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H835" t="n">
         <v>30600</v>
@@ -24700,7 +24700,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G839" t="n">
-        <v>0.911919891834259</v>
+        <v>0.911919951438904</v>
       </c>
       <c r="H839" t="n">
         <v>300</v>
@@ -24758,7 +24758,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G841" t="n">
-        <v>0.901085317134857</v>
+        <v>0.901085257530212</v>
       </c>
       <c r="H841" t="n">
         <v>45900</v>
@@ -24787,7 +24787,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G842" t="n">
-        <v>0.890250504016876</v>
+        <v>0.890250563621521</v>
       </c>
       <c r="H842" t="n">
         <v>21000</v>
@@ -24845,7 +24845,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G844" t="n">
-        <v>0.92094886302948</v>
+        <v>0.920948803424835</v>
       </c>
       <c r="H844" t="n">
         <v>35100</v>
@@ -24932,7 +24932,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G847" t="n">
-        <v>0.984151303768158</v>
+        <v>0.984151244163513</v>
       </c>
       <c r="H847" t="n">
         <v>6600</v>
@@ -25077,7 +25077,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G852" t="n">
-        <v>1.02478134632111</v>
+        <v>1.02478122711182</v>
       </c>
       <c r="H852" t="n">
         <v>109800</v>
@@ -25222,7 +25222,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G857" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H857" t="n">
         <v>135300</v>
@@ -25309,7 +25309,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G860" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H860" t="n">
         <v>18000</v>
@@ -25396,7 +25396,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G863" t="n">
-        <v>1.06089699268341</v>
+        <v>1.06089675426483</v>
       </c>
       <c r="H863" t="n">
         <v>3900</v>
@@ -25425,7 +25425,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G864" t="n">
-        <v>1.10604155063629</v>
+        <v>1.106041431427</v>
       </c>
       <c r="H864" t="n">
         <v>43500</v>
@@ -25512,7 +25512,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G867" t="n">
-        <v>1.08346915245056</v>
+        <v>1.08346927165985</v>
       </c>
       <c r="H867" t="n">
         <v>25800</v>
@@ -25570,7 +25570,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H869" t="n">
         <v>38100</v>
@@ -25628,7 +25628,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G871" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H871" t="n">
         <v>7500</v>
@@ -25657,7 +25657,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G872" t="n">
-        <v>1.1421571969986</v>
+        <v>1.14215695858002</v>
       </c>
       <c r="H872" t="n">
         <v>46800</v>
@@ -25686,7 +25686,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G873" t="n">
-        <v>1.16472935676575</v>
+        <v>1.16472947597504</v>
       </c>
       <c r="H873" t="n">
         <v>48300</v>
@@ -25744,7 +25744,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>1.16472935676575</v>
+        <v>1.16472947597504</v>
       </c>
       <c r="H875" t="n">
         <v>158700</v>
@@ -25802,7 +25802,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G877" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H877" t="n">
         <v>32400</v>
@@ -25860,7 +25860,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G879" t="n">
-        <v>1.27307629585266</v>
+        <v>1.27307617664337</v>
       </c>
       <c r="H879" t="n">
         <v>146400</v>
@@ -25918,7 +25918,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G881" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H881" t="n">
         <v>324000</v>
@@ -25947,7 +25947,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G882" t="n">
-        <v>1.24598968029022</v>
+        <v>1.24598956108093</v>
       </c>
       <c r="H882" t="n">
         <v>376800</v>
@@ -26005,7 +26005,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G884" t="n">
-        <v>1.2550185918808</v>
+        <v>1.25501847267151</v>
       </c>
       <c r="H884" t="n">
         <v>78600</v>
@@ -26034,7 +26034,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G885" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H885" t="n">
         <v>49200</v>
@@ -26121,7 +26121,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G888" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H888" t="n">
         <v>5100</v>
@@ -26237,7 +26237,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G892" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H892" t="n">
         <v>12600</v>
@@ -26440,7 +26440,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G899" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H899" t="n">
         <v>11400</v>
@@ -26498,7 +26498,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G901" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H901" t="n">
         <v>68700</v>
@@ -26527,7 +26527,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G902" t="n">
-        <v>1.19633054733276</v>
+        <v>1.19633066654205</v>
       </c>
       <c r="H902" t="n">
         <v>20400</v>
@@ -26585,7 +26585,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G904" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H904" t="n">
         <v>900</v>
@@ -26672,7 +26672,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G907" t="n">
-        <v>1.19181621074677</v>
+        <v>1.19181609153748</v>
       </c>
       <c r="H907" t="n">
         <v>4500</v>
@@ -26701,7 +26701,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G908" t="n">
-        <v>1.1421571969986</v>
+        <v>1.14215695858002</v>
       </c>
       <c r="H908" t="n">
         <v>3600</v>
@@ -26788,7 +26788,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G911" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H911" t="n">
         <v>2100</v>
@@ -26817,7 +26817,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G912" t="n">
-        <v>1.101527094841</v>
+        <v>1.10152697563171</v>
       </c>
       <c r="H912" t="n">
         <v>1200</v>
@@ -26875,7 +26875,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G914" t="n">
-        <v>1.10604155063629</v>
+        <v>1.106041431427</v>
       </c>
       <c r="H914" t="n">
         <v>900</v>
@@ -26904,7 +26904,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G915" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H915" t="n">
         <v>13500</v>
@@ -26962,7 +26962,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G917" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H917" t="n">
         <v>3300</v>
@@ -26991,7 +26991,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G918" t="n">
-        <v>1.09249806404114</v>
+        <v>1.09249818325043</v>
       </c>
       <c r="H918" t="n">
         <v>0</v>
@@ -27020,7 +27020,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>1.16472935676575</v>
+        <v>1.16472947597504</v>
       </c>
       <c r="H919" t="n">
         <v>21000</v>
@@ -27049,7 +27049,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G920" t="n">
-        <v>1.16021478176117</v>
+        <v>1.16021490097046</v>
       </c>
       <c r="H920" t="n">
         <v>3900</v>
@@ -27078,7 +27078,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G921" t="n">
-        <v>1.16021478176117</v>
+        <v>1.16021490097046</v>
       </c>
       <c r="H921" t="n">
         <v>3000</v>
@@ -27107,7 +27107,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G922" t="n">
-        <v>1.16472935676575</v>
+        <v>1.16472947597504</v>
       </c>
       <c r="H922" t="n">
         <v>15000</v>
@@ -27136,7 +27136,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G923" t="n">
-        <v>1.1421571969986</v>
+        <v>1.14215695858002</v>
       </c>
       <c r="H923" t="n">
         <v>4200</v>
@@ -27194,7 +27194,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G925" t="n">
-        <v>1.1421571969986</v>
+        <v>1.14215695858002</v>
       </c>
       <c r="H925" t="n">
         <v>1200</v>
@@ -27223,7 +27223,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G926" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H926" t="n">
         <v>16500</v>
@@ -27252,7 +27252,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G927" t="n">
-        <v>1.22793185710907</v>
+        <v>1.22793173789978</v>
       </c>
       <c r="H927" t="n">
         <v>60300</v>
@@ -27281,7 +27281,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G928" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H928" t="n">
         <v>10200</v>
@@ -27310,7 +27310,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G929" t="n">
-        <v>1.22341728210449</v>
+        <v>1.22341740131378</v>
       </c>
       <c r="H929" t="n">
         <v>0</v>
@@ -27339,7 +27339,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G930" t="n">
-        <v>1.24598968029022</v>
+        <v>1.24598956108093</v>
       </c>
       <c r="H930" t="n">
         <v>8400</v>
@@ -27368,7 +27368,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G931" t="n">
-        <v>1.2550185918808</v>
+        <v>1.25501847267151</v>
       </c>
       <c r="H931" t="n">
         <v>17400</v>
@@ -27397,7 +27397,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G932" t="n">
-        <v>1.2550185918808</v>
+        <v>1.25501847267151</v>
       </c>
       <c r="H932" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G935" t="n">
-        <v>1.6793771982193</v>
+        <v>1.67937731742859</v>
       </c>
       <c r="H935" t="n">
         <v>272400</v>
@@ -27542,7 +27542,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G937" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H937" t="n">
         <v>201600</v>
@@ -27571,7 +27571,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G938" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H938" t="n">
         <v>60000</v>
@@ -27600,7 +27600,7 @@
         <v>1.75</v>
       </c>
       <c r="G939" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H939" t="n">
         <v>30600</v>
@@ -27658,7 +27658,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G941" t="n">
-        <v>1.64777612686157</v>
+        <v>1.64777624607086</v>
       </c>
       <c r="H941" t="n">
         <v>159900</v>
@@ -27716,7 +27716,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H943" t="n">
         <v>35700</v>
@@ -27803,7 +27803,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G946" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H946" t="n">
         <v>20700</v>
@@ -28064,7 +28064,7 @@
         <v>1.5</v>
       </c>
       <c r="G955" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H955" t="n">
         <v>54600</v>
@@ -28093,7 +28093,7 @@
         <v>1.5</v>
       </c>
       <c r="G956" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H956" t="n">
         <v>15000</v>
@@ -28238,7 +28238,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G961" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H961" t="n">
         <v>116400</v>
@@ -28325,7 +28325,7 @@
         <v>1.5</v>
       </c>
       <c r="G964" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H964" t="n">
         <v>15900</v>
@@ -28354,7 +28354,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G965" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H965" t="n">
         <v>12900</v>
@@ -28412,7 +28412,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G967" t="n">
-        <v>1.35885107517242</v>
+        <v>1.35885083675385</v>
       </c>
       <c r="H967" t="n">
         <v>54900</v>
@@ -28441,7 +28441,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G968" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H968" t="n">
         <v>28500</v>
@@ -28499,7 +28499,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G970" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H970" t="n">
         <v>59100</v>
@@ -28847,7 +28847,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G982" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H982" t="n">
         <v>41400</v>
@@ -28992,7 +28992,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G987" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H987" t="n">
         <v>38700</v>
@@ -29050,7 +29050,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G989" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H989" t="n">
         <v>57300</v>
@@ -29195,7 +29195,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G994" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H994" t="n">
         <v>6600</v>
@@ -29224,7 +29224,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H995" t="n">
         <v>3300</v>
@@ -29253,7 +29253,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G996" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H996" t="n">
         <v>28800</v>
@@ -29340,7 +29340,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G999" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H999" t="n">
         <v>10500</v>
@@ -29572,7 +29572,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H1007" t="n">
         <v>3900</v>
@@ -29659,7 +29659,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1010" t="n">
         <v>4800</v>
@@ -29688,7 +29688,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1011" t="n">
         <v>900</v>
@@ -29717,7 +29717,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.43108236789703</v>
+        <v>1.43108224868774</v>
       </c>
       <c r="H1012" t="n">
         <v>37800</v>
@@ -29862,7 +29862,7 @@
         <v>1.5</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1017" t="n">
         <v>26400</v>
@@ -29891,7 +29891,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H1018" t="n">
         <v>7200</v>
@@ -29949,7 +29949,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.32273542881012</v>
+        <v>1.32273530960083</v>
       </c>
       <c r="H1020" t="n">
         <v>10500</v>
@@ -29978,7 +29978,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.30919194221497</v>
+        <v>1.30919206142426</v>
       </c>
       <c r="H1021" t="n">
         <v>6900</v>
@@ -30007,7 +30007,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.26856184005737</v>
+        <v>1.26856195926666</v>
       </c>
       <c r="H1022" t="n">
         <v>40200</v>
@@ -30036,7 +30036,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.30467748641968</v>
+        <v>1.30467760562897</v>
       </c>
       <c r="H1023" t="n">
         <v>300</v>
@@ -30065,7 +30065,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.28210532665253</v>
+        <v>1.28210520744324</v>
       </c>
       <c r="H1024" t="n">
         <v>8100</v>
@@ -30094,7 +30094,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.28210532665253</v>
+        <v>1.28210520744324</v>
       </c>
       <c r="H1025" t="n">
         <v>7800</v>
@@ -30123,7 +30123,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.27759063243866</v>
+        <v>1.27759075164795</v>
       </c>
       <c r="H1026" t="n">
         <v>12600</v>
@@ -30181,7 +30181,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.3317643404007</v>
+        <v>1.33176422119141</v>
       </c>
       <c r="H1028" t="n">
         <v>19200</v>
@@ -30210,7 +30210,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1029" t="n">
         <v>8700</v>
@@ -30268,7 +30268,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H1031" t="n">
         <v>16200</v>
@@ -30326,7 +30326,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1033" t="n">
         <v>9300</v>
@@ -30355,7 +30355,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1034" t="n">
         <v>24000</v>
@@ -30442,7 +30442,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1037" t="n">
         <v>2100</v>
@@ -30616,7 +30616,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1043" t="n">
         <v>4800</v>
@@ -30993,7 +30993,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.40399551391602</v>
+        <v>1.40399539470673</v>
       </c>
       <c r="H1056" t="n">
         <v>2100</v>
@@ -31167,7 +31167,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1062" t="n">
         <v>7800</v>
@@ -31196,7 +31196,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.34079313278198</v>
+        <v>1.34079325199127</v>
       </c>
       <c r="H1063" t="n">
         <v>6000</v>
@@ -31254,7 +31254,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.27307629585266</v>
+        <v>1.27307617664337</v>
       </c>
       <c r="H1065" t="n">
         <v>64500</v>
@@ -31312,7 +31312,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.28210532665253</v>
+        <v>1.28210520744324</v>
       </c>
       <c r="H1067" t="n">
         <v>4200</v>
@@ -31341,7 +31341,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.2595329284668</v>
+        <v>1.25953304767609</v>
       </c>
       <c r="H1068" t="n">
         <v>2100</v>
@@ -31370,7 +31370,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.2595329284668</v>
+        <v>1.25953304767609</v>
       </c>
       <c r="H1069" t="n">
         <v>600</v>
@@ -31399,7 +31399,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.2595329284668</v>
+        <v>1.25953304767609</v>
       </c>
       <c r="H1070" t="n">
         <v>600</v>
@@ -31515,7 +31515,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.18730163574219</v>
+        <v>1.18730175495148</v>
       </c>
       <c r="H1074" t="n">
         <v>1800</v>
@@ -31602,7 +31602,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.2956485748291</v>
+        <v>1.29564845561981</v>
       </c>
       <c r="H1077" t="n">
         <v>52800</v>
@@ -31660,7 +31660,7 @@
         <v>1.5</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1079" t="n">
         <v>71400</v>
@@ -31718,7 +31718,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1081" t="n">
         <v>22200</v>
@@ -31747,7 +31747,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H1082" t="n">
         <v>25500</v>
@@ -31834,7 +31834,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1085" t="n">
         <v>9300</v>
@@ -31892,7 +31892,7 @@
         <v>1.75</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1087" t="n">
         <v>179400</v>
@@ -32008,7 +32008,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1091" t="n">
         <v>9000</v>
@@ -32066,7 +32066,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1093" t="n">
         <v>3600</v>
@@ -32095,7 +32095,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1094" t="n">
         <v>21000</v>
@@ -32356,7 +32356,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1103" t="n">
         <v>9300</v>
@@ -32472,7 +32472,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1107" t="n">
         <v>1200</v>
@@ -32530,7 +32530,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1109" t="n">
         <v>3300</v>
@@ -32617,7 +32617,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.35885107517242</v>
+        <v>1.35885083675385</v>
       </c>
       <c r="H1112" t="n">
         <v>9600</v>
@@ -32733,7 +32733,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1116" t="n">
         <v>300</v>
@@ -32791,7 +32791,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1118" t="n">
         <v>1200</v>
@@ -32820,7 +32820,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1119" t="n">
         <v>0</v>
@@ -33023,7 +33023,7 @@
         <v>1.5</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1126" t="n">
         <v>65700</v>
@@ -33052,7 +33052,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.30016303062439</v>
+        <v>1.30016314983368</v>
       </c>
       <c r="H1127" t="n">
         <v>50400</v>
@@ -33081,7 +33081,7 @@
         <v>1.5</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1128" t="n">
         <v>42600</v>
@@ -33313,7 +33313,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H1136" t="n">
         <v>13200</v>
@@ -33400,7 +33400,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1139" t="n">
         <v>4200</v>
@@ -33429,7 +33429,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H1140" t="n">
         <v>6300</v>
@@ -33458,7 +33458,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1141" t="n">
         <v>5400</v>
@@ -33661,7 +33661,7 @@
         <v>1.5</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1148" t="n">
         <v>21900</v>
@@ -33922,7 +33922,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1157" t="n">
         <v>14100</v>
@@ -34763,7 +34763,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1186" t="n">
         <v>38400</v>
@@ -35024,7 +35024,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1195" t="n">
         <v>6600</v>
@@ -35053,7 +35053,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1196" t="n">
         <v>0</v>
@@ -35082,7 +35082,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1197" t="n">
         <v>600</v>
@@ -35111,7 +35111,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1198" t="n">
         <v>11400</v>
@@ -35140,7 +35140,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1199" t="n">
         <v>0</v>
@@ -35256,7 +35256,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1203" t="n">
         <v>2700</v>
@@ -35488,7 +35488,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1211" t="n">
         <v>36000</v>
@@ -35546,7 +35546,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1213" t="n">
         <v>23400</v>
@@ -35575,7 +35575,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1214" t="n">
         <v>13200</v>
@@ -35604,7 +35604,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1215" t="n">
         <v>0</v>
@@ -35633,7 +35633,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1216" t="n">
         <v>6600</v>
@@ -35691,7 +35691,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1218" t="n">
         <v>5400</v>
@@ -35981,7 +35981,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.48977017402649</v>
+        <v>1.4897700548172</v>
       </c>
       <c r="H1228" t="n">
         <v>21900</v>
@@ -36358,7 +36358,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1241" t="n">
         <v>2700</v>
@@ -36677,7 +36677,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H1252" t="n">
         <v>8700</v>
@@ -36706,7 +36706,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H1253" t="n">
         <v>11100</v>
@@ -37373,7 +37373,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1276" t="n">
         <v>8100</v>
@@ -37402,7 +37402,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.43108236789703</v>
+        <v>1.43108224868774</v>
       </c>
       <c r="H1277" t="n">
         <v>300</v>
@@ -37460,7 +37460,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1279" t="n">
         <v>1500</v>
@@ -37489,7 +37489,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.45816886425018</v>
+        <v>1.45816898345947</v>
       </c>
       <c r="H1280" t="n">
         <v>0</v>
@@ -37634,7 +37634,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H1285" t="n">
         <v>28500</v>
@@ -37837,7 +37837,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.40399551391602</v>
+        <v>1.40399539470673</v>
       </c>
       <c r="H1292" t="n">
         <v>13500</v>
@@ -37953,7 +37953,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1296" t="n">
         <v>1500</v>
@@ -37982,7 +37982,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.43559670448303</v>
+        <v>1.43559682369232</v>
       </c>
       <c r="H1297" t="n">
         <v>2400</v>
@@ -38069,7 +38069,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1300" t="n">
         <v>19800</v>
@@ -38098,7 +38098,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.42205333709717</v>
+        <v>1.42205345630646</v>
       </c>
       <c r="H1301" t="n">
         <v>0</v>
@@ -38359,7 +38359,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.43108236789703</v>
+        <v>1.43108224868774</v>
       </c>
       <c r="H1310" t="n">
         <v>1800</v>
@@ -38504,7 +38504,7 @@
         <v>1.5</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1315" t="n">
         <v>4200</v>
@@ -38533,7 +38533,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1316" t="n">
         <v>55800</v>
@@ -38765,7 +38765,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1324" t="n">
         <v>13800</v>
@@ -38794,7 +38794,7 @@
         <v>1.5</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1325" t="n">
         <v>12600</v>
@@ -38823,7 +38823,7 @@
         <v>1.5</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1326" t="n">
         <v>9300</v>
@@ -38852,7 +38852,7 @@
         <v>1.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1327" t="n">
         <v>10500</v>
@@ -38968,7 +38968,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1331" t="n">
         <v>48900</v>
@@ -38997,7 +38997,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1332" t="n">
         <v>10500</v>
@@ -39055,7 +39055,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.35885107517242</v>
+        <v>1.35885083675385</v>
       </c>
       <c r="H1334" t="n">
         <v>31200</v>
@@ -39142,7 +39142,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.34982204437256</v>
+        <v>1.34982216358185</v>
       </c>
       <c r="H1337" t="n">
         <v>60300</v>
@@ -39200,7 +39200,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.38142311573029</v>
+        <v>1.38142323493958</v>
       </c>
       <c r="H1339" t="n">
         <v>6300</v>
@@ -39374,7 +39374,7 @@
         <v>1.5</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1345" t="n">
         <v>22800</v>
@@ -39722,7 +39722,7 @@
         <v>1.5</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1357" t="n">
         <v>8100</v>
@@ -39751,7 +39751,7 @@
         <v>1.5</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1358" t="n">
         <v>3000</v>
@@ -39809,7 +39809,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1360" t="n">
         <v>3600</v>
@@ -39983,7 +39983,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1366" t="n">
         <v>4500</v>
@@ -40041,7 +40041,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1368" t="n">
         <v>300</v>
@@ -40128,7 +40128,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.36787986755371</v>
+        <v>1.36787974834442</v>
       </c>
       <c r="H1371" t="n">
         <v>8100</v>
@@ -40157,7 +40157,7 @@
         <v>1.5</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.35433650016785</v>
+        <v>1.35433661937714</v>
       </c>
       <c r="H1372" t="n">
         <v>432000</v>
@@ -40505,7 +40505,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.40399551391602</v>
+        <v>1.40399539470673</v>
       </c>
       <c r="H1384" t="n">
         <v>900</v>
@@ -40534,7 +40534,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.40399551391602</v>
+        <v>1.40399539470673</v>
       </c>
       <c r="H1385" t="n">
         <v>0</v>
@@ -40563,7 +40563,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.40399551391602</v>
+        <v>1.40399539470673</v>
       </c>
       <c r="H1386" t="n">
         <v>0</v>
@@ -40592,7 +40592,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.40399551391602</v>
+        <v>1.40399539470673</v>
       </c>
       <c r="H1387" t="n">
         <v>6000</v>
@@ -40621,7 +40621,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.40399551391602</v>
+        <v>1.40399539470673</v>
       </c>
       <c r="H1388" t="n">
         <v>14100</v>
@@ -40737,7 +40737,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.64777612686157</v>
+        <v>1.64777624607086</v>
       </c>
       <c r="H1392" t="n">
         <v>238200</v>
@@ -40766,7 +40766,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1393" t="n">
         <v>120900</v>
@@ -40882,7 +40882,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.6026314496994</v>
+        <v>1.60263156890869</v>
       </c>
       <c r="H1397" t="n">
         <v>105900</v>
@@ -40940,7 +40940,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H1399" t="n">
         <v>21600</v>
@@ -41201,7 +41201,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1408" t="n">
         <v>18000</v>
@@ -41288,7 +41288,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H1411" t="n">
         <v>9000</v>
@@ -41375,7 +41375,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.57554471492767</v>
+        <v>1.57554483413696</v>
       </c>
       <c r="H1414" t="n">
         <v>6600</v>
@@ -41404,7 +41404,7 @@
         <v>1.75</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1415" t="n">
         <v>1200</v>
@@ -41462,7 +41462,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1417" t="n">
         <v>17700</v>
@@ -41520,7 +41520,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.6026314496994</v>
+        <v>1.60263156890869</v>
       </c>
       <c r="H1419" t="n">
         <v>10500</v>
@@ -41549,7 +41549,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1420" t="n">
         <v>6000</v>
@@ -41578,7 +41578,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1421" t="n">
         <v>16200</v>
@@ -41607,7 +41607,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1422" t="n">
         <v>28500</v>
@@ -41636,7 +41636,7 @@
         <v>1.75</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1423" t="n">
         <v>13500</v>
@@ -41665,7 +41665,7 @@
         <v>1.75</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1424" t="n">
         <v>0</v>
@@ -41694,7 +41694,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1425" t="n">
         <v>17400</v>
@@ -41723,7 +41723,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1426" t="n">
         <v>4800</v>
@@ -41752,7 +41752,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1427" t="n">
         <v>19500</v>
@@ -41810,7 +41810,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.59811699390411</v>
+        <v>1.5981171131134</v>
       </c>
       <c r="H1429" t="n">
         <v>8100</v>
@@ -41839,7 +41839,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1430" t="n">
         <v>12300</v>
@@ -41868,7 +41868,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1431" t="n">
         <v>5100</v>
@@ -41897,7 +41897,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.57554471492767</v>
+        <v>1.57554483413696</v>
       </c>
       <c r="H1432" t="n">
         <v>12000</v>
@@ -41926,7 +41926,7 @@
         <v>1.75</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1433" t="n">
         <v>20100</v>
@@ -42071,7 +42071,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1438" t="n">
         <v>16800</v>
@@ -42100,7 +42100,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1439" t="n">
         <v>10800</v>
@@ -42187,7 +42187,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1442" t="n">
         <v>900</v>
@@ -42332,7 +42332,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.48525559902191</v>
+        <v>1.4852557182312</v>
       </c>
       <c r="H1447" t="n">
         <v>31500</v>
@@ -42361,7 +42361,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.49428451061249</v>
+        <v>1.49428462982178</v>
       </c>
       <c r="H1448" t="n">
         <v>49200</v>
@@ -42419,7 +42419,7 @@
         <v>1.75</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1450" t="n">
         <v>17100</v>
@@ -42477,7 +42477,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1452" t="n">
         <v>6600</v>
@@ -42506,7 +42506,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1453" t="n">
         <v>0</v>
@@ -42535,7 +42535,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1454" t="n">
         <v>3300</v>
@@ -42564,7 +42564,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1455" t="n">
         <v>300</v>
@@ -42883,7 +42883,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1466" t="n">
         <v>4200</v>
@@ -42912,7 +42912,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1467" t="n">
         <v>3000</v>
@@ -43028,7 +43028,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H1471" t="n">
         <v>23400</v>
@@ -43086,7 +43086,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.6026314496994</v>
+        <v>1.60263156890869</v>
       </c>
       <c r="H1473" t="n">
         <v>121200</v>
@@ -43115,7 +43115,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1474" t="n">
         <v>50700</v>
@@ -43173,7 +43173,7 @@
         <v>1.75</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1476" t="n">
         <v>4500</v>
@@ -43231,7 +43231,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1478" t="n">
         <v>32700</v>
@@ -43260,7 +43260,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1479" t="n">
         <v>0</v>
@@ -43318,7 +43318,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1481" t="n">
         <v>6300</v>
@@ -43695,7 +43695,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1494" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1494" t="n">
         <v>8100</v>
@@ -43753,7 +43753,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1496" t="n">
         <v>3300</v>
@@ -43782,7 +43782,7 @@
         <v>1.75</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1497" t="n">
         <v>22800</v>
@@ -43840,7 +43840,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1499" t="n">
         <v>3000</v>
@@ -43869,7 +43869,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1500" t="n">
         <v>0</v>
@@ -43956,7 +43956,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1503" t="n">
-        <v>1.55297267436981</v>
+        <v>1.55297255516052</v>
       </c>
       <c r="H1503" t="n">
         <v>7500</v>
@@ -44043,7 +44043,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H1506" t="n">
         <v>10200</v>
@@ -44101,7 +44101,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H1508" t="n">
         <v>2700</v>
@@ -44130,7 +44130,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.52588582038879</v>
+        <v>1.52588593959808</v>
       </c>
       <c r="H1509" t="n">
         <v>11100</v>
@@ -44246,7 +44246,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.57554471492767</v>
+        <v>1.57554483413696</v>
       </c>
       <c r="H1513" t="n">
         <v>1200</v>
@@ -44275,7 +44275,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.56651592254639</v>
+        <v>1.56651604175568</v>
       </c>
       <c r="H1514" t="n">
         <v>3900</v>
@@ -44304,7 +44304,7 @@
         <v>1.75</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1515" t="n">
         <v>900</v>
@@ -44362,7 +44362,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1517" t="n">
         <v>10200</v>
@@ -44391,7 +44391,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1518" t="n">
-        <v>1.57554471492767</v>
+        <v>1.57554483413696</v>
       </c>
       <c r="H1518" t="n">
         <v>5400</v>
@@ -44478,7 +44478,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1521" t="n">
         <v>11100</v>
@@ -44507,7 +44507,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.54394376277924</v>
+        <v>1.54394352436066</v>
       </c>
       <c r="H1522" t="n">
         <v>4200</v>
@@ -44565,7 +44565,7 @@
         <v>1.75</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1524" t="n">
         <v>44400</v>
@@ -44594,7 +44594,7 @@
         <v>1.75</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1525" t="n">
         <v>0</v>
@@ -44623,7 +44623,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1526" t="n">
         <v>1800</v>
@@ -44652,7 +44652,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1527" t="n">
         <v>2700</v>
@@ -44681,7 +44681,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1528" t="n">
         <v>12600</v>
@@ -44710,7 +44710,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1529" t="n">
         <v>7500</v>
@@ -44739,7 +44739,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1530" t="n">
         <v>5100</v>
@@ -44768,7 +44768,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.59360265731812</v>
+        <v>1.59360253810883</v>
       </c>
       <c r="H1531" t="n">
         <v>0</v>
@@ -44797,7 +44797,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1532" t="n">
         <v>600</v>
@@ -44826,7 +44826,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.65680515766144</v>
+        <v>1.65680503845215</v>
       </c>
       <c r="H1533" t="n">
         <v>82800</v>
@@ -44855,7 +44855,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.71097850799561</v>
+        <v>1.71097838878632</v>
       </c>
       <c r="H1534" t="n">
         <v>162900</v>
@@ -44971,7 +44971,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1538" t="n">
-        <v>1.65680515766144</v>
+        <v>1.65680503845215</v>
       </c>
       <c r="H1538" t="n">
         <v>7500</v>
@@ -45058,7 +45058,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1541" t="n">
-        <v>1.64777612686157</v>
+        <v>1.64777624607086</v>
       </c>
       <c r="H1541" t="n">
         <v>2700</v>
@@ -45087,7 +45087,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1542" t="n">
         <v>12600</v>
@@ -45145,7 +45145,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1544" t="n">
         <v>6300</v>
@@ -45174,7 +45174,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1545" t="n">
         <v>600</v>
@@ -45203,7 +45203,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1546" t="n">
-        <v>1.62068939208984</v>
+        <v>1.62068927288055</v>
       </c>
       <c r="H1546" t="n">
         <v>3000</v>
@@ -45232,7 +45232,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.58908808231354</v>
+        <v>1.58908820152283</v>
       </c>
       <c r="H1547" t="n">
         <v>6300</v>
@@ -45261,7 +45261,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.58457374572754</v>
+        <v>1.58457362651825</v>
       </c>
       <c r="H1548" t="n">
         <v>4200</v>
@@ -45290,7 +45290,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1549" t="n">
         <v>10500</v>
@@ -45319,7 +45319,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1550" t="n">
-        <v>1.66583395004272</v>
+        <v>1.66583383083344</v>
       </c>
       <c r="H1550" t="n">
         <v>5100</v>
@@ -45348,7 +45348,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1551" t="n">
         <v>27000</v>
@@ -45377,7 +45377,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1552" t="n">
         <v>6300</v>
@@ -45406,7 +45406,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1553" t="n">
-        <v>1.70194959640503</v>
+        <v>1.70194947719574</v>
       </c>
       <c r="H1553" t="n">
         <v>44400</v>
@@ -45493,7 +45493,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1556" t="n">
-        <v>1.6793771982193</v>
+        <v>1.67937731742859</v>
       </c>
       <c r="H1556" t="n">
         <v>3300</v>
@@ -45609,7 +45609,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.70194959640503</v>
+        <v>1.70194947719574</v>
       </c>
       <c r="H1560" t="n">
         <v>2400</v>
@@ -45725,7 +45725,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.6748628616333</v>
+        <v>1.67486274242401</v>
       </c>
       <c r="H1564" t="n">
         <v>8700</v>
@@ -45754,7 +45754,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1565" t="n">
-        <v>1.66583395004272</v>
+        <v>1.66583383083344</v>
       </c>
       <c r="H1565" t="n">
         <v>8400</v>
@@ -45783,7 +45783,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1566" t="n">
-        <v>1.65680515766144</v>
+        <v>1.65680503845215</v>
       </c>
       <c r="H1566" t="n">
         <v>2700</v>
@@ -45812,7 +45812,7 @@
         <v>1.75</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.58005940914154</v>
+        <v>1.58005917072296</v>
       </c>
       <c r="H1567" t="n">
         <v>38700</v>
@@ -45957,7 +45957,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.64777612686157</v>
+        <v>1.64777624607086</v>
       </c>
       <c r="H1572" t="n">
         <v>13200</v>
@@ -45986,7 +45986,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1573" t="n">
-        <v>1.61166036128998</v>
+        <v>1.61166048049927</v>
       </c>
       <c r="H1573" t="n">
         <v>8700</v>
@@ -46218,7 +46218,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H1581" t="n">
         <v>8400</v>
@@ -46305,7 +46305,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H1584" t="n">
         <v>7200</v>
@@ -46363,7 +46363,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.60714590549469</v>
+        <v>1.60714602470398</v>
       </c>
       <c r="H1586" t="n">
         <v>7500</v>
@@ -46450,7 +46450,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.62068939208984</v>
+        <v>1.62068927288055</v>
       </c>
       <c r="H1589" t="n">
         <v>18900</v>
@@ -46508,7 +46508,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.62068939208984</v>
+        <v>1.62068927288055</v>
       </c>
       <c r="H1591" t="n">
         <v>11400</v>
@@ -46624,7 +46624,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.64326155185699</v>
+        <v>1.64326167106628</v>
       </c>
       <c r="H1595" t="n">
         <v>1500</v>
@@ -46740,7 +46740,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.84189772605896</v>
+        <v>1.84189760684967</v>
       </c>
       <c r="H1599" t="n">
         <v>343200</v>
@@ -46827,7 +46827,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.04956269264221</v>
+        <v>2.04956245422363</v>
       </c>
       <c r="H1602" t="n">
         <v>380700</v>
@@ -46856,7 +46856,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.12179398536682</v>
+        <v>2.12179350852966</v>
       </c>
       <c r="H1603" t="n">
         <v>147900</v>
@@ -46914,7 +46914,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.12179398536682</v>
+        <v>2.12179350852966</v>
       </c>
       <c r="H1605" t="n">
         <v>38100</v>
@@ -47030,7 +47030,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.04956269264221</v>
+        <v>2.04956245422363</v>
       </c>
       <c r="H1609" t="n">
         <v>36000</v>
@@ -47175,7 +47175,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.96830260753632</v>
+        <v>1.96830248832703</v>
       </c>
       <c r="H1614" t="n">
         <v>6300</v>
@@ -47233,7 +47233,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.01344680786133</v>
+        <v>2.01344704627991</v>
       </c>
       <c r="H1616" t="n">
         <v>28200</v>
@@ -47262,7 +47262,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.0224757194519</v>
+        <v>2.02247595787048</v>
       </c>
       <c r="H1617" t="n">
         <v>12600</v>
@@ -47291,7 +47291,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1618" t="n">
-        <v>2.0224757194519</v>
+        <v>2.02247595787048</v>
       </c>
       <c r="H1618" t="n">
         <v>73200</v>
@@ -47320,7 +47320,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.0224757194519</v>
+        <v>2.02247595787048</v>
       </c>
       <c r="H1619" t="n">
         <v>2100</v>
@@ -47349,7 +47349,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.01344680786133</v>
+        <v>2.01344704627991</v>
       </c>
       <c r="H1620" t="n">
         <v>57900</v>
@@ -47407,7 +47407,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.0224757194519</v>
+        <v>2.02247595787048</v>
       </c>
       <c r="H1622" t="n">
         <v>100200</v>
@@ -47465,7 +47465,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.01344680786133</v>
+        <v>2.01344704627991</v>
       </c>
       <c r="H1624" t="n">
         <v>25500</v>
@@ -47523,7 +47523,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.10373592376709</v>
+        <v>2.10373616218567</v>
       </c>
       <c r="H1626" t="n">
         <v>31800</v>
@@ -47668,7 +47668,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1631" t="n">
         <v>23100</v>
@@ -47697,7 +47697,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.5172746181488</v>
+        <v>2.51727485656738</v>
       </c>
       <c r="H1632" t="n">
         <v>41100</v>
@@ -47726,7 +47726,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.59213781356812</v>
+        <v>2.59213805198669</v>
       </c>
       <c r="H1633" t="n">
         <v>87600</v>
@@ -47871,7 +47871,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.13489580154419</v>
+        <v>3.13489603996277</v>
       </c>
       <c r="H1638" t="n">
         <v>112200</v>
@@ -47987,7 +47987,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1642" t="n">
         <v>209700</v>
@@ -48074,7 +48074,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.87287497520447</v>
+        <v>2.87287473678589</v>
       </c>
       <c r="H1645" t="n">
         <v>21300</v>
@@ -48190,7 +48190,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1649" t="n">
         <v>22800</v>
@@ -48248,7 +48248,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1651" t="n">
         <v>10500</v>
@@ -48306,7 +48306,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1653" t="n">
         <v>4800</v>
@@ -48364,7 +48364,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1655" t="n">
         <v>9000</v>
@@ -48451,7 +48451,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1658" t="n">
         <v>3900</v>
@@ -48567,7 +48567,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1662" t="n">
         <v>5400</v>
@@ -48625,7 +48625,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1664" t="n">
         <v>2400</v>
@@ -48654,7 +48654,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1665" t="n">
         <v>4500</v>
@@ -48683,7 +48683,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1666" t="n">
         <v>3900</v>
@@ -48712,7 +48712,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1667" t="n">
         <v>13800</v>
@@ -48741,7 +48741,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1668" t="n">
         <v>12600</v>
@@ -48915,7 +48915,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1674" t="n">
         <v>5700</v>
@@ -48973,7 +48973,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.81672763824463</v>
+        <v>2.81672739982605</v>
       </c>
       <c r="H1676" t="n">
         <v>5400</v>
@@ -49408,7 +49408,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1691" t="n">
         <v>3300</v>
@@ -49553,7 +49553,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1696" t="n">
         <v>7800</v>
@@ -49582,7 +49582,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1697" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1697" t="n">
         <v>16800</v>
@@ -49727,7 +49727,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.87287497520447</v>
+        <v>2.87287473678589</v>
       </c>
       <c r="H1702" t="n">
         <v>16500</v>
@@ -49843,7 +49843,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.92902255058289</v>
+        <v>2.92902231216431</v>
       </c>
       <c r="H1706" t="n">
         <v>13800</v>
@@ -49930,7 +49930,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1709" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1709" t="n">
         <v>300</v>
@@ -49959,7 +49959,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1710" t="n">
         <v>600</v>
@@ -49988,7 +49988,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.87287497520447</v>
+        <v>2.87287473678589</v>
       </c>
       <c r="H1711" t="n">
         <v>28800</v>
@@ -50075,7 +50075,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.91030645370483</v>
+        <v>2.91030621528625</v>
       </c>
       <c r="H1714" t="n">
         <v>5100</v>
@@ -50249,7 +50249,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.92902255058289</v>
+        <v>2.92902231216431</v>
       </c>
       <c r="H1720" t="n">
         <v>29100</v>
@@ -50336,7 +50336,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.92902255058289</v>
+        <v>2.92902231216431</v>
       </c>
       <c r="H1723" t="n">
         <v>26700</v>
@@ -50597,7 +50597,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1732" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1732" t="n">
         <v>48000</v>
@@ -50626,7 +50626,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1733" t="n">
         <v>64500</v>
@@ -50771,7 +50771,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1738" t="n">
-        <v>2.35819053649902</v>
+        <v>2.35819029808044</v>
       </c>
       <c r="H1738" t="n">
         <v>38400</v>
@@ -50800,7 +50800,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.35819053649902</v>
+        <v>2.35819029808044</v>
       </c>
       <c r="H1739" t="n">
         <v>18300</v>
@@ -50829,7 +50829,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.35819053649902</v>
+        <v>2.35819029808044</v>
       </c>
       <c r="H1740" t="n">
         <v>19200</v>
@@ -50887,7 +50887,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.36754846572876</v>
+        <v>2.36754822731018</v>
       </c>
       <c r="H1742" t="n">
         <v>5100</v>
@@ -50974,7 +50974,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H1745" t="n">
         <v>174000</v>
@@ -51177,7 +51177,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.47048544883728</v>
+        <v>2.4704852104187</v>
       </c>
       <c r="H1752" t="n">
         <v>7500</v>
@@ -51380,7 +51380,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1759" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1759" t="n">
         <v>600</v>
@@ -51409,7 +51409,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1760" t="n">
         <v>9000</v>
@@ -51438,7 +51438,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1761" t="n">
         <v>6600</v>
@@ -51641,7 +51641,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.41433787345886</v>
+        <v>2.41433763504028</v>
       </c>
       <c r="H1768" t="n">
         <v>30000</v>
@@ -51844,7 +51844,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.64828515052795</v>
+        <v>2.64828538894653</v>
       </c>
       <c r="H1775" t="n">
         <v>13200</v>
@@ -51960,7 +51960,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.65764331817627</v>
+        <v>2.65764307975769</v>
       </c>
       <c r="H1779" t="n">
         <v>22500</v>
@@ -51989,7 +51989,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1780" t="n">
         <v>26700</v>
@@ -52047,7 +52047,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1782" t="n">
         <v>14100</v>
@@ -52076,7 +52076,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1783" t="n">
         <v>46200</v>
@@ -52105,7 +52105,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.732506275177</v>
+        <v>2.73250651359558</v>
       </c>
       <c r="H1784" t="n">
         <v>15000</v>
@@ -52134,7 +52134,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.69507479667664</v>
+        <v>2.69507503509521</v>
       </c>
       <c r="H1785" t="n">
         <v>35700</v>
@@ -52163,7 +52163,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1786" t="n">
         <v>19800</v>
@@ -52192,7 +52192,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1787" t="n">
-        <v>2.69507479667664</v>
+        <v>2.69507503509521</v>
       </c>
       <c r="H1787" t="n">
         <v>7200</v>
@@ -52221,7 +52221,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1788" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1788" t="n">
         <v>4500</v>
@@ -52308,7 +52308,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1791" t="n">
         <v>3300</v>
@@ -52366,7 +52366,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1793" t="n">
         <v>7200</v>
@@ -52453,7 +52453,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1796" t="n">
         <v>7800</v>
@@ -52482,7 +52482,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1797" t="n">
         <v>600</v>
@@ -52511,7 +52511,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1798" t="n">
         <v>10500</v>
@@ -52569,7 +52569,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.75122213363647</v>
+        <v>2.75122237205505</v>
       </c>
       <c r="H1800" t="n">
         <v>34500</v>
@@ -52627,7 +52627,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1802" t="n">
         <v>8100</v>
@@ -52656,7 +52656,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1803" t="n">
         <v>0</v>
@@ -52685,7 +52685,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.76058030128479</v>
+        <v>2.76058006286621</v>
       </c>
       <c r="H1804" t="n">
         <v>2100</v>
@@ -52743,7 +52743,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1806" t="n">
         <v>13500</v>
@@ -52772,7 +52772,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.64828515052795</v>
+        <v>2.64828538894653</v>
       </c>
       <c r="H1807" t="n">
         <v>81600</v>
@@ -52801,7 +52801,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.64828515052795</v>
+        <v>2.64828538894653</v>
       </c>
       <c r="H1808" t="n">
         <v>0</v>
@@ -52830,7 +52830,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1809" t="n">
         <v>12000</v>
@@ -52859,7 +52859,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1810" t="n">
         <v>300</v>
@@ -53004,7 +53004,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1815" t="n">
         <v>5100</v>
@@ -53062,7 +53062,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1817" t="n">
         <v>4800</v>
@@ -53091,7 +53091,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1818" t="n">
         <v>4800</v>
@@ -53323,7 +53323,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.69507479667664</v>
+        <v>2.69507503509521</v>
       </c>
       <c r="H1826" t="n">
         <v>9900</v>
@@ -53352,7 +53352,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.70443272590637</v>
+        <v>2.70443296432495</v>
       </c>
       <c r="H1827" t="n">
         <v>6300</v>
@@ -53381,7 +53381,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.65764331817627</v>
+        <v>2.65764307975769</v>
       </c>
       <c r="H1828" t="n">
         <v>6300</v>
@@ -53816,7 +53816,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.19104337692261</v>
+        <v>3.19104361534119</v>
       </c>
       <c r="H1843" t="n">
         <v>98100</v>
@@ -53961,7 +53961,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.29398012161255</v>
+        <v>3.29398036003113</v>
       </c>
       <c r="H1848" t="n">
         <v>28200</v>
@@ -53990,7 +53990,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.29398012161255</v>
+        <v>3.29398036003113</v>
       </c>
       <c r="H1849" t="n">
         <v>10800</v>
@@ -54077,7 +54077,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.31269598007202</v>
+        <v>3.3126962184906</v>
       </c>
       <c r="H1852" t="n">
         <v>62700</v>
@@ -54106,7 +54106,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.31269598007202</v>
+        <v>3.3126962184906</v>
       </c>
       <c r="H1853" t="n">
         <v>15900</v>
@@ -54338,7 +54338,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.54664373397827</v>
+        <v>3.54664349555969</v>
       </c>
       <c r="H1861" t="n">
         <v>3600</v>
@@ -54599,7 +54599,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1870" t="n">
-        <v>3.65893840789795</v>
+        <v>3.65893864631653</v>
       </c>
       <c r="H1870" t="n">
         <v>20400</v>
@@ -54802,7 +54802,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1877" t="n">
-        <v>3.69636988639832</v>
+        <v>3.69637012481689</v>
       </c>
       <c r="H1877" t="n">
         <v>2100</v>
@@ -54860,7 +54860,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1879" t="n">
-        <v>3.75251746177673</v>
+        <v>3.75251770019531</v>
       </c>
       <c r="H1879" t="n">
         <v>9900</v>
@@ -54918,7 +54918,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1881" t="n">
-        <v>3.75251746177673</v>
+        <v>3.75251770019531</v>
       </c>
       <c r="H1881" t="n">
         <v>15900</v>
@@ -65654,6 +65654,35 @@
         <v>15900</v>
       </c>
       <c r="I2251" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2252" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2252" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="D2252" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="E2252" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="F2252" t="n">
+        <v>4.19000005722046</v>
+      </c>
+      <c r="G2252" t="n">
+        <v>4.19000005722046</v>
+      </c>
+      <c r="H2252" t="n">
+        <v>19500</v>
+      </c>
+      <c r="I2252" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -456,7 +456,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G3" t="n">
-        <v>3.66393184661865</v>
+        <v>3.66393160820007</v>
       </c>
       <c r="H3" t="n">
         <v>35400</v>
@@ -775,7 +775,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G14" t="n">
-        <v>3.64406800270081</v>
+        <v>3.64406776428223</v>
       </c>
       <c r="H14" t="n">
         <v>10200</v>
@@ -862,7 +862,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G17" t="n">
-        <v>3.59892344474792</v>
+        <v>3.5989236831665</v>
       </c>
       <c r="H17" t="n">
         <v>81900</v>
@@ -891,7 +891,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G18" t="n">
-        <v>3.65490245819092</v>
+        <v>3.6549026966095</v>
       </c>
       <c r="H18" t="n">
         <v>28200</v>
@@ -920,7 +920,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G19" t="n">
-        <v>3.65851449966431</v>
+        <v>3.65851426124573</v>
       </c>
       <c r="H19" t="n">
         <v>19500</v>
@@ -1007,7 +1007,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G22" t="n">
-        <v>3.62962198257446</v>
+        <v>3.62962174415588</v>
       </c>
       <c r="H22" t="n">
         <v>2700</v>
@@ -1094,7 +1094,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>3.56641960144043</v>
+        <v>3.56641936302185</v>
       </c>
       <c r="H25" t="n">
         <v>6600</v>
@@ -1123,7 +1123,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>3.62962198257446</v>
+        <v>3.62962174415588</v>
       </c>
       <c r="H26" t="n">
         <v>5100</v>
@@ -1239,7 +1239,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G30" t="n">
-        <v>3.57544827461243</v>
+        <v>3.57544851303101</v>
       </c>
       <c r="H30" t="n">
         <v>300</v>
@@ -1268,7 +1268,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>3.57544827461243</v>
+        <v>3.57544851303101</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G37" t="n">
-        <v>3.53030395507812</v>
+        <v>3.53030371665955</v>
       </c>
       <c r="H37" t="n">
         <v>10200</v>
@@ -1471,7 +1471,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>3.52127504348755</v>
+        <v>3.52127528190613</v>
       </c>
       <c r="H38" t="n">
         <v>3600</v>
@@ -1500,7 +1500,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G39" t="n">
-        <v>3.52127504348755</v>
+        <v>3.52127528190613</v>
       </c>
       <c r="H39" t="n">
         <v>600</v>
@@ -1529,7 +1529,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H40" t="n">
         <v>6300</v>
@@ -1558,7 +1558,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G41" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H42" t="n">
         <v>3900</v>
@@ -1616,7 +1616,7 @@
         <v>3.75</v>
       </c>
       <c r="G43" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H43" t="n">
         <v>300</v>
@@ -1645,7 +1645,7 @@
         <v>3.75</v>
       </c>
       <c r="G44" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H44" t="n">
         <v>300</v>
@@ -1790,7 +1790,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>3.57544827461243</v>
+        <v>3.57544851303101</v>
       </c>
       <c r="H49" t="n">
         <v>1800</v>
@@ -1848,7 +1848,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H51" t="n">
         <v>17400</v>
@@ -1906,7 +1906,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G53" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H53" t="n">
         <v>1500</v>
@@ -1935,7 +1935,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G54" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G55" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G56" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G57" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G58" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G60" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G61" t="n">
-        <v>3.46710133552551</v>
+        <v>3.46710109710693</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H62" t="n">
         <v>1200</v>
@@ -2196,7 +2196,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>3.33166766166687</v>
+        <v>3.33166790008545</v>
       </c>
       <c r="H63" t="n">
         <v>600</v>
@@ -2225,7 +2225,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G64" t="n">
-        <v>3.44001483917236</v>
+        <v>3.44001460075378</v>
       </c>
       <c r="H64" t="n">
         <v>900</v>
@@ -2254,7 +2254,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G65" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H65" t="n">
         <v>1500</v>
@@ -2283,7 +2283,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G66" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G67" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G68" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G69" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G70" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G71" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H85" t="n">
         <v>7500</v>
@@ -2863,7 +2863,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H86" t="n">
         <v>2400</v>
@@ -2892,7 +2892,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G87" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H87" t="n">
         <v>3300</v>
@@ -2921,7 +2921,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G88" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G89" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>3.34972548484802</v>
+        <v>3.3497257232666</v>
       </c>
       <c r="H90" t="n">
         <v>900</v>
@@ -3008,7 +3008,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.34972548484802</v>
+        <v>3.3497257232666</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G92" t="n">
-        <v>3.34972548484802</v>
+        <v>3.3497257232666</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>3.34972548484802</v>
+        <v>3.3497257232666</v>
       </c>
       <c r="H99" t="n">
         <v>3600</v>
@@ -3269,7 +3269,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>3.34972548484802</v>
+        <v>3.3497257232666</v>
       </c>
       <c r="H100" t="n">
         <v>300</v>
@@ -3298,7 +3298,7 @@
         <v>3.75</v>
       </c>
       <c r="G101" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H101" t="n">
         <v>2400</v>
@@ -3327,7 +3327,7 @@
         <v>3.75</v>
       </c>
       <c r="G102" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>3.75</v>
       </c>
       <c r="G103" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>3.75</v>
       </c>
       <c r="G104" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G107" t="n">
-        <v>3.22332096099854</v>
+        <v>3.22332072257996</v>
       </c>
       <c r="H107" t="n">
         <v>6300</v>
@@ -3559,7 +3559,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H110" t="n">
         <v>8100</v>
@@ -3588,7 +3588,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G111" t="n">
-        <v>3.21429204940796</v>
+        <v>3.21429181098938</v>
       </c>
       <c r="H111" t="n">
         <v>30300</v>
@@ -3704,7 +3704,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>3.04274249076843</v>
+        <v>3.04274272918701</v>
       </c>
       <c r="H115" t="n">
         <v>600</v>
@@ -3733,7 +3733,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>3.04274249076843</v>
+        <v>3.04274272918701</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G119" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H119" t="n">
         <v>30900</v>
@@ -3849,7 +3849,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G120" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H120" t="n">
         <v>2100</v>
@@ -3878,7 +3878,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G121" t="n">
-        <v>3.13303208351135</v>
+        <v>3.13303184509277</v>
       </c>
       <c r="H121" t="n">
         <v>30600</v>
@@ -3965,7 +3965,7 @@
         <v>3.75</v>
       </c>
       <c r="G124" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H124" t="n">
         <v>5700</v>
@@ -3994,7 +3994,7 @@
         <v>3.75</v>
       </c>
       <c r="G125" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H125" t="n">
         <v>11100</v>
@@ -4023,7 +4023,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H126" t="n">
         <v>1800</v>
@@ -4052,7 +4052,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G127" t="n">
-        <v>3.45807266235352</v>
+        <v>3.45807242393494</v>
       </c>
       <c r="H127" t="n">
         <v>30600</v>
@@ -4168,7 +4168,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>3.42195677757263</v>
+        <v>3.42195701599121</v>
       </c>
       <c r="H131" t="n">
         <v>1500</v>
@@ -4197,7 +4197,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>3.43098568916321</v>
+        <v>3.43098592758179</v>
       </c>
       <c r="H132" t="n">
         <v>2100</v>
@@ -4226,7 +4226,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G133" t="n">
-        <v>3.33166766166687</v>
+        <v>3.33166790008545</v>
       </c>
       <c r="H133" t="n">
         <v>300</v>
@@ -4255,7 +4255,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>3.33166766166687</v>
+        <v>3.33166790008545</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G135" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H135" t="n">
         <v>300</v>
@@ -4313,7 +4313,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G138" t="n">
-        <v>3.28652334213257</v>
+        <v>3.28652310371399</v>
       </c>
       <c r="H138" t="n">
         <v>900</v>
@@ -4429,7 +4429,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H140" t="n">
         <v>11700</v>
@@ -4458,7 +4458,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G141" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H141" t="n">
         <v>2100</v>
@@ -4487,7 +4487,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G142" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G143" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G145" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G146" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G148" t="n">
-        <v>3.26846528053284</v>
+        <v>3.26846551895142</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G149" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H149" t="n">
         <v>3900</v>
@@ -4719,7 +4719,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G151" t="n">
-        <v>3.29555249214172</v>
+        <v>3.29555225372314</v>
       </c>
       <c r="H151" t="n">
         <v>900</v>
@@ -4777,7 +4777,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G152" t="n">
-        <v>3.37681245803833</v>
+        <v>3.37681221961975</v>
       </c>
       <c r="H152" t="n">
         <v>300</v>
@@ -4806,7 +4806,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G153" t="n">
-        <v>3.37681245803833</v>
+        <v>3.37681221961975</v>
       </c>
       <c r="H153" t="n">
         <v>300</v>
@@ -4835,7 +4835,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G154" t="n">
-        <v>3.37681245803833</v>
+        <v>3.37681221961975</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G155" t="n">
-        <v>3.37681245803833</v>
+        <v>3.37681221961975</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G156" t="n">
-        <v>3.37681245803833</v>
+        <v>3.37681221961975</v>
       </c>
       <c r="H156" t="n">
         <v>300</v>
@@ -5473,7 +5473,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G176" t="n">
-        <v>3.24137854576111</v>
+        <v>3.24137878417969</v>
       </c>
       <c r="H176" t="n">
         <v>2400</v>
@@ -5531,7 +5531,7 @@
         <v>3.75</v>
       </c>
       <c r="G178" t="n">
-        <v>3.38584136962891</v>
+        <v>3.38584113121033</v>
       </c>
       <c r="H178" t="n">
         <v>1500</v>
@@ -5763,7 +5763,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G186" t="n">
-        <v>3.21429204940796</v>
+        <v>3.21429181098938</v>
       </c>
       <c r="H186" t="n">
         <v>60000</v>
@@ -5821,7 +5821,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G188" t="n">
-        <v>3.21429204940796</v>
+        <v>3.21429181098938</v>
       </c>
       <c r="H188" t="n">
         <v>600</v>
@@ -5850,7 +5850,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>3.21429204940796</v>
+        <v>3.21429181098938</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G190" t="n">
-        <v>3.21429204940796</v>
+        <v>3.21429181098938</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>3.5</v>
       </c>
       <c r="G191" t="n">
-        <v>3.16011834144592</v>
+        <v>3.1601185798645</v>
       </c>
       <c r="H191" t="n">
         <v>300</v>
@@ -5937,7 +5937,7 @@
         <v>3.5</v>
       </c>
       <c r="G192" t="n">
-        <v>3.16011834144592</v>
+        <v>3.1601185798645</v>
       </c>
       <c r="H192" t="n">
         <v>2400</v>
@@ -6401,7 +6401,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G208" t="n">
-        <v>3.05177187919617</v>
+        <v>3.05177140235901</v>
       </c>
       <c r="H208" t="n">
         <v>6600</v>
@@ -6430,7 +6430,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H209" t="n">
         <v>13500</v>
@@ -6459,7 +6459,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G210" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G211" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G212" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G213" t="n">
-        <v>3.10594511032104</v>
+        <v>3.10594534873962</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G215" t="n">
-        <v>2.87119364738464</v>
+        <v>2.87119340896606</v>
       </c>
       <c r="H215" t="n">
         <v>2100</v>
@@ -6633,7 +6633,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G216" t="n">
-        <v>2.87119364738464</v>
+        <v>2.87119340896606</v>
       </c>
       <c r="H216" t="n">
         <v>21000</v>
@@ -6662,7 +6662,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G217" t="n">
-        <v>2.87119364738464</v>
+        <v>2.87119340896606</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G220" t="n">
-        <v>2.66352844238281</v>
+        <v>2.66352868080139</v>
       </c>
       <c r="H220" t="n">
         <v>2100</v>
@@ -7271,7 +7271,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489262580872</v>
       </c>
       <c r="H238" t="n">
         <v>11100</v>
@@ -7300,7 +7300,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489262580872</v>
       </c>
       <c r="H239" t="n">
         <v>1200</v>
@@ -7329,7 +7329,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489262580872</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G241" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489262580872</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>2.46489238739014</v>
+        <v>2.46489262580872</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G250" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H250" t="n">
         <v>600</v>
@@ -7648,7 +7648,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G252" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G253" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>2.41071891784668</v>
+        <v>2.41071915626526</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>2.32945895195007</v>
+        <v>2.32945871353149</v>
       </c>
       <c r="H256" t="n">
         <v>1500</v>
@@ -7822,7 +7822,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>2.32945895195007</v>
+        <v>2.32945871353149</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>2.5</v>
       </c>
       <c r="G259" t="n">
-        <v>2.25722765922546</v>
+        <v>2.25722742080688</v>
       </c>
       <c r="H259" t="n">
         <v>9900</v>
@@ -7938,7 +7938,7 @@
         <v>2.5</v>
       </c>
       <c r="G261" t="n">
-        <v>2.25722765922546</v>
+        <v>2.25722742080688</v>
       </c>
       <c r="H261" t="n">
         <v>2400</v>
@@ -7967,7 +7967,7 @@
         <v>2.5</v>
       </c>
       <c r="G262" t="n">
-        <v>2.25722765922546</v>
+        <v>2.25722742080688</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G263" t="n">
-        <v>2.32042980194092</v>
+        <v>2.32042956352234</v>
       </c>
       <c r="H263" t="n">
         <v>2100</v>
@@ -8025,7 +8025,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G264" t="n">
-        <v>2.32042980194092</v>
+        <v>2.32042956352234</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G265" t="n">
-        <v>2.32042980194092</v>
+        <v>2.32042956352234</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.32042980194092</v>
+        <v>2.32042956352234</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G268" t="n">
-        <v>2.47392129898071</v>
+        <v>2.47392153739929</v>
       </c>
       <c r="H268" t="n">
         <v>1500</v>
@@ -8170,7 +8170,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G269" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H269" t="n">
         <v>2400</v>
@@ -8344,7 +8344,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G275" t="n">
-        <v>2.30237197875977</v>
+        <v>2.30237221717834</v>
       </c>
       <c r="H275" t="n">
         <v>2100</v>
@@ -8373,7 +8373,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G276" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H276" t="n">
         <v>1200</v>
@@ -8402,7 +8402,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G277" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H277" t="n">
         <v>3600</v>
@@ -8431,7 +8431,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G278" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H278" t="n">
         <v>3600</v>
@@ -8460,7 +8460,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H279" t="n">
         <v>4800</v>
@@ -8518,7 +8518,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G281" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H281" t="n">
         <v>21000</v>
@@ -8547,7 +8547,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G282" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H282" t="n">
         <v>900</v>
@@ -8576,7 +8576,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G283" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H283" t="n">
         <v>1500</v>
@@ -8605,7 +8605,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G284" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G285" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H285" t="n">
         <v>2100</v>
@@ -8663,7 +8663,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G286" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G287" t="n">
-        <v>2.212082862854</v>
+        <v>2.21208310127258</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>2.15790963172913</v>
+        <v>2.15790939331055</v>
       </c>
       <c r="H290" t="n">
         <v>20700</v>
@@ -8808,7 +8808,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>2.12179350852966</v>
+        <v>2.12179398536682</v>
       </c>
       <c r="H291" t="n">
         <v>2400</v>
@@ -8837,7 +8837,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G292" t="n">
-        <v>2.05859136581421</v>
+        <v>2.05859160423279</v>
       </c>
       <c r="H292" t="n">
         <v>18900</v>
@@ -9011,7 +9011,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G298" t="n">
-        <v>1.93218684196472</v>
+        <v>1.93218672275543</v>
       </c>
       <c r="H298" t="n">
         <v>1500</v>
@@ -9040,7 +9040,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G299" t="n">
-        <v>1.94121587276459</v>
+        <v>1.9412157535553</v>
       </c>
       <c r="H299" t="n">
         <v>1200</v>
@@ -9069,7 +9069,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G300" t="n">
-        <v>1.87801325321198</v>
+        <v>1.87801313400269</v>
       </c>
       <c r="H300" t="n">
         <v>7200</v>
@@ -9098,7 +9098,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G301" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H301" t="n">
         <v>35700</v>
@@ -9127,7 +9127,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>1.97733116149902</v>
+        <v>1.9773313999176</v>
       </c>
       <c r="H302" t="n">
         <v>4200</v>
@@ -9156,7 +9156,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G303" t="n">
-        <v>1.97733116149902</v>
+        <v>1.9773313999176</v>
       </c>
       <c r="H303" t="n">
         <v>300</v>
@@ -9185,7 +9185,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G304" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H304" t="n">
         <v>600</v>
@@ -9243,7 +9243,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G306" t="n">
-        <v>2.04053354263306</v>
+        <v>2.04053378105164</v>
       </c>
       <c r="H306" t="n">
         <v>3600</v>
@@ -9359,7 +9359,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>2.04053354263306</v>
+        <v>2.04053378105164</v>
       </c>
       <c r="H310" t="n">
         <v>900</v>
@@ -9388,7 +9388,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G311" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H311" t="n">
         <v>1200</v>
@@ -9417,7 +9417,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G312" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G313" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H315" t="n">
         <v>300</v>
@@ -9533,7 +9533,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G316" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G318" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H318" t="n">
         <v>600</v>
@@ -9620,7 +9620,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G319" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G320" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G321" t="n">
-        <v>1.95024478435516</v>
+        <v>1.95024466514587</v>
       </c>
       <c r="H321" t="n">
         <v>600</v>
@@ -9707,7 +9707,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G322" t="n">
-        <v>1.95024478435516</v>
+        <v>1.95024466514587</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G323" t="n">
-        <v>1.95024478435516</v>
+        <v>1.95024466514587</v>
       </c>
       <c r="H323" t="n">
         <v>600</v>
@@ -9765,7 +9765,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G324" t="n">
-        <v>1.95024478435516</v>
+        <v>1.95024466514587</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>1.92315793037415</v>
+        <v>1.92315804958344</v>
       </c>
       <c r="H325" t="n">
         <v>600</v>
@@ -9823,7 +9823,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>2.04956245422363</v>
+        <v>2.04956269264221</v>
       </c>
       <c r="H326" t="n">
         <v>5700</v>
@@ -9881,7 +9881,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G328" t="n">
-        <v>1.91412878036499</v>
+        <v>1.91412889957428</v>
       </c>
       <c r="H328" t="n">
         <v>51000</v>
@@ -9939,7 +9939,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>1.84189760684967</v>
+        <v>1.84189772605896</v>
       </c>
       <c r="H330" t="n">
         <v>29100</v>
@@ -10171,7 +10171,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G338" t="n">
-        <v>2.04053354263306</v>
+        <v>2.04053378105164</v>
       </c>
       <c r="H338" t="n">
         <v>18000</v>
@@ -10200,7 +10200,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G339" t="n">
-        <v>2.05859136581421</v>
+        <v>2.05859160423279</v>
       </c>
       <c r="H339" t="n">
         <v>54900</v>
@@ -10229,7 +10229,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G340" t="n">
-        <v>2.00441813468933</v>
+        <v>2.00441789627075</v>
       </c>
       <c r="H340" t="n">
         <v>300</v>
@@ -10258,7 +10258,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G341" t="n">
-        <v>2.04053354263306</v>
+        <v>2.04053378105164</v>
       </c>
       <c r="H341" t="n">
         <v>1200</v>
@@ -10287,7 +10287,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G342" t="n">
-        <v>2.00441813468933</v>
+        <v>2.00441789627075</v>
       </c>
       <c r="H342" t="n">
         <v>2400</v>
@@ -10345,7 +10345,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G344" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H344" t="n">
         <v>13200</v>
@@ -10374,7 +10374,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G345" t="n">
-        <v>1.93218684196472</v>
+        <v>1.93218672275543</v>
       </c>
       <c r="H345" t="n">
         <v>5700</v>
@@ -10519,7 +10519,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G350" t="n">
-        <v>1.87801325321198</v>
+        <v>1.87801313400269</v>
       </c>
       <c r="H350" t="n">
         <v>2400</v>
@@ -10925,7 +10925,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G364" t="n">
-        <v>1.73355066776276</v>
+        <v>1.73355054855347</v>
       </c>
       <c r="H364" t="n">
         <v>2400</v>
@@ -11099,7 +11099,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G370" t="n">
-        <v>1.68840622901917</v>
+        <v>1.68840610980988</v>
       </c>
       <c r="H370" t="n">
         <v>2400</v>
@@ -11128,7 +11128,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G371" t="n">
-        <v>1.68840622901917</v>
+        <v>1.68840610980988</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>1.78772413730621</v>
+        <v>1.7877242565155</v>
       </c>
       <c r="H381" t="n">
         <v>98700</v>
@@ -11447,7 +11447,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G382" t="n">
-        <v>1.7154928445816</v>
+        <v>1.71549296379089</v>
       </c>
       <c r="H382" t="n">
         <v>9600</v>
@@ -11476,7 +11476,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G383" t="n">
-        <v>1.7154928445816</v>
+        <v>1.71549296379089</v>
       </c>
       <c r="H383" t="n">
         <v>23400</v>
@@ -11563,7 +11563,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G386" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H386" t="n">
         <v>5100</v>
@@ -11592,7 +11592,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G387" t="n">
-        <v>1.68840622901917</v>
+        <v>1.68840610980988</v>
       </c>
       <c r="H387" t="n">
         <v>6300</v>
@@ -11708,7 +11708,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G391" t="n">
-        <v>1.7154928445816</v>
+        <v>1.71549296379089</v>
       </c>
       <c r="H391" t="n">
         <v>4800</v>
@@ -11795,7 +11795,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G394" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H394" t="n">
         <v>5100</v>
@@ -11824,7 +11824,7 @@
         <v>1.75</v>
       </c>
       <c r="G395" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H395" t="n">
         <v>3900</v>
@@ -11911,7 +11911,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H398" t="n">
         <v>1200</v>
@@ -12085,7 +12085,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H404" t="n">
         <v>80700</v>
@@ -12317,7 +12317,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H412" t="n">
         <v>900</v>
@@ -12578,7 +12578,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G421" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H421" t="n">
         <v>1500</v>
@@ -12607,7 +12607,7 @@
         <v>1.5</v>
       </c>
       <c r="G422" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H422" t="n">
         <v>300</v>
@@ -12636,7 +12636,7 @@
         <v>1.5</v>
       </c>
       <c r="G423" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H423" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>1.5</v>
       </c>
       <c r="G424" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H434" t="n">
         <v>25500</v>
@@ -13216,7 +13216,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G443" t="n">
-        <v>1.22793173789978</v>
+        <v>1.22793185710907</v>
       </c>
       <c r="H443" t="n">
         <v>6000</v>
@@ -13390,7 +13390,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G449" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H449" t="n">
         <v>71700</v>
@@ -13448,7 +13448,7 @@
         <v>1.75</v>
       </c>
       <c r="G451" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H451" t="n">
         <v>17400</v>
@@ -13477,7 +13477,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H452" t="n">
         <v>5100</v>
@@ -13622,7 +13622,7 @@
         <v>1.5</v>
       </c>
       <c r="G457" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H457" t="n">
         <v>3000</v>
@@ -13651,7 +13651,7 @@
         <v>1.5</v>
       </c>
       <c r="G458" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H458" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>1.5</v>
       </c>
       <c r="G459" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H459" t="n">
         <v>9300</v>
@@ -13709,7 +13709,7 @@
         <v>1.5</v>
       </c>
       <c r="G460" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H460" t="n">
         <v>300</v>
@@ -13738,7 +13738,7 @@
         <v>1.5</v>
       </c>
       <c r="G461" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>1.5</v>
       </c>
       <c r="G462" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>1.5</v>
       </c>
       <c r="G463" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H463" t="n">
         <v>4200</v>
@@ -13854,7 +13854,7 @@
         <v>1.5</v>
       </c>
       <c r="G465" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H465" t="n">
         <v>20100</v>
@@ -13883,7 +13883,7 @@
         <v>1.5</v>
       </c>
       <c r="G466" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H466" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H475" t="n">
         <v>49500</v>
@@ -14173,7 +14173,7 @@
         <v>1.75</v>
       </c>
       <c r="G476" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H476" t="n">
         <v>21600</v>
@@ -14202,7 +14202,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G477" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H477" t="n">
         <v>18600</v>
@@ -14231,7 +14231,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G478" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H478" t="n">
         <v>31500</v>
@@ -14260,7 +14260,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H479" t="n">
         <v>39600</v>
@@ -14318,7 +14318,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G481" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H481" t="n">
         <v>30900</v>
@@ -14463,7 +14463,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G486" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H486" t="n">
         <v>16800</v>
@@ -14521,7 +14521,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G488" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H488" t="n">
         <v>6000</v>
@@ -14695,7 +14695,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G494" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H494" t="n">
         <v>7200</v>
@@ -14840,7 +14840,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G499" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H499" t="n">
         <v>42000</v>
@@ -14898,7 +14898,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G501" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H501" t="n">
         <v>9900</v>
@@ -14927,7 +14927,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G502" t="n">
-        <v>1.63423264026642</v>
+        <v>1.63423275947571</v>
       </c>
       <c r="H502" t="n">
         <v>19200</v>
@@ -14956,7 +14956,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G503" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H503" t="n">
         <v>44700</v>
@@ -14985,7 +14985,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G504" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H504" t="n">
         <v>5400</v>
@@ -15130,7 +15130,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G509" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H509" t="n">
         <v>3600</v>
@@ -15217,7 +15217,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H512" t="n">
         <v>36000</v>
@@ -15304,7 +15304,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G515" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H515" t="n">
         <v>7500</v>
@@ -15420,7 +15420,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G519" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H519" t="n">
         <v>4800</v>
@@ -15478,7 +15478,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G521" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H521" t="n">
         <v>600</v>
@@ -15507,7 +15507,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H522" t="n">
         <v>2400</v>
@@ -15536,7 +15536,7 @@
         <v>1.75</v>
       </c>
       <c r="G523" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H523" t="n">
         <v>9900</v>
@@ -15594,7 +15594,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G525" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H525" t="n">
         <v>37500</v>
@@ -15623,7 +15623,7 @@
         <v>1.75</v>
       </c>
       <c r="G526" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H526" t="n">
         <v>92100</v>
@@ -15826,7 +15826,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G533" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H533" t="n">
         <v>5400</v>
@@ -15855,7 +15855,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G534" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H534" t="n">
         <v>72000</v>
@@ -15884,7 +15884,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G535" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H535" t="n">
         <v>105300</v>
@@ -15942,7 +15942,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G537" t="n">
-        <v>1.29113411903381</v>
+        <v>1.29113399982452</v>
       </c>
       <c r="H537" t="n">
         <v>8700</v>
@@ -16116,7 +16116,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G543" t="n">
-        <v>1.29113411903381</v>
+        <v>1.29113399982452</v>
       </c>
       <c r="H543" t="n">
         <v>45600</v>
@@ -16261,7 +16261,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G548" t="n">
-        <v>1.22793173789978</v>
+        <v>1.22793185710907</v>
       </c>
       <c r="H548" t="n">
         <v>21900</v>
@@ -16290,7 +16290,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G549" t="n">
-        <v>1.19181609153748</v>
+        <v>1.19181621074677</v>
       </c>
       <c r="H549" t="n">
         <v>45900</v>
@@ -16319,7 +16319,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G550" t="n">
-        <v>1.19181609153748</v>
+        <v>1.19181621074677</v>
       </c>
       <c r="H550" t="n">
         <v>19800</v>
@@ -16435,7 +16435,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G554" t="n">
-        <v>1.08346927165985</v>
+        <v>1.08346915245056</v>
       </c>
       <c r="H554" t="n">
         <v>29100</v>
@@ -16493,7 +16493,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G556" t="n">
-        <v>1.02026677131653</v>
+        <v>1.02026689052582</v>
       </c>
       <c r="H556" t="n">
         <v>72900</v>
@@ -16522,7 +16522,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G557" t="n">
-        <v>1.02026677131653</v>
+        <v>1.02026689052582</v>
       </c>
       <c r="H557" t="n">
         <v>37800</v>
@@ -16551,7 +16551,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G558" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H558" t="n">
         <v>19500</v>
@@ -16638,7 +16638,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G561" t="n">
-        <v>0.984151244163513</v>
+        <v>0.984151303768158</v>
       </c>
       <c r="H561" t="n">
         <v>8100</v>
@@ -16725,7 +16725,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H564" t="n">
         <v>15300</v>
@@ -16754,7 +16754,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G565" t="n">
-        <v>0.939006626605988</v>
+        <v>0.939006567001343</v>
       </c>
       <c r="H565" t="n">
         <v>2400</v>
@@ -16841,7 +16841,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G568" t="n">
-        <v>0.80357301235199</v>
+        <v>0.803572952747345</v>
       </c>
       <c r="H568" t="n">
         <v>9600</v>
@@ -16986,7 +16986,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G573" t="n">
-        <v>0.866775333881378</v>
+        <v>0.866775274276733</v>
       </c>
       <c r="H573" t="n">
         <v>10800</v>
@@ -17131,7 +17131,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G578" t="n">
-        <v>0.975122392177582</v>
+        <v>0.975122332572937</v>
       </c>
       <c r="H578" t="n">
         <v>14700</v>
@@ -17189,7 +17189,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G580" t="n">
-        <v>1.00220906734467</v>
+        <v>1.00220894813538</v>
       </c>
       <c r="H580" t="n">
         <v>1500</v>
@@ -17247,7 +17247,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G582" t="n">
-        <v>1.02478122711182</v>
+        <v>1.02478134632111</v>
       </c>
       <c r="H582" t="n">
         <v>1200</v>
@@ -17334,7 +17334,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G585" t="n">
-        <v>1.02478122711182</v>
+        <v>1.02478134632111</v>
       </c>
       <c r="H585" t="n">
         <v>15600</v>
@@ -17363,7 +17363,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G586" t="n">
-        <v>1.02478122711182</v>
+        <v>1.02478134632111</v>
       </c>
       <c r="H586" t="n">
         <v>9600</v>
@@ -17450,7 +17450,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G589" t="n">
-        <v>1.00220906734467</v>
+        <v>1.00220894813538</v>
       </c>
       <c r="H589" t="n">
         <v>10800</v>
@@ -17479,7 +17479,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G590" t="n">
-        <v>0.984151244163513</v>
+        <v>0.984151303768158</v>
       </c>
       <c r="H590" t="n">
         <v>18000</v>
@@ -17508,7 +17508,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G591" t="n">
-        <v>0.952549993991852</v>
+        <v>0.952549934387207</v>
       </c>
       <c r="H591" t="n">
         <v>102000</v>
@@ -17537,7 +17537,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G592" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H592" t="n">
         <v>4200</v>
@@ -17566,7 +17566,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G593" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H593" t="n">
         <v>12900</v>
@@ -17595,7 +17595,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G594" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H594" t="n">
         <v>1500</v>
@@ -17624,7 +17624,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H595" t="n">
         <v>15900</v>
@@ -17653,7 +17653,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>0.939006626605988</v>
+        <v>0.939006567001343</v>
       </c>
       <c r="H596" t="n">
         <v>39300</v>
@@ -17682,7 +17682,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G597" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H597" t="n">
         <v>15000</v>
@@ -17711,7 +17711,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G598" t="n">
-        <v>0.952549993991852</v>
+        <v>0.952549934387207</v>
       </c>
       <c r="H598" t="n">
         <v>21600</v>
@@ -17740,7 +17740,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G599" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H599" t="n">
         <v>2700</v>
@@ -17798,7 +17798,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G601" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H601" t="n">
         <v>17100</v>
@@ -17827,7 +17827,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G602" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H602" t="n">
         <v>13200</v>
@@ -17856,7 +17856,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G603" t="n">
-        <v>0.939006626605988</v>
+        <v>0.939006567001343</v>
       </c>
       <c r="H603" t="n">
         <v>9600</v>
@@ -17914,7 +17914,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G605" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H605" t="n">
         <v>23400</v>
@@ -17972,7 +17972,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G607" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H607" t="n">
         <v>7800</v>
@@ -18030,7 +18030,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G609" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H609" t="n">
         <v>38400</v>
@@ -18059,7 +18059,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H610" t="n">
         <v>52200</v>
@@ -18088,7 +18088,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G611" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H611" t="n">
         <v>195300</v>
@@ -18262,7 +18262,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G617" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H617" t="n">
         <v>13200</v>
@@ -18320,7 +18320,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G619" t="n">
-        <v>0.893862068653107</v>
+        <v>0.893862128257751</v>
       </c>
       <c r="H619" t="n">
         <v>41100</v>
@@ -18552,7 +18552,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G627" t="n">
-        <v>1.04283916950226</v>
+        <v>1.04283905029297</v>
       </c>
       <c r="H627" t="n">
         <v>258300</v>
@@ -18581,7 +18581,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G628" t="n">
-        <v>0.988665580749512</v>
+        <v>0.988665699958801</v>
       </c>
       <c r="H628" t="n">
         <v>45600</v>
@@ -18610,7 +18610,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G629" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H629" t="n">
         <v>36000</v>
@@ -18639,7 +18639,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G630" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H630" t="n">
         <v>20400</v>
@@ -18668,7 +18668,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>0.997694611549377</v>
+        <v>0.997694551944733</v>
       </c>
       <c r="H631" t="n">
         <v>19200</v>
@@ -18755,7 +18755,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G634" t="n">
-        <v>1.02478122711182</v>
+        <v>1.02478134632111</v>
       </c>
       <c r="H634" t="n">
         <v>5700</v>
@@ -18784,7 +18784,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G635" t="n">
-        <v>1.0292956829071</v>
+        <v>1.02929580211639</v>
       </c>
       <c r="H635" t="n">
         <v>5700</v>
@@ -18842,7 +18842,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G637" t="n">
-        <v>0.984151244163513</v>
+        <v>0.984151303768158</v>
       </c>
       <c r="H637" t="n">
         <v>3900</v>
@@ -18900,7 +18900,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H639" t="n">
         <v>2400</v>
@@ -18929,7 +18929,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G640" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H640" t="n">
         <v>18600</v>
@@ -19016,7 +19016,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G643" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H643" t="n">
         <v>9000</v>
@@ -19045,7 +19045,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G644" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H644" t="n">
         <v>10800</v>
@@ -19074,7 +19074,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G645" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H645" t="n">
         <v>9000</v>
@@ -19103,7 +19103,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>0.939006626605988</v>
+        <v>0.939006567001343</v>
       </c>
       <c r="H646" t="n">
         <v>7200</v>
@@ -19132,7 +19132,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>0.939006626605988</v>
+        <v>0.939006567001343</v>
       </c>
       <c r="H647" t="n">
         <v>1500</v>
@@ -19190,7 +19190,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G649" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H649" t="n">
         <v>3000</v>
@@ -19248,7 +19248,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G651" t="n">
-        <v>0.975122392177582</v>
+        <v>0.975122332572937</v>
       </c>
       <c r="H651" t="n">
         <v>2700</v>
@@ -19335,7 +19335,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G654" t="n">
-        <v>0.970607936382294</v>
+        <v>0.970607876777649</v>
       </c>
       <c r="H654" t="n">
         <v>7500</v>
@@ -19364,7 +19364,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G655" t="n">
-        <v>1.00220906734467</v>
+        <v>1.00220894813538</v>
       </c>
       <c r="H655" t="n">
         <v>2400</v>
@@ -19422,7 +19422,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G657" t="n">
-        <v>0.984151244163513</v>
+        <v>0.984151303768158</v>
       </c>
       <c r="H657" t="n">
         <v>5400</v>
@@ -19480,7 +19480,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G659" t="n">
-        <v>0.970607936382294</v>
+        <v>0.970607876777649</v>
       </c>
       <c r="H659" t="n">
         <v>12300</v>
@@ -19509,7 +19509,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G660" t="n">
-        <v>0.970607936382294</v>
+        <v>0.970607876777649</v>
       </c>
       <c r="H660" t="n">
         <v>0</v>
@@ -19567,7 +19567,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G662" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H662" t="n">
         <v>300</v>
@@ -19625,7 +19625,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G664" t="n">
-        <v>0.952549993991852</v>
+        <v>0.952549934387207</v>
       </c>
       <c r="H664" t="n">
         <v>300</v>
@@ -19654,7 +19654,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G665" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H665" t="n">
         <v>1800</v>
@@ -19712,7 +19712,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G667" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H667" t="n">
         <v>3900</v>
@@ -19770,7 +19770,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G669" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H669" t="n">
         <v>300</v>
@@ -19799,7 +19799,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G670" t="n">
-        <v>0.970607936382294</v>
+        <v>0.970607876777649</v>
       </c>
       <c r="H670" t="n">
         <v>2100</v>
@@ -19857,7 +19857,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G672" t="n">
-        <v>0.961578965187073</v>
+        <v>0.961579024791718</v>
       </c>
       <c r="H672" t="n">
         <v>300</v>
@@ -19886,7 +19886,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G673" t="n">
-        <v>0.988665580749512</v>
+        <v>0.988665699958801</v>
       </c>
       <c r="H673" t="n">
         <v>3300</v>
@@ -19915,7 +19915,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G674" t="n">
-        <v>0.988665580749512</v>
+        <v>0.988665699958801</v>
       </c>
       <c r="H674" t="n">
         <v>300</v>
@@ -20002,7 +20002,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G677" t="n">
-        <v>0.975122392177582</v>
+        <v>0.975122332572937</v>
       </c>
       <c r="H677" t="n">
         <v>10500</v>
@@ -20031,7 +20031,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G678" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H678" t="n">
         <v>9300</v>
@@ -20176,7 +20176,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>0.939006626605988</v>
+        <v>0.939006567001343</v>
       </c>
       <c r="H683" t="n">
         <v>23100</v>
@@ -20205,7 +20205,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G684" t="n">
-        <v>0.907405495643616</v>
+        <v>0.907405436038971</v>
       </c>
       <c r="H684" t="n">
         <v>29700</v>
@@ -20263,7 +20263,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H686" t="n">
         <v>3000</v>
@@ -20292,7 +20292,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G687" t="n">
-        <v>0.952549993991852</v>
+        <v>0.952549934387207</v>
       </c>
       <c r="H687" t="n">
         <v>3600</v>
@@ -20379,7 +20379,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G690" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H690" t="n">
         <v>3600</v>
@@ -20408,7 +20408,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G691" t="n">
-        <v>0.957064390182495</v>
+        <v>0.95706444978714</v>
       </c>
       <c r="H691" t="n">
         <v>600</v>
@@ -20466,7 +20466,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G693" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H693" t="n">
         <v>15600</v>
@@ -20495,7 +20495,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G694" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H694" t="n">
         <v>29100</v>
@@ -20553,7 +20553,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G696" t="n">
-        <v>0.952549993991852</v>
+        <v>0.952549934387207</v>
       </c>
       <c r="H696" t="n">
         <v>12000</v>
@@ -20611,7 +20611,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G698" t="n">
-        <v>0.970607936382294</v>
+        <v>0.970607876777649</v>
       </c>
       <c r="H698" t="n">
         <v>21600</v>
@@ -20756,7 +20756,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>0.911919951438904</v>
+        <v>0.911919891834259</v>
       </c>
       <c r="H703" t="n">
         <v>11700</v>
@@ -20814,7 +20814,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G705" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H705" t="n">
         <v>900</v>
@@ -20843,7 +20843,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G706" t="n">
-        <v>0.84330016374588</v>
+        <v>0.843300223350525</v>
       </c>
       <c r="H706" t="n">
         <v>67500</v>
@@ -21017,7 +21017,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G712" t="n">
-        <v>0.787320911884308</v>
+        <v>0.787320971488953</v>
       </c>
       <c r="H712" t="n">
         <v>32100</v>
@@ -21075,7 +21075,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G714" t="n">
-        <v>0.776486277580261</v>
+        <v>0.776486337184906</v>
       </c>
       <c r="H714" t="n">
         <v>10800</v>
@@ -21278,7 +21278,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G721" t="n">
-        <v>0.698837578296661</v>
+        <v>0.698837637901306</v>
       </c>
       <c r="H721" t="n">
         <v>20700</v>
@@ -21510,7 +21510,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G729" t="n">
-        <v>0.619383275508881</v>
+        <v>0.619383215904236</v>
       </c>
       <c r="H729" t="n">
         <v>9600</v>
@@ -21539,7 +21539,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G730" t="n">
-        <v>0.662722051143646</v>
+        <v>0.662721991539001</v>
       </c>
       <c r="H730" t="n">
         <v>3900</v>
@@ -21626,7 +21626,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G733" t="n">
-        <v>0.651887357234955</v>
+        <v>0.65188729763031</v>
       </c>
       <c r="H733" t="n">
         <v>3600</v>
@@ -21655,7 +21655,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G734" t="n">
-        <v>0.653693020343781</v>
+        <v>0.65369313955307</v>
       </c>
       <c r="H734" t="n">
         <v>27900</v>
@@ -21713,7 +21713,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G736" t="n">
-        <v>0.678973972797394</v>
+        <v>0.678974032402039</v>
       </c>
       <c r="H736" t="n">
         <v>4200</v>
@@ -21742,7 +21742,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G737" t="n">
-        <v>0.68439131975174</v>
+        <v>0.684391379356384</v>
       </c>
       <c r="H737" t="n">
         <v>14700</v>
@@ -21829,7 +21829,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G740" t="n">
-        <v>0.644664227962494</v>
+        <v>0.644664168357849</v>
       </c>
       <c r="H740" t="n">
         <v>3600</v>
@@ -21858,7 +21858,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G741" t="n">
-        <v>0.657304644584656</v>
+        <v>0.657304584980011</v>
       </c>
       <c r="H741" t="n">
         <v>20100</v>
@@ -21916,7 +21916,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G743" t="n">
-        <v>0.662722051143646</v>
+        <v>0.662721991539001</v>
       </c>
       <c r="H743" t="n">
         <v>73200</v>
@@ -21945,7 +21945,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G744" t="n">
-        <v>0.675362527370453</v>
+        <v>0.675362467765808</v>
       </c>
       <c r="H744" t="n">
         <v>18000</v>
@@ -22090,7 +22090,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G749" t="n">
-        <v>0.720506966114044</v>
+        <v>0.720507025718689</v>
       </c>
       <c r="H749" t="n">
         <v>48300</v>
@@ -22119,7 +22119,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G750" t="n">
-        <v>0.709672272205353</v>
+        <v>0.709672331809998</v>
       </c>
       <c r="H750" t="n">
         <v>35100</v>
@@ -22177,7 +22177,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G752" t="n">
-        <v>0.675362527370453</v>
+        <v>0.675362467765808</v>
       </c>
       <c r="H752" t="n">
         <v>33600</v>
@@ -22206,7 +22206,7 @@
         <v>0.75</v>
       </c>
       <c r="G753" t="n">
-        <v>0.677168309688568</v>
+        <v>0.677168250083923</v>
       </c>
       <c r="H753" t="n">
         <v>36600</v>
@@ -22235,7 +22235,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G754" t="n">
-        <v>0.675362527370453</v>
+        <v>0.675362467765808</v>
       </c>
       <c r="H754" t="n">
         <v>27900</v>
@@ -22264,7 +22264,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G755" t="n">
-        <v>0.698837578296661</v>
+        <v>0.698837637901306</v>
       </c>
       <c r="H755" t="n">
         <v>134100</v>
@@ -22322,7 +22322,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G757" t="n">
-        <v>0.68439131975174</v>
+        <v>0.684391379356384</v>
       </c>
       <c r="H757" t="n">
         <v>34500</v>
@@ -22641,7 +22641,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G768" t="n">
-        <v>0.798155665397644</v>
+        <v>0.798155605792999</v>
       </c>
       <c r="H768" t="n">
         <v>107700</v>
@@ -22670,7 +22670,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G769" t="n">
-        <v>0.787320911884308</v>
+        <v>0.787320971488953</v>
       </c>
       <c r="H769" t="n">
         <v>28800</v>
@@ -22757,7 +22757,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G772" t="n">
-        <v>0.798155665397644</v>
+        <v>0.798155605792999</v>
       </c>
       <c r="H772" t="n">
         <v>56700</v>
@@ -22786,7 +22786,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G773" t="n">
-        <v>0.776486277580261</v>
+        <v>0.776486337184906</v>
       </c>
       <c r="H773" t="n">
         <v>17700</v>
@@ -22844,7 +22844,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G775" t="n">
-        <v>0.776486277580261</v>
+        <v>0.776486337184906</v>
       </c>
       <c r="H775" t="n">
         <v>10800</v>
@@ -22873,7 +22873,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G776" t="n">
-        <v>0.801767230033875</v>
+        <v>0.80176717042923</v>
       </c>
       <c r="H776" t="n">
         <v>99600</v>
@@ -22902,7 +22902,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G777" t="n">
-        <v>0.787320911884308</v>
+        <v>0.787320971488953</v>
       </c>
       <c r="H777" t="n">
         <v>15000</v>
@@ -22989,7 +22989,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G780" t="n">
-        <v>0.80899041891098</v>
+        <v>0.808990359306335</v>
       </c>
       <c r="H780" t="n">
         <v>34200</v>
@@ -23018,7 +23018,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G781" t="n">
-        <v>0.80357301235199</v>
+        <v>0.803572952747345</v>
       </c>
       <c r="H781" t="n">
         <v>27000</v>
@@ -23047,7 +23047,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G782" t="n">
-        <v>0.801767230033875</v>
+        <v>0.80176717042923</v>
       </c>
       <c r="H782" t="n">
         <v>21600</v>
@@ -23076,7 +23076,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G783" t="n">
-        <v>0.794544100761414</v>
+        <v>0.794544041156769</v>
       </c>
       <c r="H783" t="n">
         <v>92100</v>
@@ -23105,7 +23105,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G784" t="n">
-        <v>0.80899041891098</v>
+        <v>0.808990359306335</v>
       </c>
       <c r="H784" t="n">
         <v>44700</v>
@@ -23134,7 +23134,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G785" t="n">
-        <v>0.80357301235199</v>
+        <v>0.803572952747345</v>
       </c>
       <c r="H785" t="n">
         <v>7500</v>
@@ -23424,7 +23424,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>0.7692631483078</v>
+        <v>0.769263088703156</v>
       </c>
       <c r="H795" t="n">
         <v>9900</v>
@@ -23511,7 +23511,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G798" t="n">
-        <v>0.798155665397644</v>
+        <v>0.798155605792999</v>
       </c>
       <c r="H798" t="n">
         <v>40200</v>
@@ -23540,7 +23540,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G799" t="n">
-        <v>0.819825053215027</v>
+        <v>0.819824993610382</v>
       </c>
       <c r="H799" t="n">
         <v>312600</v>
@@ -23569,7 +23569,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G800" t="n">
-        <v>0.823436677455902</v>
+        <v>0.823436617851257</v>
       </c>
       <c r="H800" t="n">
         <v>87300</v>
@@ -23598,7 +23598,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G801" t="n">
-        <v>0.834271371364594</v>
+        <v>0.834271311759949</v>
       </c>
       <c r="H801" t="n">
         <v>39300</v>
@@ -23627,7 +23627,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G802" t="n">
-        <v>0.827048182487488</v>
+        <v>0.827048122882843</v>
       </c>
       <c r="H802" t="n">
         <v>36900</v>
@@ -23685,7 +23685,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G804" t="n">
-        <v>0.857746422290802</v>
+        <v>0.857746481895447</v>
       </c>
       <c r="H804" t="n">
         <v>87300</v>
@@ -23772,7 +23772,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>0.893862068653107</v>
+        <v>0.893862128257751</v>
       </c>
       <c r="H807" t="n">
         <v>214500</v>
@@ -23801,7 +23801,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G808" t="n">
-        <v>0.890250563621521</v>
+        <v>0.890250504016876</v>
       </c>
       <c r="H808" t="n">
         <v>21600</v>
@@ -23888,7 +23888,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G811" t="n">
-        <v>0.857746422290802</v>
+        <v>0.857746481895447</v>
       </c>
       <c r="H811" t="n">
         <v>22500</v>
@@ -24120,7 +24120,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G819" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H819" t="n">
         <v>47400</v>
@@ -24149,7 +24149,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G820" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H820" t="n">
         <v>38100</v>
@@ -24265,7 +24265,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G824" t="n">
-        <v>0.911919951438904</v>
+        <v>0.911919891834259</v>
       </c>
       <c r="H824" t="n">
         <v>29700</v>
@@ -24381,7 +24381,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G828" t="n">
-        <v>0.872192740440369</v>
+        <v>0.872192680835724</v>
       </c>
       <c r="H828" t="n">
         <v>37500</v>
@@ -24410,7 +24410,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G829" t="n">
-        <v>0.879415810108185</v>
+        <v>0.87941575050354</v>
       </c>
       <c r="H829" t="n">
         <v>30300</v>
@@ -24497,7 +24497,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G832" t="n">
-        <v>0.893862068653107</v>
+        <v>0.893862128257751</v>
       </c>
       <c r="H832" t="n">
         <v>12000</v>
@@ -24584,7 +24584,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G835" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H835" t="n">
         <v>30600</v>
@@ -24613,7 +24613,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G836" t="n">
-        <v>0.925463259220123</v>
+        <v>0.925463199615479</v>
       </c>
       <c r="H836" t="n">
         <v>18000</v>
@@ -24671,7 +24671,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G838" t="n">
-        <v>0.907405495643616</v>
+        <v>0.907405436038971</v>
       </c>
       <c r="H838" t="n">
         <v>3900</v>
@@ -24700,7 +24700,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G839" t="n">
-        <v>0.911919951438904</v>
+        <v>0.911919891834259</v>
       </c>
       <c r="H839" t="n">
         <v>300</v>
@@ -24729,7 +24729,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G840" t="n">
-        <v>0.907405495643616</v>
+        <v>0.907405436038971</v>
       </c>
       <c r="H840" t="n">
         <v>900</v>
@@ -24787,7 +24787,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G842" t="n">
-        <v>0.890250563621521</v>
+        <v>0.890250504016876</v>
       </c>
       <c r="H842" t="n">
         <v>21000</v>
@@ -24845,7 +24845,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G844" t="n">
-        <v>0.920948803424835</v>
+        <v>0.92094886302948</v>
       </c>
       <c r="H844" t="n">
         <v>35100</v>
@@ -24903,7 +24903,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G846" t="n">
-        <v>0.966093420982361</v>
+        <v>0.966093361377716</v>
       </c>
       <c r="H846" t="n">
         <v>119100</v>
@@ -24932,7 +24932,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G847" t="n">
-        <v>0.984151244163513</v>
+        <v>0.984151303768158</v>
       </c>
       <c r="H847" t="n">
         <v>6600</v>
@@ -24990,7 +24990,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G849" t="n">
-        <v>1.0292956829071</v>
+        <v>1.02929580211639</v>
       </c>
       <c r="H849" t="n">
         <v>90600</v>
@@ -25077,7 +25077,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G852" t="n">
-        <v>1.02478122711182</v>
+        <v>1.02478134632111</v>
       </c>
       <c r="H852" t="n">
         <v>109800</v>
@@ -25135,7 +25135,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G854" t="n">
-        <v>1.0292956829071</v>
+        <v>1.02929580211639</v>
       </c>
       <c r="H854" t="n">
         <v>5400</v>
@@ -25222,7 +25222,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G857" t="n">
-        <v>1.10152697563171</v>
+        <v>1.101527094841</v>
       </c>
       <c r="H857" t="n">
         <v>135300</v>
@@ -25396,7 +25396,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G863" t="n">
-        <v>1.06089675426483</v>
+        <v>1.06089699268341</v>
       </c>
       <c r="H863" t="n">
         <v>3900</v>
@@ -25425,7 +25425,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G864" t="n">
-        <v>1.106041431427</v>
+        <v>1.10604155063629</v>
       </c>
       <c r="H864" t="n">
         <v>43500</v>
@@ -25454,7 +25454,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G865" t="n">
-        <v>1.09701263904572</v>
+        <v>1.09701251983643</v>
       </c>
       <c r="H865" t="n">
         <v>21600</v>
@@ -25483,7 +25483,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G866" t="n">
-        <v>1.07895481586456</v>
+        <v>1.07895469665527</v>
       </c>
       <c r="H866" t="n">
         <v>8100</v>
@@ -25512,7 +25512,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G867" t="n">
-        <v>1.08346927165985</v>
+        <v>1.08346915245056</v>
       </c>
       <c r="H867" t="n">
         <v>25800</v>
@@ -25628,7 +25628,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G871" t="n">
-        <v>1.10152697563171</v>
+        <v>1.101527094841</v>
       </c>
       <c r="H871" t="n">
         <v>7500</v>
@@ -25657,7 +25657,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G872" t="n">
-        <v>1.14215695858002</v>
+        <v>1.14215707778931</v>
       </c>
       <c r="H872" t="n">
         <v>46800</v>
@@ -25686,7 +25686,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G873" t="n">
-        <v>1.16472947597504</v>
+        <v>1.16472935676575</v>
       </c>
       <c r="H873" t="n">
         <v>48300</v>
@@ -25715,7 +25715,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G874" t="n">
-        <v>1.15570044517517</v>
+        <v>1.15570056438446</v>
       </c>
       <c r="H874" t="n">
         <v>54300</v>
@@ -25744,7 +25744,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>1.16472947597504</v>
+        <v>1.16472935676575</v>
       </c>
       <c r="H875" t="n">
         <v>158700</v>
@@ -25802,7 +25802,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G877" t="n">
-        <v>1.19181609153748</v>
+        <v>1.19181621074677</v>
       </c>
       <c r="H877" t="n">
         <v>32400</v>
@@ -25831,7 +25831,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>1.20535945892334</v>
+        <v>1.20535957813263</v>
       </c>
       <c r="H878" t="n">
         <v>25200</v>
@@ -25860,7 +25860,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G879" t="n">
-        <v>1.27307617664337</v>
+        <v>1.27307629585266</v>
       </c>
       <c r="H879" t="n">
         <v>146400</v>
@@ -25889,7 +25889,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G880" t="n">
-        <v>1.31370639801025</v>
+        <v>1.31370651721954</v>
       </c>
       <c r="H880" t="n">
         <v>138600</v>
@@ -26034,7 +26034,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G885" t="n">
-        <v>1.22341740131378</v>
+        <v>1.22341728210449</v>
       </c>
       <c r="H885" t="n">
         <v>49200</v>
@@ -26063,7 +26063,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G886" t="n">
-        <v>1.20535945892334</v>
+        <v>1.20535957813263</v>
       </c>
       <c r="H886" t="n">
         <v>24000</v>
@@ -26092,7 +26092,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G887" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244631290436</v>
       </c>
       <c r="H887" t="n">
         <v>7800</v>
@@ -26121,7 +26121,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G888" t="n">
-        <v>1.22793173789978</v>
+        <v>1.22793185710907</v>
       </c>
       <c r="H888" t="n">
         <v>5100</v>
@@ -26179,7 +26179,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G890" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244631290436</v>
       </c>
       <c r="H890" t="n">
         <v>3000</v>
@@ -26237,7 +26237,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G892" t="n">
-        <v>1.22793173789978</v>
+        <v>1.22793185710907</v>
       </c>
       <c r="H892" t="n">
         <v>12600</v>
@@ -26266,7 +26266,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G893" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244631290436</v>
       </c>
       <c r="H893" t="n">
         <v>5100</v>
@@ -26295,7 +26295,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G894" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244631290436</v>
       </c>
       <c r="H894" t="n">
         <v>900</v>
@@ -26324,7 +26324,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G895" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244631290436</v>
       </c>
       <c r="H895" t="n">
         <v>3000</v>
@@ -26440,7 +26440,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G899" t="n">
-        <v>1.22341740131378</v>
+        <v>1.22341728210449</v>
       </c>
       <c r="H899" t="n">
         <v>11400</v>
@@ -26498,7 +26498,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G901" t="n">
-        <v>1.19181609153748</v>
+        <v>1.19181621074677</v>
       </c>
       <c r="H901" t="n">
         <v>68700</v>
@@ -26585,7 +26585,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G904" t="n">
-        <v>1.22341740131378</v>
+        <v>1.22341728210449</v>
       </c>
       <c r="H904" t="n">
         <v>900</v>
@@ -26672,7 +26672,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G907" t="n">
-        <v>1.19181609153748</v>
+        <v>1.19181621074677</v>
       </c>
       <c r="H907" t="n">
         <v>4500</v>
@@ -26701,7 +26701,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G908" t="n">
-        <v>1.14215695858002</v>
+        <v>1.14215707778931</v>
       </c>
       <c r="H908" t="n">
         <v>3600</v>
@@ -26788,7 +26788,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G911" t="n">
-        <v>1.10152697563171</v>
+        <v>1.101527094841</v>
       </c>
       <c r="H911" t="n">
         <v>2100</v>
@@ -26817,7 +26817,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G912" t="n">
-        <v>1.10152697563171</v>
+        <v>1.101527094841</v>
       </c>
       <c r="H912" t="n">
         <v>1200</v>
@@ -26875,7 +26875,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G914" t="n">
-        <v>1.106041431427</v>
+        <v>1.10604155063629</v>
       </c>
       <c r="H914" t="n">
         <v>900</v>
@@ -26933,7 +26933,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G916" t="n">
-        <v>1.07895481586456</v>
+        <v>1.07895469665527</v>
       </c>
       <c r="H916" t="n">
         <v>26100</v>
@@ -27020,7 +27020,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>1.16472947597504</v>
+        <v>1.16472935676575</v>
       </c>
       <c r="H919" t="n">
         <v>21000</v>
@@ -27049,7 +27049,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G920" t="n">
-        <v>1.16021490097046</v>
+        <v>1.16021478176117</v>
       </c>
       <c r="H920" t="n">
         <v>3900</v>
@@ -27078,7 +27078,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G921" t="n">
-        <v>1.16021490097046</v>
+        <v>1.16021478176117</v>
       </c>
       <c r="H921" t="n">
         <v>3000</v>
@@ -27107,7 +27107,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G922" t="n">
-        <v>1.16472947597504</v>
+        <v>1.16472935676575</v>
       </c>
       <c r="H922" t="n">
         <v>15000</v>
@@ -27136,7 +27136,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G923" t="n">
-        <v>1.14215695858002</v>
+        <v>1.14215707778931</v>
       </c>
       <c r="H923" t="n">
         <v>4200</v>
@@ -27165,7 +27165,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G924" t="n">
-        <v>1.15118598937988</v>
+        <v>1.15118610858917</v>
       </c>
       <c r="H924" t="n">
         <v>9600</v>
@@ -27194,7 +27194,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G925" t="n">
-        <v>1.14215695858002</v>
+        <v>1.14215707778931</v>
       </c>
       <c r="H925" t="n">
         <v>1200</v>
@@ -27223,7 +27223,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G926" t="n">
-        <v>1.22793173789978</v>
+        <v>1.22793185710907</v>
       </c>
       <c r="H926" t="n">
         <v>16500</v>
@@ -27252,7 +27252,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G927" t="n">
-        <v>1.22793173789978</v>
+        <v>1.22793185710907</v>
       </c>
       <c r="H927" t="n">
         <v>60300</v>
@@ -27281,7 +27281,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G928" t="n">
-        <v>1.22341740131378</v>
+        <v>1.22341728210449</v>
       </c>
       <c r="H928" t="n">
         <v>10200</v>
@@ -27310,7 +27310,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G929" t="n">
-        <v>1.22341740131378</v>
+        <v>1.22341728210449</v>
       </c>
       <c r="H929" t="n">
         <v>0</v>
@@ -27513,7 +27513,7 @@
         <v>1.875</v>
       </c>
       <c r="G936" t="n">
-        <v>1.69292068481445</v>
+        <v>1.69292056560516</v>
       </c>
       <c r="H936" t="n">
         <v>592500</v>
@@ -27542,7 +27542,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G937" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H937" t="n">
         <v>201600</v>
@@ -27571,7 +27571,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G938" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H938" t="n">
         <v>60000</v>
@@ -27600,7 +27600,7 @@
         <v>1.75</v>
       </c>
       <c r="G939" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H939" t="n">
         <v>30600</v>
@@ -27629,7 +27629,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G940" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H940" t="n">
         <v>57000</v>
@@ -27658,7 +27658,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G941" t="n">
-        <v>1.64777624607086</v>
+        <v>1.64777612686157</v>
       </c>
       <c r="H941" t="n">
         <v>159900</v>
@@ -27716,7 +27716,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H943" t="n">
         <v>35700</v>
@@ -27803,7 +27803,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G946" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H946" t="n">
         <v>20700</v>
@@ -28064,7 +28064,7 @@
         <v>1.5</v>
       </c>
       <c r="G955" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H955" t="n">
         <v>54600</v>
@@ -28093,7 +28093,7 @@
         <v>1.5</v>
       </c>
       <c r="G956" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H956" t="n">
         <v>15000</v>
@@ -28238,7 +28238,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G961" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H961" t="n">
         <v>116400</v>
@@ -28325,7 +28325,7 @@
         <v>1.5</v>
       </c>
       <c r="G964" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H964" t="n">
         <v>15900</v>
@@ -28412,7 +28412,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G967" t="n">
-        <v>1.35885083675385</v>
+        <v>1.35885095596313</v>
       </c>
       <c r="H967" t="n">
         <v>54900</v>
@@ -28499,7 +28499,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G970" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H970" t="n">
         <v>59100</v>
@@ -28847,7 +28847,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G982" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H982" t="n">
         <v>41400</v>
@@ -28876,7 +28876,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G983" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H983" t="n">
         <v>18900</v>
@@ -28934,7 +28934,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G985" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H985" t="n">
         <v>24000</v>
@@ -28992,7 +28992,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G987" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H987" t="n">
         <v>38700</v>
@@ -29050,7 +29050,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G989" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H989" t="n">
         <v>57300</v>
@@ -29079,7 +29079,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G990" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H990" t="n">
         <v>18300</v>
@@ -29195,7 +29195,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G994" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H994" t="n">
         <v>6600</v>
@@ -29224,7 +29224,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H995" t="n">
         <v>3300</v>
@@ -29253,7 +29253,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G996" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H996" t="n">
         <v>28800</v>
@@ -29340,7 +29340,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G999" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H999" t="n">
         <v>10500</v>
@@ -29572,7 +29572,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H1007" t="n">
         <v>3900</v>
@@ -29659,7 +29659,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.4897700548172</v>
+        <v>1.48977017402649</v>
       </c>
       <c r="H1010" t="n">
         <v>4800</v>
@@ -29688,7 +29688,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1011" t="n">
         <v>900</v>
@@ -29862,7 +29862,7 @@
         <v>1.5</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1017" t="n">
         <v>26400</v>
@@ -30036,7 +30036,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.30467760562897</v>
+        <v>1.30467748641968</v>
       </c>
       <c r="H1023" t="n">
         <v>300</v>
@@ -30181,7 +30181,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.33176422119141</v>
+        <v>1.3317643404007</v>
       </c>
       <c r="H1028" t="n">
         <v>19200</v>
@@ -30268,7 +30268,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H1031" t="n">
         <v>16200</v>
@@ -30413,7 +30413,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1036" t="n">
         <v>27900</v>
@@ -30442,7 +30442,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1037" t="n">
         <v>2100</v>
@@ -30616,7 +30616,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1043" t="n">
         <v>4800</v>
@@ -31109,7 +31109,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1060" t="n">
         <v>5700</v>
@@ -31196,7 +31196,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.34079325199127</v>
+        <v>1.34079313278198</v>
       </c>
       <c r="H1063" t="n">
         <v>6000</v>
@@ -31254,7 +31254,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.27307617664337</v>
+        <v>1.27307629585266</v>
       </c>
       <c r="H1065" t="n">
         <v>64500</v>
@@ -31283,7 +31283,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.29113411903381</v>
+        <v>1.29113399982452</v>
       </c>
       <c r="H1066" t="n">
         <v>2700</v>
@@ -31341,7 +31341,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.25953304767609</v>
+        <v>1.2595329284668</v>
       </c>
       <c r="H1068" t="n">
         <v>2100</v>
@@ -31370,7 +31370,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.25953304767609</v>
+        <v>1.2595329284668</v>
       </c>
       <c r="H1069" t="n">
         <v>600</v>
@@ -31399,7 +31399,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.25953304767609</v>
+        <v>1.2595329284668</v>
       </c>
       <c r="H1070" t="n">
         <v>600</v>
@@ -31428,7 +31428,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.23244619369507</v>
+        <v>1.23244631290436</v>
       </c>
       <c r="H1071" t="n">
         <v>6900</v>
@@ -31602,7 +31602,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.29564845561981</v>
+        <v>1.2956485748291</v>
       </c>
       <c r="H1077" t="n">
         <v>52800</v>
@@ -31660,7 +31660,7 @@
         <v>1.5</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1079" t="n">
         <v>71400</v>
@@ -31747,7 +31747,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H1082" t="n">
         <v>25500</v>
@@ -31805,7 +31805,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1084" t="n">
         <v>15300</v>
@@ -31834,7 +31834,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1085" t="n">
         <v>9300</v>
@@ -31892,7 +31892,7 @@
         <v>1.75</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1087" t="n">
         <v>179400</v>
@@ -32008,7 +32008,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1091" t="n">
         <v>9000</v>
@@ -32066,7 +32066,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1093" t="n">
         <v>3600</v>
@@ -32095,7 +32095,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1094" t="n">
         <v>21000</v>
@@ -32182,7 +32182,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1097" t="n">
         <v>1800</v>
@@ -32356,7 +32356,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1103" t="n">
         <v>9300</v>
@@ -32501,7 +32501,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1108" t="n">
         <v>3600</v>
@@ -32530,7 +32530,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1109" t="n">
         <v>3300</v>
@@ -32617,7 +32617,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.35885083675385</v>
+        <v>1.35885095596313</v>
       </c>
       <c r="H1112" t="n">
         <v>9600</v>
@@ -32675,7 +32675,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1114" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1114" t="n">
         <v>11100</v>
@@ -33023,7 +33023,7 @@
         <v>1.5</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1126" t="n">
         <v>65700</v>
@@ -33081,7 +33081,7 @@
         <v>1.5</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1128" t="n">
         <v>42600</v>
@@ -33313,7 +33313,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H1136" t="n">
         <v>13200</v>
@@ -33429,7 +33429,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H1140" t="n">
         <v>6300</v>
@@ -33458,7 +33458,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1141" t="n">
         <v>5400</v>
@@ -33661,7 +33661,7 @@
         <v>1.5</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1148" t="n">
         <v>21900</v>
@@ -33922,7 +33922,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1157" t="n">
         <v>14100</v>
@@ -34763,7 +34763,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1186" t="n">
         <v>38400</v>
@@ -35024,7 +35024,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1195" t="n">
         <v>6600</v>
@@ -35053,7 +35053,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1196" t="n">
         <v>0</v>
@@ -35082,7 +35082,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1197" t="n">
         <v>600</v>
@@ -35111,7 +35111,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1198" t="n">
         <v>11400</v>
@@ -35140,7 +35140,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1199" t="n">
         <v>0</v>
@@ -35256,7 +35256,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.4897700548172</v>
+        <v>1.48977017402649</v>
       </c>
       <c r="H1203" t="n">
         <v>2700</v>
@@ -35517,7 +35517,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1212" t="n">
         <v>600</v>
@@ -35546,7 +35546,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.4897700548172</v>
+        <v>1.48977017402649</v>
       </c>
       <c r="H1213" t="n">
         <v>23400</v>
@@ -35633,7 +35633,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.4897700548172</v>
+        <v>1.48977017402649</v>
       </c>
       <c r="H1216" t="n">
         <v>6600</v>
@@ -35981,7 +35981,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.4897700548172</v>
+        <v>1.48977017402649</v>
       </c>
       <c r="H1228" t="n">
         <v>21900</v>
@@ -36358,7 +36358,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1241" t="n">
         <v>2700</v>
@@ -36387,7 +36387,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H1242" t="n">
         <v>10500</v>
@@ -36677,7 +36677,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H1252" t="n">
         <v>8700</v>
@@ -36706,7 +36706,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H1253" t="n">
         <v>11100</v>
@@ -37025,7 +37025,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1264" t="n">
         <v>6000</v>
@@ -37054,7 +37054,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.47622680664062</v>
+        <v>1.47622692584991</v>
       </c>
       <c r="H1265" t="n">
         <v>0</v>
@@ -37344,7 +37344,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1275" t="n">
         <v>4200</v>
@@ -37373,7 +37373,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1276" t="n">
         <v>8100</v>
@@ -37547,7 +37547,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1282" t="n">
         <v>4500</v>
@@ -37576,7 +37576,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1283" t="n">
         <v>0</v>
@@ -37634,7 +37634,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H1285" t="n">
         <v>28500</v>
@@ -37924,7 +37924,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1295" t="n">
         <v>3000</v>
@@ -37953,7 +37953,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1296" t="n">
         <v>1500</v>
@@ -37982,7 +37982,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.43559682369232</v>
+        <v>1.43559670448303</v>
       </c>
       <c r="H1297" t="n">
         <v>2400</v>
@@ -38011,7 +38011,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1298" t="n">
         <v>7200</v>
@@ -38069,7 +38069,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1300" t="n">
         <v>19800</v>
@@ -38098,7 +38098,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.42205345630646</v>
+        <v>1.42205333709717</v>
       </c>
       <c r="H1301" t="n">
         <v>0</v>
@@ -38156,7 +38156,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1303" t="n">
         <v>1500</v>
@@ -38185,7 +38185,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1304" t="n">
         <v>7500</v>
@@ -38272,7 +38272,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1307" t="n">
         <v>8400</v>
@@ -38504,7 +38504,7 @@
         <v>1.5</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1315" t="n">
         <v>4200</v>
@@ -38794,7 +38794,7 @@
         <v>1.5</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1325" t="n">
         <v>12600</v>
@@ -38823,7 +38823,7 @@
         <v>1.5</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1326" t="n">
         <v>9300</v>
@@ -38852,7 +38852,7 @@
         <v>1.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1327" t="n">
         <v>10500</v>
@@ -38910,7 +38910,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.34530758857727</v>
+        <v>1.34530770778656</v>
       </c>
       <c r="H1329" t="n">
         <v>14400</v>
@@ -39055,7 +39055,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.35885083675385</v>
+        <v>1.35885095596313</v>
       </c>
       <c r="H1334" t="n">
         <v>31200</v>
@@ -39142,7 +39142,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.34982216358185</v>
+        <v>1.34982204437256</v>
       </c>
       <c r="H1337" t="n">
         <v>60300</v>
@@ -39374,7 +39374,7 @@
         <v>1.5</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1345" t="n">
         <v>22800</v>
@@ -39722,7 +39722,7 @@
         <v>1.5</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1357" t="n">
         <v>8100</v>
@@ -39751,7 +39751,7 @@
         <v>1.5</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1358" t="n">
         <v>3000</v>
@@ -40157,7 +40157,7 @@
         <v>1.5</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.35433661937714</v>
+        <v>1.35433650016785</v>
       </c>
       <c r="H1372" t="n">
         <v>432000</v>
@@ -40186,7 +40186,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1373" t="n">
         <v>41100</v>
@@ -40215,7 +40215,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1374" t="n">
         <v>17400</v>
@@ -40244,7 +40244,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1375" t="n">
         <v>1500</v>
@@ -40273,7 +40273,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1376" t="n">
         <v>16500</v>
@@ -40302,7 +40302,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1377" t="n">
         <v>12300</v>
@@ -40331,7 +40331,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1378" t="n">
         <v>9300</v>
@@ -40360,7 +40360,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1379" t="n">
         <v>10200</v>
@@ -40389,7 +40389,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.41302454471588</v>
+        <v>1.41302442550659</v>
       </c>
       <c r="H1380" t="n">
         <v>0</v>
@@ -40650,7 +40650,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1389" t="n">
         <v>13500</v>
@@ -40679,7 +40679,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.42656779289246</v>
+        <v>1.42656791210175</v>
       </c>
       <c r="H1390" t="n">
         <v>0</v>
@@ -40737,7 +40737,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.64777624607086</v>
+        <v>1.64777612686157</v>
       </c>
       <c r="H1392" t="n">
         <v>238200</v>
@@ -40766,7 +40766,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H1393" t="n">
         <v>120900</v>
@@ -40853,7 +40853,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.63423264026642</v>
+        <v>1.63423275947571</v>
       </c>
       <c r="H1396" t="n">
         <v>66000</v>
@@ -40940,7 +40940,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H1399" t="n">
         <v>21600</v>
@@ -41172,7 +41172,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.63423264026642</v>
+        <v>1.63423275947571</v>
       </c>
       <c r="H1407" t="n">
         <v>6600</v>
@@ -41201,7 +41201,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1408" t="n">
         <v>18000</v>
@@ -41288,7 +41288,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H1411" t="n">
         <v>9000</v>
@@ -41375,7 +41375,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.57554483413696</v>
+        <v>1.57554471492767</v>
       </c>
       <c r="H1414" t="n">
         <v>6600</v>
@@ -41404,7 +41404,7 @@
         <v>1.75</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1415" t="n">
         <v>1200</v>
@@ -41462,7 +41462,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1417" t="n">
         <v>17700</v>
@@ -41549,7 +41549,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.61166048049927</v>
+        <v>1.61166036128998</v>
       </c>
       <c r="H1420" t="n">
         <v>6000</v>
@@ -41578,7 +41578,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1421" t="n">
         <v>16200</v>
@@ -41607,7 +41607,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1422" t="n">
         <v>28500</v>
@@ -41636,7 +41636,7 @@
         <v>1.75</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1423" t="n">
         <v>13500</v>
@@ -41665,7 +41665,7 @@
         <v>1.75</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1424" t="n">
         <v>0</v>
@@ -41694,7 +41694,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.61166048049927</v>
+        <v>1.61166036128998</v>
       </c>
       <c r="H1425" t="n">
         <v>17400</v>
@@ -41723,7 +41723,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.61166048049927</v>
+        <v>1.61166036128998</v>
       </c>
       <c r="H1426" t="n">
         <v>4800</v>
@@ -41752,7 +41752,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H1427" t="n">
         <v>19500</v>
@@ -41839,7 +41839,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1430" t="n">
         <v>12300</v>
@@ -41868,7 +41868,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1431" t="n">
         <v>5100</v>
@@ -41897,7 +41897,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.57554483413696</v>
+        <v>1.57554471492767</v>
       </c>
       <c r="H1432" t="n">
         <v>12000</v>
@@ -41926,7 +41926,7 @@
         <v>1.75</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1433" t="n">
         <v>20100</v>
@@ -42071,7 +42071,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1438" t="n">
         <v>16800</v>
@@ -42100,7 +42100,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1439" t="n">
         <v>10800</v>
@@ -42187,7 +42187,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1442" t="n">
         <v>900</v>
@@ -42332,7 +42332,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.4852557182312</v>
+        <v>1.48525559902191</v>
       </c>
       <c r="H1447" t="n">
         <v>31500</v>
@@ -42361,7 +42361,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.49428462982178</v>
+        <v>1.49428451061249</v>
       </c>
       <c r="H1448" t="n">
         <v>49200</v>
@@ -42419,7 +42419,7 @@
         <v>1.75</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1450" t="n">
         <v>17100</v>
@@ -42477,7 +42477,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1452" t="n">
         <v>6600</v>
@@ -42506,7 +42506,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1453" t="n">
         <v>0</v>
@@ -42535,7 +42535,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1454" t="n">
         <v>3300</v>
@@ -42564,7 +42564,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1455" t="n">
         <v>300</v>
@@ -42883,7 +42883,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1466" t="n">
         <v>4200</v>
@@ -42912,7 +42912,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1467" t="n">
         <v>3000</v>
@@ -43028,7 +43028,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H1471" t="n">
         <v>23400</v>
@@ -43115,7 +43115,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1474" t="n">
         <v>50700</v>
@@ -43173,7 +43173,7 @@
         <v>1.75</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1476" t="n">
         <v>4500</v>
@@ -43231,7 +43231,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1478" t="n">
         <v>32700</v>
@@ -43260,7 +43260,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1479" t="n">
         <v>0</v>
@@ -43318,7 +43318,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1481" t="n">
         <v>6300</v>
@@ -43550,7 +43550,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1489" t="n">
-        <v>1.52137124538422</v>
+        <v>1.52137136459351</v>
       </c>
       <c r="H1489" t="n">
         <v>18300</v>
@@ -43695,7 +43695,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1494" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1494" t="n">
         <v>8100</v>
@@ -43753,7 +43753,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1496" t="n">
         <v>3300</v>
@@ -43782,7 +43782,7 @@
         <v>1.75</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1497" t="n">
         <v>22800</v>
@@ -43840,7 +43840,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1499" t="n">
         <v>3000</v>
@@ -43869,7 +43869,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1500" t="n">
         <v>0</v>
@@ -43956,7 +43956,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1503" t="n">
-        <v>1.55297255516052</v>
+        <v>1.55297267436981</v>
       </c>
       <c r="H1503" t="n">
         <v>7500</v>
@@ -44043,7 +44043,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H1506" t="n">
         <v>10200</v>
@@ -44101,7 +44101,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H1508" t="n">
         <v>2700</v>
@@ -44130,7 +44130,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.52588593959808</v>
+        <v>1.5258857011795</v>
       </c>
       <c r="H1509" t="n">
         <v>11100</v>
@@ -44246,7 +44246,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.57554483413696</v>
+        <v>1.57554471492767</v>
       </c>
       <c r="H1513" t="n">
         <v>1200</v>
@@ -44275,7 +44275,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.56651604175568</v>
+        <v>1.56651592254639</v>
       </c>
       <c r="H1514" t="n">
         <v>3900</v>
@@ -44304,7 +44304,7 @@
         <v>1.75</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1515" t="n">
         <v>900</v>
@@ -44362,7 +44362,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1517" t="n">
         <v>10200</v>
@@ -44391,7 +44391,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1518" t="n">
-        <v>1.57554483413696</v>
+        <v>1.57554471492767</v>
       </c>
       <c r="H1518" t="n">
         <v>5400</v>
@@ -44478,7 +44478,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1521" t="n">
         <v>11100</v>
@@ -44507,7 +44507,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.54394352436066</v>
+        <v>1.54394364356995</v>
       </c>
       <c r="H1522" t="n">
         <v>4200</v>
@@ -44565,7 +44565,7 @@
         <v>1.75</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1524" t="n">
         <v>44400</v>
@@ -44594,7 +44594,7 @@
         <v>1.75</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1525" t="n">
         <v>0</v>
@@ -44623,7 +44623,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1526" t="n">
         <v>1800</v>
@@ -44652,7 +44652,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1527" t="n">
         <v>2700</v>
@@ -44681,7 +44681,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.61166048049927</v>
+        <v>1.61166036128998</v>
       </c>
       <c r="H1528" t="n">
         <v>12600</v>
@@ -44710,7 +44710,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H1529" t="n">
         <v>7500</v>
@@ -44739,7 +44739,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1530" t="n">
         <v>5100</v>
@@ -44768,7 +44768,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.59360253810883</v>
+        <v>1.59360265731812</v>
       </c>
       <c r="H1531" t="n">
         <v>0</v>
@@ -44797,7 +44797,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1532" t="n">
         <v>600</v>
@@ -44855,7 +44855,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.71097838878632</v>
+        <v>1.71097850799561</v>
       </c>
       <c r="H1534" t="n">
         <v>162900</v>
@@ -44942,7 +44942,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.63423264026642</v>
+        <v>1.63423275947571</v>
       </c>
       <c r="H1537" t="n">
         <v>64800</v>
@@ -45058,7 +45058,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1541" t="n">
-        <v>1.64777624607086</v>
+        <v>1.64777612686157</v>
       </c>
       <c r="H1541" t="n">
         <v>2700</v>
@@ -45087,7 +45087,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.67486274242401</v>
+        <v>1.6748628616333</v>
       </c>
       <c r="H1542" t="n">
         <v>12600</v>
@@ -45116,7 +45116,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.63423264026642</v>
+        <v>1.63423275947571</v>
       </c>
       <c r="H1543" t="n">
         <v>51000</v>
@@ -45145,7 +45145,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H1544" t="n">
         <v>6300</v>
@@ -45174,7 +45174,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H1545" t="n">
         <v>600</v>
@@ -45203,7 +45203,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1546" t="n">
-        <v>1.62068927288055</v>
+        <v>1.62068939208984</v>
       </c>
       <c r="H1546" t="n">
         <v>3000</v>
@@ -45232,7 +45232,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.58908820152283</v>
+        <v>1.58908808231354</v>
       </c>
       <c r="H1547" t="n">
         <v>6300</v>
@@ -45261,7 +45261,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.58457362651825</v>
+        <v>1.58457374572754</v>
       </c>
       <c r="H1548" t="n">
         <v>4200</v>
@@ -45290,7 +45290,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H1549" t="n">
         <v>10500</v>
@@ -45319,7 +45319,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1550" t="n">
-        <v>1.66583383083344</v>
+        <v>1.66583395004272</v>
       </c>
       <c r="H1550" t="n">
         <v>5100</v>
@@ -45348,7 +45348,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.67486274242401</v>
+        <v>1.6748628616333</v>
       </c>
       <c r="H1551" t="n">
         <v>27000</v>
@@ -45377,7 +45377,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.67486274242401</v>
+        <v>1.6748628616333</v>
       </c>
       <c r="H1552" t="n">
         <v>6300</v>
@@ -45464,7 +45464,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1555" t="n">
-        <v>1.68840622901917</v>
+        <v>1.68840610980988</v>
       </c>
       <c r="H1555" t="n">
         <v>7800</v>
@@ -45522,7 +45522,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.68840622901917</v>
+        <v>1.68840610980988</v>
       </c>
       <c r="H1557" t="n">
         <v>126300</v>
@@ -45638,7 +45638,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.68840622901917</v>
+        <v>1.68840610980988</v>
       </c>
       <c r="H1561" t="n">
         <v>26100</v>
@@ -45667,7 +45667,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1562" t="n">
-        <v>1.68840622901917</v>
+        <v>1.68840610980988</v>
       </c>
       <c r="H1562" t="n">
         <v>9900</v>
@@ -45696,7 +45696,7 @@
         <v>1.875</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.69292068481445</v>
+        <v>1.69292056560516</v>
       </c>
       <c r="H1563" t="n">
         <v>3000</v>
@@ -45725,7 +45725,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.67486274242401</v>
+        <v>1.6748628616333</v>
       </c>
       <c r="H1564" t="n">
         <v>8700</v>
@@ -45754,7 +45754,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1565" t="n">
-        <v>1.66583383083344</v>
+        <v>1.66583395004272</v>
       </c>
       <c r="H1565" t="n">
         <v>8400</v>
@@ -45812,7 +45812,7 @@
         <v>1.75</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.58005917072296</v>
+        <v>1.58005928993225</v>
       </c>
       <c r="H1567" t="n">
         <v>38700</v>
@@ -45957,7 +45957,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.64777624607086</v>
+        <v>1.64777612686157</v>
       </c>
       <c r="H1572" t="n">
         <v>13200</v>
@@ -45986,7 +45986,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1573" t="n">
-        <v>1.61166048049927</v>
+        <v>1.61166036128998</v>
       </c>
       <c r="H1573" t="n">
         <v>8700</v>
@@ -46131,7 +46131,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.63423264026642</v>
+        <v>1.63423275947571</v>
       </c>
       <c r="H1578" t="n">
         <v>3300</v>
@@ -46218,7 +46218,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H1581" t="n">
         <v>8400</v>
@@ -46276,7 +46276,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.63423264026642</v>
+        <v>1.63423275947571</v>
       </c>
       <c r="H1583" t="n">
         <v>12600</v>
@@ -46305,7 +46305,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H1584" t="n">
         <v>7200</v>
@@ -46363,7 +46363,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.60714602470398</v>
+        <v>1.60714590549469</v>
       </c>
       <c r="H1586" t="n">
         <v>7500</v>
@@ -46450,7 +46450,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.62068927288055</v>
+        <v>1.62068939208984</v>
       </c>
       <c r="H1589" t="n">
         <v>18900</v>
@@ -46508,7 +46508,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.62068927288055</v>
+        <v>1.62068939208984</v>
       </c>
       <c r="H1591" t="n">
         <v>11400</v>
@@ -46624,7 +46624,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.64326167106628</v>
+        <v>1.64326155185699</v>
       </c>
       <c r="H1595" t="n">
         <v>1500</v>
@@ -46740,7 +46740,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.84189760684967</v>
+        <v>1.84189772605896</v>
       </c>
       <c r="H1599" t="n">
         <v>343200</v>
@@ -46827,7 +46827,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.04956245422363</v>
+        <v>2.04956269264221</v>
       </c>
       <c r="H1602" t="n">
         <v>380700</v>
@@ -46856,7 +46856,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.12179350852966</v>
+        <v>2.12179398536682</v>
       </c>
       <c r="H1603" t="n">
         <v>147900</v>
@@ -46914,7 +46914,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.12179350852966</v>
+        <v>2.12179398536682</v>
       </c>
       <c r="H1605" t="n">
         <v>38100</v>
@@ -46943,7 +46943,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1606" t="n">
-        <v>2.05859136581421</v>
+        <v>2.05859160423279</v>
       </c>
       <c r="H1606" t="n">
         <v>98400</v>
@@ -47030,7 +47030,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.04956245422363</v>
+        <v>2.04956269264221</v>
       </c>
       <c r="H1609" t="n">
         <v>36000</v>
@@ -47088,7 +47088,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1611" t="n">
-        <v>1.99538922309875</v>
+        <v>1.99538910388947</v>
       </c>
       <c r="H1611" t="n">
         <v>20700</v>
@@ -47175,7 +47175,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.96830248832703</v>
+        <v>1.96830260753632</v>
       </c>
       <c r="H1614" t="n">
         <v>6300</v>
@@ -47233,7 +47233,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.01344704627991</v>
+        <v>2.01344680786133</v>
       </c>
       <c r="H1616" t="n">
         <v>28200</v>
@@ -47349,7 +47349,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.01344704627991</v>
+        <v>2.01344680786133</v>
       </c>
       <c r="H1620" t="n">
         <v>57900</v>
@@ -47378,7 +47378,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.00441813468933</v>
+        <v>2.00441789627075</v>
       </c>
       <c r="H1621" t="n">
         <v>34800</v>
@@ -47436,7 +47436,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1623" t="n">
-        <v>2.00441813468933</v>
+        <v>2.00441789627075</v>
       </c>
       <c r="H1623" t="n">
         <v>6000</v>
@@ -47465,7 +47465,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.01344704627991</v>
+        <v>2.01344680786133</v>
       </c>
       <c r="H1624" t="n">
         <v>25500</v>
@@ -47494,7 +47494,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1625" t="n">
-        <v>2.00441813468933</v>
+        <v>2.00441789627075</v>
       </c>
       <c r="H1625" t="n">
         <v>14100</v>
@@ -47523,7 +47523,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.10373616218567</v>
+        <v>2.10373592376709</v>
       </c>
       <c r="H1626" t="n">
         <v>31800</v>
@@ -47552,7 +47552,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H1627" t="n">
         <v>192000</v>
@@ -47668,7 +47668,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1631" t="n">
         <v>23100</v>
@@ -47697,7 +47697,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.51727485656738</v>
+        <v>2.5172746181488</v>
       </c>
       <c r="H1632" t="n">
         <v>41100</v>
@@ -47726,7 +47726,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.59213805198669</v>
+        <v>2.59213781356812</v>
       </c>
       <c r="H1633" t="n">
         <v>87600</v>
@@ -47871,7 +47871,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.13489603996277</v>
+        <v>3.13489580154419</v>
       </c>
       <c r="H1638" t="n">
         <v>112200</v>
@@ -47987,7 +47987,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1642" t="n">
         <v>209700</v>
@@ -48074,7 +48074,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.87287473678589</v>
+        <v>2.87287497520447</v>
       </c>
       <c r="H1645" t="n">
         <v>21300</v>
@@ -48190,7 +48190,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1649" t="n">
         <v>22800</v>
@@ -48248,7 +48248,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1651" t="n">
         <v>10500</v>
@@ -48306,7 +48306,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1653" t="n">
         <v>4800</v>
@@ -48364,7 +48364,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1655" t="n">
         <v>9000</v>
@@ -48451,7 +48451,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1658" t="n">
         <v>3900</v>
@@ -48567,7 +48567,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1662" t="n">
         <v>5400</v>
@@ -48625,7 +48625,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.73250651359558</v>
+        <v>2.732506275177</v>
       </c>
       <c r="H1664" t="n">
         <v>2400</v>
@@ -48654,7 +48654,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1665" t="n">
         <v>4500</v>
@@ -48683,7 +48683,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1666" t="n">
         <v>3900</v>
@@ -48712,7 +48712,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1667" t="n">
         <v>13800</v>
@@ -48741,7 +48741,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1668" t="n">
         <v>12600</v>
@@ -48915,7 +48915,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1674" t="n">
         <v>5700</v>
@@ -48973,7 +48973,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.81672739982605</v>
+        <v>2.81672763824463</v>
       </c>
       <c r="H1676" t="n">
         <v>5400</v>
@@ -49408,7 +49408,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.73250651359558</v>
+        <v>2.732506275177</v>
       </c>
       <c r="H1691" t="n">
         <v>3300</v>
@@ -49553,7 +49553,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.91030621528625</v>
+        <v>2.91030645370483</v>
       </c>
       <c r="H1696" t="n">
         <v>7800</v>
@@ -49582,7 +49582,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1697" t="n">
-        <v>2.91030621528625</v>
+        <v>2.91030645370483</v>
       </c>
       <c r="H1697" t="n">
         <v>16800</v>
@@ -49727,7 +49727,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.87287473678589</v>
+        <v>2.87287497520447</v>
       </c>
       <c r="H1702" t="n">
         <v>16500</v>
@@ -49843,7 +49843,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.92902231216431</v>
+        <v>2.92902255058289</v>
       </c>
       <c r="H1706" t="n">
         <v>13800</v>
@@ -49930,7 +49930,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1709" t="n">
-        <v>2.91030621528625</v>
+        <v>2.91030645370483</v>
       </c>
       <c r="H1709" t="n">
         <v>300</v>
@@ -49959,7 +49959,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.91030621528625</v>
+        <v>2.91030645370483</v>
       </c>
       <c r="H1710" t="n">
         <v>600</v>
@@ -49988,7 +49988,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.87287473678589</v>
+        <v>2.87287497520447</v>
       </c>
       <c r="H1711" t="n">
         <v>28800</v>
@@ -50075,7 +50075,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.91030621528625</v>
+        <v>2.91030645370483</v>
       </c>
       <c r="H1714" t="n">
         <v>5100</v>
@@ -50249,7 +50249,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.92902231216431</v>
+        <v>2.92902255058289</v>
       </c>
       <c r="H1720" t="n">
         <v>29100</v>
@@ -50336,7 +50336,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.92902231216431</v>
+        <v>2.92902255058289</v>
       </c>
       <c r="H1723" t="n">
         <v>26700</v>
@@ -50597,7 +50597,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1732" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1732" t="n">
         <v>48000</v>
@@ -50626,7 +50626,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1733" t="n">
         <v>64500</v>
@@ -50771,7 +50771,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1738" t="n">
-        <v>2.35819029808044</v>
+        <v>2.35819053649902</v>
       </c>
       <c r="H1738" t="n">
         <v>38400</v>
@@ -50800,7 +50800,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.35819029808044</v>
+        <v>2.35819053649902</v>
       </c>
       <c r="H1739" t="n">
         <v>18300</v>
@@ -50829,7 +50829,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.35819029808044</v>
+        <v>2.35819053649902</v>
       </c>
       <c r="H1740" t="n">
         <v>19200</v>
@@ -50887,7 +50887,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.36754822731018</v>
+        <v>2.36754846572876</v>
       </c>
       <c r="H1742" t="n">
         <v>5100</v>
@@ -50974,7 +50974,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.31140089035034</v>
+        <v>2.31140112876892</v>
       </c>
       <c r="H1745" t="n">
         <v>174000</v>
@@ -51177,7 +51177,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.4704852104187</v>
+        <v>2.47048544883728</v>
       </c>
       <c r="H1752" t="n">
         <v>7500</v>
@@ -51380,7 +51380,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1759" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1759" t="n">
         <v>600</v>
@@ -51409,7 +51409,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1760" t="n">
         <v>9000</v>
@@ -51438,7 +51438,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1761" t="n">
         <v>6600</v>
@@ -51641,7 +51641,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.41433763504028</v>
+        <v>2.41433787345886</v>
       </c>
       <c r="H1768" t="n">
         <v>30000</v>
@@ -51844,7 +51844,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.64828538894653</v>
+        <v>2.64828515052795</v>
       </c>
       <c r="H1775" t="n">
         <v>13200</v>
@@ -51960,7 +51960,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.65764307975769</v>
+        <v>2.65764331817627</v>
       </c>
       <c r="H1779" t="n">
         <v>22500</v>
@@ -51989,7 +51989,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.73250651359558</v>
+        <v>2.732506275177</v>
       </c>
       <c r="H1780" t="n">
         <v>26700</v>
@@ -52047,7 +52047,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1782" t="n">
         <v>14100</v>
@@ -52076,7 +52076,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.73250651359558</v>
+        <v>2.732506275177</v>
       </c>
       <c r="H1783" t="n">
         <v>46200</v>
@@ -52105,7 +52105,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.73250651359558</v>
+        <v>2.732506275177</v>
       </c>
       <c r="H1784" t="n">
         <v>15000</v>
@@ -52134,7 +52134,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.69507503509521</v>
+        <v>2.69507479667664</v>
       </c>
       <c r="H1785" t="n">
         <v>35700</v>
@@ -52163,7 +52163,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1786" t="n">
         <v>19800</v>
@@ -52192,7 +52192,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1787" t="n">
-        <v>2.69507503509521</v>
+        <v>2.69507479667664</v>
       </c>
       <c r="H1787" t="n">
         <v>7200</v>
@@ -52221,7 +52221,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1788" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1788" t="n">
         <v>4500</v>
@@ -52308,7 +52308,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1791" t="n">
         <v>3300</v>
@@ -52366,7 +52366,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1793" t="n">
         <v>7200</v>
@@ -52453,7 +52453,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1796" t="n">
         <v>7800</v>
@@ -52482,7 +52482,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1797" t="n">
         <v>600</v>
@@ -52511,7 +52511,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1798" t="n">
         <v>10500</v>
@@ -52569,7 +52569,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.75122237205505</v>
+        <v>2.75122213363647</v>
       </c>
       <c r="H1800" t="n">
         <v>34500</v>
@@ -52627,7 +52627,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1802" t="n">
         <v>8100</v>
@@ -52656,7 +52656,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1803" t="n">
         <v>0</v>
@@ -52685,7 +52685,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.76058006286621</v>
+        <v>2.76058030128479</v>
       </c>
       <c r="H1804" t="n">
         <v>2100</v>
@@ -52743,7 +52743,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1806" t="n">
         <v>13500</v>
@@ -52772,7 +52772,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.64828538894653</v>
+        <v>2.64828515052795</v>
       </c>
       <c r="H1807" t="n">
         <v>81600</v>
@@ -52801,7 +52801,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.64828538894653</v>
+        <v>2.64828515052795</v>
       </c>
       <c r="H1808" t="n">
         <v>0</v>
@@ -52830,7 +52830,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1809" t="n">
         <v>12000</v>
@@ -52859,7 +52859,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1810" t="n">
         <v>300</v>
@@ -53004,7 +53004,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1815" t="n">
         <v>5100</v>
@@ -53062,7 +53062,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1817" t="n">
         <v>4800</v>
@@ -53091,7 +53091,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1818" t="n">
         <v>4800</v>
@@ -53323,7 +53323,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.69507503509521</v>
+        <v>2.69507479667664</v>
       </c>
       <c r="H1826" t="n">
         <v>9900</v>
@@ -53352,7 +53352,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.70443296432495</v>
+        <v>2.70443272590637</v>
       </c>
       <c r="H1827" t="n">
         <v>6300</v>
@@ -53381,7 +53381,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.65764307975769</v>
+        <v>2.65764331817627</v>
       </c>
       <c r="H1828" t="n">
         <v>6300</v>
@@ -53816,7 +53816,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.19104361534119</v>
+        <v>3.19104337692261</v>
       </c>
       <c r="H1843" t="n">
         <v>98100</v>
@@ -53961,7 +53961,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.29398036003113</v>
+        <v>3.29398012161255</v>
       </c>
       <c r="H1848" t="n">
         <v>28200</v>
@@ -53990,7 +53990,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.29398036003113</v>
+        <v>3.29398012161255</v>
       </c>
       <c r="H1849" t="n">
         <v>10800</v>
@@ -54077,7 +54077,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.3126962184906</v>
+        <v>3.31269598007202</v>
       </c>
       <c r="H1852" t="n">
         <v>62700</v>
@@ -54106,7 +54106,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.3126962184906</v>
+        <v>3.31269598007202</v>
       </c>
       <c r="H1853" t="n">
         <v>15900</v>
@@ -54338,7 +54338,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.54664349555969</v>
+        <v>3.54664373397827</v>
       </c>
       <c r="H1861" t="n">
         <v>3600</v>
@@ -54599,7 +54599,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1870" t="n">
-        <v>3.65893864631653</v>
+        <v>3.65893840789795</v>
       </c>
       <c r="H1870" t="n">
         <v>20400</v>
@@ -54802,7 +54802,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1877" t="n">
-        <v>3.69637012481689</v>
+        <v>3.69636988639832</v>
       </c>
       <c r="H1877" t="n">
         <v>2100</v>
@@ -54860,7 +54860,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1879" t="n">
-        <v>3.75251770019531</v>
+        <v>3.75251746177673</v>
       </c>
       <c r="H1879" t="n">
         <v>9900</v>
@@ -54918,7 +54918,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1881" t="n">
-        <v>3.75251770019531</v>
+        <v>3.75251746177673</v>
       </c>
       <c r="H1881" t="n">
         <v>15900</v>
@@ -65683,6 +65683,35 @@
         <v>19500</v>
       </c>
       <c r="I2252" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2253" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2253" t="n">
+        <v>4.23000001907349</v>
+      </c>
+      <c r="D2253" t="n">
+        <v>4.23000001907349</v>
+      </c>
+      <c r="E2253" t="n">
+        <v>4.23000001907349</v>
+      </c>
+      <c r="F2253" t="n">
+        <v>4.21000003814697</v>
+      </c>
+      <c r="G2253" t="n">
+        <v>4.21000003814697</v>
+      </c>
+      <c r="H2253" t="n">
+        <v>600</v>
+      </c>
+      <c r="I2253" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DBA.MI.xlsx
+++ b/data/DBA.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H2" t="n">
         <v>326100</v>
@@ -514,7 +514,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H5" t="n">
         <v>14700</v>
@@ -630,7 +630,7 @@
         <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H9" t="n">
         <v>1200</v>
@@ -833,7 +833,7 @@
         <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H16" t="n">
         <v>600</v>
@@ -978,7 +978,7 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H21" t="n">
         <v>2100</v>
@@ -1007,7 +1007,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G22" t="n">
-        <v>3.62962174415588</v>
+        <v>3.62962198257446</v>
       </c>
       <c r="H22" t="n">
         <v>2700</v>
@@ -1036,7 +1036,7 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H23" t="n">
         <v>28500</v>
@@ -1065,7 +1065,7 @@
         <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>3.62962174415588</v>
+        <v>3.62962198257446</v>
       </c>
       <c r="H26" t="n">
         <v>5100</v>
@@ -1181,7 +1181,7 @@
         <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H28" t="n">
         <v>11400</v>
@@ -1210,7 +1210,7 @@
         <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>3.61156392097473</v>
+        <v>3.61156415939331</v>
       </c>
       <c r="H29" t="n">
         <v>4800</v>
@@ -1442,7 +1442,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G37" t="n">
-        <v>3.53030371665955</v>
+        <v>3.53030395507812</v>
       </c>
       <c r="H37" t="n">
         <v>10200</v>
@@ -1471,7 +1471,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>3.52127528190613</v>
+        <v>3.52127504348755</v>
       </c>
       <c r="H38" t="n">
         <v>3600</v>
@@ -1500,7 +1500,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G39" t="n">
-        <v>3.52127528190613</v>
+        <v>3.52127504348755</v>
       </c>
       <c r="H39" t="n">
         <v>600</v>
@@ -1616,7 +1616,7 @@
         <v>3.75</v>
       </c>
       <c r="G43" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H43" t="n">
         <v>300</v>
@@ -1645,7 +1645,7 @@
         <v>3.75</v>
       </c>
       <c r="G44" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H44" t="n">
         <v>300</v>
@@ -1848,7 +1848,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H51" t="n">
         <v>17400</v>
@@ -1906,7 +1906,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G53" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H53" t="n">
         <v>1500</v>
@@ -1935,7 +1935,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G54" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G55" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G56" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G57" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G58" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G60" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G61" t="n">
-        <v>3.46710109710693</v>
+        <v>3.46710133552551</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G65" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H65" t="n">
         <v>1500</v>
@@ -2283,7 +2283,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G66" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G67" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G68" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G69" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G70" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G71" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H85" t="n">
         <v>7500</v>
@@ -2863,7 +2863,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H86" t="n">
         <v>2400</v>
@@ -2892,7 +2892,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G87" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H87" t="n">
         <v>3300</v>
@@ -2921,7 +2921,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G88" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G89" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>3.75</v>
       </c>
       <c r="G101" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H101" t="n">
         <v>2400</v>
@@ -3327,7 +3327,7 @@
         <v>3.75</v>
       </c>
       <c r="G102" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>3.75</v>
       </c>
       <c r="G103" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>3.75</v>
       </c>
       <c r="G104" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>3.35875463485718</v>
+        <v>3.3587543964386</v>
       </c>
       <c r="H105" t="n">
         <v>900</v>
@@ -3617,7 +3617,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>3.20526313781738</v>
+        <v>3.2052628993988</v>
       </c>
       <c r="H112" t="n">
         <v>900</v>
@@ -3704,7 +3704,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>3.04274272918701</v>
+        <v>3.04274249076843</v>
       </c>
       <c r="H115" t="n">
         <v>600</v>
@@ -3733,7 +3733,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>3.04274272918701</v>
+        <v>3.04274249076843</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>3.75</v>
       </c>
       <c r="G124" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H124" t="n">
         <v>5700</v>
@@ -3994,7 +3994,7 @@
         <v>3.75</v>
       </c>
       <c r="G125" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H125" t="n">
         <v>11100</v>
@@ -4052,7 +4052,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G127" t="n">
-        <v>3.45807242393494</v>
+        <v>3.45807266235352</v>
       </c>
       <c r="H127" t="n">
         <v>30600</v>
@@ -4197,7 +4197,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>3.43098592758179</v>
+        <v>3.43098568916321</v>
       </c>
       <c r="H132" t="n">
         <v>2100</v>
@@ -4429,7 +4429,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H140" t="n">
         <v>11700</v>
@@ -4458,7 +4458,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G141" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H141" t="n">
         <v>2100</v>
@@ -4487,7 +4487,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G142" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G143" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G145" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G146" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G148" t="n">
-        <v>3.26846551895142</v>
+        <v>3.26846528053284</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G152" t="n">
-        <v>3.37681221961975</v>
+        <v>3.37681245803833</v>
       </c>
       <c r="H152" t="n">
         <v>300</v>
@@ -4806,7 +4806,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G153" t="n">
-        <v>3.37681221961975</v>
+        <v>3.37681245803833</v>
       </c>
       <c r="H153" t="n">
         <v>300</v>
@@ -4835,7 +4835,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G154" t="n">
-        <v>3.37681221961975</v>
+        <v>3.37681245803833</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G155" t="n">
-        <v>3.37681221961975</v>
+        <v>3.37681245803833</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G156" t="n">
-        <v>3.37681221961975</v>
+        <v>3.37681245803833</v>
       </c>
       <c r="H156" t="n">
         <v>300</v>
@@ -5531,7 +5531,7 @@
         <v>3.75</v>
       </c>
       <c r="G178" t="n">
-        <v>3.38584113121033</v>
+        <v>3.38584136962891</v>
       </c>
       <c r="H178" t="n">
         <v>1500</v>
@@ -5792,7 +5792,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>3.19623422622681</v>
+        <v>3.19623398780823</v>
       </c>
       <c r="H187" t="n">
         <v>6600</v>
@@ -5908,7 +5908,7 @@
         <v>3.5</v>
       </c>
       <c r="G191" t="n">
-        <v>3.1601185798645</v>
+        <v>3.16011881828308</v>
       </c>
       <c r="H191" t="n">
         <v>300</v>
@@ -5937,7 +5937,7 @@
         <v>3.5</v>
       </c>
       <c r="G192" t="n">
-        <v>3.1601185798645</v>
+        <v>3.16011881828308</v>
       </c>
       <c r="H192" t="n">
         <v>2400</v>
@@ -5995,7 +5995,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>3.19623422622681</v>
+        <v>3.19623398780823</v>
       </c>
       <c r="H194" t="n">
         <v>600</v>
@@ -6401,7 +6401,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G208" t="n">
-        <v>3.05177140235901</v>
+        <v>3.05177164077759</v>
       </c>
       <c r="H208" t="n">
         <v>6600</v>
@@ -6778,7 +6778,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G221" t="n">
-        <v>2.60032629966736</v>
+        <v>2.60032606124878</v>
       </c>
       <c r="H221" t="n">
         <v>900</v>
@@ -6807,7 +6807,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H222" t="n">
         <v>3900</v>
@@ -6836,7 +6836,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G223" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G225" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H225" t="n">
         <v>1200</v>
@@ -6923,7 +6923,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G226" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H228" t="n">
         <v>2700</v>
@@ -7010,7 +7010,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G230" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G231" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G232" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>2.61838412284851</v>
+        <v>2.61838388442993</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G236" t="n">
-        <v>2.51003694534302</v>
+        <v>2.5100371837616</v>
       </c>
       <c r="H236" t="n">
         <v>2700</v>
@@ -7242,7 +7242,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G237" t="n">
-        <v>2.51003694534302</v>
+        <v>2.5100371837616</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7271,7 +7271,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>2.46489262580872</v>
+        <v>2.46489238739014</v>
       </c>
       <c r="H238" t="n">
         <v>11100</v>
@@ -7300,7 +7300,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>2.46489262580872</v>
+        <v>2.46489238739014</v>
       </c>
       <c r="H239" t="n">
         <v>1200</v>
@@ -7329,7 +7329,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>2.46489262580872</v>
+        <v>2.46489238739014</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G241" t="n">
-        <v>2.46489262580872</v>
+        <v>2.46489238739014</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>2.46489262580872</v>
+        <v>2.46489238739014</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G249" t="n">
-        <v>2.51003694534302</v>
+        <v>2.5100371837616</v>
       </c>
       <c r="H249" t="n">
         <v>2100</v>
@@ -7619,7 +7619,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G250" t="n">
-        <v>2.41071915626526</v>
+        <v>2.41071891784668</v>
       </c>
       <c r="H250" t="n">
         <v>600</v>
@@ -7648,7 +7648,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>2.41071915626526</v>
+        <v>2.41071891784668</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G252" t="n">
-        <v>2.41071915626526</v>
+        <v>2.41071891784668</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G253" t="n">
-        <v>2.41071915626526</v>
+        <v>2.41071891784668</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>2.41071915626526</v>
+        <v>2.41071891784668</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G268" t="n">
-        <v>2.47392153739929</v>
+        <v>2.47392129898071</v>
       </c>
       <c r="H268" t="n">
         <v>1500</v>
@@ -8170,7 +8170,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G269" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H269" t="n">
         <v>2400</v>
@@ -8344,7 +8344,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G275" t="n">
-        <v>2.30237221717834</v>
+        <v>2.30237197875977</v>
       </c>
       <c r="H275" t="n">
         <v>2100</v>
@@ -8373,7 +8373,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G276" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H276" t="n">
         <v>1200</v>
@@ -8402,7 +8402,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G277" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H277" t="n">
         <v>3600</v>
@@ -8518,7 +8518,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G281" t="n">
-        <v>2.31140112876892</v>
+        <v>2.31140089035034</v>
       </c>
       <c r="H281" t="n">
         <v>21000</v>
@@ -8721,7 +8721,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>2.18499636650085</v>
+        <v>2.18499612808228</v>
       </c>
       <c r="H288" t="n">
         <v>1200</v>
@@ -8750,7 +8750,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G289" t="n">
-        <v>2.18499636650085</v>
+        <v>2.18499612808228</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>2.15790939331055</v>
+        <v>2.15790963172913</v>
       </c>
       <c r="H290" t="n">
         <v>20700</v>
@@ -8837,7 +8837,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G292" t="n">
-        <v>2.05859160423279</v>
+        <v>2.05859136581421</v>
       </c>
       <c r="H292" t="n">
         <v>18900</v>
@@ -8953,7 +8953,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G296" t="n">
-        <v>2.02247595787048</v>
+        <v>2.0224757194519</v>
       </c>
       <c r="H296" t="n">
         <v>1800</v>
@@ -9011,7 +9011,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G298" t="n">
-        <v>1.93218672275543</v>
+        <v>1.93218684196472</v>
       </c>
       <c r="H298" t="n">
         <v>1500</v>
@@ -9069,7 +9069,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G300" t="n">
-        <v>1.87801313400269</v>
+        <v>1.87801325321198</v>
       </c>
       <c r="H300" t="n">
         <v>7200</v>
@@ -9127,7 +9127,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>1.9773313999176</v>
+        <v>1.97733128070831</v>
       </c>
       <c r="H302" t="n">
         <v>4200</v>
@@ -9156,7 +9156,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G303" t="n">
-        <v>1.9773313999176</v>
+        <v>1.97733128070831</v>
       </c>
       <c r="H303" t="n">
         <v>300</v>
@@ -9475,7 +9475,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G314" t="n">
-        <v>2.02247595787048</v>
+        <v>2.0224757194519</v>
       </c>
       <c r="H314" t="n">
         <v>1800</v>
@@ -9678,7 +9678,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G321" t="n">
-        <v>1.95024466514587</v>
+        <v>1.95024478435516</v>
       </c>
       <c r="H321" t="n">
         <v>600</v>
@@ -9707,7 +9707,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G322" t="n">
-        <v>1.95024466514587</v>
+        <v>1.95024478435516</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G323" t="n">
-        <v>1.95024466514587</v>
+        <v>1.95024478435516</v>
       </c>
       <c r="H323" t="n">
         <v>600</v>
@@ -9765,7 +9765,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G324" t="n">
-        <v>1.95024466514587</v>
+        <v>1.95024478435516</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>1.92315804958344</v>
+        <v>1.92315793037415</v>
       </c>
       <c r="H325" t="n">
         <v>600</v>
@@ -10142,7 +10142,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G337" t="n">
-        <v>2.02247595787048</v>
+        <v>2.0224757194519</v>
       </c>
       <c r="H337" t="n">
         <v>300</v>
@@ -10200,7 +10200,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G339" t="n">
-        <v>2.05859160423279</v>
+        <v>2.05859136581421</v>
       </c>
       <c r="H339" t="n">
         <v>54900</v>
@@ -10229,7 +10229,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G340" t="n">
-        <v>2.00441789627075</v>
+        <v>2.00441813468933</v>
       </c>
       <c r="H340" t="n">
         <v>300</v>
@@ -10287,7 +10287,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G342" t="n">
-        <v>2.00441789627075</v>
+        <v>2.00441813468933</v>
       </c>
       <c r="H342" t="n">
         <v>2400</v>
@@ -10374,7 +10374,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G345" t="n">
-        <v>1.93218672275543</v>
+        <v>1.93218684196472</v>
       </c>
       <c r="H345" t="n">
         <v>5700</v>
@@ -10519,7 +10519,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G350" t="n">
-        <v>1.87801313400269</v>
+        <v>1.87801325321198</v>
       </c>
       <c r="H350" t="n">
         <v>2400</v>
@@ -10635,7 +10635,7 @@
         <v>2</v>
       </c>
       <c r="G354" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H354" t="n">
         <v>21600</v>
@@ -10693,7 +10693,7 @@
         <v>2</v>
       </c>
       <c r="G356" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H356" t="n">
         <v>1500</v>
@@ -10722,7 +10722,7 @@
         <v>2</v>
       </c>
       <c r="G357" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>2</v>
       </c>
       <c r="G358" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
         <v>2</v>
       </c>
       <c r="G359" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>2</v>
       </c>
       <c r="G360" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>2</v>
       </c>
       <c r="G361" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>2</v>
       </c>
       <c r="G362" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>2</v>
       </c>
       <c r="G363" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10925,7 +10925,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G364" t="n">
-        <v>1.73355054855347</v>
+        <v>1.73355066776276</v>
       </c>
       <c r="H364" t="n">
         <v>2400</v>
@@ -10954,7 +10954,7 @@
         <v>2</v>
       </c>
       <c r="G365" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H365" t="n">
         <v>3000</v>
@@ -10983,7 +10983,7 @@
         <v>2</v>
       </c>
       <c r="G366" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G370" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H370" t="n">
         <v>2400</v>
@@ -11128,7 +11128,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G371" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>2</v>
       </c>
       <c r="G378" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H378" t="n">
         <v>2100</v>
@@ -11360,7 +11360,7 @@
         <v>2</v>
       </c>
       <c r="G379" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>2</v>
       </c>
       <c r="G380" t="n">
-        <v>1.80578196048737</v>
+        <v>1.80578207969666</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G382" t="n">
-        <v>1.71549296379089</v>
+        <v>1.7154928445816</v>
       </c>
       <c r="H382" t="n">
         <v>9600</v>
@@ -11476,7 +11476,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G383" t="n">
-        <v>1.71549296379089</v>
+        <v>1.7154928445816</v>
       </c>
       <c r="H383" t="n">
         <v>23400</v>
@@ -11592,7 +11592,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G387" t="n">
-        <v>1.68840610980988</v>
+        <v>1.68840622901917</v>
       </c>
       <c r="H387" t="n">
         <v>6300</v>
@@ -11679,7 +11679,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G390" t="n">
-        <v>1.67937731742859</v>
+        <v>1.6793771982193</v>
       </c>
       <c r="H390" t="n">
         <v>2400</v>
@@ -11708,7 +11708,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G391" t="n">
-        <v>1.71549296379089</v>
+        <v>1.7154928445816</v>
       </c>
       <c r="H391" t="n">
         <v>4800</v>
@@ -11824,7 +11824,7 @@
         <v>1.75</v>
       </c>
       <c r="G395" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H395" t="n">
         <v>3900</v>
@@ -11853,7 +11853,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G396" t="n">
-        <v>1.5981171131134</v>
+        <v>1.59811699390411</v>
       </c>
       <c r="H396" t="n">
         <v>12600</v>
@@ -11911,7 +11911,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H398" t="n">
         <v>1200</v>
@@ -12085,7 +12085,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H404" t="n">
         <v>80700</v>
@@ -12317,7 +12317,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H412" t="n">
         <v>900</v>
@@ -12433,7 +12433,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G416" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H416" t="n">
         <v>2100</v>
@@ -12549,7 +12549,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G420" t="n">
-        <v>1.38142323493958</v>
+        <v>1.38142311573029</v>
       </c>
       <c r="H420" t="n">
         <v>300</v>
@@ -12578,7 +12578,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G421" t="n">
-        <v>1.34530770778656</v>
+        <v>1.34530758857727</v>
       </c>
       <c r="H421" t="n">
         <v>1500</v>
@@ -12723,7 +12723,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G426" t="n">
-        <v>1.28210520744324</v>
+        <v>1.28210532665253</v>
       </c>
       <c r="H426" t="n">
         <v>5100</v>
@@ -12868,7 +12868,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G431" t="n">
-        <v>1.28210520744324</v>
+        <v>1.28210532665253</v>
       </c>
       <c r="H431" t="n">
         <v>11700</v>
@@ -12897,7 +12897,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G432" t="n">
-        <v>1.30016314983368</v>
+        <v>1.30016303062439</v>
       </c>
       <c r="H432" t="n">
         <v>900</v>
@@ -12926,7 +12926,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G433" t="n">
-        <v>1.30919206142426</v>
+        <v>1.30919194221497</v>
       </c>
       <c r="H433" t="n">
         <v>300</v>
@@ -12955,7 +12955,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>1.34530770778656</v>
+        <v>1.34530758857727</v>
       </c>
       <c r="H434" t="n">
         <v>25500</v>
@@ -13013,7 +13013,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>1.30016314983368</v>
+        <v>1.30016303062439</v>
       </c>
       <c r="H436" t="n">
         <v>4200</v>
@@ -13042,7 +13042,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G437" t="n">
-        <v>1.30016314983368</v>
+        <v>1.30016303062439</v>
       </c>
       <c r="H437" t="n">
         <v>39900</v>
@@ -13071,7 +13071,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G438" t="n">
-        <v>1.30919206142426</v>
+        <v>1.30919194221497</v>
       </c>
       <c r="H438" t="n">
         <v>27900</v>
@@ -13100,7 +13100,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G439" t="n">
-        <v>1.30016314983368</v>
+        <v>1.30016303062439</v>
       </c>
       <c r="H439" t="n">
         <v>6000</v>
@@ -13129,7 +13129,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G440" t="n">
-        <v>1.30016314983368</v>
+        <v>1.30016303062439</v>
       </c>
       <c r="H440" t="n">
         <v>1500</v>
@@ -13158,7 +13158,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G441" t="n">
-        <v>1.30016314983368</v>
+        <v>1.30016303062439</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G442" t="n">
-        <v>1.24598956108093</v>
+        <v>1.24598968029022</v>
       </c>
       <c r="H442" t="n">
         <v>79500</v>
@@ -13448,7 +13448,7 @@
         <v>1.75</v>
       </c>
       <c r="G451" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H451" t="n">
         <v>17400</v>
@@ -13477,7 +13477,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H452" t="n">
         <v>5100</v>
@@ -13970,7 +13970,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G469" t="n">
-        <v>1.67937731742859</v>
+        <v>1.6793771982193</v>
       </c>
       <c r="H469" t="n">
         <v>347100</v>
@@ -14028,7 +14028,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G471" t="n">
-        <v>1.5981171131134</v>
+        <v>1.59811699390411</v>
       </c>
       <c r="H471" t="n">
         <v>32400</v>
@@ -14144,7 +14144,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H475" t="n">
         <v>49500</v>
@@ -14173,7 +14173,7 @@
         <v>1.75</v>
       </c>
       <c r="G476" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H476" t="n">
         <v>21600</v>
@@ -14260,7 +14260,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H479" t="n">
         <v>39600</v>
@@ -14695,7 +14695,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G494" t="n">
-        <v>1.42656791210175</v>
+        <v>1.42656779289246</v>
       </c>
       <c r="H494" t="n">
         <v>7200</v>
@@ -14869,7 +14869,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>1.5981171131134</v>
+        <v>1.59811699390411</v>
       </c>
       <c r="H500" t="n">
         <v>22200</v>
@@ -14927,7 +14927,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G502" t="n">
-        <v>1.63423275947571</v>
+        <v>1.63423264026642</v>
       </c>
       <c r="H502" t="n">
         <v>19200</v>
@@ -15043,7 +15043,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G506" t="n">
-        <v>1.5981171131134</v>
+        <v>1.59811699390411</v>
       </c>
       <c r="H506" t="n">
         <v>8700</v>
@@ -15072,7 +15072,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G507" t="n">
-        <v>1.5981171131134</v>
+        <v>1.59811699390411</v>
       </c>
       <c r="H507" t="n">
         <v>10500</v>
@@ -15101,7 +15101,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G508" t="n">
-        <v>1.5981171131134</v>
+        <v>1.59811699390411</v>
       </c>
       <c r="H508" t="n">
         <v>12600</v>
@@ -15130,7 +15130,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G509" t="n">
-        <v>1.5258857011795</v>
+        <v>1.52588582038879</v>
       </c>
       <c r="H509" t="n">
         <v>3600</v>
@@ -15217,7 +15217,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>1.54394364356995</v>
+        <v>1.54394376277924</v>
       </c>
       <c r="H512" t="n">
         <v>36000</v>
@@ -15536,7 +15536,7 @@
         <v>1.75</v>
       </c>
       <c r="G523" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H523" t="n">
         <v>9900</v>
@@ -15623,7 +15623,7 @@
         <v>1.75</v>
       </c>
       <c r="G526" t="n">
-        <v>1.58005928993225</v>
+        <v>1.58005940914154</v>
       </c>
       <c r="H526" t="n">
         <v>92100</v>
@@ -15855,7 +15855,7 @@
         <v>1.490000